--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -11,6 +11,7 @@
     <sheet name="COSTOS UNIFICADOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="TABLERO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="DECISIONES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="INFRAESTRUCTURA" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COSTOS UNIFICADOS'!$A$4:$L$4</definedName>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;(&quot;$&quot;#,##0);-"/>
     <numFmt numFmtId="167" formatCode="&quot;US$&quot;#,##0;(&quot;US$&quot;#,##0);-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +90,14 @@
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -109,12 +116,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,6 +132,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -191,6 +203,33 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -218,36 +257,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -280,8 +298,20 @@
     <xf numFmtId="3" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -823,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -970,7 +1000,7 @@
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>IF(H6="",N(J6),IF(E6="USD",H6,H6/TABLERO!$C$4))</f>
+        <f>IF(D6="Bonificado",0,IF(H6="",N(J6),IF(E6="USD",H6,H6/TABLERO!$C$4)))</f>
         <v/>
       </c>
       <c r="J6" s="12" t="n">
@@ -989,7 +1019,7 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Infraestructura y mobiliario</t>
+          <t>Infraestructura La Rural (a filtrar)</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -999,12 +1029,12 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>Paneles oficina producción 25 m², sala staff 100 m², depósito 64 m² (2.500 barras), camarín speakers, mobiliario, dirección técnica, guardia eléctrica y técnica. NO incluye sillas (fila aparte).</t>
+          <t>Escenario provisional: sólo panelería (oficina de producción, sala de staff, depósito de las barras) + dirección técnica + guardias eléctrica y técnica. Se descontó TODO el mobiliario ($49.636.342) porque Agustina lo consigue aparte más barato. FALTA que marque qué ítems se quedan.</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Cotizado</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -1013,7 +1043,7 @@
         </is>
       </c>
       <c r="F7" s="19" t="n">
-        <v>23994708.2</v>
+        <v>16858366.2</v>
       </c>
       <c r="G7" s="20" t="n"/>
       <c r="H7" s="21">
@@ -1021,7 +1051,7 @@
         <v/>
       </c>
       <c r="I7" s="22">
-        <f>IF(H7="",N(J7),IF(E7="USD",H7,H7/TABLERO!$C$4))</f>
+        <f>IF(D7="Bonificado",0,IF(H7="",N(J7),IF(E7="USD",H7,H7/TABLERO!$C$4)))</f>
         <v/>
       </c>
       <c r="J7" s="23" t="n"/>
@@ -1031,29 +1061,29 @@
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Mail criccio@larural.com.ar 17/08/2026 · total del PDF $66.494.708 menos $42.500.000 de sillas</t>
+          <t>Mail criccio@larural.com.ar 17/08/2026 · total del PDF $66.494.708,20 · ver hoja INFRAESTRUCTURA</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>Sillas del público (5.000)</t>
+          <t>Sillas del público (5.500)</t>
         </is>
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>La Rural — Infraestructura</t>
+          <t>FDL Eventos</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>Silla imperio bordó 5.000 u. a $8.500 c/u, dentro del presupuesto de infraestructura</t>
+          <t>4.500 sillas plásticas Munro reforzadas + 1.000 sillas hotel negro + flete. NO incluye armado.</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>Alternativa</t>
+          <t>Cotizado</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
@@ -1062,47 +1092,51 @@
         </is>
       </c>
       <c r="F8" s="28" t="n">
-        <v>42500000</v>
-      </c>
-      <c r="G8" s="29" t="n"/>
+        <v>25800000</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>0.21</v>
+      </c>
       <c r="H8" s="30">
         <f>IF(F8="","",F8*(1+N(G8)))</f>
         <v/>
       </c>
       <c r="I8" s="31">
-        <f>IF(H8="",N(J8),IF(E8="USD",H8,H8/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J8" s="32" t="n"/>
+        <f>IF(D8="Bonificado",0,IF(H8="",N(J8),IF(E8="USD",H8,H8/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="32" t="n">
+        <v>16500</v>
+      </c>
       <c r="K8" s="31">
         <f>IF(D8="Alternativa","",I8-N(J8))</f>
         <v/>
       </c>
       <c r="L8" s="33" t="inlineStr">
         <is>
-          <t>Mail criccio@larural.com.ar 17/08/2026</t>
+          <t>Mail fdleventos@gmail.com 07/08/2026 · pendiente de resolver facturación al exterior</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Sillas del público (5.500)</t>
+          <t>Montaje, acomodación y desmontaje de sillas</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>FDL Eventos</t>
+          <t>En negociación</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>4.500 sillas plásticas Munro reforzadas + 1.000 sillas hotel negro + flete. NO incluye armado.</t>
+          <t>Montaje previo, acomodación el sábado a la noche después de la dinámica y desmontaje el domingo.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Cotizado</t>
+          <t>En negociación</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -1111,617 +1145,652 @@
         </is>
       </c>
       <c r="F9" s="19" t="n">
-        <v>25800000</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.21</v>
-      </c>
+        <v>900000</v>
+      </c>
+      <c r="G9" s="20" t="n"/>
       <c r="H9" s="21">
         <f>IF(F9="","",F9*(1+N(G9)))</f>
         <v/>
       </c>
       <c r="I9" s="22">
-        <f>IF(H9="",N(J9),IF(E9="USD",H9,H9/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J9" s="23" t="n">
-        <v>16500</v>
-      </c>
+        <f>IF(D9="Bonificado",0,IF(H9="",N(J9),IF(E9="USD",H9,H9/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="23" t="n"/>
       <c r="K9" s="22">
         <f>IF(D9="Alternativa","",I9-N(J9))</f>
         <v/>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Mail fdleventos@gmail.com 07/08/2026 · pendiente de resolver facturación al exterior</t>
+          <t>Negociación de Agustina · cerrar el número antes de firmar las sillas</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Conectividad WiFi</t>
+          <t>Replanteo de sillas (ingeniero)</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>La Rural — Servicios de Conectividad</t>
+          <t>Sin cotizar</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>2 redes privadas de 30 Mbps (técnica + staff/acreditación), 2 al 4 de octubre</t>
+          <t>Replanteo del layout de sillas del pabellón. Confirmado que va aparte de la dirección técnica de La Rural.</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Cotizado</t>
+          <t>Sin cotizar</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>1438728.01</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H10" s="21">
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="22">
         <f>IF(F10="","",F10*(1+N(G10)))</f>
         <v/>
       </c>
       <c r="I10" s="22">
-        <f>IF(H10="",N(J10),IF(E10="USD",H10,H10/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>800</v>
-      </c>
+        <f>IF(D10="Bonificado",0,IF(H10="",N(J10),IF(E10="USD",H10,H10/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="23" t="n"/>
       <c r="K10" s="22">
         <f>IF(D10="Alternativa","",I10-N(J10))</f>
         <v/>
       </c>
       <c r="L10" s="24" t="inlineStr">
         <is>
+          <t>Pendiente de pedir presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Conectividad WiFi</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>La Rural — Servicios de Conectividad</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>2 redes privadas de 30 Mbps (técnica + staff/acreditación), del 2 al 4 de octubre</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>1438728.01</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H11" s="30">
+        <f>IF(F11="","",F11*(1+N(G11)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="31">
+        <f>IF(D11="Bonificado",0,IF(H11="",N(J11),IF(E11="USD",H11,H11/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="32" t="n">
+        <v>800</v>
+      </c>
+      <c r="K11" s="31">
+        <f>IF(D11="Alternativa","",I11-N(J11))</f>
+        <v/>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
           <t>Mail conectividad@larural.com.ar 16/06/2026</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Subtotal Sede</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-      <c r="I11" s="36">
-        <f>SUMIF($D$6:$D$10,"&lt;&gt;Alternativa",$I$6:$I$10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="36">
-        <f>SUM($J$6:$J$10)</f>
-        <v/>
-      </c>
-      <c r="K11" s="36">
-        <f>I11-J11</f>
-        <v/>
-      </c>
-      <c r="L11" s="35" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="36">
+        <f>SUMIF($D$6:$D$11,"&lt;&gt;Alternativa",$I$6:$I$11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="36">
+        <f>SUM($J$6:$J$11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="36">
+        <f>I12-J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>TÉCNICA</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Producción técnica integral</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Prina</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>LED 40 m² + video 4 cámaras + sonido Adamson + iluminación + estructura, staff y guardias. 50% anticipo.</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Producción técnica</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Cerrado por Agustina</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Sonido, iluminación, video y LED. Cerrado en dólares.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="14">
+        <f>IF(F14="","",F14*(1+N(G14)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="14">
+        <f>IF(D14="Bonificado",0,IF(H14="",N(J14),IF(E14="USD",H14,H14/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>34000</v>
+      </c>
+      <c r="K14" s="14">
+        <f>IF(D14="Alternativa","",I14-N(J14))</f>
+        <v/>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina · reemplaza la cotización vencida de Prina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Entelado</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Cerrado por Agustina</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Entelado del pabellón. Negociado a la mitad de lo que estaba cotizado.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="38">
+        <f>IF(F15="","",F15*(1+N(G15)))</f>
+        <v/>
+      </c>
+      <c r="I15" s="14">
+        <f>IF(D15="Bonificado",0,IF(H15="",N(J15),IF(E15="USD",H15,H15/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="14">
+        <f>IF(D15="Alternativa","",I15-N(J15))</f>
+        <v/>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina · US$16.000 aprox. al dólar de referencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Circuito cerrado (CCTV)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Cerrado por Agustina</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Circuito cerrado de cámaras para el pabellón.</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>6209</v>
+      </c>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14">
+        <f>IF(F16="","",F16*(1+N(G16)))</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>IF(D16="Bonificado",0,IF(H16="",N(J16),IF(E16="USD",H16,H16/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="14">
+        <f>IF(D16="Alternativa","",I16-N(J16))</f>
+        <v/>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>Bonificado por el proveedor de técnica</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>Sin costo</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>500 vallas y efectos especiales, sin cargo. Es lo que evita el gasto de vallado que estaba presupuestado.</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E17" s="40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="43" t="n"/>
+      <c r="H17" s="44">
+        <f>IF(F17="","",F17*(1+N(G17)))</f>
+        <v/>
+      </c>
+      <c r="I17" s="44">
+        <f>IF(D17="Bonificado",0,IF(H17="",N(J17),IF(E17="USD",H17,H17/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="42" t="n"/>
+      <c r="K17" s="44">
+        <f>IF(D17="Alternativa","",I17-N(J17))</f>
+        <v/>
+      </c>
+      <c r="L17" s="45" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>Subtotal Técnica</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="35" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
+      <c r="H18" s="35" t="n"/>
+      <c r="I18" s="36">
+        <f>SUMIF($D$14:$D$17,"&lt;&gt;Alternativa",$I$14:$I$17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="36">
+        <f>SUM($J$14:$J$17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="36">
+        <f>I18-J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Seguridad y vigilancia</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Road Seguridad S.A.</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>263 horas de vigilancia (armado, evento y desarme) + planos de evacuación $715.000 + supervisión general $795.000</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F13" s="19" t="n">
-        <v>48885000</v>
-      </c>
-      <c r="G13" s="20" t="n">
+      <c r="F20" s="28" t="n">
+        <v>7218928.96</v>
+      </c>
+      <c r="G20" s="29" t="n">
         <v>0.21</v>
       </c>
-      <c r="H13" s="21">
-        <f>IF(F13="","",F13*(1+N(G13)))</f>
-        <v/>
-      </c>
-      <c r="I13" s="22">
-        <f>IF(H13="",N(J13),IF(E13="USD",H13,H13/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J13" s="23" t="n">
-        <v>34000</v>
-      </c>
-      <c r="K13" s="22">
-        <f>IF(D13="Alternativa","",I13-N(J13))</f>
-        <v/>
-      </c>
-      <c r="L13" s="24" t="inlineStr">
-        <is>
-          <t>Mail valentin.andina@prina.net 18/06/2026 · validez 10 días (VENCIDA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>Pantallas LED (alternativa parcial)</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>VMG</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>Sólo pantallas LED 65 m² con operadores y traslado</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>Alternativa</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="H20" s="30">
+        <f>IF(F20="","",F20*(1+N(G20)))</f>
+        <v/>
+      </c>
+      <c r="I20" s="31">
+        <f>IF(D20="Bonificado",0,IF(H20="",N(J20),IF(E20="USD",H20,H20/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="32" t="n"/>
+      <c r="K20" s="31">
+        <f>IF(D20="Alternativa","",I20-N(J20))</f>
+        <v/>
+      </c>
+      <c r="L20" s="33" t="inlineStr">
+        <is>
+          <t>Mail presupuestos@roadseguridad.com.ar 12/08/2026 (versión V3, lista para firmar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Servicio médico</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Vittal — Socorro Médico Privado</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>1 UTIM TRI con dos médicos + enfermero/chofer, los tres días (2, 3 y 4 de octubre)</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F14" s="28" t="n">
-        <v>12625000</v>
-      </c>
-      <c r="G14" s="29" t="n">
+      <c r="F21" s="28" t="n">
+        <v>6366521.27</v>
+      </c>
+      <c r="G21" s="29" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H21" s="30">
+        <f>IF(F21="","",F21*(1+N(G21)))</f>
+        <v/>
+      </c>
+      <c r="I21" s="31">
+        <f>IF(D21="Bonificado",0,IF(H21="",N(J21),IF(E21="USD",H21,H21/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="32" t="n"/>
+      <c r="K21" s="31">
+        <f>IF(D21="Alternativa","",I21-N(J21))</f>
+        <v/>
+      </c>
+      <c r="L21" s="33" t="inlineStr">
+        <is>
+          <t>Mail vtomas@vittal.com.ar 28/08/2026 · tarifas actualizadas, sin consultorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Higia Eventos</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>205,5 horas de limpieza: auditorio, baños y guardarropas, del 2 al 5 de octubre</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>3367440.91</v>
+      </c>
+      <c r="G22" s="29" t="n">
         <v>0.21</v>
       </c>
-      <c r="H14" s="30">
-        <f>IF(F14="","",F14*(1+N(G14)))</f>
-        <v/>
-      </c>
-      <c r="I14" s="31">
-        <f>IF(H14="",N(J14),IF(E14="USD",H14,H14/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J14" s="32" t="n"/>
-      <c r="K14" s="31">
-        <f>IF(D14="Alternativa","",I14-N(J14))</f>
-        <v/>
-      </c>
-      <c r="L14" s="33" t="inlineStr">
-        <is>
-          <t>Mail presupuestos@vmg-web.com 29/06/2026 · recotiza si el dólar salta más de 15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>Subtotal Técnica</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="36">
-        <f>SUMIF($D$13:$D$14,"&lt;&gt;Alternativa",$I$13:$I$14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="36">
-        <f>SUM($J$13:$J$14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="36">
-        <f>I15-J15</f>
-        <v/>
-      </c>
-      <c r="L15" s="35" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>SERVICIOS</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Seguridad y vigilancia</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Road Seguridad S.A.</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>263 horas de vigilancia (armado, evento y desarme) + planos de evacuación $715.000 + supervisión general $795.000</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="H22" s="30">
+        <f>IF(F22="","",F22*(1+N(G22)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="31">
+        <f>IF(D22="Bonificado",0,IF(H22="",N(J22),IF(E22="USD",H22,H22/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="32" t="n"/>
+      <c r="K22" s="31">
+        <f>IF(D22="Alternativa","",I22-N(J22))</f>
+        <v/>
+      </c>
+      <c r="L22" s="33" t="inlineStr">
+        <is>
+          <t>Mail higiaeventos 22/06/2026 (reenviado 29/06) · 50% de anticipo antes del armado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Retiro de residuos</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Gale Servicios</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Roll off con disposición final incluida. Cotización base abril 2026.</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F17" s="19" t="n">
-        <v>7218928.96</v>
-      </c>
-      <c r="G17" s="20" t="n">
+      <c r="F23" s="28" t="n">
+        <v>1471608.62</v>
+      </c>
+      <c r="G23" s="29" t="n">
         <v>0.21</v>
       </c>
-      <c r="H17" s="21">
-        <f>IF(F17="","",F17*(1+N(G17)))</f>
-        <v/>
-      </c>
-      <c r="I17" s="22">
-        <f>IF(H17="",N(J17),IF(E17="USD",H17,H17/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J17" s="23" t="n"/>
-      <c r="K17" s="22">
-        <f>IF(D17="Alternativa","",I17-N(J17))</f>
-        <v/>
-      </c>
-      <c r="L17" s="24" t="inlineStr">
-        <is>
-          <t>Mail presupuestos@roadseguridad.com.ar 12/08/2026 (versión V3 con las modificaciones pedidas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Servicio médico</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Vittal — Socorro Médico Privado</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>1 UTIM TRI con dos médicos + enfermero/chofer, los tres días (2, 3 y 4 de octubre)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>6366521.27</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="H18" s="21">
-        <f>IF(F18="","",F18*(1+N(G18)))</f>
-        <v/>
-      </c>
-      <c r="I18" s="22">
-        <f>IF(H18="",N(J18),IF(E18="USD",H18,H18/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J18" s="23" t="n"/>
-      <c r="K18" s="22">
-        <f>IF(D18="Alternativa","",I18-N(J18))</f>
-        <v/>
-      </c>
-      <c r="L18" s="24" t="inlineStr">
-        <is>
-          <t>Mail vtomas@vittal.com.ar 28/08/2026 · tarifas actualizadas, sin consultorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Higia Eventos</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>205,5 horas de limpieza: auditorio, baños y guardarropas, del 2 al 5 de octubre</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>3367440.91</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H19" s="21">
-        <f>IF(F19="","",F19*(1+N(G19)))</f>
-        <v/>
-      </c>
-      <c r="I19" s="22">
-        <f>IF(H19="",N(J19),IF(E19="USD",H19,H19/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J19" s="23" t="n"/>
-      <c r="K19" s="22">
-        <f>IF(D19="Alternativa","",I19-N(J19))</f>
-        <v/>
-      </c>
-      <c r="L19" s="24" t="inlineStr">
-        <is>
-          <t>Mail higiaeventos 22/06/2026 (reenviado 29/06) · 50% de anticipo antes del armado</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Retiro de residuos</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Gale Servicios</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Roll off con disposición final incluida. Cotización base abril 2026.</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>1471608.62</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H20" s="21">
-        <f>IF(F20="","",F20*(1+N(G20)))</f>
-        <v/>
-      </c>
-      <c r="I20" s="22">
-        <f>IF(H20="",N(J20),IF(E20="USD",H20,H20/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J20" s="23" t="n"/>
-      <c r="K20" s="22">
-        <f>IF(D20="Alternativa","",I20-N(J20))</f>
-        <v/>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="H23" s="30">
+        <f>IF(F23="","",F23*(1+N(G23)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="31">
+        <f>IF(D23="Bonificado",0,IF(H23="",N(J23),IF(E23="USD",H23,H23/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="32" t="n"/>
+      <c r="K23" s="31">
+        <f>IF(D23="Alternativa","",I23-N(J23))</f>
+        <v/>
+      </c>
+      <c r="L23" s="33" t="inlineStr">
         <is>
           <t>Mail higiaeventos 22/06/2026 (adjunto Gale) · se factura 100% por adelantado</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Seguro de accidentes personales</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Chanes Seguros</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>Cobertura MIA (muerte, invalidez y asistencia médica) para 150 personas, exigida por La Rural</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="n">
-        <v>953151.9300000001</v>
-      </c>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="21">
-        <f>IF(F21="","",F21*(1+N(G21)))</f>
-        <v/>
-      </c>
-      <c r="I21" s="22">
-        <f>IF(H21="",N(J21),IF(E21="USD",H21,H21/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J21" s="23" t="n">
-        <v>400</v>
-      </c>
-      <c r="K21" s="22">
-        <f>IF(D21="Alternativa","",I21-N(J21))</f>
-        <v/>
-      </c>
-      <c r="L21" s="24" t="inlineStr">
-        <is>
-          <t>Mail nestor@chanesseguros.com.ar 13/07/2026 · premio único, cotizado para 15-19/07</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>Subtotal Servicios</t>
-        </is>
-      </c>
-      <c r="B22" s="35" t="n"/>
-      <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="35" t="n"/>
-      <c r="G22" s="35" t="n"/>
-      <c r="H22" s="35" t="n"/>
-      <c r="I22" s="36">
-        <f>SUMIF($D$17:$D$21,"&lt;&gt;Alternativa",$I$17:$I$21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="36">
-        <f>SUM($J$17:$J$21)</f>
-        <v/>
-      </c>
-      <c r="K22" s="36">
-        <f>I22-J22</f>
-        <v/>
-      </c>
-      <c r="L22" s="35" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>MERCH</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Cintas portacredencial (1.300)</t>
+          <t>Baños químicos — ecobaños</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>Blocko</t>
+          <t>Sin cotizar</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>Cinta raso 25 mm impresa 4 colores dos caras + mosquetón zamak, $1.346 c/u</t>
+          <t>Decidido: ecobaños, no los químicos tradicionales. Más limpios, mejor a la vista y ecofriendly. Falta pedir presupuesto.</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Cotizado</t>
+          <t>Sin cotizar</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>1749800</v>
-      </c>
-      <c r="G24" s="20" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H24" s="21">
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="22">
         <f>IF(F24="","",F24*(1+N(G24)))</f>
         <v/>
       </c>
       <c r="I24" s="22">
-        <f>IF(H24="",N(J24),IF(E24="USD",H24,H24/TABLERO!$C$4))</f>
+        <f>IF(D24="Bonificado",0,IF(H24="",N(J24),IF(E24="USD",H24,H24/TABLERO!$C$4)))</f>
         <v/>
       </c>
       <c r="J24" s="23" t="n"/>
@@ -1731,930 +1800,1222 @@
       </c>
       <c r="L24" s="24" t="inlineStr">
         <is>
+          <t>Decisión de Agustina · pendiente de cotizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>Seguro de accidentes personales</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Chanes Seguros</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Cobertura MIA (muerte, invalidez y asistencia médica) para 150 personas, exigida por La Rural</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>953151.9300000001</v>
+      </c>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="30">
+        <f>IF(F25="","",F25*(1+N(G25)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="31">
+        <f>IF(D25="Bonificado",0,IF(H25="",N(J25),IF(E25="USD",H25,H25/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="32" t="n">
+        <v>400</v>
+      </c>
+      <c r="K25" s="31">
+        <f>IF(D25="Alternativa","",I25-N(J25))</f>
+        <v/>
+      </c>
+      <c r="L25" s="33" t="inlineStr">
+        <is>
+          <t>Mail nestor@chanesseguros.com.ar 13/07/2026 · premio único, cotizado para 15-19/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t>Subtotal Servicios</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="n"/>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="36">
+        <f>SUMIF($D$20:$D$25,"&lt;&gt;Alternativa",$I$20:$I$25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="36">
+        <f>SUM($J$20:$J$25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="36">
+        <f>I26-J26</f>
+        <v/>
+      </c>
+      <c r="L26" s="35" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>MERCH</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Cintas portacredencial (1.300)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Blocko</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Cinta raso 25 mm impresa 4 colores dos caras + mosquetón zamak, $1.346 c/u</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>1749800</v>
+      </c>
+      <c r="G28" s="29" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H28" s="30">
+        <f>IF(F28="","",F28*(1+N(G28)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="31">
+        <f>IF(D28="Bonificado",0,IF(H28="",N(J28),IF(E28="USD",H28,H28/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="32" t="n"/>
+      <c r="K28" s="31">
+        <f>IF(D28="Alternativa","",I28-N(J28))</f>
+        <v/>
+      </c>
+      <c r="L28" s="33" t="inlineStr">
+        <is>
           <t>Mail hola@blocko.com.ar 09/06/2026 · producción 3 semanas</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Pañuelos</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Proveedor Colombia</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Contrato cerrado, 50% abonado el 24/06. Saldo US$5.491 programado al 13/09.</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Contratado</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>10982</v>
       </c>
-      <c r="G25" s="13" t="n"/>
-      <c r="H25" s="14">
-        <f>IF(F25="","",F25*(1+N(G25)))</f>
-        <v/>
-      </c>
-      <c r="I25" s="14">
-        <f>IF(H25="",N(J25),IF(E25="USD",H25,H25/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="14">
-        <f>IF(D25="Alternativa","",I25-N(J25))</f>
-        <v/>
-      </c>
-      <c r="L25" s="15" t="inlineStr">
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="14">
+        <f>IF(F29="","",F29*(1+N(G29)))</f>
+        <v/>
+      </c>
+      <c r="I29" s="14">
+        <f>IF(D29="Bonificado",0,IF(H29="",N(J29),IF(E29="USD",H29,H29/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="14">
+        <f>IF(D29="Alternativa","",I29-N(J29))</f>
+        <v/>
+      </c>
+      <c r="L29" s="15" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Lanyards</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Proveedor Colombia</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Contrato cerrado, 50% abonado el 25/06. Saldo US$850 al 13/09.</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Contratado</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>1698.59</v>
       </c>
-      <c r="G26" s="13" t="n"/>
-      <c r="H26" s="14">
-        <f>IF(F26="","",F26*(1+N(G26)))</f>
-        <v/>
-      </c>
-      <c r="I26" s="14">
-        <f>IF(H26="",N(J26),IF(E26="USD",H26,H26/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="14">
-        <f>IF(D26="Alternativa","",I26-N(J26))</f>
-        <v/>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="14">
+        <f>IF(F30="","",F30*(1+N(G30)))</f>
+        <v/>
+      </c>
+      <c r="I30" s="14">
+        <f>IF(D30="Bonificado",0,IF(H30="",N(J30),IF(E30="USD",H30,H30/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="14">
+        <f>IF(D30="Alternativa","",I30-N(J30))</f>
+        <v/>
+      </c>
+      <c r="L30" s="15" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Gorras</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Proveedor Colombia</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Pagado 100% el 25/06</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Contratado</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>1825</v>
       </c>
-      <c r="G27" s="13" t="n"/>
-      <c r="H27" s="14">
-        <f>IF(F27="","",F27*(1+N(G27)))</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>IF(H27="",N(J27),IF(E27="USD",H27,H27/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J27" s="12" t="n">
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="14">
+        <f>IF(F31="","",F31*(1+N(G31)))</f>
+        <v/>
+      </c>
+      <c r="I31" s="14">
+        <f>IF(D31="Bonificado",0,IF(H31="",N(J31),IF(E31="USD",H31,H31/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="K27" s="14">
-        <f>IF(D27="Alternativa","",I27-N(J27))</f>
-        <v/>
-      </c>
-      <c r="L27" s="15" t="inlineStr">
+      <c r="K31" s="14">
+        <f>IF(D31="Alternativa","",I31-N(J31))</f>
+        <v/>
+      </c>
+      <c r="L31" s="15" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Gráfica Argentina</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Proveedor Colombia</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Contrato cerrado, saldo US$1.839 al 13/09</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Contratado</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>2481</v>
       </c>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="14">
-        <f>IF(F28="","",F28*(1+N(G28)))</f>
-        <v/>
-      </c>
-      <c r="I28" s="14">
-        <f>IF(H28="",N(J28),IF(E28="USD",H28,H28/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="14">
-        <f>IF(D28="Alternativa","",I28-N(J28))</f>
-        <v/>
-      </c>
-      <c r="L28" s="15" t="inlineStr">
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="14">
+        <f>IF(F32="","",F32*(1+N(G32)))</f>
+        <v/>
+      </c>
+      <c r="I32" s="14">
+        <f>IF(D32="Bonificado",0,IF(H32="",N(J32),IF(E32="USD",H32,H32/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="14">
+        <f>IF(D32="Alternativa","",I32-N(J32))</f>
+        <v/>
+      </c>
+      <c r="L32" s="15" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="37" t="inlineStr">
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Marquetería y enmarcado</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Enmarcado de las certificaciones y los premios. Rubro nuevo, no estaba en ninguna planilla.</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="22">
+        <f>IF(F33="","",F33*(1+N(G33)))</f>
+        <v/>
+      </c>
+      <c r="I33" s="22">
+        <f>IF(D33="Bonificado",0,IF(H33="",N(J33),IF(E33="USD",H33,H33/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="22">
+        <f>IF(D33="Alternativa","",I33-N(J33))</f>
+        <v/>
+      </c>
+      <c r="L33" s="24" t="inlineStr">
+        <is>
+          <t>Agregado por Agustina · pendiente de cotizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Resto de merch e impresos</t>
         </is>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Varios (merch desde Colombia)</t>
         </is>
       </c>
-      <c r="C29" s="39" t="inlineStr">
-        <is>
-          <t>Contratos, cheques, escarapelas, bolsas, camisetas, mapas, diplomas, placas, manillas</t>
-        </is>
-      </c>
-      <c r="D29" s="37" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Contratos, cheques, escarapelas, bolsas, camisetas, mapas, diplomas, placas y manillas</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F29" s="40" t="n"/>
-      <c r="G29" s="41" t="n"/>
-      <c r="H29" s="42">
-        <f>IF(F29="","",F29*(1+N(G29)))</f>
-        <v/>
-      </c>
-      <c r="I29" s="42">
-        <f>IF(H29="",N(J29),IF(E29="USD",H29,H29/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J29" s="40" t="n">
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="22">
+        <f>IF(F34="","",F34*(1+N(G34)))</f>
+        <v/>
+      </c>
+      <c r="I34" s="22">
+        <f>IF(D34="Bonificado",0,IF(H34="",N(J34),IF(E34="USD",H34,H34/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J34" s="23" t="n">
         <v>8689</v>
       </c>
-      <c r="K29" s="42">
-        <f>IF(D29="Alternativa","",I29-N(J29))</f>
-        <v/>
-      </c>
-      <c r="L29" s="43" t="inlineStr">
+      <c r="K34" s="22">
+        <f>IF(D34="Alternativa","",I34-N(J34))</f>
+        <v/>
+      </c>
+      <c r="L34" s="24" t="inlineStr">
         <is>
           <t>Estimado de la hoja Argentina del master; sin cotización argentina</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>Subtotal Merch</t>
         </is>
       </c>
-      <c r="B30" s="35" t="n"/>
-      <c r="C30" s="35" t="n"/>
-      <c r="D30" s="35" t="n"/>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-      <c r="G30" s="35" t="n"/>
-      <c r="H30" s="35" t="n"/>
-      <c r="I30" s="36">
-        <f>SUMIF($D$24:$D$29,"&lt;&gt;Alternativa",$I$24:$I$29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="36">
-        <f>SUM($J$24:$J$29)</f>
-        <v/>
-      </c>
-      <c r="K30" s="36">
-        <f>I30-J30</f>
-        <v/>
-      </c>
-      <c r="L30" s="35" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B35" s="35" t="n"/>
+      <c r="C35" s="35" t="n"/>
+      <c r="D35" s="35" t="n"/>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="35" t="n"/>
+      <c r="G35" s="35" t="n"/>
+      <c r="H35" s="35" t="n"/>
+      <c r="I35" s="36">
+        <f>SUMIF($D$28:$D$34,"&lt;&gt;Alternativa",$I$28:$I$34)</f>
+        <v/>
+      </c>
+      <c r="J35" s="36">
+        <f>SUM($J$28:$J$34)</f>
+        <v/>
+      </c>
+      <c r="K35" s="36">
+        <f>I35-J35</f>
+        <v/>
+      </c>
+      <c r="L35" s="35" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>CATERING</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
-      <c r="L31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Catering VIP, staff y equipo</t>
         </is>
       </c>
-      <c r="B32" s="38" t="inlineStr">
-        <is>
-          <t>A definir (Teist / Ambient / Azulado)</t>
-        </is>
-      </c>
-      <c r="C32" s="39" t="inlineStr">
-        <is>
-          <t>AmbientHouse cotizó viandas a $28.500 + IVA por persona por día con base mínima de 480, y se rechazó por estar a precio de consumidor final. Teist envió propuesta el 26/06 sin cerrar.</t>
-        </is>
-      </c>
-      <c r="D32" s="37" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Grupo Ambient</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Número final por las dos propuestas juntas: 600 lunchbox para los VIP + desayuno, almuerzo y cena para 150 personas.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>13582</v>
+      </c>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="14">
+        <f>IF(F37="","",F37*(1+N(G37)))</f>
+        <v/>
+      </c>
+      <c r="I37" s="14">
+        <f>IF(D37="Bonificado",0,IF(H37="",N(J37),IF(E37="USD",H37,H37/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>33820</v>
+      </c>
+      <c r="K37" s="14">
+        <f>IF(D37="Alternativa","",I37-N(J37))</f>
+        <v/>
+      </c>
+      <c r="L37" s="15" t="inlineStr">
+        <is>
+          <t>Cierre de Agustina con Grupo Ambient · reemplaza la estimación de $25.000.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>Food trucks</t>
+        </is>
+      </c>
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>Sin costo</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>No los paga la producción.</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="43" t="n"/>
+      <c r="H38" s="44">
+        <f>IF(F38="","",F38*(1+N(G38)))</f>
+        <v/>
+      </c>
+      <c r="I38" s="44">
+        <f>IF(D38="Bonificado",0,IF(H38="",N(J38),IF(E38="USD",H38,H38/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J38" s="42" t="n"/>
+      <c r="K38" s="44">
+        <f>IF(D38="Alternativa","",I38-N(J38))</f>
+        <v/>
+      </c>
+      <c r="L38" s="45" t="inlineStr">
+        <is>
+          <t>Confirmado por Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>Subtotal Catering</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="n"/>
+      <c r="C39" s="35" t="n"/>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="35" t="n"/>
+      <c r="G39" s="35" t="n"/>
+      <c r="H39" s="35" t="n"/>
+      <c r="I39" s="36">
+        <f>SUMIF($D$37:$D$38,"&lt;&gt;Alternativa",$I$37:$I$38)</f>
+        <v/>
+      </c>
+      <c r="J39" s="36">
+        <f>SUM($J$37:$J$38)</f>
+        <v/>
+      </c>
+      <c r="K39" s="36">
+        <f>I39-J39</f>
+        <v/>
+      </c>
+      <c r="L39" s="35" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCCIÓN</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Unifilas</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>A definir</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Estimado del sheet, sin cotización</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E32" s="38" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F32" s="40" t="n"/>
-      <c r="G32" s="41" t="n"/>
-      <c r="H32" s="42">
-        <f>IF(F32="","",F32*(1+N(G32)))</f>
-        <v/>
-      </c>
-      <c r="I32" s="42">
-        <f>IF(H32="",N(J32),IF(E32="USD",H32,H32/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J32" s="40" t="n">
-        <v>33820</v>
-      </c>
-      <c r="K32" s="42">
-        <f>IF(D32="Alternativa","",I32-N(J32))</f>
-        <v/>
-      </c>
-      <c r="L32" s="43" t="inlineStr">
-        <is>
-          <t>Estimado de la hoja Argentina del master; ninguna cotización aceptada todavía</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="34" t="inlineStr">
-        <is>
-          <t>Subtotal Catering</t>
-        </is>
-      </c>
-      <c r="B33" s="35" t="n"/>
-      <c r="C33" s="35" t="n"/>
-      <c r="D33" s="35" t="n"/>
-      <c r="E33" s="35" t="n"/>
-      <c r="F33" s="35" t="n"/>
-      <c r="G33" s="35" t="n"/>
-      <c r="H33" s="35" t="n"/>
-      <c r="I33" s="36">
-        <f>SUMIF($D$32:$D$32,"&lt;&gt;Alternativa",$I$32:$I$32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="36">
-        <f>SUM($J$32:$J$32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="36">
-        <f>I33-J33</f>
-        <v/>
-      </c>
-      <c r="L33" s="35" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>PRODUCCIÓN</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
-        <is>
-          <t>Unifilas y vallado</t>
-        </is>
-      </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="22">
+        <f>IF(F41="","",F41*(1+N(G41)))</f>
+        <v/>
+      </c>
+      <c r="I41" s="22">
+        <f>IF(D41="Bonificado",0,IF(H41="",N(J41),IF(E41="USD",H41,H41/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J41" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K41" s="22">
+        <f>IF(D41="Alternativa","",I41-N(J41))</f>
+        <v/>
+      </c>
+      <c r="L41" s="24" t="inlineStr">
+        <is>
+          <t>Hoja Argentina del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>Vallado (500 vallas)</t>
+        </is>
+      </c>
+      <c r="B42" s="40" t="inlineStr">
+        <is>
+          <t>Bonificado por técnica</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
+        </is>
+      </c>
+      <c r="D42" s="39" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E42" s="40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F42" s="42" t="n"/>
+      <c r="G42" s="43" t="n"/>
+      <c r="H42" s="44">
+        <f>IF(F42="","",F42*(1+N(G42)))</f>
+        <v/>
+      </c>
+      <c r="I42" s="44">
+        <f>IF(D42="Bonificado",0,IF(H42="",N(J42),IF(E42="USD",H42,H42/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J42" s="42" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K42" s="44">
+        <f>IF(D42="Alternativa","",I42-N(J42))</f>
+        <v/>
+      </c>
+      <c r="L42" s="45" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C35" s="39" t="inlineStr">
-        <is>
-          <t>Estimado del sheet, sin cotización</t>
-        </is>
-      </c>
-      <c r="D35" s="37" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Estimado del sheet</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E35" s="38" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F35" s="40" t="n"/>
-      <c r="G35" s="41" t="n"/>
-      <c r="H35" s="42">
-        <f>IF(F35="","",F35*(1+N(G35)))</f>
-        <v/>
-      </c>
-      <c r="I35" s="42">
-        <f>IF(H35="",N(J35),IF(E35="USD",H35,H35/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J35" s="40" t="n">
-        <v>2450</v>
-      </c>
-      <c r="K35" s="42">
-        <f>IF(D35="Alternativa","",I35-N(J35))</f>
-        <v/>
-      </c>
-      <c r="L35" s="43" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master (unifilas US$1.200 + vallas US$1.250)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="37" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="B36" s="38" t="inlineStr">
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="22">
+        <f>IF(F43="","",F43*(1+N(G43)))</f>
+        <v/>
+      </c>
+      <c r="I43" s="22">
+        <f>IF(D43="Bonificado",0,IF(H43="",N(J43),IF(E43="USD",H43,H43/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J43" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="K43" s="22">
+        <f>IF(D43="Alternativa","",I43-N(J43))</f>
+        <v/>
+      </c>
+      <c r="L43" s="24" t="inlineStr">
+        <is>
+          <t>Hoja Argentina del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Escoltas (2)</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C36" s="39" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>Estimado del sheet</t>
         </is>
       </c>
-      <c r="D36" s="37" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E36" s="38" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F36" s="40" t="n"/>
-      <c r="G36" s="41" t="n"/>
-      <c r="H36" s="42">
-        <f>IF(F36="","",F36*(1+N(G36)))</f>
-        <v/>
-      </c>
-      <c r="I36" s="42">
-        <f>IF(H36="",N(J36),IF(E36="USD",H36,H36/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J36" s="40" t="n">
-        <v>500</v>
-      </c>
-      <c r="K36" s="42">
-        <f>IF(D36="Alternativa","",I36-N(J36))</f>
-        <v/>
-      </c>
-      <c r="L36" s="43" t="inlineStr">
+      <c r="F44" s="23" t="n"/>
+      <c r="G44" s="20" t="n"/>
+      <c r="H44" s="22">
+        <f>IF(F44="","",F44*(1+N(G44)))</f>
+        <v/>
+      </c>
+      <c r="I44" s="22">
+        <f>IF(D44="Bonificado",0,IF(H44="",N(J44),IF(E44="USD",H44,H44/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K44" s="22">
+        <f>IF(D44="Alternativa","",I44-N(J44))</f>
+        <v/>
+      </c>
+      <c r="L44" s="24" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="37" t="inlineStr">
-        <is>
-          <t>Escoltas (2)</t>
-        </is>
-      </c>
-      <c r="B37" s="38" t="inlineStr">
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Master Mind Hit</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C37" s="39" t="inlineStr">
-        <is>
-          <t>Estimado del sheet</t>
-        </is>
-      </c>
-      <c r="D37" s="37" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Sala adicional</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E37" s="38" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F37" s="40" t="n"/>
-      <c r="G37" s="41" t="n"/>
-      <c r="H37" s="42">
-        <f>IF(F37="","",F37*(1+N(G37)))</f>
-        <v/>
-      </c>
-      <c r="I37" s="42">
-        <f>IF(H37="",N(J37),IF(E37="USD",H37,H37/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J37" s="40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K37" s="42">
-        <f>IF(D37="Alternativa","",I37-N(J37))</f>
-        <v/>
-      </c>
-      <c r="L37" s="43" t="inlineStr">
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="20" t="n"/>
+      <c r="H45" s="22">
+        <f>IF(F45="","",F45*(1+N(G45)))</f>
+        <v/>
+      </c>
+      <c r="I45" s="22">
+        <f>IF(D45="Bonificado",0,IF(H45="",N(J45),IF(E45="USD",H45,H45/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J45" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K45" s="22">
+        <f>IF(D45="Alternativa","",I45-N(J45))</f>
+        <v/>
+      </c>
+      <c r="L45" s="24" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="37" t="inlineStr">
-        <is>
-          <t>Master Mind Hit</t>
-        </is>
-      </c>
-      <c r="B38" s="38" t="inlineStr">
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Personal logístico</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C38" s="39" t="inlineStr">
-        <is>
-          <t>Sala adicional</t>
-        </is>
-      </c>
-      <c r="D38" s="37" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>La hoja del master lo tiene en US$0</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E38" s="38" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F38" s="40" t="n"/>
-      <c r="G38" s="41" t="n"/>
-      <c r="H38" s="42">
-        <f>IF(F38="","",F38*(1+N(G38)))</f>
-        <v/>
-      </c>
-      <c r="I38" s="42">
-        <f>IF(H38="",N(J38),IF(E38="USD",H38,H38/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J38" s="40" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K38" s="42">
-        <f>IF(D38="Alternativa","",I38-N(J38))</f>
-        <v/>
-      </c>
-      <c r="L38" s="43" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="37" t="inlineStr">
-        <is>
-          <t>Personal logístico</t>
-        </is>
-      </c>
-      <c r="B39" s="38" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C39" s="39" t="inlineStr">
-        <is>
-          <t>La hoja del master lo tiene en US$0</t>
-        </is>
-      </c>
-      <c r="D39" s="37" t="inlineStr">
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="22">
+        <f>IF(F46="","",F46*(1+N(G46)))</f>
+        <v/>
+      </c>
+      <c r="I46" s="22">
+        <f>IF(D46="Bonificado",0,IF(H46="",N(J46),IF(E46="USD",H46,H46/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J46" s="23" t="n"/>
+      <c r="K46" s="22">
+        <f>IF(D46="Alternativa","",I46-N(J46))</f>
+        <v/>
+      </c>
+      <c r="L46" s="24" t="inlineStr">
+        <is>
+          <t>Hoja Argentina del master · valor en cero</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Intercoms</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Proveedor Colombia</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Contrato US$560, sin abonar, 2 cuotas al 24/08 y 23/09</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Contratado</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>560</v>
+      </c>
+      <c r="G47" s="13" t="n"/>
+      <c r="H47" s="14">
+        <f>IF(F47="","",F47*(1+N(G47)))</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>IF(D47="Bonificado",0,IF(H47="",N(J47),IF(E47="USD",H47,H47/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="14">
+        <f>IF(D47="Alternativa","",I47-N(J47))</f>
+        <v/>
+      </c>
+      <c r="L47" s="15" t="inlineStr">
+        <is>
+          <t>Hoja PAGOS del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>Subtotal Producción</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="35" t="n"/>
+      <c r="G48" s="35" t="n"/>
+      <c r="H48" s="35" t="n"/>
+      <c r="I48" s="36">
+        <f>SUMIF($D$41:$D$47,"&lt;&gt;Alternativa",$I$41:$I$47)</f>
+        <v/>
+      </c>
+      <c r="J48" s="36">
+        <f>SUM($J$41:$J$47)</f>
+        <v/>
+      </c>
+      <c r="K48" s="36">
+        <f>I48-J48</f>
+        <v/>
+      </c>
+      <c r="L48" s="35" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Vuelos del equipo</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E39" s="38" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>No hay ninguna cotización de vuelos a Buenos Aires en el correo ni monto en la hoja del master</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F39" s="40" t="n"/>
-      <c r="G39" s="41" t="n"/>
-      <c r="H39" s="42">
-        <f>IF(F39="","",F39*(1+N(G39)))</f>
-        <v/>
-      </c>
-      <c r="I39" s="42">
-        <f>IF(H39="",N(J39),IF(E39="USD",H39,H39/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J39" s="40" t="n"/>
-      <c r="K39" s="42">
-        <f>IF(D39="Alternativa","",I39-N(J39))</f>
-        <v/>
-      </c>
-      <c r="L39" s="43" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master · valor en cero</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Intercoms</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Proveedor Colombia</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>Contrato US$560, sin abonar, 2 cuotas al 24/08 y 23/09</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>Contratado</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="F50" s="23" t="n"/>
+      <c r="G50" s="20" t="n"/>
+      <c r="H50" s="22">
+        <f>IF(F50="","",F50*(1+N(G50)))</f>
+        <v/>
+      </c>
+      <c r="I50" s="22">
+        <f>IF(D50="Bonificado",0,IF(H50="",N(J50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J50" s="23" t="n"/>
+      <c r="K50" s="22">
+        <f>IF(D50="Alternativa","",I50-N(J50))</f>
+        <v/>
+      </c>
+      <c r="L50" s="24" t="inlineStr">
+        <is>
+          <t>No encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Alojamiento del equipo</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>No hay cotización de hotel en Buenos Aires en el correo ni monto en la hoja del master</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>560</v>
-      </c>
-      <c r="G40" s="13" t="n"/>
-      <c r="H40" s="14">
-        <f>IF(F40="","",F40*(1+N(G40)))</f>
-        <v/>
-      </c>
-      <c r="I40" s="14">
-        <f>IF(H40="",N(J40),IF(E40="USD",H40,H40/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="14">
-        <f>IF(D40="Alternativa","",I40-N(J40))</f>
-        <v/>
-      </c>
-      <c r="L40" s="15" t="inlineStr">
-        <is>
-          <t>Hoja PAGOS del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>Subtotal Producción</t>
-        </is>
-      </c>
-      <c r="B41" s="35" t="n"/>
-      <c r="C41" s="35" t="n"/>
-      <c r="D41" s="35" t="n"/>
-      <c r="E41" s="35" t="n"/>
-      <c r="F41" s="35" t="n"/>
-      <c r="G41" s="35" t="n"/>
-      <c r="H41" s="35" t="n"/>
-      <c r="I41" s="36">
-        <f>SUMIF($D$35:$D$40,"&lt;&gt;Alternativa",$I$35:$I$40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="36">
-        <f>SUM($J$35:$J$40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="36">
-        <f>I41-J41</f>
-        <v/>
-      </c>
-      <c r="L41" s="35" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>EQUIPO</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-      <c r="L42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="37" t="inlineStr">
-        <is>
-          <t>Vuelos del equipo</t>
-        </is>
-      </c>
-      <c r="B43" s="38" t="inlineStr">
+      <c r="F51" s="23" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="22">
+        <f>IF(F51="","",F51*(1+N(G51)))</f>
+        <v/>
+      </c>
+      <c r="I51" s="22">
+        <f>IF(D51="Bonificado",0,IF(H51="",N(J51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J51" s="23" t="n"/>
+      <c r="K51" s="22">
+        <f>IF(D51="Alternativa","",I51-N(J51))</f>
+        <v/>
+      </c>
+      <c r="L51" s="24" t="inlineStr">
+        <is>
+          <t>No encontrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Traslados internos y viáticos</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C43" s="39" t="inlineStr">
-        <is>
-          <t>No hay ninguna cotización de vuelos a Buenos Aires en el correo ni monto en la hoja del master</t>
-        </is>
-      </c>
-      <c r="D43" s="37" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Sin registro</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E43" s="38" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F43" s="40" t="n"/>
-      <c r="G43" s="41" t="n"/>
-      <c r="H43" s="42">
-        <f>IF(F43="","",F43*(1+N(G43)))</f>
-        <v/>
-      </c>
-      <c r="I43" s="42">
-        <f>IF(H43="",N(J43),IF(E43="USD",H43,H43/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J43" s="40" t="n"/>
-      <c r="K43" s="42">
-        <f>IF(D43="Alternativa","",I43-N(J43))</f>
-        <v/>
-      </c>
-      <c r="L43" s="43" t="inlineStr">
+      <c r="F52" s="23" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="22">
+        <f>IF(F52="","",F52*(1+N(G52)))</f>
+        <v/>
+      </c>
+      <c r="I52" s="22">
+        <f>IF(D52="Bonificado",0,IF(H52="",N(J52),IF(E52="USD",H52,H52/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J52" s="23" t="n"/>
+      <c r="K52" s="22">
+        <f>IF(D52="Alternativa","",I52-N(J52))</f>
+        <v/>
+      </c>
+      <c r="L52" s="24" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="37" t="inlineStr">
-        <is>
-          <t>Alojamiento del equipo</t>
-        </is>
-      </c>
-      <c r="B44" s="38" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C44" s="39" t="inlineStr">
-        <is>
-          <t>No hay cotización de hotel en Buenos Aires en el correo ni monto en la hoja del master</t>
-        </is>
-      </c>
-      <c r="D44" s="37" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E44" s="38" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="41" t="n"/>
-      <c r="H44" s="42">
-        <f>IF(F44="","",F44*(1+N(G44)))</f>
-        <v/>
-      </c>
-      <c r="I44" s="42">
-        <f>IF(H44="",N(J44),IF(E44="USD",H44,H44/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J44" s="40" t="n"/>
-      <c r="K44" s="42">
-        <f>IF(D44="Alternativa","",I44-N(J44))</f>
-        <v/>
-      </c>
-      <c r="L44" s="43" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="37" t="inlineStr">
-        <is>
-          <t>Traslados internos y viáticos</t>
-        </is>
-      </c>
-      <c r="B45" s="38" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C45" s="39" t="inlineStr">
-        <is>
-          <t>Sin registro</t>
-        </is>
-      </c>
-      <c r="D45" s="37" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E45" s="38" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F45" s="40" t="n"/>
-      <c r="G45" s="41" t="n"/>
-      <c r="H45" s="42">
-        <f>IF(F45="","",F45*(1+N(G45)))</f>
-        <v/>
-      </c>
-      <c r="I45" s="42">
-        <f>IF(H45="",N(J45),IF(E45="USD",H45,H45/TABLERO!$C$4))</f>
-        <v/>
-      </c>
-      <c r="J45" s="40" t="n"/>
-      <c r="K45" s="42">
-        <f>IF(D45="Alternativa","",I45-N(J45))</f>
-        <v/>
-      </c>
-      <c r="L45" s="43" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>Subtotal Equipo</t>
         </is>
       </c>
-      <c r="B46" s="35" t="n"/>
-      <c r="C46" s="35" t="n"/>
-      <c r="D46" s="35" t="n"/>
-      <c r="E46" s="35" t="n"/>
-      <c r="F46" s="35" t="n"/>
-      <c r="G46" s="35" t="n"/>
-      <c r="H46" s="35" t="n"/>
-      <c r="I46" s="36">
-        <f>SUMIF($D$43:$D$45,"&lt;&gt;Alternativa",$I$43:$I$45)</f>
-        <v/>
-      </c>
-      <c r="J46" s="36">
-        <f>SUM($J$43:$J$45)</f>
-        <v/>
-      </c>
-      <c r="K46" s="36">
-        <f>I46-J46</f>
-        <v/>
-      </c>
-      <c r="L46" s="35" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="B53" s="35" t="n"/>
+      <c r="C53" s="35" t="n"/>
+      <c r="D53" s="35" t="n"/>
+      <c r="E53" s="35" t="n"/>
+      <c r="F53" s="35" t="n"/>
+      <c r="G53" s="35" t="n"/>
+      <c r="H53" s="35" t="n"/>
+      <c r="I53" s="36">
+        <f>SUMIF($D$50:$D$52,"&lt;&gt;Alternativa",$I$50:$I$52)</f>
+        <v/>
+      </c>
+      <c r="J53" s="36">
+        <f>SUM($J$50:$J$52)</f>
+        <v/>
+      </c>
+      <c r="K53" s="36">
+        <f>I53-J53</f>
+        <v/>
+      </c>
+      <c r="L53" s="35" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="46" t="inlineStr">
         <is>
           <t>COSTO TOTAL DEL EVENTO</t>
         </is>
       </c>
-      <c r="I48" s="45">
-        <f>I11+I15+I22+I30+I33+I41+I46</f>
-        <v/>
-      </c>
-      <c r="J48" s="45">
-        <f>J11+J15+J22+J30+J33+J41+J46</f>
-        <v/>
-      </c>
-      <c r="K48" s="45">
-        <f>K11+K15+K22+K30+K33+K41+K46</f>
+      <c r="I55" s="47">
+        <f>I12+I18+I26+I35+I39+I48+I53</f>
+        <v/>
+      </c>
+      <c r="J55" s="47">
+        <f>J12+J18+J26+J35+J39+J48+J53</f>
+        <v/>
+      </c>
+      <c r="K55" s="47">
+        <f>K12+K18+K26+K35+K39+K48+K53</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:L4"/>
   <mergeCells count="7">
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A49:L49"/>
     <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2696,8 +3057,8 @@
           <t>Tipo de cambio (ARS por USD)</t>
         </is>
       </c>
-      <c r="C4" s="46" t="n">
-        <v>1535</v>
+      <c r="C4" s="48" t="n">
+        <v>1530</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -2706,7 +3067,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>COSTO DEL EVENTO</t>
         </is>
@@ -2718,8 +3079,8 @@
           <t>Costo total (cotizaciones reales + estimados)</t>
         </is>
       </c>
-      <c r="C7" s="48">
-        <f>'COSTOS UNIFICADOS'!I48</f>
+      <c r="C7" s="50">
+        <f>'COSTOS UNIFICADOS'!I55</f>
         <v/>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2734,8 +3095,8 @@
           <t>Lo que decía el presupuesto original</t>
         </is>
       </c>
-      <c r="C8" s="48">
-        <f>'COSTOS UNIFICADOS'!J48</f>
+      <c r="C8" s="50">
+        <f>'COSTOS UNIFICADOS'!J55</f>
         <v/>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2750,8 +3111,8 @@
           <t>Diferencia contra el presupuesto</t>
         </is>
       </c>
-      <c r="C9" s="49">
-        <f>'COSTOS UNIFICADOS'!K48</f>
+      <c r="C9" s="51">
+        <f>'COSTOS UNIFICADOS'!K55</f>
         <v/>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2761,44 +3122,44 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>COSTO POR PERSONA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Base de cálculo</t>
         </is>
       </c>
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C12" s="52" t="inlineStr">
         <is>
           <t>Costo por persona</t>
         </is>
       </c>
-      <c r="E12" s="50" t="inlineStr">
+      <c r="E12" s="52" t="inlineStr">
         <is>
           <t>Qué incluye</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="inlineStr">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>Aforo general</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="54" t="n">
         <v>5000</v>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="55">
         <f>IFERROR($C$7/B13,"")</f>
         <v/>
       </c>
@@ -2809,15 +3170,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n">
+      <c r="B14" s="54" t="n">
         <v>1000</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="55">
         <f>IFERROR($C$7/B14,"")</f>
         <v/>
       </c>
@@ -2828,15 +3189,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="51" t="inlineStr">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t>Asistentes pagos (general + VIP)</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="54" t="n">
         <v>6000</v>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="55">
         <f>IFERROR($C$7/B15,"")</f>
         <v/>
       </c>
@@ -2847,15 +3208,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t>Mastermind del martes</t>
         </is>
       </c>
-      <c r="B16" s="52" t="n">
+      <c r="B16" s="54" t="n">
         <v>246</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="55">
         <f>IFERROR($C$7/B16,"")</f>
         <v/>
       </c>
@@ -2866,15 +3227,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="51" t="inlineStr">
+      <c r="A17" s="53" t="inlineStr">
         <is>
           <t>Total de personas en el predio</t>
         </is>
       </c>
-      <c r="B17" s="52" t="n">
+      <c r="B17" s="54" t="n">
         <v>6108</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="55">
         <f>IFERROR($C$7/B17,"")</f>
         <v/>
       </c>
@@ -2892,7 +3253,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>ESTADO DE LOS RUBROS</t>
         </is>
@@ -2904,7 +3265,7 @@
           <t>Contratado (hay contrato o anticipo)</t>
         </is>
       </c>
-      <c r="C21" s="54">
+      <c r="C21" s="56">
         <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Contratado",'COSTOS UNIFICADOS'!$I:$I)</f>
         <v/>
       </c>
@@ -2920,7 +3281,7 @@
           <t>Cotizado (hay presupuesto formal)</t>
         </is>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="50">
         <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Cotizado",'COSTOS UNIFICADOS'!$I:$I)</f>
         <v/>
       </c>
@@ -2936,7 +3297,7 @@
           <t>Sin cotizar (sólo estimado o nada)</t>
         </is>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="57">
         <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Sin cotizar",'COSTOS UNIFICADOS'!$I:$I)</f>
         <v/>
       </c>
@@ -2952,7 +3313,7 @@
           <t>Alternativas descartadas (no suman)</t>
         </is>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="58">
         <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Alternativa",'COSTOS UNIFICADOS'!$I:$I)</f>
         <v/>
       </c>
@@ -2968,7 +3329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3020,124 +3381,1306 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Sillas del público</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>La Rural: 5.000 sillas imperio bordó por $42.500.000 (sin IVA, armado incluido)</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>FDL Eventos: 5.500 sillas por $25.800.000 + IVA, sin armado ni facturación al exterior resuelta</t>
-        </is>
-      </c>
-      <c r="D5" s="42">
-        <f>(42500000-25800000*1.21)/TABLERO!$C$4</f>
-        <v/>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>Pedir a La Rural el costo del armado por separado. Si armar las de FDL cuesta menos que la diferencia, conviene FDL.</t>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Infraestructura de La Rural</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Presupuesto completo: $66.494.708 (US$43.461), con las 5.000 sillas y todo el mobiliario</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Sólo panelería + dirección técnica + guardias: $16.858.366 (US$11.019). El mobiliario se compra aparte.</t>
+        </is>
+      </c>
+      <c r="D5" s="22">
+        <f>(66494708.2-16858366.2)/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Agustina marca ítem por ítem qué se queda. La hoja INFRAESTRUCTURA tiene las 28 líneas del presupuesto para filtrar.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Técnica</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>Prina integral: $48.885.000 + IVA (sonido, luces, LED, video, estructura y staff)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Armado por partes: VMG sólo LED $12.625.000 + IVA, más sonido e iluminación por separado</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>La cotización de Prina venció en junio. Pedir revalidación a Prina, Sound-Light y Dixi con el mismo pliego y comparar en una sola planilla.</t>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Montaje de las sillas</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>La Rural con las sillas incluidas y armadas</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>FDL Eventos + montaje/acomodación/desmontaje negociado en $900.000</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>Con FDL a $31.218.000 más $900.000 de montaje son US$20.992 contra US$27.778 de La Rural. Cerrar el número del montaje y firmar.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Catering</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>AmbientHouse: viandas $28.500 + IVA por persona por día, base mínima 480</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Teist: propuesta del 26/06 sin cerrar. Azulado nunca envió.</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>Es el hueco más grande del presupuesto. Definir alcance (¿desayuno VIP para 1.000?) y pedir tres cotizaciones comparables esta semana.</t>
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Catering — cerrado</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Grupo Ambient: US$13.582 por las dos propuestas</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>La planilla tenía US$33.820 estimados</t>
+        </is>
+      </c>
+      <c r="D7" s="22">
+        <f>13582-33820</f>
+        <v/>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>Cerrado. Es la mejor negociación del evento: US$20.238 por debajo de lo presupuestado.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Rubros nuevos sin cotizar</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Ecobaños, marquetería de certificaciones y premios, replanteo de sillas con ingeniero</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Hoy entran en US$0</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>Pedir las tres cotizaciones esta semana. Son los últimos huecos que quedan además de vuelos y alojamiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Vuelos y alojamiento del equipo</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>No hay ni un mail ni una línea en el sheet. Con 8 personas del equipo interno, es plata que hoy no está en ningún número.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>No hay ni un mail ni una línea en el sheet. Con 8 personas de equipo interno, es el hueco más grande que queda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Facturación al exterior</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>FDL Eventos y Vittal no confirmaron si pueden facturar a la empresa de EE.UU.</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Buscar proveedores que sí facturen, o resolver un circuito de pago local</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>Resolverlo antes de firmar: es el punto que puede trabar los dos contratos.</t>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>Resolverlo antes de firmar: puede trabar los dos contratos.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Presupuesto de infraestructura de La Rural, línea por línea</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Las 28 líneas del PDF del 17/08. Marcá SÍ o NO en la columna "¿Se queda?" y el subtotal se recalcula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Ítem</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Precio (ARS)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>¿Se queda?</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Si se queda (ARS)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PANELERÍA (montaje de estructuras)</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="60" t="n"/>
+      <c r="D5" s="60" t="n"/>
+      <c r="E5" s="60" t="n"/>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="60" t="n"/>
+      <c r="H5" s="60" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>PANELERÍA (montaje de estructuras)</t>
+        </is>
+      </c>
+      <c r="C6" s="62" t="inlineStr">
+        <is>
+          <t>Oficina de producción — 25 m² (panelería + puerta + iluminación)</t>
+        </is>
+      </c>
+      <c r="D6" s="63" t="n">
+        <v>1314575</v>
+      </c>
+      <c r="E6" s="55">
+        <f>D6/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F6" s="64" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="G6" s="65">
+        <f>IF(F6="SÍ",D6,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="61" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="61" t="inlineStr">
+        <is>
+          <t>PANELERÍA (montaje de estructuras)</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="inlineStr">
+        <is>
+          <t>Sala de staff — 100 m² (panelería + puerta + iluminación)</t>
+        </is>
+      </c>
+      <c r="D7" s="63" t="n">
+        <v>5258300</v>
+      </c>
+      <c r="E7" s="55">
+        <f>D7/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="G7" s="65">
+        <f>IF(F7="SÍ",D7,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="61" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="61" t="inlineStr">
+        <is>
+          <t>PANELERÍA (montaje de estructuras)</t>
+        </is>
+      </c>
+      <c r="C8" s="62" t="inlineStr">
+        <is>
+          <t>Depósito 8×8 para las 2.500 barras — 64 m²</t>
+        </is>
+      </c>
+      <c r="D8" s="63" t="n">
+        <v>3365312</v>
+      </c>
+      <c r="E8" s="55">
+        <f>D8/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="64" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="G8" s="65">
+        <f>IF(F8="SÍ",D8,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="61" t="inlineStr">
+        <is>
+          <t>Depósito para las 2.500 barras de la dinámica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MOBILIARIO · oficina de producción</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="60" t="n"/>
+      <c r="D9" s="60" t="n"/>
+      <c r="E9" s="60" t="n"/>
+      <c r="F9" s="60" t="n"/>
+      <c r="G9" s="60" t="n"/>
+      <c r="H9" s="60" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="61" t="inlineStr">
+        <is>
+          <t>oficina de producción</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="inlineStr">
+        <is>
+          <t>Mesa redonda 1,60 ×2</t>
+        </is>
+      </c>
+      <c r="D10" s="63" t="n">
+        <v>236000</v>
+      </c>
+      <c r="E10" s="55">
+        <f>D10/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F10" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" s="65">
+        <f>IF(F10="SÍ",D10,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="61" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>oficina de producción</t>
+        </is>
+      </c>
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>Silla imperio bordó ×10</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="n">
+        <v>85000</v>
+      </c>
+      <c r="E11" s="55">
+        <f>D11/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F11" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" s="65">
+        <f>IF(F11="SÍ",D11,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="61" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="61" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>oficina de producción</t>
+        </is>
+      </c>
+      <c r="C12" s="62" t="inlineStr">
+        <is>
+          <t>Sillón Valencia 2C ×2</t>
+        </is>
+      </c>
+      <c r="D12" s="63" t="n">
+        <v>254000</v>
+      </c>
+      <c r="E12" s="55">
+        <f>D12/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F12" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G12" s="65">
+        <f>IF(F12="SÍ",D12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="61" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="61" t="inlineStr">
+        <is>
+          <t>oficina de producción</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>Sillón BRNO ×2</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="n">
+        <v>160000</v>
+      </c>
+      <c r="E13" s="55">
+        <f>D13/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F13" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G13" s="65">
+        <f>IF(F13="SÍ",D13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="61" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="61" t="inlineStr">
+        <is>
+          <t>oficina de producción</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="inlineStr">
+        <is>
+          <t>Mesa ratona ×1</t>
+        </is>
+      </c>
+      <c r="D14" s="63" t="n">
+        <v>118000</v>
+      </c>
+      <c r="E14" s="55">
+        <f>D14/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F14" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G14" s="65">
+        <f>IF(F14="SÍ",D14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="61" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="61" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="61" t="inlineStr">
+        <is>
+          <t>oficina de producción</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>Perchero de pie ×1</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E15" s="55">
+        <f>D15/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G15" s="65">
+        <f>IF(F15="SÍ",D15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="61" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="61" t="inlineStr">
+        <is>
+          <t>oficina de producción</t>
+        </is>
+      </c>
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>Tacho de basura grande ×1</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="n">
+        <v>56300</v>
+      </c>
+      <c r="E16" s="55">
+        <f>D16/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F16" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" s="65">
+        <f>IF(F16="SÍ",D16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="61" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MOBILIARIO · sala de staff</t>
+        </is>
+      </c>
+      <c r="B17" s="60" t="n"/>
+      <c r="C17" s="60" t="n"/>
+      <c r="D17" s="60" t="n"/>
+      <c r="E17" s="60" t="n"/>
+      <c r="F17" s="60" t="n"/>
+      <c r="G17" s="60" t="n"/>
+      <c r="H17" s="60" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="61" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="61" t="inlineStr">
+        <is>
+          <t>sala de staff</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="inlineStr">
+        <is>
+          <t>Mesa redonda 1,60 ×5</t>
+        </is>
+      </c>
+      <c r="D18" s="63" t="n">
+        <v>590000</v>
+      </c>
+      <c r="E18" s="55">
+        <f>D18/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F18" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" s="65">
+        <f>IF(F18="SÍ",D18,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="61" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="61" t="inlineStr">
+        <is>
+          <t>sala de staff</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
+        <is>
+          <t>Silla imperio bordó ×40</t>
+        </is>
+      </c>
+      <c r="D19" s="63" t="n">
+        <v>340000</v>
+      </c>
+      <c r="E19" s="55">
+        <f>D19/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F19" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G19" s="65">
+        <f>IF(F19="SÍ",D19,0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="61" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="61" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="61" t="inlineStr">
+        <is>
+          <t>sala de staff</t>
+        </is>
+      </c>
+      <c r="C20" s="62" t="inlineStr">
+        <is>
+          <t>Perchero de pie ×1</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E20" s="55">
+        <f>D20/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F20" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G20" s="65">
+        <f>IF(F20="SÍ",D20,0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="61" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="61" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="61" t="inlineStr">
+        <is>
+          <t>sala de staff</t>
+        </is>
+      </c>
+      <c r="C21" s="62" t="inlineStr">
+        <is>
+          <t>Tacho de basura grande ×1</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="n">
+        <v>56300</v>
+      </c>
+      <c r="E21" s="55">
+        <f>D21/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F21" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G21" s="65">
+        <f>IF(F21="SÍ",D21,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="61" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MOBILIARIO · sala principal</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="n"/>
+      <c r="C22" s="60" t="n"/>
+      <c r="D22" s="60" t="n"/>
+      <c r="E22" s="60" t="n"/>
+      <c r="F22" s="60" t="n"/>
+      <c r="G22" s="60" t="n"/>
+      <c r="H22" s="60" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="61" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>sala principal</t>
+        </is>
+      </c>
+      <c r="C23" s="62" t="inlineStr">
+        <is>
+          <t>Silla imperio bordó ×5.000</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="E23" s="55">
+        <f>D23/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F23" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G23" s="65">
+        <f>IF(F23="SÍ",D23,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="61" t="inlineStr">
+        <is>
+          <t>Reemplazadas por las 5.500 sillas de FDL Eventos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="61" t="n">
+        <v>16</v>
+      </c>
+      <c r="B24" s="61" t="inlineStr">
+        <is>
+          <t>sala principal</t>
+        </is>
+      </c>
+      <c r="C24" s="62" t="inlineStr">
+        <is>
+          <t>Mesa 1,80 × 0,90 ×40</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="E24" s="55">
+        <f>D24/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G24" s="65">
+        <f>IF(F24="SÍ",D24,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="61" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="61" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="61" t="inlineStr">
+        <is>
+          <t>sala principal</t>
+        </is>
+      </c>
+      <c r="C25" s="62" t="inlineStr">
+        <is>
+          <t>Mantel ×40</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E25" s="55">
+        <f>D25/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F25" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G25" s="65">
+        <f>IF(F25="SÍ",D25,0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="61" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="61" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="61" t="inlineStr">
+        <is>
+          <t>sala principal</t>
+        </is>
+      </c>
+      <c r="C26" s="62" t="inlineStr">
+        <is>
+          <t>Mantel redondo ×8</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="n">
+        <v>256000</v>
+      </c>
+      <c r="E26" s="55">
+        <f>D26/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F26" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" s="65">
+        <f>IF(F26="SÍ",D26,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="61" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MOBILIARIO · camarín de speakers</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="n"/>
+      <c r="C27" s="60" t="n"/>
+      <c r="D27" s="60" t="n"/>
+      <c r="E27" s="60" t="n"/>
+      <c r="F27" s="60" t="n"/>
+      <c r="G27" s="60" t="n"/>
+      <c r="H27" s="60" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="61" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="61" t="inlineStr">
+        <is>
+          <t>camarín de speakers</t>
+        </is>
+      </c>
+      <c r="C28" s="62" t="inlineStr">
+        <is>
+          <t>Mesa redonda 1,60 ×1</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="n">
+        <v>118000</v>
+      </c>
+      <c r="E28" s="55">
+        <f>D28/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F28" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G28" s="65">
+        <f>IF(F28="SÍ",D28,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="61" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="61" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="61" t="inlineStr">
+        <is>
+          <t>camarín de speakers</t>
+        </is>
+      </c>
+      <c r="C29" s="62" t="inlineStr">
+        <is>
+          <t>Espejo ×1</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="n">
+        <v>79500</v>
+      </c>
+      <c r="E29" s="55">
+        <f>D29/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F29" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G29" s="65">
+        <f>IF(F29="SÍ",D29,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="61" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="61" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="61" t="inlineStr">
+        <is>
+          <t>camarín de speakers</t>
+        </is>
+      </c>
+      <c r="C30" s="62" t="inlineStr">
+        <is>
+          <t>Juego de living (sillones + mesa ratona)</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="n">
+        <v>1103642</v>
+      </c>
+      <c r="E30" s="55">
+        <f>D30/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F30" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" s="65">
+        <f>IF(F30="SÍ",D30,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="61" t="inlineStr">
+        <is>
+          <t>El mobiliario "más fino" del camarín: candidato a contratárselo a La Rural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="61" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="61" t="inlineStr">
+        <is>
+          <t>camarín de speakers</t>
+        </is>
+      </c>
+      <c r="C31" s="62" t="inlineStr">
+        <is>
+          <t>Perchero de pie ×1</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E31" s="55">
+        <f>D31/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F31" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G31" s="65">
+        <f>IF(F31="SÍ",D31,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="61" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="61" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="61" t="inlineStr">
+        <is>
+          <t>camarín de speakers</t>
+        </is>
+      </c>
+      <c r="C32" s="62" t="inlineStr">
+        <is>
+          <t>Tacho de basura grande ×1</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="n">
+        <v>56300</v>
+      </c>
+      <c r="E32" s="55">
+        <f>D32/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F32" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" s="65">
+        <f>IF(F32="SÍ",D32,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="61" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MOBILIARIO · escenario y técnica</t>
+        </is>
+      </c>
+      <c r="B33" s="60" t="n"/>
+      <c r="C33" s="60" t="n"/>
+      <c r="D33" s="60" t="n"/>
+      <c r="E33" s="60" t="n"/>
+      <c r="F33" s="60" t="n"/>
+      <c r="G33" s="60" t="n"/>
+      <c r="H33" s="60" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="61" t="n">
+        <v>24</v>
+      </c>
+      <c r="B34" s="61" t="inlineStr">
+        <is>
+          <t>escenario y técnica</t>
+        </is>
+      </c>
+      <c r="C34" s="62" t="inlineStr">
+        <is>
+          <t>Mesa cocktail alta (escenario) ×1</t>
+        </is>
+      </c>
+      <c r="D34" s="63" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E34" s="55">
+        <f>D34/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G34" s="65">
+        <f>IF(F34="SÍ",D34,0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="61" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="61" t="n">
+        <v>25</v>
+      </c>
+      <c r="B35" s="61" t="inlineStr">
+        <is>
+          <t>escenario y técnica</t>
+        </is>
+      </c>
+      <c r="C35" s="62" t="inlineStr">
+        <is>
+          <t>Mesa alta para DJ ×1</t>
+        </is>
+      </c>
+      <c r="D35" s="63" t="n">
+        <v>62300</v>
+      </c>
+      <c r="E35" s="55">
+        <f>D35/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G35" s="65">
+        <f>IF(F35="SÍ",D35,0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="61" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GENERALES</t>
+        </is>
+      </c>
+      <c r="B36" s="60" t="n"/>
+      <c r="C36" s="60" t="n"/>
+      <c r="D36" s="60" t="n"/>
+      <c r="E36" s="60" t="n"/>
+      <c r="F36" s="60" t="n"/>
+      <c r="G36" s="60" t="n"/>
+      <c r="H36" s="60" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="61" t="n">
+        <v>26</v>
+      </c>
+      <c r="B37" s="61" t="inlineStr">
+        <is>
+          <t>GENERALES</t>
+        </is>
+      </c>
+      <c r="C37" s="62" t="inlineStr">
+        <is>
+          <t>Dirección técnica de todo el evento + replanteo</t>
+        </is>
+      </c>
+      <c r="D37" s="63" t="n">
+        <v>5149179.2</v>
+      </c>
+      <c r="E37" s="55">
+        <f>D37/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="G37" s="65">
+        <f>IF(F37="SÍ",D37,0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="61" t="inlineStr">
+        <is>
+          <t>Ojo: el replanteo de sillas va aparte, con ingeniero propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="61" t="n">
+        <v>27</v>
+      </c>
+      <c r="B38" s="61" t="inlineStr">
+        <is>
+          <t>GENERALES</t>
+        </is>
+      </c>
+      <c r="C38" s="62" t="inlineStr">
+        <is>
+          <t>Guardia eléctrica × 2 días</t>
+        </is>
+      </c>
+      <c r="D38" s="63" t="n">
+        <v>865800</v>
+      </c>
+      <c r="E38" s="55">
+        <f>D38/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F38" s="64" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="G38" s="65">
+        <f>IF(F38="SÍ",D38,0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="61" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="61" t="n">
+        <v>28</v>
+      </c>
+      <c r="B39" s="61" t="inlineStr">
+        <is>
+          <t>GENERALES</t>
+        </is>
+      </c>
+      <c r="C39" s="62" t="inlineStr">
+        <is>
+          <t>Guardia técnica × 2 días</t>
+        </is>
+      </c>
+      <c r="D39" s="63" t="n">
+        <v>905200</v>
+      </c>
+      <c r="E39" s="55">
+        <f>D39/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="F39" s="64" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="G39" s="65">
+        <f>IF(F39="SÍ",D39,0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="61" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL del presupuesto de La Rural</t>
+        </is>
+      </c>
+      <c r="D41" s="66">
+        <f>SUM(D6:D39)</f>
+        <v/>
+      </c>
+      <c r="E41" s="36">
+        <f>D41/TABLERO!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Lo que se queda (marcado SÍ)</t>
+        </is>
+      </c>
+      <c r="D42" s="67">
+        <f>SUM(G6:G39)</f>
+        <v/>
+      </c>
+      <c r="E42" s="68">
+        <f>D42/TABLERO!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Lo que se saca (marcado NO)</t>
+        </is>
+      </c>
+      <c r="D43" s="69">
+        <f>D41-D42</f>
+        <v/>
+      </c>
+      <c r="E43" s="70">
+        <f>D43/TABLERO!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Lo marcado hoy es el escenario provisional cargado en COSTOS UNIFICADOS: panelería + dirección técnica + guardias. Cambiá los SÍ/NO y llevá el nuevo total a esa hoja.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F10 F11 F12 F13 F14 F15 F16 F18 F19 F20 F21 F23 F24 F25 F26 F28 F29 F30 F31 F32 F34 F35 F37 F38 F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SÍ,NO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -11,7 +11,8 @@
     <sheet name="COSTOS UNIFICADOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="TABLERO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="DECISIONES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="INFRAESTRUCTURA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AHORROS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="INFRAESTRUCTURA" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COSTOS UNIFICADOS'!$A$4:$L$4</definedName>
@@ -28,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;(&quot;$&quot;#,##0);-"/>
     <numFmt numFmtId="167" formatCode="&quot;US$&quot;#,##0;(&quot;US$&quot;#,##0);-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +90,12 @@
       <name val="Arial"/>
       <color rgb="00008000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -166,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -203,6 +210,33 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -228,33 +262,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -300,7 +307,15 @@
     <xf numFmtId="167" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1017,253 +1032,253 @@
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Infraestructura La Rural (a filtrar)</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Infraestructura y mobiliario de stands</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>La Rural — Jefatura de Infraestructura</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Escenario provisional: sólo panelería (oficina de producción, sala de staff, depósito de las barras) + dirección técnica + guardias eléctrica y técnica. Se descontó TODO el mobiliario ($49.636.342) porque Agustina lo consigue aparte más barato. FALTA que marque qué ítems se quedan.</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Definido: armado de los stands y su mobiliario. Stand de staff 100 m², stand de producción menos de 50 m², y el mobiliario del camarín de speakers. Falta pedirles los espejos.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>9270</v>
+      </c>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="14">
+        <f>IF(F7="","",F7*(1+N(G7)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="14">
+        <f>IF(D7="Bonificado",0,IF(H7="",N(J7),IF(E7="USD",H7,H7/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="14">
+        <f>IF(D7="Alternativa","",I7-N(J7))</f>
+        <v/>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>Definición de Agustina sobre el presupuesto de $66.494.708 del 17/08 · ver hoja AHORROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Sillas del público (5.500)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>FDL Eventos</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>4.500 sillas plásticas Munro reforzadas + 1.000 sillas hotel negro + flete. NO incluye armado.</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n">
-        <v>16858366.2</v>
-      </c>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="21">
-        <f>IF(F7="","",F7*(1+N(G7)))</f>
-        <v/>
-      </c>
-      <c r="I7" s="22">
-        <f>IF(D7="Bonificado",0,IF(H7="",N(J7),IF(E7="USD",H7,H7/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="22">
-        <f>IF(D7="Alternativa","",I7-N(J7))</f>
-        <v/>
-      </c>
-      <c r="L7" s="24" t="inlineStr">
-        <is>
-          <t>Mail criccio@larural.com.ar 17/08/2026 · total del PDF $66.494.708,20 · ver hoja INFRAESTRUCTURA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>Sillas del público (5.500)</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>FDL Eventos</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>4.500 sillas plásticas Munro reforzadas + 1.000 sillas hotel negro + flete. NO incluye armado.</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="F8" s="19" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H8" s="21">
+        <f>IF(F8="","",F8*(1+N(G8)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>IF(D8="Bonificado",0,IF(H8="",N(J8),IF(E8="USD",H8,H8/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>16500</v>
+      </c>
+      <c r="K8" s="22">
+        <f>IF(D8="Alternativa","",I8-N(J8))</f>
+        <v/>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Mail fdleventos@gmail.com 07/08/2026 · pendiente de resolver facturación al exterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Montaje, acomodación y desmontaje de sillas</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>En negociación</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Montaje previo, acomodación el sábado a la noche después de la dinámica y desmontaje el domingo.</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>En negociación</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>900000</v>
+      </c>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="30">
+        <f>IF(F9="","",F9*(1+N(G9)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="31">
+        <f>IF(D9="Bonificado",0,IF(H9="",N(J9),IF(E9="USD",H9,H9/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="32" t="n"/>
+      <c r="K9" s="31">
+        <f>IF(D9="Alternativa","",I9-N(J9))</f>
+        <v/>
+      </c>
+      <c r="L9" s="33" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina · cerrar el número antes de firmar las sillas</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Replanteo de sillas (ingeniero)</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Replanteo del layout de sillas del pabellón. Confirmado que va aparte de la dirección técnica de La Rural.</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="31">
+        <f>IF(F10="","",F10*(1+N(G10)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="31">
+        <f>IF(D10="Bonificado",0,IF(H10="",N(J10),IF(E10="USD",H10,H10/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="32" t="n"/>
+      <c r="K10" s="31">
+        <f>IF(D10="Alternativa","",I10-N(J10))</f>
+        <v/>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>Pendiente de pedir presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Conectividad WiFi</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>La Rural — Servicios de Conectividad</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>2 redes privadas de 30 Mbps (técnica + staff/acreditación), del 2 al 4 de octubre</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n">
-        <v>25800000</v>
-      </c>
-      <c r="G8" s="29" t="n">
+      <c r="F11" s="19" t="n">
+        <v>1466063.84</v>
+      </c>
+      <c r="G11" s="20" t="n">
         <v>0.21</v>
       </c>
-      <c r="H8" s="30">
-        <f>IF(F8="","",F8*(1+N(G8)))</f>
-        <v/>
-      </c>
-      <c r="I8" s="31">
-        <f>IF(D8="Bonificado",0,IF(H8="",N(J8),IF(E8="USD",H8,H8/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J8" s="32" t="n">
-        <v>16500</v>
-      </c>
-      <c r="K8" s="31">
-        <f>IF(D8="Alternativa","",I8-N(J8))</f>
-        <v/>
-      </c>
-      <c r="L8" s="33" t="inlineStr">
-        <is>
-          <t>Mail fdleventos@gmail.com 07/08/2026 · pendiente de resolver facturación al exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Montaje, acomodación y desmontaje de sillas</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>En negociación</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Montaje previo, acomodación el sábado a la noche después de la dinámica y desmontaje el domingo.</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>En negociación</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>900000</v>
-      </c>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="21">
-        <f>IF(F9="","",F9*(1+N(G9)))</f>
-        <v/>
-      </c>
-      <c r="I9" s="22">
-        <f>IF(D9="Bonificado",0,IF(H9="",N(J9),IF(E9="USD",H9,H9/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="22">
-        <f>IF(D9="Alternativa","",I9-N(J9))</f>
-        <v/>
-      </c>
-      <c r="L9" s="24" t="inlineStr">
-        <is>
-          <t>Negociación de Agustina · cerrar el número antes de firmar las sillas</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Replanteo de sillas (ingeniero)</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Replanteo del layout de sillas del pabellón. Confirmado que va aparte de la dirección técnica de La Rural.</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="22">
-        <f>IF(F10="","",F10*(1+N(G10)))</f>
-        <v/>
-      </c>
-      <c r="I10" s="22">
-        <f>IF(D10="Bonificado",0,IF(H10="",N(J10),IF(E10="USD",H10,H10/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J10" s="23" t="n"/>
-      <c r="K10" s="22">
-        <f>IF(D10="Alternativa","",I10-N(J10))</f>
-        <v/>
-      </c>
-      <c r="L10" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente de pedir presupuesto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Conectividad WiFi</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>La Rural — Servicios de Conectividad</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>2 redes privadas de 30 Mbps (técnica + staff/acreditación), del 2 al 4 de octubre</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>1438728.01</v>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H11" s="30">
+      <c r="H11" s="21">
         <f>IF(F11="","",F11*(1+N(G11)))</f>
         <v/>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="22">
         <f>IF(D11="Bonificado",0,IF(H11="",N(J11),IF(E11="USD",H11,H11/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J11" s="32" t="n">
+      <c r="J11" s="23" t="n">
         <v>800</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="22">
         <f>IF(D11="Alternativa","",I11-N(J11))</f>
         <v/>
       </c>
-      <c r="L11" s="33" t="inlineStr">
-        <is>
-          <t>Mail conectividad@larural.com.ar 16/06/2026</t>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>Mail conectividad@larural.com.ar 05/08/2026 · presupuesto N.º 2, base IPC junio (el del 16/06 era $1.438.728)</t>
         </is>
       </c>
     </row>
@@ -1554,302 +1569,302 @@
       <c r="L19" s="8" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Seguridad y vigilancia</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Road Seguridad S.A.</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>263 horas de vigilancia (armado, evento y desarme) + planos de evacuación $715.000 + supervisión general $795.000</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="19" t="n">
         <v>7218928.96</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="20" t="n">
         <v>0.21</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="21">
         <f>IF(F20="","",F20*(1+N(G20)))</f>
         <v/>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="22">
         <f>IF(D20="Bonificado",0,IF(H20="",N(J20),IF(E20="USD",H20,H20/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J20" s="32" t="n"/>
-      <c r="K20" s="31">
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="22">
         <f>IF(D20="Alternativa","",I20-N(J20))</f>
         <v/>
       </c>
-      <c r="L20" s="33" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>Mail presupuestos@roadseguridad.com.ar 12/08/2026 (versión V3, lista para firmar)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Servicio médico</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Vittal — Socorro Médico Privado</t>
         </is>
       </c>
-      <c r="C21" s="27" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>1 UTIM TRI con dos médicos + enfermero/chofer, los tres días (2, 3 y 4 de octubre)</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="19" t="n">
         <v>6366521.27</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="20" t="n">
         <v>0.105</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="21">
         <f>IF(F21="","",F21*(1+N(G21)))</f>
         <v/>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="22">
         <f>IF(D21="Bonificado",0,IF(H21="",N(J21),IF(E21="USD",H21,H21/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="31">
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="22">
         <f>IF(D21="Alternativa","",I21-N(J21))</f>
         <v/>
       </c>
-      <c r="L21" s="33" t="inlineStr">
+      <c r="L21" s="24" t="inlineStr">
         <is>
           <t>Mail vtomas@vittal.com.ar 28/08/2026 · tarifas actualizadas, sin consultorio</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Higia Eventos</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>205,5 horas de limpieza: auditorio, baños y guardarropas, del 2 al 5 de octubre</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="19" t="n">
         <v>3367440.91</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="20" t="n">
         <v>0.21</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="21">
         <f>IF(F22="","",F22*(1+N(G22)))</f>
         <v/>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="22">
         <f>IF(D22="Bonificado",0,IF(H22="",N(J22),IF(E22="USD",H22,H22/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J22" s="32" t="n"/>
-      <c r="K22" s="31">
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="22">
         <f>IF(D22="Alternativa","",I22-N(J22))</f>
         <v/>
       </c>
-      <c r="L22" s="33" t="inlineStr">
+      <c r="L22" s="24" t="inlineStr">
         <is>
           <t>Mail higiaeventos 22/06/2026 (reenviado 29/06) · 50% de anticipo antes del armado</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Retiro de residuos</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Gale Servicios</t>
         </is>
       </c>
-      <c r="C23" s="27" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>Roll off con disposición final incluida. Cotización base abril 2026.</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="19" t="n">
         <v>1471608.62</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="20" t="n">
         <v>0.21</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="21">
         <f>IF(F23="","",F23*(1+N(G23)))</f>
         <v/>
       </c>
-      <c r="I23" s="31">
+      <c r="I23" s="22">
         <f>IF(D23="Bonificado",0,IF(H23="",N(J23),IF(E23="USD",H23,H23/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="31">
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="22">
         <f>IF(D23="Alternativa","",I23-N(J23))</f>
         <v/>
       </c>
-      <c r="L23" s="33" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>Mail higiaeventos 22/06/2026 (adjunto Gale) · se factura 100% por adelantado</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Baños químicos — ecobaños</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>Decidido: ecobaños, no los químicos tradicionales. Más limpios, mejor a la vista y ecofriendly. Falta pedir presupuesto.</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="22">
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="29" t="n"/>
+      <c r="H24" s="31">
         <f>IF(F24="","",F24*(1+N(G24)))</f>
         <v/>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="31">
         <f>IF(D24="Bonificado",0,IF(H24="",N(J24),IF(E24="USD",H24,H24/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J24" s="23" t="n"/>
-      <c r="K24" s="22">
+      <c r="J24" s="32" t="n"/>
+      <c r="K24" s="31">
         <f>IF(D24="Alternativa","",I24-N(J24))</f>
         <v/>
       </c>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="33" t="inlineStr">
         <is>
           <t>Decisión de Agustina · pendiente de cotizar</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Seguro de accidentes personales</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Chanes Seguros</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>Cobertura MIA (muerte, invalidez y asistencia médica) para 150 personas, exigida por La Rural</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E25" s="26" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="19" t="n">
         <v>953151.9300000001</v>
       </c>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="30">
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="21">
         <f>IF(F25="","",F25*(1+N(G25)))</f>
         <v/>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="22">
         <f>IF(D25="Bonificado",0,IF(H25="",N(J25),IF(E25="USD",H25,H25/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J25" s="32" t="n">
+      <c r="J25" s="23" t="n">
         <v>400</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="22">
         <f>IF(D25="Alternativa","",I25-N(J25))</f>
         <v/>
       </c>
-      <c r="L25" s="33" t="inlineStr">
+      <c r="L25" s="24" t="inlineStr">
         <is>
           <t>Mail nestor@chanesseguros.com.ar 13/07/2026 · premio único, cotizado para 15-19/07</t>
         </is>
@@ -1901,51 +1916,51 @@
       <c r="L27" s="8" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Cintas portacredencial (1.300)</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Blocko</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>Cinta raso 25 mm impresa 4 colores dos caras + mosquetón zamak, $1.346 c/u</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="19" t="n">
         <v>1749800</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="20" t="n">
         <v>0.21</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="21">
         <f>IF(F28="","",F28*(1+N(G28)))</f>
         <v/>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="22">
         <f>IF(D28="Bonificado",0,IF(H28="",N(J28),IF(E28="USD",H28,H28/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J28" s="32" t="n"/>
-      <c r="K28" s="31">
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="22">
         <f>IF(D28="Alternativa","",I28-N(J28))</f>
         <v/>
       </c>
-      <c r="L28" s="33" t="inlineStr">
+      <c r="L28" s="24" t="inlineStr">
         <is>
           <t>Mail hola@blocko.com.ar 09/06/2026 · producción 3 semanas</t>
         </is>
@@ -2150,96 +2165,96 @@
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Marquetería y enmarcado</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="27" t="inlineStr">
         <is>
           <t>Enmarcado de las certificaciones y los premios. Rubro nuevo, no estaba en ninguna planilla.</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F33" s="23" t="n"/>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="22">
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="29" t="n"/>
+      <c r="H33" s="31">
         <f>IF(F33="","",F33*(1+N(G33)))</f>
         <v/>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="31">
         <f>IF(D33="Bonificado",0,IF(H33="",N(J33),IF(E33="USD",H33,H33/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J33" s="23" t="n"/>
-      <c r="K33" s="22">
+      <c r="J33" s="32" t="n"/>
+      <c r="K33" s="31">
         <f>IF(D33="Alternativa","",I33-N(J33))</f>
         <v/>
       </c>
-      <c r="L33" s="24" t="inlineStr">
+      <c r="L33" s="33" t="inlineStr">
         <is>
           <t>Agregado por Agustina · pendiente de cotizar</t>
         </is>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Resto de merch e impresos</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Varios (merch desde Colombia)</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>Contratos, cheques, escarapelas, bolsas, camisetas, mapas, diplomas, placas y manillas</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="20" t="n"/>
-      <c r="H34" s="22">
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="31">
         <f>IF(F34="","",F34*(1+N(G34)))</f>
         <v/>
       </c>
-      <c r="I34" s="22">
+      <c r="I34" s="31">
         <f>IF(D34="Bonificado",0,IF(H34="",N(J34),IF(E34="USD",H34,H34/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J34" s="23" t="n">
+      <c r="J34" s="32" t="n">
         <v>8689</v>
       </c>
-      <c r="K34" s="22">
+      <c r="K34" s="31">
         <f>IF(D34="Alternativa","",I34-N(J34))</f>
         <v/>
       </c>
-      <c r="L34" s="24" t="inlineStr">
+      <c r="L34" s="33" t="inlineStr">
         <is>
           <t>Estimado de la hoja Argentina del master; sin cotización argentina</t>
         </is>
@@ -2434,49 +2449,49 @@
       <c r="L40" s="8" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>Unifilas</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>Estimado del sheet, sin cotización</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F41" s="23" t="n"/>
-      <c r="G41" s="20" t="n"/>
-      <c r="H41" s="22">
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="29" t="n"/>
+      <c r="H41" s="31">
         <f>IF(F41="","",F41*(1+N(G41)))</f>
         <v/>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="31">
         <f>IF(D41="Bonificado",0,IF(H41="",N(J41),IF(E41="USD",H41,H41/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J41" s="23" t="n">
+      <c r="J41" s="32" t="n">
         <v>1200</v>
       </c>
-      <c r="K41" s="22">
+      <c r="K41" s="31">
         <f>IF(D41="Alternativa","",I41-N(J41))</f>
         <v/>
       </c>
-      <c r="L41" s="24" t="inlineStr">
+      <c r="L41" s="33" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
@@ -2532,194 +2547,194 @@
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>DJ</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>Estimado del sheet</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F43" s="23" t="n"/>
-      <c r="G43" s="20" t="n"/>
-      <c r="H43" s="22">
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="29" t="n"/>
+      <c r="H43" s="31">
         <f>IF(F43="","",F43*(1+N(G43)))</f>
         <v/>
       </c>
-      <c r="I43" s="22">
+      <c r="I43" s="31">
         <f>IF(D43="Bonificado",0,IF(H43="",N(J43),IF(E43="USD",H43,H43/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J43" s="23" t="n">
+      <c r="J43" s="32" t="n">
         <v>500</v>
       </c>
-      <c r="K43" s="22">
+      <c r="K43" s="31">
         <f>IF(D43="Alternativa","",I43-N(J43))</f>
         <v/>
       </c>
-      <c r="L43" s="24" t="inlineStr">
+      <c r="L43" s="33" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>Escoltas (2)</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>Estimado del sheet</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F44" s="23" t="n"/>
-      <c r="G44" s="20" t="n"/>
-      <c r="H44" s="22">
+      <c r="F44" s="32" t="n"/>
+      <c r="G44" s="29" t="n"/>
+      <c r="H44" s="31">
         <f>IF(F44="","",F44*(1+N(G44)))</f>
         <v/>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="31">
         <f>IF(D44="Bonificado",0,IF(H44="",N(J44),IF(E44="USD",H44,H44/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J44" s="23" t="n">
+      <c r="J44" s="32" t="n">
         <v>1000</v>
       </c>
-      <c r="K44" s="22">
+      <c r="K44" s="31">
         <f>IF(D44="Alternativa","",I44-N(J44))</f>
         <v/>
       </c>
-      <c r="L44" s="24" t="inlineStr">
+      <c r="L44" s="33" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>Master Mind Hit</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>Sala adicional</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F45" s="23" t="n"/>
-      <c r="G45" s="20" t="n"/>
-      <c r="H45" s="22">
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="29" t="n"/>
+      <c r="H45" s="31">
         <f>IF(F45="","",F45*(1+N(G45)))</f>
         <v/>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="31">
         <f>IF(D45="Bonificado",0,IF(H45="",N(J45),IF(E45="USD",H45,H45/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J45" s="23" t="n">
+      <c r="J45" s="32" t="n">
         <v>3000</v>
       </c>
-      <c r="K45" s="22">
+      <c r="K45" s="31">
         <f>IF(D45="Alternativa","",I45-N(J45))</f>
         <v/>
       </c>
-      <c r="L45" s="24" t="inlineStr">
+      <c r="L45" s="33" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>Personal logístico</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>La hoja del master lo tiene en US$0</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F46" s="23" t="n"/>
-      <c r="G46" s="20" t="n"/>
-      <c r="H46" s="22">
+      <c r="F46" s="32" t="n"/>
+      <c r="G46" s="29" t="n"/>
+      <c r="H46" s="31">
         <f>IF(F46="","",F46*(1+N(G46)))</f>
         <v/>
       </c>
-      <c r="I46" s="22">
+      <c r="I46" s="31">
         <f>IF(D46="Bonificado",0,IF(H46="",N(J46),IF(E46="USD",H46,H46/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J46" s="23" t="n"/>
-      <c r="K46" s="22">
+      <c r="J46" s="32" t="n"/>
+      <c r="K46" s="31">
         <f>IF(D46="Alternativa","",I46-N(J46))</f>
         <v/>
       </c>
-      <c r="L46" s="24" t="inlineStr">
+      <c r="L46" s="33" t="inlineStr">
         <is>
           <t>Hoja Argentina del master · valor en cero</t>
         </is>
@@ -2820,141 +2835,141 @@
       <c r="L49" s="8" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="25" t="inlineStr">
         <is>
           <t>Vuelos del equipo</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>No hay ninguna cotización de vuelos a Buenos Aires en el correo ni monto en la hoja del master</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F50" s="23" t="n"/>
-      <c r="G50" s="20" t="n"/>
-      <c r="H50" s="22">
+      <c r="F50" s="32" t="n"/>
+      <c r="G50" s="29" t="n"/>
+      <c r="H50" s="31">
         <f>IF(F50="","",F50*(1+N(G50)))</f>
         <v/>
       </c>
-      <c r="I50" s="22">
+      <c r="I50" s="31">
         <f>IF(D50="Bonificado",0,IF(H50="",N(J50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J50" s="23" t="n"/>
-      <c r="K50" s="22">
+      <c r="J50" s="32" t="n"/>
+      <c r="K50" s="31">
         <f>IF(D50="Alternativa","",I50-N(J50))</f>
         <v/>
       </c>
-      <c r="L50" s="24" t="inlineStr">
+      <c r="L50" s="33" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>Alojamiento del equipo</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>No hay cotización de hotel en Buenos Aires en el correo ni monto en la hoja del master</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F51" s="23" t="n"/>
-      <c r="G51" s="20" t="n"/>
-      <c r="H51" s="22">
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="29" t="n"/>
+      <c r="H51" s="31">
         <f>IF(F51="","",F51*(1+N(G51)))</f>
         <v/>
       </c>
-      <c r="I51" s="22">
+      <c r="I51" s="31">
         <f>IF(D51="Bonificado",0,IF(H51="",N(J51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J51" s="23" t="n"/>
-      <c r="K51" s="22">
+      <c r="J51" s="32" t="n"/>
+      <c r="K51" s="31">
         <f>IF(D51="Alternativa","",I51-N(J51))</f>
         <v/>
       </c>
-      <c r="L51" s="24" t="inlineStr">
+      <c r="L51" s="33" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="25" t="inlineStr">
         <is>
           <t>Traslados internos y viáticos</t>
         </is>
       </c>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>Sin registro</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="25" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F52" s="23" t="n"/>
-      <c r="G52" s="20" t="n"/>
-      <c r="H52" s="22">
+      <c r="F52" s="32" t="n"/>
+      <c r="G52" s="29" t="n"/>
+      <c r="H52" s="31">
         <f>IF(F52="","",F52*(1+N(G52)))</f>
         <v/>
       </c>
-      <c r="I52" s="22">
+      <c r="I52" s="31">
         <f>IF(D52="Bonificado",0,IF(H52="",N(J52),IF(E52="USD",H52,H52/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="J52" s="23" t="n"/>
-      <c r="K52" s="22">
+      <c r="J52" s="32" t="n"/>
+      <c r="K52" s="31">
         <f>IF(D52="Alternativa","",I52-N(J52))</f>
         <v/>
       </c>
-      <c r="L52" s="24" t="inlineStr">
+      <c r="L52" s="33" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
@@ -3381,144 +3396,144 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Infraestructura de La Rural</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Presupuesto completo: $66.494.708 (US$43.461), con las 5.000 sillas y todo el mobiliario</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Sólo panelería + dirección técnica + guardias: $16.858.366 (US$11.019). El mobiliario se compra aparte.</t>
         </is>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="31">
         <f>(66494708.2-16858366.2)/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>Agustina marca ítem por ítem qué se queda. La hoja INFRAESTRUCTURA tiene las 28 líneas del presupuesto para filtrar.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Montaje de las sillas</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>La Rural con las sillas incluidas y armadas</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>FDL Eventos + montaje/acomodación/desmontaje negociado en $900.000</t>
         </is>
       </c>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>Con FDL a $31.218.000 más $900.000 de montaje son US$20.992 contra US$27.778 de La Rural. Cerrar el número del montaje y firmar.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Catering — cerrado</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Grupo Ambient: US$13.582 por las dos propuestas</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>La planilla tenía US$33.820 estimados</t>
         </is>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="31">
         <f>13582-33820</f>
         <v/>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>Cerrado. Es la mejor negociación del evento: US$20.238 por debajo de lo presupuestado.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Rubros nuevos sin cotizar</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Ecobaños, marquetería de certificaciones y premios, replanteo de sillas con ingeniero</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Hoy entran en US$0</t>
         </is>
       </c>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Pedir las tres cotizaciones esta semana. Son los últimos huecos que quedan además de vuelos y alojamiento.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Vuelos y alojamiento del equipo</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>No hay ni un mail ni una línea en el sheet. Con 8 personas de equipo interno, es el hueco más grande que queda.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Facturación al exterior</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>FDL Eventos y Vittal no confirmaron si pueden facturar a la empresa de EE.UU.</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>Buscar proveedores que sí facturen, o resolver un circuito de pago local</t>
         </is>
       </c>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>Resolverlo antes de firmar: puede trabar los dos contratos.</t>
         </is>
@@ -3530,6 +3545,383 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lo cotizado contra lo que se cerró</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cuánto se bajó rubro por rubro. La columna "Respaldo" dice si la referencia está documentada en el correo o si es un dato aportado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Rubro</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Referencia cotizada</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Ref. en pesos</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Ref. USD</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Lo que se cerró</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado en pesos</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado USD</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Ahorro USD</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Ahorro %</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Respaldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Infraestructura y mobiliario</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Grupo MET, cotización de mobiliario</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="D5" s="22">
+        <f>C5/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Armado de stands + mobiliario, definido por Agustina</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>14183100</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>9270</v>
+      </c>
+      <c r="H5" s="59">
+        <f>D5-G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="60">
+        <f>IFERROR(H5/D5,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="24" t="inlineStr">
+        <is>
+          <t>La cotización de Grupo MET no está en el correo: dato aportado por Agustina. En el correo sí está el presupuesto de La Rural del 17/08 por $66.494.708 (con las 5.000 sillas adentro).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Sillas del público</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>La Rural: 5.000 sillas imperio bordó, armado incluido</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="D6" s="22">
+        <f>C6/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>FDL Eventos 5.500 sillas + montaje, acomodación y desmontaje</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>32118000</v>
+      </c>
+      <c r="G6" s="22">
+        <f>F6/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="H6" s="59">
+        <f>D6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="60">
+        <f>IFERROR(H6/D6,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>Mail criccio@larural.com.ar 17/08 y mail fdleventos@gmail.com 07/08. El montaje ($900.000) está en negociación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Entelado</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Primera cotización recibida</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="D7" s="22">
+        <f>C7/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Negociado a la mitad</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="G7" s="22">
+        <f>F7/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="H7" s="59">
+        <f>D7-G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="60">
+        <f>IFERROR(H7/D7,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="24" t="inlineStr">
+        <is>
+          <t>Dato aportado por Agustina; la cotización inicial no está en el correo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Primera propuesta de Grupo Ambient</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="D8" s="22">
+        <f>C8/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>600 lunchbox VIP + desayuno, almuerzo y cena para 150 personas</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="23" t="n">
+        <v>13582</v>
+      </c>
+      <c r="H8" s="59">
+        <f>D8-G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="60">
+        <f>IFERROR(H8/D8,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>Cierre informado por Agustina. En el correo está la propuesta de AmbientHouse del 16/06 a $28.500 + IVA por persona por día con base mínima de 480.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Vallado del público</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Presupuestado en la hoja de Argentina</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="23" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>500 vallas bonificadas por el proveedor de técnica</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="59">
+        <f>D9-G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="60">
+        <f>IFERROR(H9/D9,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina. Además bonifican los efectos especiales, que no estaban valorizados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>AHORRO TOTAL</t>
+        </is>
+      </c>
+      <c r="D10" s="61">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="61">
+        <f>SUM(G5:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="61">
+        <f>SUM(H5:H9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>TÉCNICA — la comparación no es directa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Se cerró con Grupo MET en US$60.000 (unos $91.800.000 al dólar de referencia), con todos los agregados que se fueron sumando después de la visita al predio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Las otras cotizaciones fueron sobre el pliego base, que según Agustina no cubría lo que necesita el pabellón. Por eso no se pueden restar sin más:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Sound-Light (16/06): no se pudo abrir el PDF, el mail pesa 33 MB. En el mail del 19/06 se les dice que las otras cotizaciones son "prácticamente la mitad", así que estaba cerca de los $100.000.000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 2MG (24/06): $53.655.470, con descuento especial $45.000.000 + IVA. Con los adicionales de iluminación y estructura llega a unos $78.000.000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Validez de 10 días, vencida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · VMG (29/06): $12.625.000 + IVA, sólo las pantallas LED de 65 m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Para poder mostrar un ahorro defendible en técnica hace falta el PDF de Grupo MET y el alcance final, para compararlo contra el mismo alcance de los otros tres.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3605,1014 +3997,1014 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="B5" s="60" t="n"/>
-      <c r="C5" s="60" t="n"/>
-      <c r="D5" s="60" t="n"/>
-      <c r="E5" s="60" t="n"/>
-      <c r="F5" s="60" t="n"/>
-      <c r="G5" s="60" t="n"/>
-      <c r="H5" s="60" t="n"/>
+      <c r="B5" s="64" t="n"/>
+      <c r="C5" s="64" t="n"/>
+      <c r="D5" s="64" t="n"/>
+      <c r="E5" s="64" t="n"/>
+      <c r="F5" s="64" t="n"/>
+      <c r="G5" s="64" t="n"/>
+      <c r="H5" s="64" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="n">
+      <c r="A6" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>Oficina de producción — 25 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D6" s="63" t="n">
+      <c r="D6" s="67" t="n">
         <v>1314575</v>
       </c>
       <c r="E6" s="55">
         <f>D6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F6" s="64" t="inlineStr">
+      <c r="F6" s="68" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="69">
         <f>IF(F6="SÍ",D6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="61" t="inlineStr"/>
+      <c r="H6" s="65" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="n">
+      <c r="A7" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="65" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>Sala de staff — 100 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D7" s="63" t="n">
+      <c r="D7" s="67" t="n">
         <v>5258300</v>
       </c>
       <c r="E7" s="55">
         <f>D7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F7" s="64" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="69">
         <f>IF(F7="SÍ",D7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="61" t="inlineStr"/>
+      <c r="H7" s="65" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="n">
+      <c r="A8" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="65" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>Depósito 8×8 para las 2.500 barras — 64 m²</t>
         </is>
       </c>
-      <c r="D8" s="63" t="n">
+      <c r="D8" s="67" t="n">
         <v>3365312</v>
       </c>
       <c r="E8" s="55">
         <f>D8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="64" t="inlineStr">
+      <c r="F8" s="68" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G8" s="65">
+      <c r="G8" s="69">
         <f>IF(F8="SÍ",D8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="61" t="inlineStr">
+      <c r="H8" s="65" t="inlineStr">
         <is>
           <t>Depósito para las 2.500 barras de la dinámica.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · oficina de producción</t>
         </is>
       </c>
-      <c r="B9" s="60" t="n"/>
-      <c r="C9" s="60" t="n"/>
-      <c r="D9" s="60" t="n"/>
-      <c r="E9" s="60" t="n"/>
-      <c r="F9" s="60" t="n"/>
-      <c r="G9" s="60" t="n"/>
-      <c r="H9" s="60" t="n"/>
+      <c r="B9" s="64" t="n"/>
+      <c r="C9" s="64" t="n"/>
+      <c r="D9" s="64" t="n"/>
+      <c r="E9" s="64" t="n"/>
+      <c r="F9" s="64" t="n"/>
+      <c r="G9" s="64" t="n"/>
+      <c r="H9" s="64" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="n">
+      <c r="A10" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×2</t>
         </is>
       </c>
-      <c r="D10" s="63" t="n">
+      <c r="D10" s="67" t="n">
         <v>236000</v>
       </c>
       <c r="E10" s="55">
         <f>D10/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="64" t="inlineStr">
+      <c r="F10" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G10" s="65">
+      <c r="G10" s="69">
         <f>IF(F10="SÍ",D10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="61" t="inlineStr"/>
+      <c r="H10" s="65" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="n">
+      <c r="A11" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="65" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="66" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×10</t>
         </is>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="67" t="n">
         <v>85000</v>
       </c>
       <c r="E11" s="55">
         <f>D11/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="64" t="inlineStr">
+      <c r="F11" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G11" s="65">
+      <c r="G11" s="69">
         <f>IF(F11="SÍ",D11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="61" t="inlineStr"/>
+      <c r="H11" s="65" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="n">
+      <c r="A12" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="65" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>Sillón Valencia 2C ×2</t>
         </is>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="67" t="n">
         <v>254000</v>
       </c>
       <c r="E12" s="55">
         <f>D12/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="64" t="inlineStr">
+      <c r="F12" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="69">
         <f>IF(F12="SÍ",D12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="61" t="inlineStr"/>
+      <c r="H12" s="65" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="n">
+      <c r="A13" s="65" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="C13" s="66" t="inlineStr">
         <is>
           <t>Sillón BRNO ×2</t>
         </is>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="67" t="n">
         <v>160000</v>
       </c>
       <c r="E13" s="55">
         <f>D13/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="64" t="inlineStr">
+      <c r="F13" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="65">
+      <c r="G13" s="69">
         <f>IF(F13="SÍ",D13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="61" t="inlineStr"/>
+      <c r="H13" s="65" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="n">
+      <c r="A14" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C14" s="62" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>Mesa ratona ×1</t>
         </is>
       </c>
-      <c r="D14" s="63" t="n">
+      <c r="D14" s="67" t="n">
         <v>118000</v>
       </c>
       <c r="E14" s="55">
         <f>D14/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="64" t="inlineStr">
+      <c r="F14" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="65">
+      <c r="G14" s="69">
         <f>IF(F14="SÍ",D14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="61" t="inlineStr"/>
+      <c r="H14" s="65" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="61" t="n">
+      <c r="A15" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="65" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D15" s="63" t="n">
+      <c r="D15" s="67" t="n">
         <v>40000</v>
       </c>
       <c r="E15" s="55">
         <f>D15/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="64" t="inlineStr">
+      <c r="F15" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G15" s="65">
+      <c r="G15" s="69">
         <f>IF(F15="SÍ",D15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="61" t="inlineStr"/>
+      <c r="H15" s="65" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="61" t="n">
+      <c r="A16" s="65" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C16" s="62" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D16" s="63" t="n">
+      <c r="D16" s="67" t="n">
         <v>56300</v>
       </c>
       <c r="E16" s="55">
         <f>D16/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="64" t="inlineStr">
+      <c r="F16" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G16" s="65">
+      <c r="G16" s="69">
         <f>IF(F16="SÍ",D16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="61" t="inlineStr"/>
+      <c r="H16" s="65" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="59" t="inlineStr">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala de staff</t>
         </is>
       </c>
-      <c r="B17" s="60" t="n"/>
-      <c r="C17" s="60" t="n"/>
-      <c r="D17" s="60" t="n"/>
-      <c r="E17" s="60" t="n"/>
-      <c r="F17" s="60" t="n"/>
-      <c r="G17" s="60" t="n"/>
-      <c r="H17" s="60" t="n"/>
+      <c r="B17" s="64" t="n"/>
+      <c r="C17" s="64" t="n"/>
+      <c r="D17" s="64" t="n"/>
+      <c r="E17" s="64" t="n"/>
+      <c r="F17" s="64" t="n"/>
+      <c r="G17" s="64" t="n"/>
+      <c r="H17" s="64" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="61" t="n">
+      <c r="A18" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="65" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="66" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×5</t>
         </is>
       </c>
-      <c r="D18" s="63" t="n">
+      <c r="D18" s="67" t="n">
         <v>590000</v>
       </c>
       <c r="E18" s="55">
         <f>D18/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="64" t="inlineStr">
+      <c r="F18" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G18" s="65">
+      <c r="G18" s="69">
         <f>IF(F18="SÍ",D18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="61" t="inlineStr"/>
+      <c r="H18" s="65" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="n">
+      <c r="A19" s="65" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="65" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="66" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×40</t>
         </is>
       </c>
-      <c r="D19" s="63" t="n">
+      <c r="D19" s="67" t="n">
         <v>340000</v>
       </c>
       <c r="E19" s="55">
         <f>D19/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="64" t="inlineStr">
+      <c r="F19" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G19" s="65">
+      <c r="G19" s="69">
         <f>IF(F19="SÍ",D19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="61" t="inlineStr"/>
+      <c r="H19" s="65" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="n">
+      <c r="A20" s="65" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="C20" s="66" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D20" s="63" t="n">
+      <c r="D20" s="67" t="n">
         <v>40000</v>
       </c>
       <c r="E20" s="55">
         <f>D20/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="64" t="inlineStr">
+      <c r="F20" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="65">
+      <c r="G20" s="69">
         <f>IF(F20="SÍ",D20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="61" t="inlineStr"/>
+      <c r="H20" s="65" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="n">
+      <c r="A21" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="B21" s="65" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="C21" s="66" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D21" s="63" t="n">
+      <c r="D21" s="67" t="n">
         <v>56300</v>
       </c>
       <c r="E21" s="55">
         <f>D21/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F21" s="64" t="inlineStr">
+      <c r="F21" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="65">
+      <c r="G21" s="69">
         <f>IF(F21="SÍ",D21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="61" t="inlineStr"/>
+      <c r="H21" s="65" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="59" t="inlineStr">
+      <c r="A22" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala principal</t>
         </is>
       </c>
-      <c r="B22" s="60" t="n"/>
-      <c r="C22" s="60" t="n"/>
-      <c r="D22" s="60" t="n"/>
-      <c r="E22" s="60" t="n"/>
-      <c r="F22" s="60" t="n"/>
-      <c r="G22" s="60" t="n"/>
-      <c r="H22" s="60" t="n"/>
+      <c r="B22" s="64" t="n"/>
+      <c r="C22" s="64" t="n"/>
+      <c r="D22" s="64" t="n"/>
+      <c r="E22" s="64" t="n"/>
+      <c r="F22" s="64" t="n"/>
+      <c r="G22" s="64" t="n"/>
+      <c r="H22" s="64" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="n">
+      <c r="A23" s="65" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C23" s="62" t="inlineStr">
+      <c r="C23" s="66" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×5.000</t>
         </is>
       </c>
-      <c r="D23" s="63" t="n">
+      <c r="D23" s="67" t="n">
         <v>42500000</v>
       </c>
       <c r="E23" s="55">
         <f>D23/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F23" s="64" t="inlineStr">
+      <c r="F23" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G23" s="65">
+      <c r="G23" s="69">
         <f>IF(F23="SÍ",D23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="61" t="inlineStr">
+      <c r="H23" s="65" t="inlineStr">
         <is>
           <t>Reemplazadas por las 5.500 sillas de FDL Eventos.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="61" t="n">
+      <c r="A24" s="65" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B24" s="65" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C24" s="62" t="inlineStr">
+      <c r="C24" s="66" t="inlineStr">
         <is>
           <t>Mesa 1,80 × 0,90 ×40</t>
         </is>
       </c>
-      <c r="D24" s="63" t="n">
+      <c r="D24" s="67" t="n">
         <v>2500000</v>
       </c>
       <c r="E24" s="55">
         <f>D24/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F24" s="64" t="inlineStr">
+      <c r="F24" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G24" s="65">
+      <c r="G24" s="69">
         <f>IF(F24="SÍ",D24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="61" t="inlineStr"/>
+      <c r="H24" s="65" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="61" t="n">
+      <c r="A25" s="65" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C25" s="62" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>Mantel ×40</t>
         </is>
       </c>
-      <c r="D25" s="63" t="n">
+      <c r="D25" s="67" t="n">
         <v>900000</v>
       </c>
       <c r="E25" s="55">
         <f>D25/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F25" s="64" t="inlineStr">
+      <c r="F25" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G25" s="65">
+      <c r="G25" s="69">
         <f>IF(F25="SÍ",D25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="61" t="inlineStr"/>
+      <c r="H25" s="65" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="61" t="n">
+      <c r="A26" s="65" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="65" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C26" s="62" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>Mantel redondo ×8</t>
         </is>
       </c>
-      <c r="D26" s="63" t="n">
+      <c r="D26" s="67" t="n">
         <v>256000</v>
       </c>
       <c r="E26" s="55">
         <f>D26/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F26" s="64" t="inlineStr">
+      <c r="F26" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G26" s="65">
+      <c r="G26" s="69">
         <f>IF(F26="SÍ",D26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="61" t="inlineStr"/>
+      <c r="H26" s="65" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr">
+      <c r="A27" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · camarín de speakers</t>
         </is>
       </c>
-      <c r="B27" s="60" t="n"/>
-      <c r="C27" s="60" t="n"/>
-      <c r="D27" s="60" t="n"/>
-      <c r="E27" s="60" t="n"/>
-      <c r="F27" s="60" t="n"/>
-      <c r="G27" s="60" t="n"/>
-      <c r="H27" s="60" t="n"/>
+      <c r="B27" s="64" t="n"/>
+      <c r="C27" s="64" t="n"/>
+      <c r="D27" s="64" t="n"/>
+      <c r="E27" s="64" t="n"/>
+      <c r="F27" s="64" t="n"/>
+      <c r="G27" s="64" t="n"/>
+      <c r="H27" s="64" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="61" t="n">
+      <c r="A28" s="65" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="B28" s="65" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C28" s="62" t="inlineStr">
+      <c r="C28" s="66" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×1</t>
         </is>
       </c>
-      <c r="D28" s="63" t="n">
+      <c r="D28" s="67" t="n">
         <v>118000</v>
       </c>
       <c r="E28" s="55">
         <f>D28/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F28" s="64" t="inlineStr">
+      <c r="F28" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G28" s="65">
+      <c r="G28" s="69">
         <f>IF(F28="SÍ",D28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="61" t="inlineStr"/>
+      <c r="H28" s="65" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="61" t="n">
+      <c r="A29" s="65" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="61" t="inlineStr">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C29" s="62" t="inlineStr">
+      <c r="C29" s="66" t="inlineStr">
         <is>
           <t>Espejo ×1</t>
         </is>
       </c>
-      <c r="D29" s="63" t="n">
+      <c r="D29" s="67" t="n">
         <v>79500</v>
       </c>
       <c r="E29" s="55">
         <f>D29/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="F29" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G29" s="65">
+      <c r="G29" s="69">
         <f>IF(F29="SÍ",D29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="61" t="inlineStr"/>
+      <c r="H29" s="65" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="61" t="n">
+      <c r="A30" s="65" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="61" t="inlineStr">
+      <c r="B30" s="65" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C30" s="62" t="inlineStr">
+      <c r="C30" s="66" t="inlineStr">
         <is>
           <t>Juego de living (sillones + mesa ratona)</t>
         </is>
       </c>
-      <c r="D30" s="63" t="n">
+      <c r="D30" s="67" t="n">
         <v>1103642</v>
       </c>
       <c r="E30" s="55">
         <f>D30/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F30" s="64" t="inlineStr">
+      <c r="F30" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G30" s="65">
+      <c r="G30" s="69">
         <f>IF(F30="SÍ",D30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="61" t="inlineStr">
+      <c r="H30" s="65" t="inlineStr">
         <is>
           <t>El mobiliario "más fino" del camarín: candidato a contratárselo a La Rural.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="61" t="n">
+      <c r="A31" s="65" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="B31" s="65" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C31" s="62" t="inlineStr">
+      <c r="C31" s="66" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D31" s="63" t="n">
+      <c r="D31" s="67" t="n">
         <v>40000</v>
       </c>
       <c r="E31" s="55">
         <f>D31/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F31" s="64" t="inlineStr">
+      <c r="F31" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G31" s="65">
+      <c r="G31" s="69">
         <f>IF(F31="SÍ",D31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="61" t="inlineStr"/>
+      <c r="H31" s="65" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="61" t="n">
+      <c r="A32" s="65" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="61" t="inlineStr">
+      <c r="B32" s="65" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C32" s="62" t="inlineStr">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D32" s="63" t="n">
+      <c r="D32" s="67" t="n">
         <v>56300</v>
       </c>
       <c r="E32" s="55">
         <f>D32/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F32" s="64" t="inlineStr">
+      <c r="F32" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G32" s="65">
+      <c r="G32" s="69">
         <f>IF(F32="SÍ",D32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="61" t="inlineStr"/>
+      <c r="H32" s="65" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="59" t="inlineStr">
+      <c r="A33" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · escenario y técnica</t>
         </is>
       </c>
-      <c r="B33" s="60" t="n"/>
-      <c r="C33" s="60" t="n"/>
-      <c r="D33" s="60" t="n"/>
-      <c r="E33" s="60" t="n"/>
-      <c r="F33" s="60" t="n"/>
-      <c r="G33" s="60" t="n"/>
-      <c r="H33" s="60" t="n"/>
+      <c r="B33" s="64" t="n"/>
+      <c r="C33" s="64" t="n"/>
+      <c r="D33" s="64" t="n"/>
+      <c r="E33" s="64" t="n"/>
+      <c r="F33" s="64" t="n"/>
+      <c r="G33" s="64" t="n"/>
+      <c r="H33" s="64" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="61" t="n">
+      <c r="A34" s="65" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="B34" s="65" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C34" s="62" t="inlineStr">
+      <c r="C34" s="66" t="inlineStr">
         <is>
           <t>Mesa cocktail alta (escenario) ×1</t>
         </is>
       </c>
-      <c r="D34" s="63" t="n">
+      <c r="D34" s="67" t="n">
         <v>45000</v>
       </c>
       <c r="E34" s="55">
         <f>D34/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F34" s="64" t="inlineStr">
+      <c r="F34" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G34" s="65">
+      <c r="G34" s="69">
         <f>IF(F34="SÍ",D34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="61" t="inlineStr"/>
+      <c r="H34" s="65" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="61" t="n">
+      <c r="A35" s="65" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B35" s="65" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C35" s="62" t="inlineStr">
+      <c r="C35" s="66" t="inlineStr">
         <is>
           <t>Mesa alta para DJ ×1</t>
         </is>
       </c>
-      <c r="D35" s="63" t="n">
+      <c r="D35" s="67" t="n">
         <v>62300</v>
       </c>
       <c r="E35" s="55">
         <f>D35/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F35" s="64" t="inlineStr">
+      <c r="F35" s="68" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G35" s="65">
+      <c r="G35" s="69">
         <f>IF(F35="SÍ",D35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="61" t="inlineStr"/>
+      <c r="H35" s="65" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="59" t="inlineStr">
+      <c r="A36" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  GENERALES</t>
         </is>
       </c>
-      <c r="B36" s="60" t="n"/>
-      <c r="C36" s="60" t="n"/>
-      <c r="D36" s="60" t="n"/>
-      <c r="E36" s="60" t="n"/>
-      <c r="F36" s="60" t="n"/>
-      <c r="G36" s="60" t="n"/>
-      <c r="H36" s="60" t="n"/>
+      <c r="B36" s="64" t="n"/>
+      <c r="C36" s="64" t="n"/>
+      <c r="D36" s="64" t="n"/>
+      <c r="E36" s="64" t="n"/>
+      <c r="F36" s="64" t="n"/>
+      <c r="G36" s="64" t="n"/>
+      <c r="H36" s="64" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="61" t="n">
+      <c r="A37" s="65" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="B37" s="65" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C37" s="62" t="inlineStr">
+      <c r="C37" s="66" t="inlineStr">
         <is>
           <t>Dirección técnica de todo el evento + replanteo</t>
         </is>
       </c>
-      <c r="D37" s="63" t="n">
+      <c r="D37" s="67" t="n">
         <v>5149179.2</v>
       </c>
       <c r="E37" s="55">
         <f>D37/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F37" s="64" t="inlineStr">
+      <c r="F37" s="68" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G37" s="65">
+      <c r="G37" s="69">
         <f>IF(F37="SÍ",D37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="61" t="inlineStr">
+      <c r="H37" s="65" t="inlineStr">
         <is>
           <t>Ojo: el replanteo de sillas va aparte, con ingeniero propio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="61" t="n">
+      <c r="A38" s="65" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="B38" s="65" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C38" s="62" t="inlineStr">
+      <c r="C38" s="66" t="inlineStr">
         <is>
           <t>Guardia eléctrica × 2 días</t>
         </is>
       </c>
-      <c r="D38" s="63" t="n">
+      <c r="D38" s="67" t="n">
         <v>865800</v>
       </c>
       <c r="E38" s="55">
         <f>D38/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F38" s="64" t="inlineStr">
+      <c r="F38" s="68" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G38" s="65">
+      <c r="G38" s="69">
         <f>IF(F38="SÍ",D38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="61" t="inlineStr"/>
+      <c r="H38" s="65" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="61" t="n">
+      <c r="A39" s="65" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="B39" s="65" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C39" s="62" t="inlineStr">
+      <c r="C39" s="66" t="inlineStr">
         <is>
           <t>Guardia técnica × 2 días</t>
         </is>
       </c>
-      <c r="D39" s="63" t="n">
+      <c r="D39" s="67" t="n">
         <v>905200</v>
       </c>
       <c r="E39" s="55">
         <f>D39/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F39" s="64" t="inlineStr">
+      <c r="F39" s="68" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G39" s="65">
+      <c r="G39" s="69">
         <f>IF(F39="SÍ",D39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="61" t="inlineStr"/>
+      <c r="H39" s="65" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="3" t="inlineStr">
@@ -4620,7 +5012,7 @@
           <t>TOTAL del presupuesto de La Rural</t>
         </is>
       </c>
-      <c r="D41" s="66">
+      <c r="D41" s="70">
         <f>SUM(D6:D39)</f>
         <v/>
       </c>
@@ -4635,11 +5027,11 @@
           <t>Lo que se queda (marcado SÍ)</t>
         </is>
       </c>
-      <c r="D42" s="67">
+      <c r="D42" s="71">
         <f>SUM(G6:G39)</f>
         <v/>
       </c>
-      <c r="E42" s="68">
+      <c r="E42" s="72">
         <f>D42/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -4650,11 +5042,11 @@
           <t>Lo que se saca (marcado NO)</t>
         </is>
       </c>
-      <c r="D43" s="69">
+      <c r="D43" s="73">
         <f>D41-D42</f>
         <v/>
       </c>
-      <c r="E43" s="70">
+      <c r="E43" s="74">
         <f>D43/TABLERO!$C$4</f>
         <v/>
       </c>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -1034,7 +1034,7 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Infraestructura y mobiliario de stands</t>
+          <t>Infraestructura La Rural (armado de stands)</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Definido: armado de los stands y su mobiliario. Stand de staff 100 m², stand de producción menos de 50 m², y el mobiliario del camarín de speakers. Falta pedirles los espejos.</t>
+          <t>Armado del stand de staff (100 m²), el de producción (menos de 50 m²) y el mobiliario del camarín de speakers. Falta pedirles los espejos. Las sillas del público van en su propia línea.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Celda TABLERO!C4, editable. Por defecto $1.535 = dólar oficial venta del Banco Nación al 02/09/2026. Todas las conversiones de pesos a dólares salen de esa única celda.</t>
+          <t>Celda TABLERO!C4, editable. $1.510, que es el dólar con el que viene trabajando Agustina. Se verificó contra dos de sus cifras: el montaje de $900.000 le da US$596 y el entelado de $24.500.000 le da US$16.225. Todas las conversiones de pesos a dólares salen de esa única celda.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>4.500 sillas plásticas Munro reforzadas + 1.000 sillas hotel negro + flete. NO incluye armado.</t>
+          <t>Presupuesto 026-2697, alquiler por 4 días: 1.000 sillas hotel caño gris tapizado negro ($7.000.000) + 4.500 sillas plásticas Munro reforzadas ($17.100.000) + flete ($1.700.000). NO incluye armado.</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>Mail fdleventos@gmail.com 07/08/2026 · pendiente de resolver facturación al exterior</t>
+          <t>Presupuesto FDL Eventos N.º 026-2697 del 07/08/2026 · pendiente de resolver facturación al exterior</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>13582</v>
+        <v>14569</v>
       </c>
       <c r="G37" s="13" t="n"/>
       <c r="H37" s="14">
@@ -3073,11 +3073,11 @@
         </is>
       </c>
       <c r="C4" s="48" t="n">
-        <v>1530</v>
+        <v>1510</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dólar oficial venta, Banco Nación, 02/09/2026. Editá esta celda y se recalcula todo el libro.</t>
+          <t>Dólar con el que trabaja Agustina. Verificado contra dos de sus cifras: $900.000 de montaje = US$596 y $24.500.000 de entelado = US$16.225. Editá esta celda y se recalcula todo el libro.</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="F8" s="19" t="n"/>
       <c r="G8" s="23" t="n">
-        <v>13582</v>
+        <v>14569</v>
       </c>
       <c r="H8" s="59">
         <f>D8-G8</f>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -10,12 +10,14 @@
     <sheet name="LEEME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="COSTOS UNIFICADOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="TABLERO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DECISIONES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="AHORROS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="INFRAESTRUCTURA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MERCH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DECISIONES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AHORROS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="INFRAESTRUCTURA" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COSTOS UNIFICADOS'!$A$4:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COSTOS UNIFICADOS'!$A$4:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MERCH'!$A$4:$O$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;(&quot;$&quot;#,##0);-"/>
     <numFmt numFmtId="167" formatCode="&quot;US$&quot;#,##0;(&quot;US$&quot;#,##0);-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +96,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
@@ -147,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -169,11 +182,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,6 +264,9 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -226,6 +286,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -253,6 +316,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -291,7 +357,16 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -307,15 +382,60 @@
     <xf numFmtId="167" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -692,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -761,71 +881,71 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Contratado = hay contrato o anticipo pagado. Cotizado = hay presupuesto formal por mail. Alternativa = segunda opción para el mismo ítem, NO suma al total. Sin cotizar = sólo hay un estimado del sheet, o ni eso.</t>
+          <t>Contratado = hay contrato o anticipo pagado. Cotizado = hay presupuesto formal por mail. Alternativa = segunda opción para el mismo ítem, NO suma al total. Otro país = es un gasto de otro evento de la gira, entra en cero. Reemplazado = estimado viejo que ya está cubierto por facturas reales, entra en cero. Sin cotizar = sólo hay un estimado del sheet, o ni eso.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Regla del total</t>
+          <t>Columna "% Argentina"</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>El total suma los ítems Contratado + Cotizado + Sin cotizar. Los marcados "Alternativa" quedan fuera para no duplicar (las sillas de La Rural vs las de FDL, y las LED de VMG contra la técnica integral de Prina).</t>
+          <t>Es la parte de cada compra que se le imputa a este evento. Vale 100% en casi todo. Los pañuelos son una compra compartida con Uruguay y van al 65% (5.500 de 8.500 unidades); la gráfica de Uruguay va al 0%.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>Regla del total</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>El total suma los ítems Contratado + Cotizado + Sin cotizar. Los marcados "Alternativa" quedan fuera para no duplicar (las sillas de La Rural vs las de FDL, y las LED de VMG contra la técnica integral de Prina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>IVA</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Las cotizaciones argentinas casi todas vienen sin IVA. La columna IVA aplica la alícuota de cada una (21% general, 10,5% el servicio médico) para llegar al costo real.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Advertencia 1 — vencimientos</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>La cotización de Prina (técnica, el ítem más caro en pesos) tenía validez de 10 días y venció en junio. VMG se reserva recotizar si el dólar salta más de 15%. La Rural ajusta el saldo por IPC. Los pesos de este libro son de la fecha de cada cotización, no de hoy.</t>
-        </is>
-      </c>
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Advertencia 2 — huecos</t>
+          <t>Advertencia 1 — vencimientos</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Catering, vuelos y alojamiento del equipo no tienen ninguna cotización cerrada. Catering entra al total con el estimado del sheet (US$39.820); vuelos y alojamiento entran en cero porque no hay ni estimado. El costo por persona es, por lo tanto, un piso.</t>
+          <t>La cotización de Prina (técnica, el ítem más caro en pesos) tenía validez de 10 días y venció en junio. VMG se reserva recotizar si el dólar salta más de 15%. La Rural ajusta el saldo por IPC. Los pesos de este libro son de la fecha de cada cotización, no de hoy.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Advertencia 3 — facturación</t>
+          <t>Advertencia 2 — huecos</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>FDL Eventos (sillas) y Vittal (servicio médico) todavía no confirmaron si pueden facturar a la empresa de EE.UU. Si no pueden, hay que resolver el circuito de pago antes de cerrar.</t>
+          <t>Vuelos y alojamiento del equipo entran en cero: no hay cotización ni estimado. Tampoco están cotizados los ecobaños, la marquetería, el replanteo de sillas ni los cheques, escarapelas, diplomas, placas y manillas. El costo por persona es, por lo tanto, un piso.</t>
         </is>
       </c>
     </row>
@@ -836,22 +956,74 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Fuentes de mail</t>
+          <t>Merch</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>La Rural infraestructura (criccio@larural.com.ar, 17/08) · La Rural conectividad (16/06) · Prina (18/06) · VMG (29/06) · Road Seguridad (12/08) · Vittal (28/08) · Higia + Gale (22/06) · Chanes Seguros (13/07) · Blocko (09/06) · FDL Eventos (07/08) · AmbientHouse (16/06).</t>
+          <t>Todo el merch sale de la carpeta de Drive "Presupuestos merch": nueve facturas reales (2601009 a 2601019) que reemplazan el renglón único de US$8.689 que traía el master. Los proveedores son argentinos (Remerasyestampados, Textil Ryu, Leotex, Derqui), no colombianos como decía la hoja PAGOS. Ver la hoja MERCH.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Merch — qué se pagó</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Las gorras están pagadas al 100%. Pañuelos, lanyards y gráfica de Argentina tienen el 50% abonado. Las remeras y el bordado de las gorras no tienen nada pagado: se debe el 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Merch — dos ajustes</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Se sacaron dos duplicaciones: las cintas de Blocko eran el mismo ítem que los lanyards de Leotex ya contratados, y la gráfica de Uruguay (US$1.233) estaba cargada en el master con país = Argentina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Advertencia 3 — facturación</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>FDL Eventos (sillas) y Vittal (servicio médico) todavía no confirmaron si pueden facturar a la empresa de EE.UU. Si no pueden, hay que resolver el circuito de pago antes de cerrar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1">
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Fuentes de mail</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>La Rural infraestructura (criccio@larural.com.ar, 17/08) · La Rural conectividad (16/06) · Prina (18/06) · VMG (29/06) · Road Seguridad (12/08) · Vittal (28/08) · Higia + Gale (22/06) · Chanes Seguros (13/07) · Blocko (09/06) · FDL Eventos (07/08) · AmbientHouse (16/06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Fuente de planilla</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>INVERSIÓN GIRA CUMBRE 2026.xlsx — hojas "Argentina (3 oct-4 oct)" y "PAGOS".</t>
         </is>
@@ -868,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -879,10 +1051,11 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="62" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -942,21 +1115,26 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
+          <t>% Argentina</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
           <t>Total USD</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Estimado del sheet
 (USD)</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
@@ -979,6 +1157,7 @@
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="8" t="n"/>
       <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
@@ -1014,18 +1193,21 @@
         <f>IF(F6="","",F6*(1+N(G6)))</f>
         <v/>
       </c>
-      <c r="I6" s="14">
-        <f>IF(D6="Bonificado",0,IF(H6="",N(J6),IF(E6="USD",H6,H6/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J6" s="12" t="n">
+      <c r="I6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14">
+        <f>IF(OR(D6="Bonificado",D6="Reemplazado"),0,N(I6)*IF(H6="",N(K6),IF(E6="USD",H6,H6/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K6" s="12" t="n">
         <v>70000</v>
       </c>
-      <c r="K6" s="14">
-        <f>IF(D6="Alternativa","",I6-N(J6))</f>
-        <v/>
-      </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="L6" s="14">
+        <f>IF(D6="Alternativa","",J6-N(K6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>Contrato CC-00957 · hoja PAGOS del master (US$43.446 abonados el 27/04)</t>
         </is>
@@ -1065,249 +1247,265 @@
         <f>IF(F7="","",F7*(1+N(G7)))</f>
         <v/>
       </c>
-      <c r="I7" s="14">
-        <f>IF(D7="Bonificado",0,IF(H7="",N(J7),IF(E7="USD",H7,H7/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="14">
-        <f>IF(D7="Alternativa","",I7-N(J7))</f>
-        <v/>
-      </c>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="14">
+        <f>IF(OR(D7="Bonificado",D7="Reemplazado"),0,N(I7)*IF(H7="",N(K7),IF(E7="USD",H7,H7/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="14">
+        <f>IF(D7="Alternativa","",J7-N(K7))</f>
+        <v/>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>Definición de Agustina sobre el presupuesto de $66.494.708 del 17/08 · ver hoja AHORROS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Sillas del público (5.500)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>FDL Eventos</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Presupuesto 026-2697, alquiler por 4 días: 1.000 sillas hotel caño gris tapizado negro ($7.000.000) + 4.500 sillas plásticas Munro reforzadas ($17.100.000) + flete ($1.700.000). NO incluye armado.</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <v>25800000</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>0.21</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="22">
         <f>IF(F8="","",F8*(1+N(G8)))</f>
         <v/>
       </c>
-      <c r="I8" s="22">
-        <f>IF(D8="Bonificado",0,IF(H8="",N(J8),IF(E8="USD",H8,H8/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J8" s="23" t="n">
+      <c r="I8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="24">
+        <f>IF(OR(D8="Bonificado",D8="Reemplazado"),0,N(I8)*IF(H8="",N(K8),IF(E8="USD",H8,H8/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K8" s="25" t="n">
         <v>16500</v>
       </c>
-      <c r="K8" s="22">
-        <f>IF(D8="Alternativa","",I8-N(J8))</f>
-        <v/>
-      </c>
-      <c r="L8" s="24" t="inlineStr">
+      <c r="L8" s="24">
+        <f>IF(D8="Alternativa","",J8-N(K8))</f>
+        <v/>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t>Presupuesto FDL Eventos N.º 026-2697 del 07/08/2026 · pendiente de resolver facturación al exterior</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Montaje, acomodación y desmontaje de sillas</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>En negociación</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Montaje previo, acomodación el sábado a la noche después de la dinámica y desmontaje el domingo.</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>En negociación</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="30" t="n">
         <v>900000</v>
       </c>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="30">
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="32">
         <f>IF(F9="","",F9*(1+N(G9)))</f>
         <v/>
       </c>
-      <c r="I9" s="31">
-        <f>IF(D9="Bonificado",0,IF(H9="",N(J9),IF(E9="USD",H9,H9/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J9" s="32" t="n"/>
-      <c r="K9" s="31">
-        <f>IF(D9="Alternativa","",I9-N(J9))</f>
-        <v/>
-      </c>
-      <c r="L9" s="33" t="inlineStr">
+      <c r="I9" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="34">
+        <f>IF(OR(D9="Bonificado",D9="Reemplazado"),0,N(I9)*IF(H9="",N(K9),IF(E9="USD",H9,H9/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="35" t="n"/>
+      <c r="L9" s="34">
+        <f>IF(D9="Alternativa","",J9-N(K9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="36" t="inlineStr">
         <is>
           <t>Negociación de Agustina · cerrar el número antes de firmar las sillas</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Replanteo de sillas (ingeniero)</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Replanteo del layout de sillas del pabellón. Confirmado que va aparte de la dirección técnica de La Rural.</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="31">
+      <c r="F10" s="35" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="34">
         <f>IF(F10="","",F10*(1+N(G10)))</f>
         <v/>
       </c>
-      <c r="I10" s="31">
-        <f>IF(D10="Bonificado",0,IF(H10="",N(J10),IF(E10="USD",H10,H10/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J10" s="32" t="n"/>
-      <c r="K10" s="31">
-        <f>IF(D10="Alternativa","",I10-N(J10))</f>
-        <v/>
-      </c>
-      <c r="L10" s="33" t="inlineStr">
+      <c r="I10" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="34">
+        <f>IF(OR(D10="Bonificado",D10="Reemplazado"),0,N(I10)*IF(H10="",N(K10),IF(E10="USD",H10,H10/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="35" t="n"/>
+      <c r="L10" s="34">
+        <f>IF(D10="Alternativa","",J10-N(K10))</f>
+        <v/>
+      </c>
+      <c r="M10" s="36" t="inlineStr">
         <is>
           <t>Pendiente de pedir presupuesto</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Conectividad WiFi</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>La Rural — Servicios de Conectividad</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>2 redes privadas de 30 Mbps (técnica + staff/acreditación), del 2 al 4 de octubre</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>1466063.84</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>0.21</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="22">
         <f>IF(F11="","",F11*(1+N(G11)))</f>
         <v/>
       </c>
-      <c r="I11" s="22">
-        <f>IF(D11="Bonificado",0,IF(H11="",N(J11),IF(E11="USD",H11,H11/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="23" t="n">
+      <c r="I11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="24">
+        <f>IF(OR(D11="Bonificado",D11="Reemplazado"),0,N(I11)*IF(H11="",N(K11),IF(E11="USD",H11,H11/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="25" t="n">
         <v>800</v>
       </c>
-      <c r="K11" s="22">
-        <f>IF(D11="Alternativa","",I11-N(J11))</f>
-        <v/>
-      </c>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="24">
+        <f>IF(D11="Alternativa","",J11-N(K11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t>Mail conectividad@larural.com.ar 05/08/2026 · presupuesto N.º 2, base IPC junio (el del 16/06 era $1.438.728)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Subtotal Sede</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n"/>
-      <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="36">
-        <f>SUMIF($D$6:$D$11,"&lt;&gt;Alternativa",$I$6:$I$11)</f>
-        <v/>
-      </c>
-      <c r="J12" s="36">
-        <f>SUM($J$6:$J$11)</f>
-        <v/>
-      </c>
-      <c r="K12" s="36">
-        <f>I12-J12</f>
-        <v/>
-      </c>
-      <c r="L12" s="35" t="n"/>
+      <c r="B12" s="38" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="38" t="n"/>
+      <c r="H12" s="38" t="n"/>
+      <c r="I12" s="38" t="n"/>
+      <c r="J12" s="39">
+        <f>SUMIF($D$6:$D$11,"&lt;&gt;Alternativa",$J$6:$J$11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="39">
+        <f>SUM($K$6:$K$11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="39">
+        <f>J12-K12</f>
+        <v/>
+      </c>
+      <c r="M12" s="38" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1326,6 +1524,7 @@
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
@@ -1361,18 +1560,21 @@
         <f>IF(F14="","",F14*(1+N(G14)))</f>
         <v/>
       </c>
-      <c r="I14" s="14">
-        <f>IF(D14="Bonificado",0,IF(H14="",N(J14),IF(E14="USD",H14,H14/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="12" t="n">
+      <c r="I14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="14">
+        <f>IF(OR(D14="Bonificado",D14="Reemplazado"),0,N(I14)*IF(H14="",N(K14),IF(E14="USD",H14,H14/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="12" t="n">
         <v>34000</v>
       </c>
-      <c r="K14" s="14">
-        <f>IF(D14="Alternativa","",I14-N(J14))</f>
-        <v/>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
+      <c r="L14" s="14">
+        <f>IF(D14="Alternativa","",J14-N(K14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
         <is>
           <t>Negociación de Agustina · reemplaza la cotización vencida de Prina</t>
         </is>
@@ -1404,24 +1606,27 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="F15" s="37" t="n">
+      <c r="F15" s="40" t="n">
         <v>24500000</v>
       </c>
       <c r="G15" s="13" t="n"/>
-      <c r="H15" s="38">
+      <c r="H15" s="41">
         <f>IF(F15="","",F15*(1+N(G15)))</f>
         <v/>
       </c>
-      <c r="I15" s="14">
-        <f>IF(D15="Bonificado",0,IF(H15="",N(J15),IF(E15="USD",H15,H15/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="14">
-        <f>IF(D15="Alternativa","",I15-N(J15))</f>
-        <v/>
-      </c>
-      <c r="L15" s="15" t="inlineStr">
+      <c r="I15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="14">
+        <f>IF(OR(D15="Bonificado",D15="Reemplazado"),0,N(I15)*IF(H15="",N(K15),IF(E15="USD",H15,H15/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="14">
+        <f>IF(D15="Alternativa","",J15-N(K15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>Negociación de Agustina · US$16.000 aprox. al dólar de referencia</t>
         </is>
@@ -1461,94 +1666,101 @@
         <f>IF(F16="","",F16*(1+N(G16)))</f>
         <v/>
       </c>
-      <c r="I16" s="14">
-        <f>IF(D16="Bonificado",0,IF(H16="",N(J16),IF(E16="USD",H16,H16/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="14">
-        <f>IF(D16="Alternativa","",I16-N(J16))</f>
-        <v/>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
+      <c r="I16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="14">
+        <f>IF(OR(D16="Bonificado",D16="Reemplazado"),0,N(I16)*IF(H16="",N(K16),IF(E16="USD",H16,H16/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="14">
+        <f>IF(D16="Alternativa","",J16-N(K16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="16" t="inlineStr">
         <is>
           <t>Negociación de Agustina</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>Bonificado por el proveedor de técnica</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>Sin costo</t>
         </is>
       </c>
-      <c r="C17" s="41" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>500 vallas y efectos especiales, sin cargo. Es lo que evita el gasto de vallado que estaba presupuestado.</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>Bonificado</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
+      <c r="E17" s="43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F17" s="42" t="n"/>
-      <c r="G17" s="43" t="n"/>
-      <c r="H17" s="44">
+      <c r="F17" s="45" t="n"/>
+      <c r="G17" s="46" t="n"/>
+      <c r="H17" s="47">
         <f>IF(F17="","",F17*(1+N(G17)))</f>
         <v/>
       </c>
-      <c r="I17" s="44">
-        <f>IF(D17="Bonificado",0,IF(H17="",N(J17),IF(E17="USD",H17,H17/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J17" s="42" t="n"/>
-      <c r="K17" s="44">
-        <f>IF(D17="Alternativa","",I17-N(J17))</f>
-        <v/>
-      </c>
-      <c r="L17" s="45" t="inlineStr">
+      <c r="I17" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="47">
+        <f>IF(OR(D17="Bonificado",D17="Reemplazado"),0,N(I17)*IF(H17="",N(K17),IF(E17="USD",H17,H17/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="45" t="n"/>
+      <c r="L17" s="47">
+        <f>IF(D17="Alternativa","",J17-N(K17))</f>
+        <v/>
+      </c>
+      <c r="M17" s="49" t="inlineStr">
         <is>
           <t>Negociación de Agustina</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>Subtotal Técnica</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="36">
-        <f>SUMIF($D$14:$D$17,"&lt;&gt;Alternativa",$I$14:$I$17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="36">
-        <f>SUM($J$14:$J$17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="36">
-        <f>I18-J18</f>
-        <v/>
-      </c>
-      <c r="L18" s="35" t="n"/>
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="38" t="n"/>
+      <c r="I18" s="38" t="n"/>
+      <c r="J18" s="39">
+        <f>SUMIF($D$14:$D$17,"&lt;&gt;Alternativa",$J$14:$J$17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="39">
+        <f>SUM($K$14:$K$17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="39">
+        <f>J18-K18</f>
+        <v/>
+      </c>
+      <c r="M18" s="38" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1567,335 +1779,355 @@
       <c r="J19" s="8" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Seguridad y vigilancia</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Road Seguridad S.A.</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>263 horas de vigilancia (armado, evento y desarme) + planos de evacuación $715.000 + supervisión general $795.000</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="20" t="n">
         <v>7218928.96</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="21" t="n">
         <v>0.21</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="22">
         <f>IF(F20="","",F20*(1+N(G20)))</f>
         <v/>
       </c>
-      <c r="I20" s="22">
-        <f>IF(D20="Bonificado",0,IF(H20="",N(J20),IF(E20="USD",H20,H20/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J20" s="23" t="n"/>
-      <c r="K20" s="22">
-        <f>IF(D20="Alternativa","",I20-N(J20))</f>
-        <v/>
-      </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="I20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="24">
+        <f>IF(OR(D20="Bonificado",D20="Reemplazado"),0,N(I20)*IF(H20="",N(K20),IF(E20="USD",H20,H20/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="24">
+        <f>IF(D20="Alternativa","",J20-N(K20))</f>
+        <v/>
+      </c>
+      <c r="M20" s="26" t="inlineStr">
         <is>
           <t>Mail presupuestos@roadseguridad.com.ar 12/08/2026 (versión V3, lista para firmar)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Servicio médico</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Vittal — Socorro Médico Privado</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>1 UTIM TRI con dos médicos + enfermero/chofer, los tres días (2, 3 y 4 de octubre)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="20" t="n">
         <v>6366521.27</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G21" s="21" t="n">
         <v>0.105</v>
       </c>
-      <c r="H21" s="21">
+      <c r="H21" s="22">
         <f>IF(F21="","",F21*(1+N(G21)))</f>
         <v/>
       </c>
-      <c r="I21" s="22">
-        <f>IF(D21="Bonificado",0,IF(H21="",N(J21),IF(E21="USD",H21,H21/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J21" s="23" t="n"/>
-      <c r="K21" s="22">
-        <f>IF(D21="Alternativa","",I21-N(J21))</f>
-        <v/>
-      </c>
-      <c r="L21" s="24" t="inlineStr">
+      <c r="I21" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="24">
+        <f>IF(OR(D21="Bonificado",D21="Reemplazado"),0,N(I21)*IF(H21="",N(K21),IF(E21="USD",H21,H21/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="24">
+        <f>IF(D21="Alternativa","",J21-N(K21))</f>
+        <v/>
+      </c>
+      <c r="M21" s="26" t="inlineStr">
         <is>
           <t>Mail vtomas@vittal.com.ar 28/08/2026 · tarifas actualizadas, sin consultorio</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Limpieza</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Higia Eventos</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>205,5 horas de limpieza: auditorio, baños y guardarropas, del 2 al 5 de octubre</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="20" t="n">
         <v>3367440.91</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="21" t="n">
         <v>0.21</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="22">
         <f>IF(F22="","",F22*(1+N(G22)))</f>
         <v/>
       </c>
-      <c r="I22" s="22">
-        <f>IF(D22="Bonificado",0,IF(H22="",N(J22),IF(E22="USD",H22,H22/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J22" s="23" t="n"/>
-      <c r="K22" s="22">
-        <f>IF(D22="Alternativa","",I22-N(J22))</f>
-        <v/>
-      </c>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="I22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="24">
+        <f>IF(OR(D22="Bonificado",D22="Reemplazado"),0,N(I22)*IF(H22="",N(K22),IF(E22="USD",H22,H22/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="24">
+        <f>IF(D22="Alternativa","",J22-N(K22))</f>
+        <v/>
+      </c>
+      <c r="M22" s="26" t="inlineStr">
         <is>
           <t>Mail higiaeventos 22/06/2026 (reenviado 29/06) · 50% de anticipo antes del armado</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Retiro de residuos</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Gale Servicios</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Roll off con disposición final incluida. Cotización base abril 2026.</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="20" t="n">
         <v>1471608.62</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="21" t="n">
         <v>0.21</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="22">
         <f>IF(F23="","",F23*(1+N(G23)))</f>
         <v/>
       </c>
-      <c r="I23" s="22">
-        <f>IF(D23="Bonificado",0,IF(H23="",N(J23),IF(E23="USD",H23,H23/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J23" s="23" t="n"/>
-      <c r="K23" s="22">
-        <f>IF(D23="Alternativa","",I23-N(J23))</f>
-        <v/>
-      </c>
-      <c r="L23" s="24" t="inlineStr">
+      <c r="I23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="24">
+        <f>IF(OR(D23="Bonificado",D23="Reemplazado"),0,N(I23)*IF(H23="",N(K23),IF(E23="USD",H23,H23/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="24">
+        <f>IF(D23="Alternativa","",J23-N(K23))</f>
+        <v/>
+      </c>
+      <c r="M23" s="26" t="inlineStr">
         <is>
           <t>Mail higiaeventos 22/06/2026 (adjunto Gale) · se factura 100% por adelantado</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Baños químicos — ecobaños</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>Decidido: ecobaños, no los químicos tradicionales. Más limpios, mejor a la vista y ecofriendly. Falta pedir presupuesto.</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="29" t="n"/>
-      <c r="H24" s="31">
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="34">
         <f>IF(F24="","",F24*(1+N(G24)))</f>
         <v/>
       </c>
-      <c r="I24" s="31">
-        <f>IF(D24="Bonificado",0,IF(H24="",N(J24),IF(E24="USD",H24,H24/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="31">
-        <f>IF(D24="Alternativa","",I24-N(J24))</f>
-        <v/>
-      </c>
-      <c r="L24" s="33" t="inlineStr">
+      <c r="I24" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="34">
+        <f>IF(OR(D24="Bonificado",D24="Reemplazado"),0,N(I24)*IF(H24="",N(K24),IF(E24="USD",H24,H24/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K24" s="35" t="n"/>
+      <c r="L24" s="34">
+        <f>IF(D24="Alternativa","",J24-N(K24))</f>
+        <v/>
+      </c>
+      <c r="M24" s="36" t="inlineStr">
         <is>
           <t>Decisión de Agustina · pendiente de cotizar</t>
         </is>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>Seguro de accidentes personales</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Chanes Seguros</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Cobertura MIA (muerte, invalidez y asistencia médica) para 150 personas, exigida por La Rural</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="20" t="n">
         <v>953151.9300000001</v>
       </c>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="21">
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="22">
         <f>IF(F25="","",F25*(1+N(G25)))</f>
         <v/>
       </c>
-      <c r="I25" s="22">
-        <f>IF(D25="Bonificado",0,IF(H25="",N(J25),IF(E25="USD",H25,H25/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J25" s="23" t="n">
+      <c r="I25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="24">
+        <f>IF(OR(D25="Bonificado",D25="Reemplazado"),0,N(I25)*IF(H25="",N(K25),IF(E25="USD",H25,H25/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K25" s="25" t="n">
         <v>400</v>
       </c>
-      <c r="K25" s="22">
-        <f>IF(D25="Alternativa","",I25-N(J25))</f>
-        <v/>
-      </c>
-      <c r="L25" s="24" t="inlineStr">
+      <c r="L25" s="24">
+        <f>IF(D25="Alternativa","",J25-N(K25))</f>
+        <v/>
+      </c>
+      <c r="M25" s="26" t="inlineStr">
         <is>
           <t>Mail nestor@chanesseguros.com.ar 13/07/2026 · premio único, cotizado para 15-19/07</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>Subtotal Servicios</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n"/>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="36">
-        <f>SUMIF($D$20:$D$25,"&lt;&gt;Alternativa",$I$20:$I$25)</f>
-        <v/>
-      </c>
-      <c r="J26" s="36">
-        <f>SUM($J$20:$J$25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="36">
-        <f>I26-J26</f>
-        <v/>
-      </c>
-      <c r="L26" s="35" t="n"/>
+      <c r="B26" s="38" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="H26" s="38" t="n"/>
+      <c r="I26" s="38" t="n"/>
+      <c r="J26" s="39">
+        <f>SUMIF($D$20:$D$25,"&lt;&gt;Alternativa",$J$20:$J$25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="39">
+        <f>SUM($K$20:$K$25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="39">
+        <f>J26-K26</f>
+        <v/>
+      </c>
+      <c r="M26" s="38" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -1914,72 +2146,76 @@
       <c r="J27" s="8" t="n"/>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Cintas portacredencial (1.300)</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>Blocko</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Cinta raso 25 mm impresa 4 colores dos caras + mosquetón zamak, $1.346 c/u</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Pañuelos / pañoletas estampados (8.500)</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>REMERASYESTAMPADOS</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Factura 2601012 del 20/06. Compra compartida Argentina + Uruguay: se imputa a Argentina el 65% (5.500 de 8.500 unidades, la misma proporcion que la grafica). El 50% ya esta abonado; el saldo se paga con la factura 2601019 por 5.276,51 USDT, de los cuales 3.429,73 son de Argentina.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Contratado</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F28" s="19" t="n">
-        <v>1749800</v>
-      </c>
-      <c r="G28" s="20" t="n">
+      <c r="F28" s="40" t="n">
+        <v>13387500</v>
+      </c>
+      <c r="G28" s="13" t="n">
         <v>0.21</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="41">
         <f>IF(F28="","",F28*(1+N(G28)))</f>
         <v/>
       </c>
-      <c r="I28" s="22">
-        <f>IF(D28="Bonificado",0,IF(H28="",N(J28),IF(E28="USD",H28,H28/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J28" s="23" t="n"/>
-      <c r="K28" s="22">
-        <f>IF(D28="Alternativa","",I28-N(J28))</f>
-        <v/>
-      </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>Mail hola@blocko.com.ar 09/06/2026 · producción 3 semanas</t>
+      <c r="I28" s="13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J28" s="14">
+        <f>IF(OR(D28="Bonificado",D28="Reemplazado"),0,N(I28)*IF(H28="",N(K28),IF(E28="USD",H28,H28/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="14">
+        <f>IF(D28="Alternativa","",J28-N(K28))</f>
+        <v/>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Presupuesto Pañuelos - Arg y Uru · facturas 2601012 (20/06) y 2601019 (16/08)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Pañuelos</t>
+          <t>Remeras premium estampadas (250)</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Proveedor Colombia</t>
+          <t>REMERASYESTAMPADOS</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Contrato cerrado, 50% abonado el 24/06. Saldo US$5.491 programado al 13/09.</t>
+          <t>Factura 2601017 del 16/08, $14.110 por unidad. Sube de 230 a 250 unidades contra la factura original 2601011, al mismo precio unitario. SIN PAGAR: se debe el 100% (2.780,64 USDT).</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -1989,46 +2225,51 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>10982</v>
-      </c>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="14">
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="n">
+        <v>3527500</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H29" s="41">
         <f>IF(F29="","",F29*(1+N(G29)))</f>
         <v/>
       </c>
-      <c r="I29" s="14">
-        <f>IF(D29="Bonificado",0,IF(H29="",N(J29),IF(E29="USD",H29,H29/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="14">
-        <f>IF(D29="Alternativa","",I29-N(J29))</f>
-        <v/>
-      </c>
-      <c r="L29" s="15" t="inlineStr">
-        <is>
-          <t>Hoja PAGOS del master</t>
+      <c r="I29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="14">
+        <f>IF(OR(D29="Bonificado",D29="Reemplazado"),0,N(I29)*IF(H29="",N(K29),IF(E29="USD",H29,H29/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="14">
+        <f>IF(D29="Alternativa","",J29-N(K29))</f>
+        <v/>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Presupuestos camisetas + pañoletas · factura 2601017 (16/08)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Lanyards</t>
+          <t>Bordado de gorras (940)</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Proveedor Colombia</t>
+          <t>REMERASYESTAMPADOS</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Contrato cerrado, 50% abonado el 25/06. Saldo US$850 al 13/09.</t>
+          <t>Bordado computarizado sobre las gorras que provee el cliente. Presupuesto del 03/07 con el descuento de $411.800 ya aplicado. Precio final, no lleva IVA. SIN PAGAR: se debe el 100% (1.721,95 USDT).</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -2038,46 +2279,49 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>1698.59</v>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="n">
+        <v>2643200</v>
       </c>
       <c r="G30" s="13" t="n"/>
-      <c r="H30" s="14">
+      <c r="H30" s="41">
         <f>IF(F30="","",F30*(1+N(G30)))</f>
         <v/>
       </c>
-      <c r="I30" s="14">
-        <f>IF(D30="Bonificado",0,IF(H30="",N(J30),IF(E30="USD",H30,H30/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="14">
-        <f>IF(D30="Alternativa","",I30-N(J30))</f>
-        <v/>
-      </c>
-      <c r="L30" s="15" t="inlineStr">
-        <is>
-          <t>Hoja PAGOS del master</t>
+      <c r="I30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="14">
+        <f>IF(OR(D30="Bonificado",D30="Reemplazado"),0,N(I30)*IF(H30="",N(K30),IF(E30="USD",H30,H30/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="14">
+        <f>IF(D30="Alternativa","",J30-N(K30))</f>
+        <v/>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Presupuesto gorras (compra y bordado) / Bordado · factura 2601016 (10/08)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Gorras</t>
+          <t>Gorras Flex unicolor/bicolor (940)</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Proveedor Colombia</t>
+          <t>TEXTIL RYU S.R.L.</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Pagado 100% el 25/06</t>
+          <t>Factura 2601009 del 20/06, pagada al 100% el 25/06. Es la compra de las gorras; el bordado va en su propia linea.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -2087,48 +2331,53 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>1825</v>
-      </c>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="14">
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="n">
+        <v>2224980</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H31" s="41">
         <f>IF(F31="","",F31*(1+N(G31)))</f>
         <v/>
       </c>
-      <c r="I31" s="14">
-        <f>IF(D31="Bonificado",0,IF(H31="",N(J31),IF(E31="USD",H31,H31/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J31" s="12" t="n">
+      <c r="I31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="14">
+        <f>IF(OR(D31="Bonificado",D31="Reemplazado"),0,N(I31)*IF(H31="",N(K31),IF(E31="USD",H31,H31/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="K31" s="14">
-        <f>IF(D31="Alternativa","",I31-N(J31))</f>
-        <v/>
-      </c>
-      <c r="L31" s="15" t="inlineStr">
-        <is>
-          <t>Hoja PAGOS del master</t>
+      <c r="L31" s="14">
+        <f>IF(D31="Alternativa","",J31-N(K31))</f>
+        <v/>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Compra de gorras · factura 2601009 · hoja PAGOS del master</t>
         </is>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Gráfica Argentina</t>
+          <t>Lanyards premium doble raso 25 mm (1.360)</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Proveedor Colombia</t>
+          <t>LEOTEX</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Contrato cerrado, saldo US$1.839 al 13/09</t>
+          <t>Sublimacion full print en ambas caras, 1.300 negros + 50 azules (la factura dice 1.360, la suma da 1.350: hay 10 de diferencia). Reemitida como 2601018 en USDT. OJO: la carpeta se llama "Nuevo pago - 50%" pero la factura viene por el total.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -2138,302 +2387,383 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="n">
+        <v>2070600</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H32" s="41">
+        <f>IF(F32="","",F32*(1+N(G32)))</f>
+        <v/>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="14">
+        <f>IF(OR(D32="Bonificado",D32="Reemplazado"),0,N(I32)*IF(H32="",N(K32),IF(E32="USD",H32,H32/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="14">
+        <f>IF(D32="Alternativa","",J32-N(K32))</f>
+        <v/>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Presupuesto Lanyards · facturas 2601013 (20/06) y 2601018 (16/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Grafica oficial CMC — Argentina</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>DERQUI IMPRESIONES</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>5.500 hojas A4, 5.500 tarjetas, 1.030 credenciales, 5.500 mapas y 1.000 bolsas de friselina. Reemitida el 16/08 para cambiar el medio de pago a USDT.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Contratado</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="n">
+        <v>3025260</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H33" s="41">
+        <f>IF(F33="","",F33*(1+N(G33)))</f>
+        <v/>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="14">
+        <f>IF(OR(D33="Bonificado",D33="Reemplazado"),0,N(I33)*IF(H33="",N(K33),IF(E33="USD",H33,H33/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="14">
+        <f>IF(D33="Alternativa","",J33-N(K33))</f>
+        <v/>
+      </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Factura/presu ARGENTINA · factura 2601014 (20/06, reemitida 16/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>Grafica oficial CMC — Uruguay</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>DERQUI IMPRESIONES</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>NO ES DE ARGENTINA. 2.800 hojas A4, 2.800 tarjetas, 530 credenciales, 2.800 mapas y 1.000 bolsas de friselina, para el evento de Uruguay. Se deja a la vista en cero porque en la hoja PAGOS del master estaba cargada como Argentina: es el monto que no cerraba.</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
+        <is>
+          <t>Otro pais</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F34" s="50" t="n">
+        <v>1564626</v>
+      </c>
+      <c r="G34" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H34" s="51">
+        <f>IF(F34="","",F34*(1+N(G34)))</f>
+        <v/>
+      </c>
+      <c r="I34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="47">
+        <f>IF(OR(D34="Bonificado",D34="Reemplazado"),0,N(I34)*IF(H34="",N(K34),IF(E34="USD",H34,H34/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="47">
+        <f>IF(D34="Alternativa","",J34-N(K34))</f>
+        <v/>
+      </c>
+      <c r="M34" s="49" t="inlineStr">
+        <is>
+          <t>Drive · Factura/presu URUGUAY · factura 2601015 (20/06, reemitida 16/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>Cintas portacredencial (1.300) — alternativa</t>
+        </is>
+      </c>
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>Blocko</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="inlineStr">
+        <is>
+          <t>Cinta raso 25 mm impresa a 4 colores dos caras + mosqueton zamak, $1.346 c/u. Es el MISMO item que los lanyards de LEOTEX, que ya esta contratado y con anticipo pagado. Estaba sumando dos veces: ahora queda como alternativa descartada.</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>Alternativa</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F35" s="50" t="n">
+        <v>1749800</v>
+      </c>
+      <c r="G35" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H35" s="51">
+        <f>IF(F35="","",F35*(1+N(G35)))</f>
+        <v/>
+      </c>
+      <c r="I35" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="47">
+        <f>IF(OR(D35="Bonificado",D35="Reemplazado"),0,N(I35)*IF(H35="",N(K35),IF(E35="USD",H35,H35/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="47">
+        <f>IF(D35="Alternativa","",J35-N(K35))</f>
+        <v/>
+      </c>
+      <c r="M35" s="49" t="inlineStr">
+        <is>
+          <t>Mail hola@blocko.com.ar 09/06/2026 · descartada contra la factura 2601013 de LEOTEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>Marqueteria y enmarcado</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="inlineStr">
+        <is>
+          <t>Enmarcado de las certificaciones y los premios. Rubro nuevo, no estaba en ninguna planilla.</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>2481</v>
-      </c>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="14">
-        <f>IF(F32="","",F32*(1+N(G32)))</f>
-        <v/>
-      </c>
-      <c r="I32" s="14">
-        <f>IF(D32="Bonificado",0,IF(H32="",N(J32),IF(E32="USD",H32,H32/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="14">
-        <f>IF(D32="Alternativa","",I32-N(J32))</f>
-        <v/>
-      </c>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>Hoja PAGOS del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>Marquetería y enmarcado</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="F36" s="35" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="34">
+        <f>IF(F36="","",F36*(1+N(G36)))</f>
+        <v/>
+      </c>
+      <c r="I36" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="34">
+        <f>IF(OR(D36="Bonificado",D36="Reemplazado"),0,N(I36)*IF(H36="",N(K36),IF(E36="USD",H36,H36/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K36" s="35" t="n"/>
+      <c r="L36" s="34">
+        <f>IF(D36="Alternativa","",J36-N(K36))</f>
+        <v/>
+      </c>
+      <c r="M36" s="36" t="inlineStr">
+        <is>
+          <t>Agregado por Agustina · pendiente de cotizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>Cheques, escarapelas, diplomas, placas y manillas</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>Enmarcado de las certificaciones y los premios. Rubro nuevo, no estaba en ninguna planilla.</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="C37" s="29" t="inlineStr">
+        <is>
+          <t>Lo unico del merch que las facturas de Drive NO cubren. Las camisetas, los mapas, las bolsas y las credenciales ya estan facturados arriba.</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="29" t="n"/>
-      <c r="H33" s="31">
-        <f>IF(F33="","",F33*(1+N(G33)))</f>
-        <v/>
-      </c>
-      <c r="I33" s="31">
-        <f>IF(D33="Bonificado",0,IF(H33="",N(J33),IF(E33="USD",H33,H33/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J33" s="32" t="n"/>
-      <c r="K33" s="31">
-        <f>IF(D33="Alternativa","",I33-N(J33))</f>
-        <v/>
-      </c>
-      <c r="L33" s="33" t="inlineStr">
-        <is>
-          <t>Agregado por Agustina · pendiente de cotizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>Resto de merch e impresos</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>Varios (merch desde Colombia)</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="inlineStr">
-        <is>
-          <t>Contratos, cheques, escarapelas, bolsas, camisetas, mapas, diplomas, placas y manillas</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="F37" s="35" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="34">
+        <f>IF(F37="","",F37*(1+N(G37)))</f>
+        <v/>
+      </c>
+      <c r="I37" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="34">
+        <f>IF(OR(D37="Bonificado",D37="Reemplazado"),0,N(I37)*IF(H37="",N(K37),IF(E37="USD",H37,H37/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K37" s="35" t="n"/>
+      <c r="L37" s="34">
+        <f>IF(D37="Alternativa","",J37-N(K37))</f>
+        <v/>
+      </c>
+      <c r="M37" s="36" t="inlineStr">
+        <is>
+          <t>Pendiente de cotizar · antes estaba dentro del estimado global de US$8.689</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>Estimado global de merch del master (reemplazado)</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="inlineStr">
+        <is>
+          <t>Varios</t>
+        </is>
+      </c>
+      <c r="C38" s="44" t="inlineStr">
+        <is>
+          <t>La hoja Argentina del master tenia US$8.689 en un solo renglon por contratos, cheques, escarapelas, bolsas, camisetas, mapas, diplomas, placas y manillas. Queda en cero como costo porque las facturas reales de arriba lo reemplazan; se conserva el estimado para poder comparar contra el presupuesto original.</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>Reemplazado</t>
+        </is>
+      </c>
+      <c r="E38" s="43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="29" t="n"/>
-      <c r="H34" s="31">
-        <f>IF(F34="","",F34*(1+N(G34)))</f>
-        <v/>
-      </c>
-      <c r="I34" s="31">
-        <f>IF(D34="Bonificado",0,IF(H34="",N(J34),IF(E34="USD",H34,H34/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J34" s="32" t="n">
+      <c r="F38" s="45" t="n"/>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="47">
+        <f>IF(F38="","",F38*(1+N(G38)))</f>
+        <v/>
+      </c>
+      <c r="I38" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="47">
+        <f>IF(OR(D38="Bonificado",D38="Reemplazado"),0,N(I38)*IF(H38="",N(K38),IF(E38="USD",H38,H38/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K38" s="45" t="n">
         <v>8689</v>
       </c>
-      <c r="K34" s="31">
-        <f>IF(D34="Alternativa","",I34-N(J34))</f>
-        <v/>
-      </c>
-      <c r="L34" s="33" t="inlineStr">
-        <is>
-          <t>Estimado de la hoja Argentina del master; sin cotización argentina</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="L38" s="47">
+        <f>IF(D38="Alternativa","",J38-N(K38))</f>
+        <v/>
+      </c>
+      <c r="M38" s="49" t="inlineStr">
+        <is>
+          <t>Hoja Argentina del master · reemplazado por las facturas 2601009 a 2601019</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>Subtotal Merch</t>
         </is>
       </c>
-      <c r="B35" s="35" t="n"/>
-      <c r="C35" s="35" t="n"/>
-      <c r="D35" s="35" t="n"/>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="35" t="n"/>
-      <c r="G35" s="35" t="n"/>
-      <c r="H35" s="35" t="n"/>
-      <c r="I35" s="36">
-        <f>SUMIF($D$28:$D$34,"&lt;&gt;Alternativa",$I$28:$I$34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="36">
-        <f>SUM($J$28:$J$34)</f>
-        <v/>
-      </c>
-      <c r="K35" s="36">
-        <f>I35-J35</f>
-        <v/>
-      </c>
-      <c r="L35" s="35" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>CATERING</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-      <c r="L36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Catering VIP, staff y equipo</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Grupo Ambient</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Número final por las dos propuestas juntas: 600 lunchbox para los VIP + desayuno, almuerzo y cena para 150 personas.</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>14569</v>
-      </c>
-      <c r="G37" s="13" t="n"/>
-      <c r="H37" s="14">
-        <f>IF(F37="","",F37*(1+N(G37)))</f>
-        <v/>
-      </c>
-      <c r="I37" s="14">
-        <f>IF(D37="Bonificado",0,IF(H37="",N(J37),IF(E37="USD",H37,H37/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>33820</v>
-      </c>
-      <c r="K37" s="14">
-        <f>IF(D37="Alternativa","",I37-N(J37))</f>
-        <v/>
-      </c>
-      <c r="L37" s="15" t="inlineStr">
-        <is>
-          <t>Cierre de Agustina con Grupo Ambient · reemplaza la estimación de $25.000.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="39" t="inlineStr">
-        <is>
-          <t>Food trucks</t>
-        </is>
-      </c>
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>Sin costo</t>
-        </is>
-      </c>
-      <c r="C38" s="41" t="inlineStr">
-        <is>
-          <t>No los paga la producción.</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>Bonificado</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F38" s="42" t="n"/>
-      <c r="G38" s="43" t="n"/>
-      <c r="H38" s="44">
-        <f>IF(F38="","",F38*(1+N(G38)))</f>
-        <v/>
-      </c>
-      <c r="I38" s="44">
-        <f>IF(D38="Bonificado",0,IF(H38="",N(J38),IF(E38="USD",H38,H38/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J38" s="42" t="n"/>
-      <c r="K38" s="44">
-        <f>IF(D38="Alternativa","",I38-N(J38))</f>
-        <v/>
-      </c>
-      <c r="L38" s="45" t="inlineStr">
-        <is>
-          <t>Confirmado por Agustina</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>Subtotal Catering</t>
-        </is>
-      </c>
-      <c r="B39" s="35" t="n"/>
-      <c r="C39" s="35" t="n"/>
-      <c r="D39" s="35" t="n"/>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="35" t="n"/>
-      <c r="G39" s="35" t="n"/>
-      <c r="H39" s="35" t="n"/>
-      <c r="I39" s="36">
-        <f>SUMIF($D$37:$D$38,"&lt;&gt;Alternativa",$I$37:$I$38)</f>
-        <v/>
-      </c>
-      <c r="J39" s="36">
-        <f>SUM($J$37:$J$38)</f>
-        <v/>
-      </c>
-      <c r="K39" s="36">
-        <f>I39-J39</f>
-        <v/>
-      </c>
-      <c r="L39" s="35" t="n"/>
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="38" t="n"/>
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="38" t="n"/>
+      <c r="J39" s="39">
+        <f>SUMIF($D$28:$D$38,"&lt;&gt;Alternativa",$J$28:$J$38)</f>
+        <v/>
+      </c>
+      <c r="K39" s="39">
+        <f>SUM($K$28:$K$38)</f>
+        <v/>
+      </c>
+      <c r="L39" s="39">
+        <f>J39-K39</f>
+        <v/>
+      </c>
+      <c r="M39" s="38" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>PRODUCCIÓN</t>
+          <t>CATERING</t>
         </is>
       </c>
       <c r="B40" s="8" t="n"/>
@@ -2447,590 +2777,775 @@
       <c r="J40" s="8" t="n"/>
       <c r="K40" s="8" t="n"/>
       <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Catering VIP, staff y equipo</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Grupo Ambient</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Número final por las dos propuestas juntas: 600 lunchbox para los VIP + desayuno, almuerzo y cena para 150 personas.</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>14569</v>
+      </c>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="14">
+        <f>IF(F41="","",F41*(1+N(G41)))</f>
+        <v/>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="14">
+        <f>IF(OR(D41="Bonificado",D41="Reemplazado"),0,N(I41)*IF(H41="",N(K41),IF(E41="USD",H41,H41/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>33820</v>
+      </c>
+      <c r="L41" s="14">
+        <f>IF(D41="Alternativa","",J41-N(K41))</f>
+        <v/>
+      </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>Cierre de Agustina con Grupo Ambient · reemplaza la estimación de $25.000.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="42" t="inlineStr">
+        <is>
+          <t>Food trucks</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>Sin costo</t>
+        </is>
+      </c>
+      <c r="C42" s="44" t="inlineStr">
+        <is>
+          <t>No los paga la producción.</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E42" s="43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F42" s="45" t="n"/>
+      <c r="G42" s="46" t="n"/>
+      <c r="H42" s="47">
+        <f>IF(F42="","",F42*(1+N(G42)))</f>
+        <v/>
+      </c>
+      <c r="I42" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="47">
+        <f>IF(OR(D42="Bonificado",D42="Reemplazado"),0,N(I42)*IF(H42="",N(K42),IF(E42="USD",H42,H42/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K42" s="45" t="n"/>
+      <c r="L42" s="47">
+        <f>IF(D42="Alternativa","",J42-N(K42))</f>
+        <v/>
+      </c>
+      <c r="M42" s="49" t="inlineStr">
+        <is>
+          <t>Confirmado por Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t>Subtotal Catering</t>
+        </is>
+      </c>
+      <c r="B43" s="38" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="38" t="n"/>
+      <c r="E43" s="38" t="n"/>
+      <c r="F43" s="38" t="n"/>
+      <c r="G43" s="38" t="n"/>
+      <c r="H43" s="38" t="n"/>
+      <c r="I43" s="38" t="n"/>
+      <c r="J43" s="39">
+        <f>SUMIF($D$41:$D$42,"&lt;&gt;Alternativa",$J$41:$J$42)</f>
+        <v/>
+      </c>
+      <c r="K43" s="39">
+        <f>SUM($K$41:$K$42)</f>
+        <v/>
+      </c>
+      <c r="L43" s="39">
+        <f>J43-K43</f>
+        <v/>
+      </c>
+      <c r="M43" s="38" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCCIÓN</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
+      <c r="M44" s="8" t="n"/>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>Unifilas</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="C45" s="29" t="inlineStr">
         <is>
           <t>Estimado del sheet, sin cotización</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D45" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="29" t="n"/>
-      <c r="H41" s="31">
-        <f>IF(F41="","",F41*(1+N(G41)))</f>
-        <v/>
-      </c>
-      <c r="I41" s="31">
-        <f>IF(D41="Bonificado",0,IF(H41="",N(J41),IF(E41="USD",H41,H41/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J41" s="32" t="n">
+      <c r="F45" s="35" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="34">
+        <f>IF(F45="","",F45*(1+N(G45)))</f>
+        <v/>
+      </c>
+      <c r="I45" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="34">
+        <f>IF(OR(D45="Bonificado",D45="Reemplazado"),0,N(I45)*IF(H45="",N(K45),IF(E45="USD",H45,H45/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K45" s="35" t="n">
         <v>1200</v>
       </c>
-      <c r="K41" s="31">
-        <f>IF(D41="Alternativa","",I41-N(J41))</f>
-        <v/>
-      </c>
-      <c r="L41" s="33" t="inlineStr">
+      <c r="L45" s="34">
+        <f>IF(D45="Alternativa","",J45-N(K45))</f>
+        <v/>
+      </c>
+      <c r="M45" s="36" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="39" t="inlineStr">
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>Vallado (500 vallas)</t>
         </is>
       </c>
-      <c r="B42" s="40" t="inlineStr">
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>Bonificado por técnica</t>
         </is>
       </c>
-      <c r="C42" s="41" t="inlineStr">
+      <c r="C46" s="44" t="inlineStr">
         <is>
           <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
         </is>
       </c>
-      <c r="D42" s="39" t="inlineStr">
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>Bonificado</t>
         </is>
       </c>
-      <c r="E42" s="40" t="inlineStr">
+      <c r="E46" s="43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F42" s="42" t="n"/>
-      <c r="G42" s="43" t="n"/>
-      <c r="H42" s="44">
-        <f>IF(F42="","",F42*(1+N(G42)))</f>
-        <v/>
-      </c>
-      <c r="I42" s="44">
-        <f>IF(D42="Bonificado",0,IF(H42="",N(J42),IF(E42="USD",H42,H42/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J42" s="42" t="n">
+      <c r="F46" s="45" t="n"/>
+      <c r="G46" s="46" t="n"/>
+      <c r="H46" s="47">
+        <f>IF(F46="","",F46*(1+N(G46)))</f>
+        <v/>
+      </c>
+      <c r="I46" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="47">
+        <f>IF(OR(D46="Bonificado",D46="Reemplazado"),0,N(I46)*IF(H46="",N(K46),IF(E46="USD",H46,H46/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K46" s="45" t="n">
         <v>1250</v>
       </c>
-      <c r="K42" s="44">
-        <f>IF(D42="Alternativa","",I42-N(J42))</f>
-        <v/>
-      </c>
-      <c r="L42" s="45" t="inlineStr">
+      <c r="L46" s="47">
+        <f>IF(D46="Alternativa","",J46-N(K46))</f>
+        <v/>
+      </c>
+      <c r="M46" s="49" t="inlineStr">
         <is>
           <t>Negociación de Agustina</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>DJ</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B47" s="28" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C43" s="27" t="inlineStr">
+      <c r="C47" s="29" t="inlineStr">
         <is>
           <t>Estimado del sheet</t>
         </is>
       </c>
-      <c r="D43" s="25" t="inlineStr">
+      <c r="D47" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E47" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="29" t="n"/>
-      <c r="H43" s="31">
-        <f>IF(F43="","",F43*(1+N(G43)))</f>
-        <v/>
-      </c>
-      <c r="I43" s="31">
-        <f>IF(D43="Bonificado",0,IF(H43="",N(J43),IF(E43="USD",H43,H43/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J43" s="32" t="n">
+      <c r="F47" s="35" t="n"/>
+      <c r="G47" s="31" t="n"/>
+      <c r="H47" s="34">
+        <f>IF(F47="","",F47*(1+N(G47)))</f>
+        <v/>
+      </c>
+      <c r="I47" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="34">
+        <f>IF(OR(D47="Bonificado",D47="Reemplazado"),0,N(I47)*IF(H47="",N(K47),IF(E47="USD",H47,H47/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K47" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="K43" s="31">
-        <f>IF(D43="Alternativa","",I43-N(J43))</f>
-        <v/>
-      </c>
-      <c r="L43" s="33" t="inlineStr">
+      <c r="L47" s="34">
+        <f>IF(D47="Alternativa","",J47-N(K47))</f>
+        <v/>
+      </c>
+      <c r="M47" s="36" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>Escoltas (2)</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C44" s="27" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
         <is>
           <t>Estimado del sheet</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E48" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F44" s="32" t="n"/>
-      <c r="G44" s="29" t="n"/>
-      <c r="H44" s="31">
-        <f>IF(F44="","",F44*(1+N(G44)))</f>
-        <v/>
-      </c>
-      <c r="I44" s="31">
-        <f>IF(D44="Bonificado",0,IF(H44="",N(J44),IF(E44="USD",H44,H44/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J44" s="32" t="n">
+      <c r="F48" s="35" t="n"/>
+      <c r="G48" s="31" t="n"/>
+      <c r="H48" s="34">
+        <f>IF(F48="","",F48*(1+N(G48)))</f>
+        <v/>
+      </c>
+      <c r="I48" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="34">
+        <f>IF(OR(D48="Bonificado",D48="Reemplazado"),0,N(I48)*IF(H48="",N(K48),IF(E48="USD",H48,H48/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K48" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="K44" s="31">
-        <f>IF(D44="Alternativa","",I44-N(J44))</f>
-        <v/>
-      </c>
-      <c r="L44" s="33" t="inlineStr">
+      <c r="L48" s="34">
+        <f>IF(D48="Alternativa","",J48-N(K48))</f>
+        <v/>
+      </c>
+      <c r="M48" s="36" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>Master Mind Hit</t>
         </is>
       </c>
-      <c r="B45" s="26" t="inlineStr">
+      <c r="B49" s="28" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C45" s="27" t="inlineStr">
+      <c r="C49" s="29" t="inlineStr">
         <is>
           <t>Sala adicional</t>
         </is>
       </c>
-      <c r="D45" s="25" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E45" s="26" t="inlineStr">
+      <c r="E49" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="29" t="n"/>
-      <c r="H45" s="31">
-        <f>IF(F45="","",F45*(1+N(G45)))</f>
-        <v/>
-      </c>
-      <c r="I45" s="31">
-        <f>IF(D45="Bonificado",0,IF(H45="",N(J45),IF(E45="USD",H45,H45/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J45" s="32" t="n">
+      <c r="F49" s="35" t="n"/>
+      <c r="G49" s="31" t="n"/>
+      <c r="H49" s="34">
+        <f>IF(F49="","",F49*(1+N(G49)))</f>
+        <v/>
+      </c>
+      <c r="I49" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="34">
+        <f>IF(OR(D49="Bonificado",D49="Reemplazado"),0,N(I49)*IF(H49="",N(K49),IF(E49="USD",H49,H49/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K49" s="35" t="n">
         <v>3000</v>
       </c>
-      <c r="K45" s="31">
-        <f>IF(D45="Alternativa","",I45-N(J45))</f>
-        <v/>
-      </c>
-      <c r="L45" s="33" t="inlineStr">
+      <c r="L49" s="34">
+        <f>IF(D49="Alternativa","",J49-N(K49))</f>
+        <v/>
+      </c>
+      <c r="M49" s="36" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>Personal logístico</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C46" s="27" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>La hoja del master lo tiene en US$0</t>
         </is>
       </c>
-      <c r="D46" s="25" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E50" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F46" s="32" t="n"/>
-      <c r="G46" s="29" t="n"/>
-      <c r="H46" s="31">
-        <f>IF(F46="","",F46*(1+N(G46)))</f>
-        <v/>
-      </c>
-      <c r="I46" s="31">
-        <f>IF(D46="Bonificado",0,IF(H46="",N(J46),IF(E46="USD",H46,H46/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J46" s="32" t="n"/>
-      <c r="K46" s="31">
-        <f>IF(D46="Alternativa","",I46-N(J46))</f>
-        <v/>
-      </c>
-      <c r="L46" s="33" t="inlineStr">
+      <c r="F50" s="35" t="n"/>
+      <c r="G50" s="31" t="n"/>
+      <c r="H50" s="34">
+        <f>IF(F50="","",F50*(1+N(G50)))</f>
+        <v/>
+      </c>
+      <c r="I50" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="34">
+        <f>IF(OR(D50="Bonificado",D50="Reemplazado"),0,N(I50)*IF(H50="",N(K50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K50" s="35" t="n"/>
+      <c r="L50" s="34">
+        <f>IF(D50="Alternativa","",J50-N(K50))</f>
+        <v/>
+      </c>
+      <c r="M50" s="36" t="inlineStr">
         <is>
           <t>Hoja Argentina del master · valor en cero</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Intercoms</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Proveedor Colombia</t>
         </is>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Contrato US$560, sin abonar, 2 cuotas al 24/08 y 23/09</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Contratado</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>560</v>
       </c>
-      <c r="G47" s="13" t="n"/>
-      <c r="H47" s="14">
-        <f>IF(F47="","",F47*(1+N(G47)))</f>
-        <v/>
-      </c>
-      <c r="I47" s="14">
-        <f>IF(D47="Bonificado",0,IF(H47="",N(J47),IF(E47="USD",H47,H47/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J47" s="12" t="n"/>
-      <c r="K47" s="14">
-        <f>IF(D47="Alternativa","",I47-N(J47))</f>
-        <v/>
-      </c>
-      <c r="L47" s="15" t="inlineStr">
+      <c r="G51" s="13" t="n"/>
+      <c r="H51" s="14">
+        <f>IF(F51="","",F51*(1+N(G51)))</f>
+        <v/>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="14">
+        <f>IF(OR(D51="Bonificado",D51="Reemplazado"),0,N(I51)*IF(H51="",N(K51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="14">
+        <f>IF(D51="Alternativa","",J51-N(K51))</f>
+        <v/>
+      </c>
+      <c r="M51" s="16" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="34" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr">
         <is>
           <t>Subtotal Producción</t>
         </is>
       </c>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="35" t="n"/>
-      <c r="G48" s="35" t="n"/>
-      <c r="H48" s="35" t="n"/>
-      <c r="I48" s="36">
-        <f>SUMIF($D$41:$D$47,"&lt;&gt;Alternativa",$I$41:$I$47)</f>
-        <v/>
-      </c>
-      <c r="J48" s="36">
-        <f>SUM($J$41:$J$47)</f>
-        <v/>
-      </c>
-      <c r="K48" s="36">
-        <f>I48-J48</f>
-        <v/>
-      </c>
-      <c r="L48" s="35" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="B52" s="38" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="38" t="n"/>
+      <c r="E52" s="38" t="n"/>
+      <c r="F52" s="38" t="n"/>
+      <c r="G52" s="38" t="n"/>
+      <c r="H52" s="38" t="n"/>
+      <c r="I52" s="38" t="n"/>
+      <c r="J52" s="39">
+        <f>SUMIF($D$45:$D$51,"&lt;&gt;Alternativa",$J$45:$J$51)</f>
+        <v/>
+      </c>
+      <c r="K52" s="39">
+        <f>SUM($K$45:$K$51)</f>
+        <v/>
+      </c>
+      <c r="L52" s="39">
+        <f>J52-K52</f>
+        <v/>
+      </c>
+      <c r="M52" s="38" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>EQUIPO</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
-    </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="8" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="8" t="n"/>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>Vuelos del equipo</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C50" s="27" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>No hay ninguna cotización de vuelos a Buenos Aires en el correo ni monto en la hoja del master</t>
         </is>
       </c>
-      <c r="D50" s="25" t="inlineStr">
+      <c r="D54" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="E54" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F50" s="32" t="n"/>
-      <c r="G50" s="29" t="n"/>
-      <c r="H50" s="31">
-        <f>IF(F50="","",F50*(1+N(G50)))</f>
-        <v/>
-      </c>
-      <c r="I50" s="31">
-        <f>IF(D50="Bonificado",0,IF(H50="",N(J50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J50" s="32" t="n"/>
-      <c r="K50" s="31">
-        <f>IF(D50="Alternativa","",I50-N(J50))</f>
-        <v/>
-      </c>
-      <c r="L50" s="33" t="inlineStr">
+      <c r="F54" s="35" t="n"/>
+      <c r="G54" s="31" t="n"/>
+      <c r="H54" s="34">
+        <f>IF(F54="","",F54*(1+N(G54)))</f>
+        <v/>
+      </c>
+      <c r="I54" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="34">
+        <f>IF(OR(D54="Bonificado",D54="Reemplazado"),0,N(I54)*IF(H54="",N(K54),IF(E54="USD",H54,H54/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K54" s="35" t="n"/>
+      <c r="L54" s="34">
+        <f>IF(D54="Alternativa","",J54-N(K54))</f>
+        <v/>
+      </c>
+      <c r="M54" s="36" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>Alojamiento del equipo</t>
         </is>
       </c>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C51" s="27" t="inlineStr">
+      <c r="C55" s="29" t="inlineStr">
         <is>
           <t>No hay cotización de hotel en Buenos Aires en el correo ni monto en la hoja del master</t>
         </is>
       </c>
-      <c r="D51" s="25" t="inlineStr">
+      <c r="D55" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E51" s="26" t="inlineStr">
+      <c r="E55" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="29" t="n"/>
-      <c r="H51" s="31">
-        <f>IF(F51="","",F51*(1+N(G51)))</f>
-        <v/>
-      </c>
-      <c r="I51" s="31">
-        <f>IF(D51="Bonificado",0,IF(H51="",N(J51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J51" s="32" t="n"/>
-      <c r="K51" s="31">
-        <f>IF(D51="Alternativa","",I51-N(J51))</f>
-        <v/>
-      </c>
-      <c r="L51" s="33" t="inlineStr">
+      <c r="F55" s="35" t="n"/>
+      <c r="G55" s="31" t="n"/>
+      <c r="H55" s="34">
+        <f>IF(F55="","",F55*(1+N(G55)))</f>
+        <v/>
+      </c>
+      <c r="I55" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="34">
+        <f>IF(OR(D55="Bonificado",D55="Reemplazado"),0,N(I55)*IF(H55="",N(K55),IF(E55="USD",H55,H55/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K55" s="35" t="n"/>
+      <c r="L55" s="34">
+        <f>IF(D55="Alternativa","",J55-N(K55))</f>
+        <v/>
+      </c>
+      <c r="M55" s="36" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="25" t="inlineStr">
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>Traslados internos y viáticos</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B56" s="28" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C52" s="27" t="inlineStr">
+      <c r="C56" s="29" t="inlineStr">
         <is>
           <t>Sin registro</t>
         </is>
       </c>
-      <c r="D52" s="25" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="E56" s="28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F52" s="32" t="n"/>
-      <c r="G52" s="29" t="n"/>
-      <c r="H52" s="31">
-        <f>IF(F52="","",F52*(1+N(G52)))</f>
-        <v/>
-      </c>
-      <c r="I52" s="31">
-        <f>IF(D52="Bonificado",0,IF(H52="",N(J52),IF(E52="USD",H52,H52/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="J52" s="32" t="n"/>
-      <c r="K52" s="31">
-        <f>IF(D52="Alternativa","",I52-N(J52))</f>
-        <v/>
-      </c>
-      <c r="L52" s="33" t="inlineStr">
+      <c r="F56" s="35" t="n"/>
+      <c r="G56" s="31" t="n"/>
+      <c r="H56" s="34">
+        <f>IF(F56="","",F56*(1+N(G56)))</f>
+        <v/>
+      </c>
+      <c r="I56" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="34">
+        <f>IF(OR(D56="Bonificado",D56="Reemplazado"),0,N(I56)*IF(H56="",N(K56),IF(E56="USD",H56,H56/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K56" s="35" t="n"/>
+      <c r="L56" s="34">
+        <f>IF(D56="Alternativa","",J56-N(K56))</f>
+        <v/>
+      </c>
+      <c r="M56" s="36" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="34" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>Subtotal Equipo</t>
         </is>
       </c>
-      <c r="B53" s="35" t="n"/>
-      <c r="C53" s="35" t="n"/>
-      <c r="D53" s="35" t="n"/>
-      <c r="E53" s="35" t="n"/>
-      <c r="F53" s="35" t="n"/>
-      <c r="G53" s="35" t="n"/>
-      <c r="H53" s="35" t="n"/>
-      <c r="I53" s="36">
-        <f>SUMIF($D$50:$D$52,"&lt;&gt;Alternativa",$I$50:$I$52)</f>
-        <v/>
-      </c>
-      <c r="J53" s="36">
-        <f>SUM($J$50:$J$52)</f>
-        <v/>
-      </c>
-      <c r="K53" s="36">
-        <f>I53-J53</f>
-        <v/>
-      </c>
-      <c r="L53" s="35" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="B57" s="38" t="n"/>
+      <c r="C57" s="38" t="n"/>
+      <c r="D57" s="38" t="n"/>
+      <c r="E57" s="38" t="n"/>
+      <c r="F57" s="38" t="n"/>
+      <c r="G57" s="38" t="n"/>
+      <c r="H57" s="38" t="n"/>
+      <c r="I57" s="38" t="n"/>
+      <c r="J57" s="39">
+        <f>SUMIF($D$54:$D$56,"&lt;&gt;Alternativa",$J$54:$J$56)</f>
+        <v/>
+      </c>
+      <c r="K57" s="39">
+        <f>SUM($K$54:$K$56)</f>
+        <v/>
+      </c>
+      <c r="L57" s="39">
+        <f>J57-K57</f>
+        <v/>
+      </c>
+      <c r="M57" s="38" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="52" t="inlineStr">
         <is>
           <t>COSTO TOTAL DEL EVENTO</t>
         </is>
       </c>
-      <c r="I55" s="47">
-        <f>I12+I18+I26+I35+I39+I48+I53</f>
-        <v/>
-      </c>
-      <c r="J55" s="47">
-        <f>J12+J18+J26+J35+J39+J48+J53</f>
-        <v/>
-      </c>
-      <c r="K55" s="47">
-        <f>K12+K18+K26+K35+K39+K48+K53</f>
+      <c r="J59" s="53">
+        <f>J12+J18+J26+J39+J43+J52+J57</f>
+        <v/>
+      </c>
+      <c r="K59" s="53">
+        <f>K12+K18+K26+K39+K43+K52+K57</f>
+        <v/>
+      </c>
+      <c r="L59" s="53">
+        <f>L12+L18+L26+L39+L43+L52+L57</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L4"/>
+  <autoFilter ref="A4:M4"/>
   <mergeCells count="7">
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A49:L49"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A44:M44"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A40:M40"/>
+    <mergeCell ref="A53:M53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3072,7 +3587,7 @@
           <t>Tipo de cambio (ARS por USD)</t>
         </is>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C4" s="54" t="n">
         <v>1510</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3082,7 +3597,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>COSTO DEL EVENTO</t>
         </is>
@@ -3094,8 +3609,8 @@
           <t>Costo total (cotizaciones reales + estimados)</t>
         </is>
       </c>
-      <c r="C7" s="50">
-        <f>'COSTOS UNIFICADOS'!I55</f>
+      <c r="C7" s="56">
+        <f>'COSTOS UNIFICADOS'!J59</f>
         <v/>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3110,8 +3625,8 @@
           <t>Lo que decía el presupuesto original</t>
         </is>
       </c>
-      <c r="C8" s="50">
-        <f>'COSTOS UNIFICADOS'!J55</f>
+      <c r="C8" s="56">
+        <f>'COSTOS UNIFICADOS'!K59</f>
         <v/>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3126,8 +3641,8 @@
           <t>Diferencia contra el presupuesto</t>
         </is>
       </c>
-      <c r="C9" s="51">
-        <f>'COSTOS UNIFICADOS'!K55</f>
+      <c r="C9" s="57">
+        <f>'COSTOS UNIFICADOS'!L59</f>
         <v/>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3137,44 +3652,44 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>COSTO POR PERSONA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="inlineStr">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>Base de cálculo</t>
         </is>
       </c>
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>Personas</t>
         </is>
       </c>
-      <c r="C12" s="52" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>Costo por persona</t>
         </is>
       </c>
-      <c r="E12" s="52" t="inlineStr">
+      <c r="E12" s="58" t="inlineStr">
         <is>
           <t>Qué incluye</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>Aforo general</t>
         </is>
       </c>
-      <c r="B13" s="54" t="n">
+      <c r="B13" s="60" t="n">
         <v>5000</v>
       </c>
-      <c r="C13" s="55">
+      <c r="C13" s="61">
         <f>IFERROR($C$7/B13,"")</f>
         <v/>
       </c>
@@ -3185,15 +3700,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="B14" s="54" t="n">
+      <c r="B14" s="60" t="n">
         <v>1000</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="61">
         <f>IFERROR($C$7/B14,"")</f>
         <v/>
       </c>
@@ -3204,15 +3719,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="53" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>Asistentes pagos (general + VIP)</t>
         </is>
       </c>
-      <c r="B15" s="54" t="n">
+      <c r="B15" s="60" t="n">
         <v>6000</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="61">
         <f>IFERROR($C$7/B15,"")</f>
         <v/>
       </c>
@@ -3223,15 +3738,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>Mastermind del martes</t>
         </is>
       </c>
-      <c r="B16" s="54" t="n">
+      <c r="B16" s="60" t="n">
         <v>246</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="61">
         <f>IFERROR($C$7/B16,"")</f>
         <v/>
       </c>
@@ -3242,15 +3757,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>Total de personas en el predio</t>
         </is>
       </c>
-      <c r="B17" s="54" t="n">
+      <c r="B17" s="60" t="n">
         <v>6108</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="61">
         <f>IFERROR($C$7/B17,"")</f>
         <v/>
       </c>
@@ -3268,7 +3783,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>ESTADO DE LOS RUBROS</t>
         </is>
@@ -3280,13 +3795,13 @@
           <t>Contratado (hay contrato o anticipo)</t>
         </is>
       </c>
-      <c r="C21" s="56">
-        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Contratado",'COSTOS UNIFICADOS'!$I:$I)</f>
+      <c r="C21" s="62">
+        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Contratado",'COSTOS UNIFICADOS'!$J:$J)</f>
         <v/>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Sede, merch de Colombia e intercoms.</t>
+          <t>Sede, las nueve facturas de merch e intercoms.</t>
         </is>
       </c>
     </row>
@@ -3296,13 +3811,13 @@
           <t>Cotizado (hay presupuesto formal)</t>
         </is>
       </c>
-      <c r="C22" s="50">
-        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Cotizado",'COSTOS UNIFICADOS'!$I:$I)</f>
+      <c r="C22" s="56">
+        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Cotizado",'COSTOS UNIFICADOS'!$J:$J)</f>
         <v/>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Infraestructura, técnica, seguridad, médico, limpieza, residuos, seguro, WiFi, cintas, sillas.</t>
+          <t>Sillas, WiFi, seguridad, servicio médico, limpieza, retiro de residuos y seguro.</t>
         </is>
       </c>
     </row>
@@ -3312,13 +3827,13 @@
           <t>Sin cotizar (sólo estimado o nada)</t>
         </is>
       </c>
-      <c r="C23" s="57">
-        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Sin cotizar",'COSTOS UNIFICADOS'!$I:$I)</f>
+      <c r="C23" s="63">
+        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Sin cotizar",'COSTOS UNIFICADOS'!$J:$J)</f>
         <v/>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Catering, vuelos, alojamiento, unifilas, DJ, escoltas, Master Mind, personal logístico.</t>
+          <t>Vuelos, alojamiento, ecobaños, marquetería, replanteo, unifilas, DJ, escoltas, Master Mind, personal logístico.</t>
         </is>
       </c>
     </row>
@@ -3328,8 +3843,8 @@
           <t>Alternativas descartadas (no suman)</t>
         </is>
       </c>
-      <c r="C24" s="58">
-        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Alternativa",'COSTOS UNIFICADOS'!$I:$I)</f>
+      <c r="C24" s="64">
+        <f>SUMIF('COSTOS UNIFICADOS'!$D:$D,"Alternativa",'COSTOS UNIFICADOS'!$J:$J)</f>
         <v/>
       </c>
     </row>
@@ -3344,7 +3859,755 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="62" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Todo el merch, factura por factura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Carpeta de Drive "Presupuestos merch" · facturas 2601009 a 2601019 · emisor IIDAI LLC. Los proveedores son argentinos, no colombianos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Ítem</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Factura</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Neto (ARS)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Total (ARS)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>USDT de la factura</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>País</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>% Argentina</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Costo Argentina (USD)</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Falta pagar · regla 50%</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>Falta pagar · según factura</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>REMERASYESTAMPADOS</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Pañuelos / pañoletas estampados</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>8.500</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>2601012 → saldo 2601019</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>20/06 → 16/08</t>
+        </is>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>13387500</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H5" s="32">
+        <f>F5*(1+N(G5))</f>
+        <v/>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>5276.51</v>
+      </c>
+      <c r="J5" s="29" t="inlineStr">
+        <is>
+          <t>Argentina + Uruguay</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L5" s="65">
+        <f>K5*H5/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M5" s="34">
+        <f>K5*5276.51</f>
+        <v/>
+      </c>
+      <c r="N5" s="34">
+        <f>K5*5276.51</f>
+        <v/>
+      </c>
+      <c r="O5" s="36" t="inlineStr">
+        <is>
+          <t>La 2601019 ya viene emitida por el 50% restante. Falta definir con Uruguay como se reparte: aca se imputa el 65% a Argentina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>REMERASYESTAMPADOS</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>Remeras premium estampadas</t>
+        </is>
+      </c>
+      <c r="C6" s="67" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D6" s="68" t="inlineStr">
+        <is>
+          <t>2601017</t>
+        </is>
+      </c>
+      <c r="E6" s="68" t="inlineStr">
+        <is>
+          <t>16/08</t>
+        </is>
+      </c>
+      <c r="F6" s="69" t="n">
+        <v>3527500</v>
+      </c>
+      <c r="G6" s="70" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H6" s="71">
+        <f>F6*(1+N(G6))</f>
+        <v/>
+      </c>
+      <c r="I6" s="72" t="n">
+        <v>2780.64</v>
+      </c>
+      <c r="J6" s="67" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="K6" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="73">
+        <f>K6*H6/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M6" s="74">
+        <f>K6*2780.64</f>
+        <v/>
+      </c>
+      <c r="N6" s="74">
+        <f>K6*2780.64</f>
+        <v/>
+      </c>
+      <c r="O6" s="75" t="inlineStr">
+        <is>
+          <t>Se debe el 100%. Sube de 230 a 250 unidades contra la factura original 2601011, al mismo precio unitario de $14.110.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>REMERASYESTAMPADOS</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="inlineStr">
+        <is>
+          <t>Bordado computarizado en gorras</t>
+        </is>
+      </c>
+      <c r="C7" s="67" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D7" s="68" t="inlineStr">
+        <is>
+          <t>2601016</t>
+        </is>
+      </c>
+      <c r="E7" s="68" t="inlineStr">
+        <is>
+          <t>10/08</t>
+        </is>
+      </c>
+      <c r="F7" s="69" t="n">
+        <v>2643200</v>
+      </c>
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="71">
+        <f>F7*(1+N(G7))</f>
+        <v/>
+      </c>
+      <c r="I7" s="72" t="n">
+        <v>1721.95</v>
+      </c>
+      <c r="J7" s="67" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="K7" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="73">
+        <f>K7*H7/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M7" s="74">
+        <f>K7*1721.95</f>
+        <v/>
+      </c>
+      <c r="N7" s="74">
+        <f>K7*1721.95</f>
+        <v/>
+      </c>
+      <c r="O7" s="75" t="inlineStr">
+        <is>
+          <t>Se debe el 100%. Precio final sin IVA, con el descuento de $411.800 ya aplicado. Las gorras las provee el cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>TEXTIL RYU S.R.L.</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Gorra Flex unicolor/bicolor</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>2601009</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>20/06</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>2224980</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H8" s="41">
+        <f>F8*(1+N(G8))</f>
+        <v/>
+      </c>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="76">
+        <f>K8*H8/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M8" s="14">
+        <f>K8*0.0</f>
+        <v/>
+      </c>
+      <c r="N8" s="14">
+        <f>K8*0.0</f>
+        <v/>
+      </c>
+      <c r="O8" s="16" t="inlineStr">
+        <is>
+          <t>Pagada al 100% el 25/06. Es la compra de la gorra, distinta del bordado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>LEOTEX</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Lanyard premium doble raso 25 mm</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>1.360</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>2601013 → 2601018</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>20/06 → 16/08</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>2070600</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H9" s="32">
+        <f>F9*(1+N(G9))</f>
+        <v/>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>1632.2</v>
+      </c>
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="65">
+        <f>K9*H9/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M9" s="34">
+        <f>K9*816.1</f>
+        <v/>
+      </c>
+      <c r="N9" s="34">
+        <f>K9*1632.2</f>
+        <v/>
+      </c>
+      <c r="O9" s="36" t="inlineStr">
+        <is>
+          <t>A CONFIRMAR: la carpeta se llama "Nuevo pago - 50%" pero la factura 2601018 viene por el total, igual que la original. El master registraba un saldo de US$850.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>DERQUI IMPRESIONES</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Grafica oficial CMC — Argentina</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>2601014</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>20/06 → 16/08</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>3025260</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H10" s="32">
+        <f>F10*(1+N(G10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>2384.73</v>
+      </c>
+      <c r="J10" s="29" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="K10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="65">
+        <f>K10*H10/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M10" s="34">
+        <f>K10*1192.37</f>
+        <v/>
+      </c>
+      <c r="N10" s="34">
+        <f>K10*2384.73</f>
+        <v/>
+      </c>
+      <c r="O10" s="36" t="inlineStr">
+        <is>
+          <t>A CONFIRMAR: la reemision del 16/08 viene por el total. El master registraba un saldo de US$1.839 al 13/09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>DERQUI IMPRESIONES</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>Grafica oficial CMC — Uruguay</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>2601015</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>20/06 → 16/08</t>
+        </is>
+      </c>
+      <c r="F11" s="50" t="n">
+        <v>1564626</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H11" s="51">
+        <f>F11*(1+N(G11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>1233.35</v>
+      </c>
+      <c r="J11" s="44" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="K11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="77">
+        <f>K11*H11/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M11" s="47">
+        <f>K11*616.68</f>
+        <v/>
+      </c>
+      <c r="N11" s="47">
+        <f>K11*1233.35</f>
+        <v/>
+      </c>
+      <c r="O11" s="49" t="inlineStr">
+        <is>
+          <t>NO ES DE ARGENTINA. En la hoja PAGOS del master estaba cargada con pais = Argentina: es el monto que inflaba el total argentino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Blocko</t>
+        </is>
+      </c>
+      <c r="B12" s="44" t="inlineStr">
+        <is>
+          <t>Cintas portacredencial (alternativa descartada)</t>
+        </is>
+      </c>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>1.300</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>presupuesto 09/06</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>09/06</t>
+        </is>
+      </c>
+      <c r="F12" s="50" t="n">
+        <v>1749800</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H12" s="51">
+        <f>F12*(1+N(G12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="45" t="n"/>
+      <c r="J12" s="44" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="K12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="77">
+        <f>K12*H12/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="M12" s="47">
+        <f>K12*0.0</f>
+        <v/>
+      </c>
+      <c r="N12" s="47">
+        <f>K12*0.0</f>
+        <v/>
+      </c>
+      <c r="O12" s="49" t="inlineStr">
+        <is>
+          <t>Es el mismo item que los lanyards de LEOTEX, que ya esta contratado. Estaba sumando dos veces en la version anterior de esta planilla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="78" t="inlineStr">
+        <is>
+          <t>TOTAL IMPUTADO A ARGENTINA</t>
+        </is>
+      </c>
+      <c r="L13" s="79">
+        <f>SUM(L5:L12)</f>
+        <v/>
+      </c>
+      <c r="M13" s="79">
+        <f>SUM(M5:M12)</f>
+        <v/>
+      </c>
+      <c r="N13" s="79">
+        <f>SUM(N5:N12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="80" t="inlineStr">
+        <is>
+          <t>CÓMO LEER LOS COLORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="81" t="inlineStr">
+        <is>
+          <t>Verde — pagado al 100%: la compra de las gorras de Textil Ryu.</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="82" t="n"/>
+      <c r="D16" s="82" t="n"/>
+      <c r="E16" s="82" t="n"/>
+      <c r="F16" s="83" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="84" t="inlineStr">
+        <is>
+          <t>Amarillo — 50% abonado, queda el saldo: pañuelos, lanyards y gráfica de Argentina.</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="82" t="n"/>
+      <c r="F17" s="83" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="85" t="inlineStr">
+        <is>
+          <t>Rojo — sin pagar nada, se debe el 100%: las remeras y el bordado de las gorras.</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="82" t="n"/>
+      <c r="F18" s="83" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="86" t="inlineStr">
+        <is>
+          <t>Gris — no suma al costo de Argentina: la gráfica de Uruguay y la cotización descartada de Blocko.</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="82" t="n"/>
+      <c r="F19" s="83" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="87" t="inlineStr">
+        <is>
+          <t>TRES COSAS QUE HAY QUE CONFIRMAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>1) Lanyards y gráfica de Argentina: las facturas reemitidas en agosto vienen por el TOTAL, pero la carpeta y el master dicen que ya se abonó el 50%. Si las facturas están bien, hay que pagar US$2.008 más de lo que sale por la regla del 50%. Una sola consulta a LEOTEX y a Derqui lo resuelve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2) Pañuelos: son 8.500 unidades compartidas entre Argentina y Uruguay y la factura no las separa. Acá se imputó el 65% a Argentina (5.500 de 8.500, la misma proporción que la gráfica). Si van todos a Argentina, el costo sube US$3.755.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>3) La gráfica de Uruguay (US$1.233) estaba cargada en el master como Argentina. Ya quedó fuera del costo argentino, pero conviene corregirla también en el master para que no se arrastre.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:O4"/>
+  <mergeCells count="7">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A22:O22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3396,144 +4659,196 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Infraestructura de La Rural</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Presupuesto completo: $66.494.708 (US$43.461), con las 5.000 sillas y todo el mobiliario</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Sólo panelería + dirección técnica + guardias: $16.858.366 (US$11.019). El mobiliario se compra aparte.</t>
         </is>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="34">
         <f>(66494708.2-16858366.2)/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Agustina marca ítem por ítem qué se queda. La hoja INFRAESTRUCTURA tiene las 28 líneas del presupuesto para filtrar.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Montaje de las sillas</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>La Rural con las sillas incluidas y armadas</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>FDL Eventos + montaje/acomodación/desmontaje negociado en $900.000</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Con FDL a $31.218.000 más $900.000 de montaje son US$20.992 contra US$27.778 de La Rural. Cerrar el número del montaje y firmar.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Catering — cerrado</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Grupo Ambient: US$13.582 por las dos propuestas</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>La planilla tenía US$33.820 estimados</t>
         </is>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="34">
         <f>13582-33820</f>
         <v/>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>Cerrado. Es la mejor negociación del evento: US$20.238 por debajo de lo presupuestado.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Rubros nuevos sin cotizar</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Ecobaños, marquetería de certificaciones y premios, replanteo de sillas con ingeniero</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Hoy entran en US$0</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Pedir las tres cotizaciones esta semana. Son los últimos huecos que quedan además de vuelos y alojamiento.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Merch — el 50% que falta pagar</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Regla del 50%: quedan US$9.941 por transferir en USDT</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Según las facturas reemitidas en agosto: US$11.949</t>
+        </is>
+      </c>
+      <c r="D9" s="34">
+        <f>11949.25-9940.79</f>
+        <v/>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Las facturas de LEOTEX (lanyards) y Derqui (gráfica ARG) vienen por el total aunque ya se abonó el 50%. Una consulta a cada proveedor cierra la diferencia. Lo urgente igual son las remeras (US$2.781) y el bordado de gorras (US$1.722): esos no tienen nada pagado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Merch — cómo se reparten los pañuelos con Uruguay</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Los 8.500 pañuelos se imputan 65% a Argentina (US$6.973)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Si van todos a Argentina: US$10.728</t>
+        </is>
+      </c>
+      <c r="D10" s="34">
+        <f>0.35*13387500*1.21/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>La factura no separa las unidades por país. Definir el reparto con Uruguay antes de cerrar el número para el CEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Vuelos y alojamiento del equipo</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>No hay ni un mail ni una línea en el sheet. Con 8 personas de equipo interno, es el hueco más grande que queda.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Facturación al exterior</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>FDL Eventos y Vittal no confirmaron si pueden facturar a la empresa de EE.UU.</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Buscar proveedores que sí facturen, o resolver un circuito de pago local</t>
         </is>
       </c>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>Resolverlo antes de firmar: puede trabar los dos contratos.</t>
         </is>
@@ -3544,7 +4859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3632,236 +4947,236 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Infraestructura y mobiliario</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Grupo MET, cotización de mobiliario</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="20" t="n">
         <v>40000000</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="24">
         <f>C5/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Armado de stands + mobiliario, definido por Agustina</t>
         </is>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <v>14183100</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="25" t="n">
         <v>9270</v>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="76">
         <f>D5-G5</f>
         <v/>
       </c>
-      <c r="I5" s="60">
+      <c r="I5" s="88">
         <f>IFERROR(H5/D5,"")</f>
         <v/>
       </c>
-      <c r="J5" s="24" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>La cotización de Grupo MET no está en el correo: dato aportado por Agustina. En el correo sí está el presupuesto de La Rural del 17/08 por $66.494.708 (con las 5.000 sillas adentro).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Sillas del público</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>La Rural: 5.000 sillas imperio bordó, armado incluido</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>42500000</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="24">
         <f>C6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>FDL Eventos 5.500 sillas + montaje, acomodación y desmontaje</t>
         </is>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>32118000</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="24">
         <f>F6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="76">
         <f>D6-G6</f>
         <v/>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="88">
         <f>IFERROR(H6/D6,"")</f>
         <v/>
       </c>
-      <c r="J6" s="24" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>Mail criccio@larural.com.ar 17/08 y mail fdleventos@gmail.com 07/08. El montaje ($900.000) está en negociación.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Entelado</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Primera cotización recibida</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>39000000</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="24">
         <f>C7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>Negociado a la mitad</t>
         </is>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>24500000</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="24">
         <f>F7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="H7" s="59">
+      <c r="H7" s="76">
         <f>D7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="60">
+      <c r="I7" s="88">
         <f>IFERROR(H7/D7,"")</f>
         <v/>
       </c>
-      <c r="J7" s="24" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Dato aportado por Agustina; la cotización inicial no está en el correo.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Catering</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Primera propuesta de Grupo Ambient</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>30000000</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="24">
         <f>C8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>600 lunchbox VIP + desayuno, almuerzo y cena para 150 personas</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="23" t="n">
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="25" t="n">
         <v>14569</v>
       </c>
-      <c r="H8" s="59">
+      <c r="H8" s="76">
         <f>D8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="60">
+      <c r="I8" s="88">
         <f>IFERROR(H8/D8,"")</f>
         <v/>
       </c>
-      <c r="J8" s="24" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>Cierre informado por Agustina. En el correo está la propuesta de AmbientHouse del 16/06 a $28.500 + IVA por persona por día con base mínima de 480.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Vallado del público</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Presupuestado en la hoja de Argentina</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="23" t="n">
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="25" t="n">
         <v>1250</v>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>500 vallas bonificadas por el proveedor de técnica</t>
         </is>
       </c>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="23" t="n">
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="76">
         <f>D9-G9</f>
         <v/>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="88">
         <f>IFERROR(H9/D9,"")</f>
         <v/>
       </c>
-      <c r="J9" s="24" t="inlineStr">
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>Negociación de Agustina. Además bonifican los efectos especiales, que no estaban valorizados.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>AHORRO TOTAL</t>
         </is>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="89">
         <f>SUM(D5:D9)</f>
         <v/>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="89">
         <f>SUM(G5:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="89">
         <f>SUM(H5:H9)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="87" t="inlineStr">
         <is>
           <t>TÉCNICA — la comparación no es directa</t>
         </is>
@@ -3921,7 +5236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3997,1014 +5312,1014 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="B5" s="64" t="n"/>
-      <c r="C5" s="64" t="n"/>
-      <c r="D5" s="64" t="n"/>
-      <c r="E5" s="64" t="n"/>
-      <c r="F5" s="64" t="n"/>
-      <c r="G5" s="64" t="n"/>
-      <c r="H5" s="64" t="n"/>
+      <c r="B5" s="91" t="n"/>
+      <c r="C5" s="91" t="n"/>
+      <c r="D5" s="91" t="n"/>
+      <c r="E5" s="91" t="n"/>
+      <c r="F5" s="91" t="n"/>
+      <c r="G5" s="91" t="n"/>
+      <c r="H5" s="91" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="n">
+      <c r="A6" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="92" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C6" s="66" t="inlineStr">
+      <c r="C6" s="93" t="inlineStr">
         <is>
           <t>Oficina de producción — 25 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D6" s="67" t="n">
+      <c r="D6" s="94" t="n">
         <v>1314575</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="61">
         <f>D6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F6" s="68" t="inlineStr">
+      <c r="F6" s="95" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G6" s="69">
+      <c r="G6" s="96">
         <f>IF(F6="SÍ",D6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="65" t="inlineStr"/>
+      <c r="H6" s="92" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="65" t="n">
+      <c r="A7" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="92" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C7" s="66" t="inlineStr">
+      <c r="C7" s="93" t="inlineStr">
         <is>
           <t>Sala de staff — 100 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D7" s="67" t="n">
+      <c r="D7" s="94" t="n">
         <v>5258300</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="61">
         <f>D7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F7" s="68" t="inlineStr">
+      <c r="F7" s="95" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G7" s="69">
+      <c r="G7" s="96">
         <f>IF(F7="SÍ",D7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="65" t="inlineStr"/>
+      <c r="H7" s="92" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="65" t="n">
+      <c r="A8" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="92" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C8" s="66" t="inlineStr">
+      <c r="C8" s="93" t="inlineStr">
         <is>
           <t>Depósito 8×8 para las 2.500 barras — 64 m²</t>
         </is>
       </c>
-      <c r="D8" s="67" t="n">
+      <c r="D8" s="94" t="n">
         <v>3365312</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="61">
         <f>D8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="68" t="inlineStr">
+      <c r="F8" s="95" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G8" s="69">
+      <c r="G8" s="96">
         <f>IF(F8="SÍ",D8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="65" t="inlineStr">
+      <c r="H8" s="92" t="inlineStr">
         <is>
           <t>Depósito para las 2.500 barras de la dinámica.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="inlineStr">
+      <c r="A9" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · oficina de producción</t>
         </is>
       </c>
-      <c r="B9" s="64" t="n"/>
-      <c r="C9" s="64" t="n"/>
-      <c r="D9" s="64" t="n"/>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="64" t="n"/>
-      <c r="G9" s="64" t="n"/>
-      <c r="H9" s="64" t="n"/>
+      <c r="B9" s="91" t="n"/>
+      <c r="C9" s="91" t="n"/>
+      <c r="D9" s="91" t="n"/>
+      <c r="E9" s="91" t="n"/>
+      <c r="F9" s="91" t="n"/>
+      <c r="G9" s="91" t="n"/>
+      <c r="H9" s="91" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="65" t="n">
+      <c r="A10" s="92" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="92" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
+      <c r="C10" s="93" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×2</t>
         </is>
       </c>
-      <c r="D10" s="67" t="n">
+      <c r="D10" s="94" t="n">
         <v>236000</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="61">
         <f>D10/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="68" t="inlineStr">
+      <c r="F10" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G10" s="69">
+      <c r="G10" s="96">
         <f>IF(F10="SÍ",D10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="65" t="inlineStr"/>
+      <c r="H10" s="92" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="65" t="n">
+      <c r="A11" s="92" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="92" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C11" s="66" t="inlineStr">
+      <c r="C11" s="93" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×10</t>
         </is>
       </c>
-      <c r="D11" s="67" t="n">
+      <c r="D11" s="94" t="n">
         <v>85000</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="61">
         <f>D11/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="68" t="inlineStr">
+      <c r="F11" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G11" s="69">
+      <c r="G11" s="96">
         <f>IF(F11="SÍ",D11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="65" t="inlineStr"/>
+      <c r="H11" s="92" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="65" t="n">
+      <c r="A12" s="92" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="92" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C12" s="66" t="inlineStr">
+      <c r="C12" s="93" t="inlineStr">
         <is>
           <t>Sillón Valencia 2C ×2</t>
         </is>
       </c>
-      <c r="D12" s="67" t="n">
+      <c r="D12" s="94" t="n">
         <v>254000</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="61">
         <f>D12/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="68" t="inlineStr">
+      <c r="F12" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G12" s="69">
+      <c r="G12" s="96">
         <f>IF(F12="SÍ",D12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="65" t="inlineStr"/>
+      <c r="H12" s="92" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="65" t="n">
+      <c r="A13" s="92" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="65" t="inlineStr">
+      <c r="B13" s="92" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C13" s="66" t="inlineStr">
+      <c r="C13" s="93" t="inlineStr">
         <is>
           <t>Sillón BRNO ×2</t>
         </is>
       </c>
-      <c r="D13" s="67" t="n">
+      <c r="D13" s="94" t="n">
         <v>160000</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="61">
         <f>D13/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="68" t="inlineStr">
+      <c r="F13" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="69">
+      <c r="G13" s="96">
         <f>IF(F13="SÍ",D13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="65" t="inlineStr"/>
+      <c r="H13" s="92" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="n">
+      <c r="A14" s="92" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="92" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C14" s="66" t="inlineStr">
+      <c r="C14" s="93" t="inlineStr">
         <is>
           <t>Mesa ratona ×1</t>
         </is>
       </c>
-      <c r="D14" s="67" t="n">
+      <c r="D14" s="94" t="n">
         <v>118000</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="61">
         <f>D14/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="68" t="inlineStr">
+      <c r="F14" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="69">
+      <c r="G14" s="96">
         <f>IF(F14="SÍ",D14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="65" t="inlineStr"/>
+      <c r="H14" s="92" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="65" t="n">
+      <c r="A15" s="92" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="65" t="inlineStr">
+      <c r="B15" s="92" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C15" s="66" t="inlineStr">
+      <c r="C15" s="93" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D15" s="67" t="n">
+      <c r="D15" s="94" t="n">
         <v>40000</v>
       </c>
-      <c r="E15" s="55">
+      <c r="E15" s="61">
         <f>D15/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="68" t="inlineStr">
+      <c r="F15" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="96">
         <f>IF(F15="SÍ",D15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="65" t="inlineStr"/>
+      <c r="H15" s="92" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="65" t="n">
+      <c r="A16" s="92" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="65" t="inlineStr">
+      <c r="B16" s="92" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C16" s="66" t="inlineStr">
+      <c r="C16" s="93" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D16" s="67" t="n">
+      <c r="D16" s="94" t="n">
         <v>56300</v>
       </c>
-      <c r="E16" s="55">
+      <c r="E16" s="61">
         <f>D16/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="68" t="inlineStr">
+      <c r="F16" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G16" s="69">
+      <c r="G16" s="96">
         <f>IF(F16="SÍ",D16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="65" t="inlineStr"/>
+      <c r="H16" s="92" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="63" t="inlineStr">
+      <c r="A17" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala de staff</t>
         </is>
       </c>
-      <c r="B17" s="64" t="n"/>
-      <c r="C17" s="64" t="n"/>
-      <c r="D17" s="64" t="n"/>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="64" t="n"/>
-      <c r="G17" s="64" t="n"/>
-      <c r="H17" s="64" t="n"/>
+      <c r="B17" s="91" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="91" t="n"/>
+      <c r="E17" s="91" t="n"/>
+      <c r="F17" s="91" t="n"/>
+      <c r="G17" s="91" t="n"/>
+      <c r="H17" s="91" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="65" t="n">
+      <c r="A18" s="92" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="65" t="inlineStr">
+      <c r="B18" s="92" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C18" s="66" t="inlineStr">
+      <c r="C18" s="93" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×5</t>
         </is>
       </c>
-      <c r="D18" s="67" t="n">
+      <c r="D18" s="94" t="n">
         <v>590000</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="61">
         <f>D18/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="68" t="inlineStr">
+      <c r="F18" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G18" s="69">
+      <c r="G18" s="96">
         <f>IF(F18="SÍ",D18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="65" t="inlineStr"/>
+      <c r="H18" s="92" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="65" t="n">
+      <c r="A19" s="92" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="65" t="inlineStr">
+      <c r="B19" s="92" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C19" s="66" t="inlineStr">
+      <c r="C19" s="93" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×40</t>
         </is>
       </c>
-      <c r="D19" s="67" t="n">
+      <c r="D19" s="94" t="n">
         <v>340000</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="61">
         <f>D19/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="68" t="inlineStr">
+      <c r="F19" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G19" s="69">
+      <c r="G19" s="96">
         <f>IF(F19="SÍ",D19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="65" t="inlineStr"/>
+      <c r="H19" s="92" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="65" t="n">
+      <c r="A20" s="92" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="65" t="inlineStr">
+      <c r="B20" s="92" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C20" s="66" t="inlineStr">
+      <c r="C20" s="93" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D20" s="67" t="n">
+      <c r="D20" s="94" t="n">
         <v>40000</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="61">
         <f>D20/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="68" t="inlineStr">
+      <c r="F20" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="69">
+      <c r="G20" s="96">
         <f>IF(F20="SÍ",D20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="65" t="inlineStr"/>
+      <c r="H20" s="92" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="65" t="n">
+      <c r="A21" s="92" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="65" t="inlineStr">
+      <c r="B21" s="92" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C21" s="66" t="inlineStr">
+      <c r="C21" s="93" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D21" s="67" t="n">
+      <c r="D21" s="94" t="n">
         <v>56300</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="61">
         <f>D21/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F21" s="68" t="inlineStr">
+      <c r="F21" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="69">
+      <c r="G21" s="96">
         <f>IF(F21="SÍ",D21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="65" t="inlineStr"/>
+      <c r="H21" s="92" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="63" t="inlineStr">
+      <c r="A22" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala principal</t>
         </is>
       </c>
-      <c r="B22" s="64" t="n"/>
-      <c r="C22" s="64" t="n"/>
-      <c r="D22" s="64" t="n"/>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="64" t="n"/>
-      <c r="G22" s="64" t="n"/>
-      <c r="H22" s="64" t="n"/>
+      <c r="B22" s="91" t="n"/>
+      <c r="C22" s="91" t="n"/>
+      <c r="D22" s="91" t="n"/>
+      <c r="E22" s="91" t="n"/>
+      <c r="F22" s="91" t="n"/>
+      <c r="G22" s="91" t="n"/>
+      <c r="H22" s="91" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="65" t="n">
+      <c r="A23" s="92" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="65" t="inlineStr">
+      <c r="B23" s="92" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C23" s="66" t="inlineStr">
+      <c r="C23" s="93" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×5.000</t>
         </is>
       </c>
-      <c r="D23" s="67" t="n">
+      <c r="D23" s="94" t="n">
         <v>42500000</v>
       </c>
-      <c r="E23" s="55">
+      <c r="E23" s="61">
         <f>D23/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F23" s="68" t="inlineStr">
+      <c r="F23" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G23" s="69">
+      <c r="G23" s="96">
         <f>IF(F23="SÍ",D23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="65" t="inlineStr">
+      <c r="H23" s="92" t="inlineStr">
         <is>
           <t>Reemplazadas por las 5.500 sillas de FDL Eventos.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="65" t="n">
+      <c r="A24" s="92" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="65" t="inlineStr">
+      <c r="B24" s="92" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C24" s="66" t="inlineStr">
+      <c r="C24" s="93" t="inlineStr">
         <is>
           <t>Mesa 1,80 × 0,90 ×40</t>
         </is>
       </c>
-      <c r="D24" s="67" t="n">
+      <c r="D24" s="94" t="n">
         <v>2500000</v>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="61">
         <f>D24/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F24" s="68" t="inlineStr">
+      <c r="F24" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G24" s="69">
+      <c r="G24" s="96">
         <f>IF(F24="SÍ",D24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="65" t="inlineStr"/>
+      <c r="H24" s="92" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="65" t="n">
+      <c r="A25" s="92" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="65" t="inlineStr">
+      <c r="B25" s="92" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C25" s="66" t="inlineStr">
+      <c r="C25" s="93" t="inlineStr">
         <is>
           <t>Mantel ×40</t>
         </is>
       </c>
-      <c r="D25" s="67" t="n">
+      <c r="D25" s="94" t="n">
         <v>900000</v>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="61">
         <f>D25/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F25" s="68" t="inlineStr">
+      <c r="F25" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G25" s="69">
+      <c r="G25" s="96">
         <f>IF(F25="SÍ",D25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="65" t="inlineStr"/>
+      <c r="H25" s="92" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="65" t="n">
+      <c r="A26" s="92" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="65" t="inlineStr">
+      <c r="B26" s="92" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C26" s="66" t="inlineStr">
+      <c r="C26" s="93" t="inlineStr">
         <is>
           <t>Mantel redondo ×8</t>
         </is>
       </c>
-      <c r="D26" s="67" t="n">
+      <c r="D26" s="94" t="n">
         <v>256000</v>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="61">
         <f>D26/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F26" s="68" t="inlineStr">
+      <c r="F26" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G26" s="69">
+      <c r="G26" s="96">
         <f>IF(F26="SÍ",D26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="65" t="inlineStr"/>
+      <c r="H26" s="92" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="63" t="inlineStr">
+      <c r="A27" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · camarín de speakers</t>
         </is>
       </c>
-      <c r="B27" s="64" t="n"/>
-      <c r="C27" s="64" t="n"/>
-      <c r="D27" s="64" t="n"/>
-      <c r="E27" s="64" t="n"/>
-      <c r="F27" s="64" t="n"/>
-      <c r="G27" s="64" t="n"/>
-      <c r="H27" s="64" t="n"/>
+      <c r="B27" s="91" t="n"/>
+      <c r="C27" s="91" t="n"/>
+      <c r="D27" s="91" t="n"/>
+      <c r="E27" s="91" t="n"/>
+      <c r="F27" s="91" t="n"/>
+      <c r="G27" s="91" t="n"/>
+      <c r="H27" s="91" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="65" t="n">
+      <c r="A28" s="92" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="65" t="inlineStr">
+      <c r="B28" s="92" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C28" s="66" t="inlineStr">
+      <c r="C28" s="93" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×1</t>
         </is>
       </c>
-      <c r="D28" s="67" t="n">
+      <c r="D28" s="94" t="n">
         <v>118000</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="61">
         <f>D28/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F28" s="68" t="inlineStr">
+      <c r="F28" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G28" s="69">
+      <c r="G28" s="96">
         <f>IF(F28="SÍ",D28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="65" t="inlineStr"/>
+      <c r="H28" s="92" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="65" t="n">
+      <c r="A29" s="92" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="65" t="inlineStr">
+      <c r="B29" s="92" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C29" s="66" t="inlineStr">
+      <c r="C29" s="93" t="inlineStr">
         <is>
           <t>Espejo ×1</t>
         </is>
       </c>
-      <c r="D29" s="67" t="n">
+      <c r="D29" s="94" t="n">
         <v>79500</v>
       </c>
-      <c r="E29" s="55">
+      <c r="E29" s="61">
         <f>D29/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F29" s="68" t="inlineStr">
+      <c r="F29" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G29" s="69">
+      <c r="G29" s="96">
         <f>IF(F29="SÍ",D29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="65" t="inlineStr"/>
+      <c r="H29" s="92" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="65" t="n">
+      <c r="A30" s="92" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="65" t="inlineStr">
+      <c r="B30" s="92" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C30" s="66" t="inlineStr">
+      <c r="C30" s="93" t="inlineStr">
         <is>
           <t>Juego de living (sillones + mesa ratona)</t>
         </is>
       </c>
-      <c r="D30" s="67" t="n">
+      <c r="D30" s="94" t="n">
         <v>1103642</v>
       </c>
-      <c r="E30" s="55">
+      <c r="E30" s="61">
         <f>D30/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F30" s="68" t="inlineStr">
+      <c r="F30" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G30" s="69">
+      <c r="G30" s="96">
         <f>IF(F30="SÍ",D30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="65" t="inlineStr">
+      <c r="H30" s="92" t="inlineStr">
         <is>
           <t>El mobiliario "más fino" del camarín: candidato a contratárselo a La Rural.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="65" t="n">
+      <c r="A31" s="92" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="65" t="inlineStr">
+      <c r="B31" s="92" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C31" s="66" t="inlineStr">
+      <c r="C31" s="93" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D31" s="67" t="n">
+      <c r="D31" s="94" t="n">
         <v>40000</v>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="61">
         <f>D31/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F31" s="68" t="inlineStr">
+      <c r="F31" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G31" s="69">
+      <c r="G31" s="96">
         <f>IF(F31="SÍ",D31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="65" t="inlineStr"/>
+      <c r="H31" s="92" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="65" t="n">
+      <c r="A32" s="92" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="65" t="inlineStr">
+      <c r="B32" s="92" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C32" s="66" t="inlineStr">
+      <c r="C32" s="93" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D32" s="67" t="n">
+      <c r="D32" s="94" t="n">
         <v>56300</v>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="61">
         <f>D32/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F32" s="68" t="inlineStr">
+      <c r="F32" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G32" s="69">
+      <c r="G32" s="96">
         <f>IF(F32="SÍ",D32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="65" t="inlineStr"/>
+      <c r="H32" s="92" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="inlineStr">
+      <c r="A33" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · escenario y técnica</t>
         </is>
       </c>
-      <c r="B33" s="64" t="n"/>
-      <c r="C33" s="64" t="n"/>
-      <c r="D33" s="64" t="n"/>
-      <c r="E33" s="64" t="n"/>
-      <c r="F33" s="64" t="n"/>
-      <c r="G33" s="64" t="n"/>
-      <c r="H33" s="64" t="n"/>
+      <c r="B33" s="91" t="n"/>
+      <c r="C33" s="91" t="n"/>
+      <c r="D33" s="91" t="n"/>
+      <c r="E33" s="91" t="n"/>
+      <c r="F33" s="91" t="n"/>
+      <c r="G33" s="91" t="n"/>
+      <c r="H33" s="91" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="65" t="n">
+      <c r="A34" s="92" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="65" t="inlineStr">
+      <c r="B34" s="92" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C34" s="66" t="inlineStr">
+      <c r="C34" s="93" t="inlineStr">
         <is>
           <t>Mesa cocktail alta (escenario) ×1</t>
         </is>
       </c>
-      <c r="D34" s="67" t="n">
+      <c r="D34" s="94" t="n">
         <v>45000</v>
       </c>
-      <c r="E34" s="55">
+      <c r="E34" s="61">
         <f>D34/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F34" s="68" t="inlineStr">
+      <c r="F34" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G34" s="69">
+      <c r="G34" s="96">
         <f>IF(F34="SÍ",D34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="65" t="inlineStr"/>
+      <c r="H34" s="92" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="65" t="n">
+      <c r="A35" s="92" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="65" t="inlineStr">
+      <c r="B35" s="92" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C35" s="66" t="inlineStr">
+      <c r="C35" s="93" t="inlineStr">
         <is>
           <t>Mesa alta para DJ ×1</t>
         </is>
       </c>
-      <c r="D35" s="67" t="n">
+      <c r="D35" s="94" t="n">
         <v>62300</v>
       </c>
-      <c r="E35" s="55">
+      <c r="E35" s="61">
         <f>D35/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F35" s="68" t="inlineStr">
+      <c r="F35" s="95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G35" s="69">
+      <c r="G35" s="96">
         <f>IF(F35="SÍ",D35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="65" t="inlineStr"/>
+      <c r="H35" s="92" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="63" t="inlineStr">
+      <c r="A36" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">  GENERALES</t>
         </is>
       </c>
-      <c r="B36" s="64" t="n"/>
-      <c r="C36" s="64" t="n"/>
-      <c r="D36" s="64" t="n"/>
-      <c r="E36" s="64" t="n"/>
-      <c r="F36" s="64" t="n"/>
-      <c r="G36" s="64" t="n"/>
-      <c r="H36" s="64" t="n"/>
+      <c r="B36" s="91" t="n"/>
+      <c r="C36" s="91" t="n"/>
+      <c r="D36" s="91" t="n"/>
+      <c r="E36" s="91" t="n"/>
+      <c r="F36" s="91" t="n"/>
+      <c r="G36" s="91" t="n"/>
+      <c r="H36" s="91" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="65" t="n">
+      <c r="A37" s="92" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="65" t="inlineStr">
+      <c r="B37" s="92" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C37" s="66" t="inlineStr">
+      <c r="C37" s="93" t="inlineStr">
         <is>
           <t>Dirección técnica de todo el evento + replanteo</t>
         </is>
       </c>
-      <c r="D37" s="67" t="n">
+      <c r="D37" s="94" t="n">
         <v>5149179.2</v>
       </c>
-      <c r="E37" s="55">
+      <c r="E37" s="61">
         <f>D37/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F37" s="68" t="inlineStr">
+      <c r="F37" s="95" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G37" s="69">
+      <c r="G37" s="96">
         <f>IF(F37="SÍ",D37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="65" t="inlineStr">
+      <c r="H37" s="92" t="inlineStr">
         <is>
           <t>Ojo: el replanteo de sillas va aparte, con ingeniero propio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="65" t="n">
+      <c r="A38" s="92" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="65" t="inlineStr">
+      <c r="B38" s="92" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C38" s="66" t="inlineStr">
+      <c r="C38" s="93" t="inlineStr">
         <is>
           <t>Guardia eléctrica × 2 días</t>
         </is>
       </c>
-      <c r="D38" s="67" t="n">
+      <c r="D38" s="94" t="n">
         <v>865800</v>
       </c>
-      <c r="E38" s="55">
+      <c r="E38" s="61">
         <f>D38/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F38" s="68" t="inlineStr">
+      <c r="F38" s="95" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G38" s="69">
+      <c r="G38" s="96">
         <f>IF(F38="SÍ",D38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="65" t="inlineStr"/>
+      <c r="H38" s="92" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="65" t="n">
+      <c r="A39" s="92" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="65" t="inlineStr">
+      <c r="B39" s="92" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C39" s="66" t="inlineStr">
+      <c r="C39" s="93" t="inlineStr">
         <is>
           <t>Guardia técnica × 2 días</t>
         </is>
       </c>
-      <c r="D39" s="67" t="n">
+      <c r="D39" s="94" t="n">
         <v>905200</v>
       </c>
-      <c r="E39" s="55">
+      <c r="E39" s="61">
         <f>D39/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F39" s="68" t="inlineStr">
+      <c r="F39" s="95" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G39" s="69">
+      <c r="G39" s="96">
         <f>IF(F39="SÍ",D39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="65" t="inlineStr"/>
+      <c r="H39" s="92" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="3" t="inlineStr">
@@ -5012,11 +6327,11 @@
           <t>TOTAL del presupuesto de La Rural</t>
         </is>
       </c>
-      <c r="D41" s="70">
+      <c r="D41" s="97">
         <f>SUM(D6:D39)</f>
         <v/>
       </c>
-      <c r="E41" s="36">
+      <c r="E41" s="39">
         <f>D41/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -5027,11 +6342,11 @@
           <t>Lo que se queda (marcado SÍ)</t>
         </is>
       </c>
-      <c r="D42" s="71">
+      <c r="D42" s="98">
         <f>SUM(G6:G39)</f>
         <v/>
       </c>
-      <c r="E42" s="72">
+      <c r="E42" s="99">
         <f>D42/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -5042,11 +6357,11 @@
           <t>Lo que se saca (marcado NO)</t>
         </is>
       </c>
-      <c r="D43" s="73">
+      <c r="D43" s="100">
         <f>D41-D42</f>
         <v/>
       </c>
-      <c r="E43" s="74">
+      <c r="E43" s="101">
         <f>D43/TABLERO!$C$4</f>
         <v/>
       </c>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -13,7 +13,8 @@
     <sheet name="MERCH" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="DECISIONES" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="AHORROS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="INFRAESTRUCTURA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="COTIZACIONES TÉCNICA" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="INFRAESTRUCTURA" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COSTOS UNIFICADOS'!$A$4:$M$4</definedName>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;(&quot;$&quot;#,##0);-"/>
     <numFmt numFmtId="167" formatCode="&quot;US$&quot;#,##0;(&quot;US$&quot;#,##0);-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,6 +110,12 @@
       <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -230,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -435,7 +442,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4865,7 +4885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5041,11 +5061,11 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Primera cotización recibida</t>
+          <t>Primer presupuesto de Grupo MET</t>
         </is>
       </c>
       <c r="C7" s="20" t="n">
-        <v>39000000</v>
+        <v>40000000</v>
       </c>
       <c r="D7" s="24">
         <f>C7/TABLERO!$C$4</f>
@@ -5053,7 +5073,7 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>Negociado a la mitad</t>
+          <t>Negociado a poco más de la mitad</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
@@ -5073,7 +5093,7 @@
       </c>
       <c r="J7" s="26" t="inlineStr">
         <is>
-          <t>Dato aportado por Agustina; la cotización inicial no está en el correo.</t>
+          <t>Dato aportado por Agustina: ni el presupuesto inicial ni el cierre están en el correo. OJO: primero dijo $24.500.000 (que es el número cargado, y el que da los US$16.225 que ella misma usa) y después $25.500.000. Confirmar cuál es antes de firmar el informe.</t>
         </is>
       </c>
     </row>
@@ -5185,49 +5205,103 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Se cerró con Grupo MET en US$60.000 (unos $91.800.000 al dólar de referencia), con todos los agregados que se fueron sumando después de la visita al predio.</t>
+          <t>Se pidió cotización de técnica a NUEVE empresas el 13 y 14 de junio. Respondieron seis con número. El detalle completo está en la hoja COTIZACIONES TÉCNICA.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Las otras cotizaciones fueron sobre el pliego base, que según Agustina no cubría lo que necesita el pabellón. Por eso no se pueden restar sin más:</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Sound-Light (16/06): no se pudo abrir el PDF, el mail pesa 33 MB. En el mail del 19/06 se les dice que las otras cotizaciones son "prácticamente la mitad", así que estaba cerca de los $100.000.000.</t>
+          <t xml:space="preserve">   · Sound-Light (16/06): el PDF no se pudo abrir, el mail pesa 33 MB. El mail del 19/06 les dice que las otras estaban "prácticamente la mitad", lo que lo ubica por encima de los $100.000.000.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 2MG (24/06): $53.655.470, con descuento especial $45.000.000 + IVA. Con los adicionales de iluminación y estructura llega a unos $78.000.000.</t>
+          <t xml:space="preserve">   · Bonetto (17/06): $94.936.000 — sonido e iluminación $69.736.000, LED $20.720.000, CCTV $4.480.000. Grúas y efectos aparte (la chispa fría la cobra POR MINUTO).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Validez de 10 días, vencida.</t>
+          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Pero cotiza 40 m² de LED cuando el rider pide 65, y deja afuera grúas y energía. Vencida.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · VMG (29/06): $12.625.000 + IVA, sólo las pantallas LED de 65 m².</t>
+          <t xml:space="preserve">   · 2MG (24/06): $45.000.000 con descuento + IVA = $54.450.000, más $19.202.700 de adicionales. Sonido más liviano, cotizado para "2000 / 5000 pax".</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Para poder mostrar un ahorro defendible en técnica hace falta el PDF de Grupo MET y el alcance final, para compararlo contra el mismo alcance de los otros tres.</t>
+          <t xml:space="preserve">   · Dixi Group (26/06): $82.000.000 + IVA = $99.220.000 llave en mano, con rigging completo, encomiendas y 4 máquinas de chispa fría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · VMG (29/06): $15.276.250 con IVA, sólo las pantallas LED de 65 m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>POR QUÉ TÉCNICA NO ENTRA EN LA TABLA DE ARRIBA: Grupo MET cerró en US$60.000 ($90.600.000) y con el circuito cerrado el paquete queda cerca de $100.000.000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Eso es prácticamente lo mismo que Dixi llave en mano y menos que Bonetto, pero está POR ENCIMA de 2MG y de Prina. Poner esa diferencia como ahorro no se sostendría</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>delante del CEO, porque los alcances no son iguales: Prina cotizó 38% menos de LED, 2MG un sonido más chico, y Grupo MET incluye lo que se agregó tras la visita al predio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LO QUE SÍ SE SOSTIENE EN TÉCNICA: las 500 vallas y los efectos especiales van bonificados. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Con los 6 disparos por día que pide el rider, en cualquiera de las otras propuestas eso es plata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>FALTA UNA SOLA COSA para cerrar el ahorro de técnica con un número: el PDF de Grupo MET con el alcance final. Es el único de los siete proveedores sin presupuesto escrito en el correo.</t>
         </is>
       </c>
     </row>
@@ -5237,6 +5311,464 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Las siete propuestas de técnica que llegaron</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Se pidió cotización a nueve empresas entre el 13 y el 14 de junio. Respondieron seis con número; Black-Out y 4A Latam nunca contestaron y una dirección rebotó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Sin IVA</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Con IVA 21%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>USD al dólar de trabajo</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Qué incluye</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Qué queda aparte</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="86" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Sound-Light</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>ventas@sound-light.com.ar (Noelia Escudero)</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="90">
+        <f>IF(E5="","",E5/TABLERO!$C$4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>Técnica integral sobre el pliego base.</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="inlineStr">
+        <is>
+          <t>Sin detalle: no se pudo abrir el adjunto.</t>
+        </is>
+      </c>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>El mail pesa 33 MB y el PDF no se puede extraer desde acá. Lo que sí está documentado es el mail del 19/06 en el que Agustina les dice que las otras cotizaciones estaban "prácticamente la mitad de lo cotizado por ustedes". Sobre las de esa fecha (Bonetto y Prina) eso lo ubica por encima de los $100.000.000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="86" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Bonetto Sonido e Iluminación</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>cristian@bonetto.net</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>94936000</v>
+      </c>
+      <c r="E6" s="22">
+        <f>D6*1.21</f>
+        <v/>
+      </c>
+      <c r="F6" s="91">
+        <f>IF(E6="","",E6/TABLERO!$C$4)</f>
+        <v/>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Sonido e iluminación $69.736.000 · pantallas LED $20.720.000 · CCTV $4.480.000. 16 L-Acoustics Kiva II, 240 LED ST18-15, 322 truss box, consola Yamaha QL5.</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>Grúas (2 autoelevadores tijera x 3 días) $4.480.000 · máquina de humo $300.000 · 2 máquinas de chispa fría $600.000 POR MINUTO · minuto adicional $150.000.</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>Presupuesto PR26-287 V.1. El PDF viene con el texto vectorizado: hubo que renderizarlo a imagen para leerlo. No aclara si los valores llevan IVA. Dice expresamente "NO CONTEMPLA RIDER DE BANDA".</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="86" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Prina</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>valentin.andina@prina.net</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>48885000</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>59150850</v>
+      </c>
+      <c r="F7" s="91">
+        <f>IF(E7="","",E7/TABLERO!$C$4)</f>
+        <v/>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>LED 40 m² $6.700.000 · CCTV 2 cámaras $4.510.000 · sonido (16 Adamson Y10) $10.465.000 · iluminación $12.490.000 · RRHH y logística $14.720.000.</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>Incluye 2 máquinas Sparkular y máquina de humo.</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>OJO CON EL ALCANCE: cotiza 40 m² de LED (6×4 + 2 de 2×4) cuando el rider pide 65 m² (7×5 + 2 de 3×5). No incluye grúas, brazos articulados ni tijeras, ni la generación de energía. Validez de 10 días: vencida desde el 28/06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="86" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2MG</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>rocio.g@2mg.net</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>54450000</v>
+      </c>
+      <c r="F8" s="91">
+        <f>IF(E8="","",E8/TABLERO!$C$4)</f>
+        <v/>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>Sonido, video (LED 65 m², medida correcta), iluminación, CCTV, efectos especiales, RRHH y logística. Total de lista $53.655.470, con descuento especial $45.000.000.</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>Extras de iluminación $10.177.500 · escenario 13×3 m con pasarela $5.692.500. Los dos juntos suman $15.870.000 sin IVA.</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>Incluye certificación de planos por escribano, eléctrico matriculado y autoelevadora, hasta 8 puntos de colgado. El sonido es más liviano que el de los otros (12 gabinetes DVA T8) y el presupuesto dice "2000 / 5000 pax". Validez 15 días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="86" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Dixi Group</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>g.judcovski@dixieventos.com.ar</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>99220000</v>
+      </c>
+      <c r="F9" s="91">
+        <f>IF(E9="","",E9/TABLERO!$C$4)</f>
+        <v/>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Llave en mano: sonido, iluminación (90 par LED, 6 beam, 8 wash), video (LED 65 m²), CCTV y rigging completo (6 puentes de 12 m, 14 aparejos de 1 T, motores).</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>Nada: es llave en mano.</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>Es el alcance más completo de todos. Incluye 4 máquinas de chispa fría con 8 disparos por día, plano general con puntos de colgado firmado por arquitecto, encomienda eléctrica de profesional matriculado y productores generales de técnica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="86" customHeight="1">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>VMG Visual Solutions</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>presupuestos@vmg-web.com</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="n">
+        <v>12625000</v>
+      </c>
+      <c r="E10" s="50" t="n">
+        <v>15276250</v>
+      </c>
+      <c r="F10" s="92">
+        <f>IF(E10="","",E10/TABLERO!$C$4)</f>
+        <v/>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>Sólo pantallas LED: 65 m² (7×5 central + 2 de 3×5), pitch 2.6 indoor blackface, con control, servidor y operador.</t>
+        </is>
+      </c>
+      <c r="H10" s="44" t="inlineStr">
+        <is>
+          <t>Todo lo demás.</t>
+        </is>
+      </c>
+      <c r="I10" s="49" t="inlineStr">
+        <is>
+          <t>NO ES COMPARABLE con las otras: es únicamente video. Sirve para poner precio al renglón de LED. No incluye estructuras de colgado, rigging, tarimas, entelados ni autoelevadores. Recotiza si el dólar salta más de 15%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="86" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Grupo MET — ES EL QUE SE CONTRATÓ</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>sin PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>lalo@somosgrupomet.com</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n">
+        <v>90600000</v>
+      </c>
+      <c r="F11" s="93">
+        <f>IF(E11="","",E11/TABLERO!$C$4)</f>
+        <v/>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Sonido, iluminación, video y LED por US$60.000. Aparte: entelado $24.500.000 y circuito cerrado US$6.209.</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Bonifica 500 vallas y los efectos especiales, que en las otras cotizaciones se pagan.</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>ES EL ÚNICO DE LOS SIETE SIN PRESUPUESTO ESCRITO EN EL CORREO. Se revisó todo el Gmail: en el hilo con Lalo Aizenberg hay ocho idas y vueltas entre el 16 y el 30 de junio y una visita al predio el 30/06, pero nunca llegó un PDF. Lo único que hay es la factura INV-11 de Mercury por US$5.000, pagada el 31/07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="87" t="inlineStr">
+        <is>
+          <t>CÓMO LEER ESTA TABLA — Y POR QUÉ NO SE PUEDE RESTAR SIN MÁS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Los siete números NO cotizan lo mismo, así que la diferencia contra Grupo MET no es un ahorro hasta que se iguale el alcance:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Grupo MET cerró en US$60.000 (unos $90.600.000) por sonido, iluminación, video y LED, con todo lo que se fue agregando después de la visita al predio del 30 de junio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Sumándole el circuito cerrado (US$6.209) el paquete de técnica queda cerca de los $100.000.000, que es prácticamente lo mismo que cotizó Dixi llave en mano ($99.220.000) y por debajo de Bonetto ($114.872.560 más grúas y efectos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · En cambio queda POR ENCIMA de 2MG con descuento ($54.450.000 más $19.202.700 de adicionales = $73.652.700) y de Prina ($59.150.850).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Pero Prina cotizó 40 m² de LED cuando el rider pide 65, y dejó afuera las grúas y la energía; y 2MG cotizó un sonido más liviano, para "2000 / 5000 pax".</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Lo que sí está documentado y se sostiene solo:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Sound-Light quedó afuera por precio, y hay un mail del 19/06 pidiéndoles que revisen porque las otras estaban "prácticamente la mitad".</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Los efectos especiales y las 500 vallas los bonifica Grupo MET. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Se pidieron nueve cotizaciones y se compararon seis. Ese trabajo está entero en el correo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t>PARA CERRAR EL AHORRO DE TÉCNICA FALTA UNA SOLA COSA: el PDF de Grupo MET con el alcance final. Con eso se puede comparar contra el mismo alcance en Dixi, Bonetto, 2MG y Prina, y recién ahí poner un número.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5312,1014 +5844,1014 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="90" t="inlineStr">
+      <c r="A5" s="95" t="inlineStr">
         <is>
           <t xml:space="preserve">  PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="B5" s="91" t="n"/>
-      <c r="C5" s="91" t="n"/>
-      <c r="D5" s="91" t="n"/>
-      <c r="E5" s="91" t="n"/>
-      <c r="F5" s="91" t="n"/>
-      <c r="G5" s="91" t="n"/>
-      <c r="H5" s="91" t="n"/>
+      <c r="B5" s="96" t="n"/>
+      <c r="C5" s="96" t="n"/>
+      <c r="D5" s="96" t="n"/>
+      <c r="E5" s="96" t="n"/>
+      <c r="F5" s="96" t="n"/>
+      <c r="G5" s="96" t="n"/>
+      <c r="H5" s="96" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="92" t="n">
+      <c r="A6" s="97" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="92" t="inlineStr">
+      <c r="B6" s="97" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C6" s="93" t="inlineStr">
+      <c r="C6" s="98" t="inlineStr">
         <is>
           <t>Oficina de producción — 25 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D6" s="94" t="n">
+      <c r="D6" s="99" t="n">
         <v>1314575</v>
       </c>
       <c r="E6" s="61">
         <f>D6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F6" s="95" t="inlineStr">
+      <c r="F6" s="100" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G6" s="96">
+      <c r="G6" s="101">
         <f>IF(F6="SÍ",D6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="92" t="inlineStr"/>
+      <c r="H6" s="97" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="92" t="n">
+      <c r="A7" s="97" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C7" s="93" t="inlineStr">
+      <c r="C7" s="98" t="inlineStr">
         <is>
           <t>Sala de staff — 100 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="99" t="n">
         <v>5258300</v>
       </c>
       <c r="E7" s="61">
         <f>D7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F7" s="95" t="inlineStr">
+      <c r="F7" s="100" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G7" s="96">
+      <c r="G7" s="101">
         <f>IF(F7="SÍ",D7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="92" t="inlineStr"/>
+      <c r="H7" s="97" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="92" t="n">
+      <c r="A8" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="92" t="inlineStr">
+      <c r="B8" s="97" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C8" s="93" t="inlineStr">
+      <c r="C8" s="98" t="inlineStr">
         <is>
           <t>Depósito 8×8 para las 2.500 barras — 64 m²</t>
         </is>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="D8" s="99" t="n">
         <v>3365312</v>
       </c>
       <c r="E8" s="61">
         <f>D8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="95" t="inlineStr">
+      <c r="F8" s="100" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="101">
         <f>IF(F8="SÍ",D8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="92" t="inlineStr">
+      <c r="H8" s="97" t="inlineStr">
         <is>
           <t>Depósito para las 2.500 barras de la dinámica.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="90" t="inlineStr">
+      <c r="A9" s="95" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · oficina de producción</t>
         </is>
       </c>
-      <c r="B9" s="91" t="n"/>
-      <c r="C9" s="91" t="n"/>
-      <c r="D9" s="91" t="n"/>
-      <c r="E9" s="91" t="n"/>
-      <c r="F9" s="91" t="n"/>
-      <c r="G9" s="91" t="n"/>
-      <c r="H9" s="91" t="n"/>
+      <c r="B9" s="96" t="n"/>
+      <c r="C9" s="96" t="n"/>
+      <c r="D9" s="96" t="n"/>
+      <c r="E9" s="96" t="n"/>
+      <c r="F9" s="96" t="n"/>
+      <c r="G9" s="96" t="n"/>
+      <c r="H9" s="96" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="92" t="n">
+      <c r="A10" s="97" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="92" t="inlineStr">
+      <c r="B10" s="97" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C10" s="93" t="inlineStr">
+      <c r="C10" s="98" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×2</t>
         </is>
       </c>
-      <c r="D10" s="94" t="n">
+      <c r="D10" s="99" t="n">
         <v>236000</v>
       </c>
       <c r="E10" s="61">
         <f>D10/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="95" t="inlineStr">
+      <c r="F10" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G10" s="96">
+      <c r="G10" s="101">
         <f>IF(F10="SÍ",D10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="92" t="inlineStr"/>
+      <c r="H10" s="97" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="92" t="n">
+      <c r="A11" s="97" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C11" s="93" t="inlineStr">
+      <c r="C11" s="98" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×10</t>
         </is>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="D11" s="99" t="n">
         <v>85000</v>
       </c>
       <c r="E11" s="61">
         <f>D11/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="95" t="inlineStr">
+      <c r="F11" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G11" s="96">
+      <c r="G11" s="101">
         <f>IF(F11="SÍ",D11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="92" t="inlineStr"/>
+      <c r="H11" s="97" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="92" t="n">
+      <c r="A12" s="97" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="92" t="inlineStr">
+      <c r="B12" s="97" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C12" s="93" t="inlineStr">
+      <c r="C12" s="98" t="inlineStr">
         <is>
           <t>Sillón Valencia 2C ×2</t>
         </is>
       </c>
-      <c r="D12" s="94" t="n">
+      <c r="D12" s="99" t="n">
         <v>254000</v>
       </c>
       <c r="E12" s="61">
         <f>D12/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="95" t="inlineStr">
+      <c r="F12" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G12" s="96">
+      <c r="G12" s="101">
         <f>IF(F12="SÍ",D12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="92" t="inlineStr"/>
+      <c r="H12" s="97" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="92" t="n">
+      <c r="A13" s="97" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="92" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C13" s="93" t="inlineStr">
+      <c r="C13" s="98" t="inlineStr">
         <is>
           <t>Sillón BRNO ×2</t>
         </is>
       </c>
-      <c r="D13" s="94" t="n">
+      <c r="D13" s="99" t="n">
         <v>160000</v>
       </c>
       <c r="E13" s="61">
         <f>D13/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="95" t="inlineStr">
+      <c r="F13" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="96">
+      <c r="G13" s="101">
         <f>IF(F13="SÍ",D13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="92" t="inlineStr"/>
+      <c r="H13" s="97" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="92" t="n">
+      <c r="A14" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="92" t="inlineStr">
+      <c r="B14" s="97" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C14" s="93" t="inlineStr">
+      <c r="C14" s="98" t="inlineStr">
         <is>
           <t>Mesa ratona ×1</t>
         </is>
       </c>
-      <c r="D14" s="94" t="n">
+      <c r="D14" s="99" t="n">
         <v>118000</v>
       </c>
       <c r="E14" s="61">
         <f>D14/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="95" t="inlineStr">
+      <c r="F14" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="96">
+      <c r="G14" s="101">
         <f>IF(F14="SÍ",D14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="92" t="inlineStr"/>
+      <c r="H14" s="97" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="92" t="n">
+      <c r="A15" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="92" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C15" s="93" t="inlineStr">
+      <c r="C15" s="98" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D15" s="94" t="n">
+      <c r="D15" s="99" t="n">
         <v>40000</v>
       </c>
       <c r="E15" s="61">
         <f>D15/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="95" t="inlineStr">
+      <c r="F15" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G15" s="96">
+      <c r="G15" s="101">
         <f>IF(F15="SÍ",D15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="92" t="inlineStr"/>
+      <c r="H15" s="97" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="92" t="n">
+      <c r="A16" s="97" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="92" t="inlineStr">
+      <c r="B16" s="97" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C16" s="93" t="inlineStr">
+      <c r="C16" s="98" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D16" s="94" t="n">
+      <c r="D16" s="99" t="n">
         <v>56300</v>
       </c>
       <c r="E16" s="61">
         <f>D16/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="95" t="inlineStr">
+      <c r="F16" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G16" s="96">
+      <c r="G16" s="101">
         <f>IF(F16="SÍ",D16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="92" t="inlineStr"/>
+      <c r="H16" s="97" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="90" t="inlineStr">
+      <c r="A17" s="95" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala de staff</t>
         </is>
       </c>
-      <c r="B17" s="91" t="n"/>
-      <c r="C17" s="91" t="n"/>
-      <c r="D17" s="91" t="n"/>
-      <c r="E17" s="91" t="n"/>
-      <c r="F17" s="91" t="n"/>
-      <c r="G17" s="91" t="n"/>
-      <c r="H17" s="91" t="n"/>
+      <c r="B17" s="96" t="n"/>
+      <c r="C17" s="96" t="n"/>
+      <c r="D17" s="96" t="n"/>
+      <c r="E17" s="96" t="n"/>
+      <c r="F17" s="96" t="n"/>
+      <c r="G17" s="96" t="n"/>
+      <c r="H17" s="96" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="92" t="n">
+      <c r="A18" s="97" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="92" t="inlineStr">
+      <c r="B18" s="97" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C18" s="93" t="inlineStr">
+      <c r="C18" s="98" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×5</t>
         </is>
       </c>
-      <c r="D18" s="94" t="n">
+      <c r="D18" s="99" t="n">
         <v>590000</v>
       </c>
       <c r="E18" s="61">
         <f>D18/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="95" t="inlineStr">
+      <c r="F18" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G18" s="96">
+      <c r="G18" s="101">
         <f>IF(F18="SÍ",D18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="92" t="inlineStr"/>
+      <c r="H18" s="97" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="92" t="n">
+      <c r="A19" s="97" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="92" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C19" s="93" t="inlineStr">
+      <c r="C19" s="98" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×40</t>
         </is>
       </c>
-      <c r="D19" s="94" t="n">
+      <c r="D19" s="99" t="n">
         <v>340000</v>
       </c>
       <c r="E19" s="61">
         <f>D19/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="95" t="inlineStr">
+      <c r="F19" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G19" s="96">
+      <c r="G19" s="101">
         <f>IF(F19="SÍ",D19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="92" t="inlineStr"/>
+      <c r="H19" s="97" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="92" t="n">
+      <c r="A20" s="97" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="92" t="inlineStr">
+      <c r="B20" s="97" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C20" s="93" t="inlineStr">
+      <c r="C20" s="98" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D20" s="94" t="n">
+      <c r="D20" s="99" t="n">
         <v>40000</v>
       </c>
       <c r="E20" s="61">
         <f>D20/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="95" t="inlineStr">
+      <c r="F20" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="96">
+      <c r="G20" s="101">
         <f>IF(F20="SÍ",D20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="92" t="inlineStr"/>
+      <c r="H20" s="97" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="92" t="n">
+      <c r="A21" s="97" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="92" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C21" s="93" t="inlineStr">
+      <c r="C21" s="98" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D21" s="94" t="n">
+      <c r="D21" s="99" t="n">
         <v>56300</v>
       </c>
       <c r="E21" s="61">
         <f>D21/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F21" s="95" t="inlineStr">
+      <c r="F21" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="96">
+      <c r="G21" s="101">
         <f>IF(F21="SÍ",D21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="92" t="inlineStr"/>
+      <c r="H21" s="97" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="90" t="inlineStr">
+      <c r="A22" s="95" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala principal</t>
         </is>
       </c>
-      <c r="B22" s="91" t="n"/>
-      <c r="C22" s="91" t="n"/>
-      <c r="D22" s="91" t="n"/>
-      <c r="E22" s="91" t="n"/>
-      <c r="F22" s="91" t="n"/>
-      <c r="G22" s="91" t="n"/>
-      <c r="H22" s="91" t="n"/>
+      <c r="B22" s="96" t="n"/>
+      <c r="C22" s="96" t="n"/>
+      <c r="D22" s="96" t="n"/>
+      <c r="E22" s="96" t="n"/>
+      <c r="F22" s="96" t="n"/>
+      <c r="G22" s="96" t="n"/>
+      <c r="H22" s="96" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="92" t="n">
+      <c r="A23" s="97" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="92" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C23" s="93" t="inlineStr">
+      <c r="C23" s="98" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×5.000</t>
         </is>
       </c>
-      <c r="D23" s="94" t="n">
+      <c r="D23" s="99" t="n">
         <v>42500000</v>
       </c>
       <c r="E23" s="61">
         <f>D23/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F23" s="95" t="inlineStr">
+      <c r="F23" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G23" s="96">
+      <c r="G23" s="101">
         <f>IF(F23="SÍ",D23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="92" t="inlineStr">
+      <c r="H23" s="97" t="inlineStr">
         <is>
           <t>Reemplazadas por las 5.500 sillas de FDL Eventos.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="92" t="n">
+      <c r="A24" s="97" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="92" t="inlineStr">
+      <c r="B24" s="97" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C24" s="93" t="inlineStr">
+      <c r="C24" s="98" t="inlineStr">
         <is>
           <t>Mesa 1,80 × 0,90 ×40</t>
         </is>
       </c>
-      <c r="D24" s="94" t="n">
+      <c r="D24" s="99" t="n">
         <v>2500000</v>
       </c>
       <c r="E24" s="61">
         <f>D24/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F24" s="95" t="inlineStr">
+      <c r="F24" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G24" s="96">
+      <c r="G24" s="101">
         <f>IF(F24="SÍ",D24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="92" t="inlineStr"/>
+      <c r="H24" s="97" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="92" t="n">
+      <c r="A25" s="97" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="92" t="inlineStr">
+      <c r="B25" s="97" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C25" s="93" t="inlineStr">
+      <c r="C25" s="98" t="inlineStr">
         <is>
           <t>Mantel ×40</t>
         </is>
       </c>
-      <c r="D25" s="94" t="n">
+      <c r="D25" s="99" t="n">
         <v>900000</v>
       </c>
       <c r="E25" s="61">
         <f>D25/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F25" s="95" t="inlineStr">
+      <c r="F25" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G25" s="96">
+      <c r="G25" s="101">
         <f>IF(F25="SÍ",D25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="92" t="inlineStr"/>
+      <c r="H25" s="97" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="92" t="n">
+      <c r="A26" s="97" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="92" t="inlineStr">
+      <c r="B26" s="97" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C26" s="93" t="inlineStr">
+      <c r="C26" s="98" t="inlineStr">
         <is>
           <t>Mantel redondo ×8</t>
         </is>
       </c>
-      <c r="D26" s="94" t="n">
+      <c r="D26" s="99" t="n">
         <v>256000</v>
       </c>
       <c r="E26" s="61">
         <f>D26/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F26" s="95" t="inlineStr">
+      <c r="F26" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G26" s="96">
+      <c r="G26" s="101">
         <f>IF(F26="SÍ",D26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="92" t="inlineStr"/>
+      <c r="H26" s="97" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="90" t="inlineStr">
+      <c r="A27" s="95" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · camarín de speakers</t>
         </is>
       </c>
-      <c r="B27" s="91" t="n"/>
-      <c r="C27" s="91" t="n"/>
-      <c r="D27" s="91" t="n"/>
-      <c r="E27" s="91" t="n"/>
-      <c r="F27" s="91" t="n"/>
-      <c r="G27" s="91" t="n"/>
-      <c r="H27" s="91" t="n"/>
+      <c r="B27" s="96" t="n"/>
+      <c r="C27" s="96" t="n"/>
+      <c r="D27" s="96" t="n"/>
+      <c r="E27" s="96" t="n"/>
+      <c r="F27" s="96" t="n"/>
+      <c r="G27" s="96" t="n"/>
+      <c r="H27" s="96" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="92" t="n">
+      <c r="A28" s="97" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="92" t="inlineStr">
+      <c r="B28" s="97" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C28" s="93" t="inlineStr">
+      <c r="C28" s="98" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×1</t>
         </is>
       </c>
-      <c r="D28" s="94" t="n">
+      <c r="D28" s="99" t="n">
         <v>118000</v>
       </c>
       <c r="E28" s="61">
         <f>D28/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F28" s="95" t="inlineStr">
+      <c r="F28" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G28" s="96">
+      <c r="G28" s="101">
         <f>IF(F28="SÍ",D28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="92" t="inlineStr"/>
+      <c r="H28" s="97" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="92" t="n">
+      <c r="A29" s="97" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="92" t="inlineStr">
+      <c r="B29" s="97" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C29" s="93" t="inlineStr">
+      <c r="C29" s="98" t="inlineStr">
         <is>
           <t>Espejo ×1</t>
         </is>
       </c>
-      <c r="D29" s="94" t="n">
+      <c r="D29" s="99" t="n">
         <v>79500</v>
       </c>
       <c r="E29" s="61">
         <f>D29/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F29" s="95" t="inlineStr">
+      <c r="F29" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G29" s="96">
+      <c r="G29" s="101">
         <f>IF(F29="SÍ",D29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="92" t="inlineStr"/>
+      <c r="H29" s="97" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="92" t="n">
+      <c r="A30" s="97" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="92" t="inlineStr">
+      <c r="B30" s="97" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C30" s="93" t="inlineStr">
+      <c r="C30" s="98" t="inlineStr">
         <is>
           <t>Juego de living (sillones + mesa ratona)</t>
         </is>
       </c>
-      <c r="D30" s="94" t="n">
+      <c r="D30" s="99" t="n">
         <v>1103642</v>
       </c>
       <c r="E30" s="61">
         <f>D30/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F30" s="95" t="inlineStr">
+      <c r="F30" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G30" s="96">
+      <c r="G30" s="101">
         <f>IF(F30="SÍ",D30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="92" t="inlineStr">
+      <c r="H30" s="97" t="inlineStr">
         <is>
           <t>El mobiliario "más fino" del camarín: candidato a contratárselo a La Rural.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="92" t="n">
+      <c r="A31" s="97" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="92" t="inlineStr">
+      <c r="B31" s="97" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C31" s="93" t="inlineStr">
+      <c r="C31" s="98" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="D31" s="99" t="n">
         <v>40000</v>
       </c>
       <c r="E31" s="61">
         <f>D31/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F31" s="95" t="inlineStr">
+      <c r="F31" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G31" s="96">
+      <c r="G31" s="101">
         <f>IF(F31="SÍ",D31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="92" t="inlineStr"/>
+      <c r="H31" s="97" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="92" t="n">
+      <c r="A32" s="97" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="92" t="inlineStr">
+      <c r="B32" s="97" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C32" s="93" t="inlineStr">
+      <c r="C32" s="98" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="D32" s="99" t="n">
         <v>56300</v>
       </c>
       <c r="E32" s="61">
         <f>D32/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F32" s="95" t="inlineStr">
+      <c r="F32" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G32" s="96">
+      <c r="G32" s="101">
         <f>IF(F32="SÍ",D32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="92" t="inlineStr"/>
+      <c r="H32" s="97" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="90" t="inlineStr">
+      <c r="A33" s="95" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · escenario y técnica</t>
         </is>
       </c>
-      <c r="B33" s="91" t="n"/>
-      <c r="C33" s="91" t="n"/>
-      <c r="D33" s="91" t="n"/>
-      <c r="E33" s="91" t="n"/>
-      <c r="F33" s="91" t="n"/>
-      <c r="G33" s="91" t="n"/>
-      <c r="H33" s="91" t="n"/>
+      <c r="B33" s="96" t="n"/>
+      <c r="C33" s="96" t="n"/>
+      <c r="D33" s="96" t="n"/>
+      <c r="E33" s="96" t="n"/>
+      <c r="F33" s="96" t="n"/>
+      <c r="G33" s="96" t="n"/>
+      <c r="H33" s="96" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="92" t="n">
+      <c r="A34" s="97" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="92" t="inlineStr">
+      <c r="B34" s="97" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C34" s="93" t="inlineStr">
+      <c r="C34" s="98" t="inlineStr">
         <is>
           <t>Mesa cocktail alta (escenario) ×1</t>
         </is>
       </c>
-      <c r="D34" s="94" t="n">
+      <c r="D34" s="99" t="n">
         <v>45000</v>
       </c>
       <c r="E34" s="61">
         <f>D34/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F34" s="95" t="inlineStr">
+      <c r="F34" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G34" s="96">
+      <c r="G34" s="101">
         <f>IF(F34="SÍ",D34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="92" t="inlineStr"/>
+      <c r="H34" s="97" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="92" t="n">
+      <c r="A35" s="97" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="92" t="inlineStr">
+      <c r="B35" s="97" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C35" s="93" t="inlineStr">
+      <c r="C35" s="98" t="inlineStr">
         <is>
           <t>Mesa alta para DJ ×1</t>
         </is>
       </c>
-      <c r="D35" s="94" t="n">
+      <c r="D35" s="99" t="n">
         <v>62300</v>
       </c>
       <c r="E35" s="61">
         <f>D35/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F35" s="95" t="inlineStr">
+      <c r="F35" s="100" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G35" s="96">
+      <c r="G35" s="101">
         <f>IF(F35="SÍ",D35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="92" t="inlineStr"/>
+      <c r="H35" s="97" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="90" t="inlineStr">
+      <c r="A36" s="95" t="inlineStr">
         <is>
           <t xml:space="preserve">  GENERALES</t>
         </is>
       </c>
-      <c r="B36" s="91" t="n"/>
-      <c r="C36" s="91" t="n"/>
-      <c r="D36" s="91" t="n"/>
-      <c r="E36" s="91" t="n"/>
-      <c r="F36" s="91" t="n"/>
-      <c r="G36" s="91" t="n"/>
-      <c r="H36" s="91" t="n"/>
+      <c r="B36" s="96" t="n"/>
+      <c r="C36" s="96" t="n"/>
+      <c r="D36" s="96" t="n"/>
+      <c r="E36" s="96" t="n"/>
+      <c r="F36" s="96" t="n"/>
+      <c r="G36" s="96" t="n"/>
+      <c r="H36" s="96" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="92" t="n">
+      <c r="A37" s="97" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="92" t="inlineStr">
+      <c r="B37" s="97" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C37" s="93" t="inlineStr">
+      <c r="C37" s="98" t="inlineStr">
         <is>
           <t>Dirección técnica de todo el evento + replanteo</t>
         </is>
       </c>
-      <c r="D37" s="94" t="n">
+      <c r="D37" s="99" t="n">
         <v>5149179.2</v>
       </c>
       <c r="E37" s="61">
         <f>D37/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F37" s="95" t="inlineStr">
+      <c r="F37" s="100" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G37" s="96">
+      <c r="G37" s="101">
         <f>IF(F37="SÍ",D37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="92" t="inlineStr">
+      <c r="H37" s="97" t="inlineStr">
         <is>
           <t>Ojo: el replanteo de sillas va aparte, con ingeniero propio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="92" t="n">
+      <c r="A38" s="97" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="92" t="inlineStr">
+      <c r="B38" s="97" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C38" s="93" t="inlineStr">
+      <c r="C38" s="98" t="inlineStr">
         <is>
           <t>Guardia eléctrica × 2 días</t>
         </is>
       </c>
-      <c r="D38" s="94" t="n">
+      <c r="D38" s="99" t="n">
         <v>865800</v>
       </c>
       <c r="E38" s="61">
         <f>D38/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F38" s="95" t="inlineStr">
+      <c r="F38" s="100" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G38" s="96">
+      <c r="G38" s="101">
         <f>IF(F38="SÍ",D38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="92" t="inlineStr"/>
+      <c r="H38" s="97" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="92" t="n">
+      <c r="A39" s="97" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="92" t="inlineStr">
+      <c r="B39" s="97" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C39" s="93" t="inlineStr">
+      <c r="C39" s="98" t="inlineStr">
         <is>
           <t>Guardia técnica × 2 días</t>
         </is>
       </c>
-      <c r="D39" s="94" t="n">
+      <c r="D39" s="99" t="n">
         <v>905200</v>
       </c>
       <c r="E39" s="61">
         <f>D39/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F39" s="95" t="inlineStr">
+      <c r="F39" s="100" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G39" s="96">
+      <c r="G39" s="101">
         <f>IF(F39="SÍ",D39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="92" t="inlineStr"/>
+      <c r="H39" s="97" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="3" t="inlineStr">
@@ -6327,7 +6859,7 @@
           <t>TOTAL del presupuesto de La Rural</t>
         </is>
       </c>
-      <c r="D41" s="97">
+      <c r="D41" s="102">
         <f>SUM(D6:D39)</f>
         <v/>
       </c>
@@ -6342,11 +6874,11 @@
           <t>Lo que se queda (marcado SÍ)</t>
         </is>
       </c>
-      <c r="D42" s="98">
+      <c r="D42" s="103">
         <f>SUM(G6:G39)</f>
         <v/>
       </c>
-      <c r="E42" s="99">
+      <c r="E42" s="104">
         <f>D42/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -6357,11 +6889,11 @@
           <t>Lo que se saca (marcado NO)</t>
         </is>
       </c>
-      <c r="D43" s="100">
+      <c r="D43" s="105">
         <f>D41-D42</f>
         <v/>
       </c>
-      <c r="E43" s="101">
+      <c r="E43" s="106">
         <f>D43/TABLERO!$C$4</f>
         <v/>
       </c>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -437,6 +437,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -464,7 +471,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -3879,7 +3885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4579,28 +4585,395 @@
       <c r="F19" s="83" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="87" t="inlineStr">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>LO QUE IBA A COSTAR CONTRA LO QUE COSTÓ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Precios unitarios de merch.cmc2026.com al 06/07/2026, dólar $1.515. Compara el proveedor que traía Cumbre contra los proveedores argentinos que consiguió Agustina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Unitario Cumbre</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Total Cumbre</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Unitario Agustina</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Total Agustina</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Ahorro</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Ahorro %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="87" t="inlineStr">
+        <is>
+          <t>Remeras estampadas</t>
+        </is>
+      </c>
+      <c r="B24" s="59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C24" s="88" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="D24" s="88" t="n">
+        <v>1617.16</v>
+      </c>
+      <c r="E24" s="88" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="F24" s="88" t="n">
+        <v>931.35</v>
+      </c>
+      <c r="G24" s="89">
+        <f>D24-F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="90">
+        <f>G24/D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="87" t="inlineStr">
+        <is>
+          <t>Gorras negras</t>
+        </is>
+      </c>
+      <c r="B25" s="59" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="C25" s="88" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D25" s="88" t="n">
+        <v>9900.99</v>
+      </c>
+      <c r="E25" s="88" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F25" s="88" t="n">
+        <v>1636.96</v>
+      </c>
+      <c r="G25" s="89">
+        <f>D25-F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="90">
+        <f>G25/D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="87" t="inlineStr">
+        <is>
+          <t>Cinta colgante / lanyard</t>
+        </is>
+      </c>
+      <c r="B26" s="59" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="C26" s="88" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D26" s="88" t="n">
+        <v>1247.52</v>
+      </c>
+      <c r="E26" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="88" t="n">
+        <v>1004.95</v>
+      </c>
+      <c r="G26" s="89">
+        <f>D26-F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="90">
+        <f>G26/D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="87" t="inlineStr">
+        <is>
+          <t>Credenciales 10 × 13 cm</t>
+        </is>
+      </c>
+      <c r="B27" s="59" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="C27" s="88" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D27" s="88" t="n">
+        <v>574.65</v>
+      </c>
+      <c r="E27" s="88" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F27" s="88" t="n">
+        <v>475.06</v>
+      </c>
+      <c r="G27" s="89">
+        <f>D27-F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="90">
+        <f>G27/D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="87" t="inlineStr">
+        <is>
+          <t>Hojas A4 (contrato)</t>
+        </is>
+      </c>
+      <c r="B28" s="59" t="inlineStr">
+        <is>
+          <t>5.500</t>
+        </is>
+      </c>
+      <c r="C28" s="88" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D28" s="88" t="n">
+        <v>1107.26</v>
+      </c>
+      <c r="E28" s="88" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F28" s="88" t="n">
+        <v>265.31</v>
+      </c>
+      <c r="G28" s="89">
+        <f>D28-F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="90">
+        <f>G28/D28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="87" t="inlineStr">
+        <is>
+          <t>Tarjetas 21,5 × 10 cm (cheque)</t>
+        </is>
+      </c>
+      <c r="B29" s="59" t="inlineStr">
+        <is>
+          <t>5.500</t>
+        </is>
+      </c>
+      <c r="C29" s="88" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D29" s="88" t="n">
+        <v>671.62</v>
+      </c>
+      <c r="E29" s="88" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F29" s="88" t="n">
+        <v>109.78</v>
+      </c>
+      <c r="G29" s="89">
+        <f>D29-F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="90">
+        <f>G29/D29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="87" t="inlineStr">
+        <is>
+          <t>Bolsas de friselina, 2 colores</t>
+        </is>
+      </c>
+      <c r="B30" s="59" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="C30" s="88" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D30" s="88" t="n">
+        <v>1141.91</v>
+      </c>
+      <c r="E30" s="88" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F30" s="88" t="n">
+        <v>644.55</v>
+      </c>
+      <c r="G30" s="89">
+        <f>D30-F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="90">
+        <f>G30/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="91" t="inlineStr">
+        <is>
+          <t>Pulseras tyvek — fuera de la comparación</t>
+        </is>
+      </c>
+      <c r="B31" s="86" t="inlineStr">
+        <is>
+          <t>5.500</t>
+        </is>
+      </c>
+      <c r="C31" s="92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D31" s="92" t="n">
+        <v>544.55</v>
+      </c>
+      <c r="E31" s="92" t="n"/>
+      <c r="F31" s="92" t="n"/>
+      <c r="G31" s="38" t="n"/>
+      <c r="H31" s="38" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="78" t="inlineStr">
+        <is>
+          <t>TOTAL DE LA CANASTA COMPARADA</t>
+        </is>
+      </c>
+      <c r="D32" s="79">
+        <f>SUM(D24:D30)</f>
+        <v/>
+      </c>
+      <c r="F32" s="79">
+        <f>SUM(F24:F30)</f>
+        <v/>
+      </c>
+      <c r="G32" s="79">
+        <f>SUM(G24:G30)</f>
+        <v/>
+      </c>
+      <c r="H32" s="93">
+        <f>G32/D32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>La gorra sola explica la mitad del ahorro: el proveedor de Cumbre la cobraba US$9,90 y Agustina la consiguió a US$1,64. Sobre 1.000 unidades son US$8.264.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Las pulseras tyvek quedan fuera de los dos lados de la cuenta porque no hay precio comparable del lado argentino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>OJO: esta canasta NO es el total del rubro merch. Los pañuelos (US$6.973) y el bordado de gorras (US$1.750) no entran en la comparación, y las cantidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>del sitio no son exactamente las de las facturas finales (remeras 100 contra 250, gorras 1.000 contra 940). Sirve para medir el ahorro por precio unitario,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>no para reemplazar el costo del rubro, que sale de las nueve facturas de arriba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay tiene su propia comparativa en el mismo sitio: US$2.396,00 contra US$755,77, con un ahorro de US$1.640,23. No entra en el costo de Argentina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="94" t="inlineStr">
         <is>
           <t>TRES COSAS QUE HAY QUE CONFIRMAR</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>1) Lanyards y gráfica de Argentina: las facturas reemitidas en agosto vienen por el TOTAL, pero la carpeta y el master dicen que ya se abonó el 50%. Si las facturas están bien, hay que pagar US$2.008 más de lo que sale por la regla del 50%. Una sola consulta a LEOTEX y a Derqui lo resuelve.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>2) Pañuelos: son 8.500 unidades compartidas entre Argentina y Uruguay y la factura no las separa. Acá se imputó el 65% a Argentina (5.500 de 8.500, la misma proporción que la gráfica). Si van todos a Argentina, el costo sube US$3.755.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>3) La gráfica de Uruguay (US$1.233) estaba cargada en el master como Argentina. Ya quedó fuera del costo argentino, pero conviene corregirla también en el master para que no se arrastre.</t>
         </is>
@@ -4610,12 +4983,12 @@
   <autoFilter ref="A4:O4"/>
   <mergeCells count="7">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A43:O43"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A42:O42"/>
+    <mergeCell ref="A44:O44"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A22:O22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4885,7 +5258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4999,7 +5372,7 @@
         <f>D5-G5</f>
         <v/>
       </c>
-      <c r="I5" s="88">
+      <c r="I5" s="95">
         <f>IFERROR(H5/D5,"")</f>
         <v/>
       </c>
@@ -5043,7 +5416,7 @@
         <f>D6-G6</f>
         <v/>
       </c>
-      <c r="I6" s="88">
+      <c r="I6" s="95">
         <f>IFERROR(H6/D6,"")</f>
         <v/>
       </c>
@@ -5087,7 +5460,7 @@
         <f>D7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="88">
+      <c r="I7" s="95">
         <f>IFERROR(H7/D7,"")</f>
         <v/>
       </c>
@@ -5128,7 +5501,7 @@
         <f>D8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="95">
         <f>IFERROR(H8/D8,"")</f>
         <v/>
       </c>
@@ -5141,165 +5514,203 @@
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Vallado del público</t>
+          <t>Merch e impresos</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Presupuestado en la hoja de Argentina</t>
+          <t>Proveedor de Cumbre, precios unitarios al 06/07</t>
         </is>
       </c>
       <c r="C9" s="20" t="n"/>
       <c r="D9" s="25" t="n">
-        <v>1250</v>
+        <v>16261.12</v>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>500 vallas bonificadas por el proveedor de técnica</t>
+          <t>Proveedores argentinos conseguidos por Agustina</t>
         </is>
       </c>
       <c r="F9" s="20" t="n"/>
       <c r="G9" s="25" t="n">
-        <v>0</v>
+        <v>5067.97</v>
       </c>
       <c r="H9" s="76">
         <f>D9-G9</f>
         <v/>
       </c>
-      <c r="I9" s="88">
+      <c r="I9" s="95">
         <f>IFERROR(H9/D9,"")</f>
         <v/>
       </c>
       <c r="J9" s="26" t="inlineStr">
         <is>
+          <t>Comparativa de merch.cmc2026.com al 06/07/2026 (dólar $1.515). Es una canasta cerrada de siete ítems: remeras, gorras, lanyards, credenciales, hojas A4, tarjetas y bolsas de friselina. Las pulseras tyvek quedan fuera de los dos lados porque no hay precio comparable. NO es el total del rubro merch: los pañuelos y el bordado de gorras no entran en esta comparación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Vallado del público</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Presupuestado en la hoja de Argentina</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="25" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>500 vallas bonificadas por el proveedor de técnica</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="76">
+        <f>D10-G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="95">
+        <f>IFERROR(H10/D10,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="26" t="inlineStr">
+        <is>
           <t>Negociación de Agustina. Además bonifican los efectos especiales, que no estaban valorizados.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="52" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>AHORRO TOTAL</t>
         </is>
       </c>
-      <c r="D10" s="89">
-        <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="89">
-        <f>SUM(G5:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="89">
-        <f>SUM(H5:H9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="87" t="inlineStr">
+      <c r="D11" s="96">
+        <f>SUM(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="96">
+        <f>SUM(G5:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="96">
+        <f>SUM(H5:H10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>TÉCNICA — la comparación no es directa</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Se pidió cotización de técnica a NUEVE empresas el 13 y 14 de junio. Respondieron seis con número. El detalle completo está en la hoja COTIZACIONES TÉCNICA.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · Sound-Light (16/06): el PDF no se pudo abrir, el mail pesa 33 MB. El mail del 19/06 les dice que las otras estaban "prácticamente la mitad", lo que lo ubica por encima de los $100.000.000.</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Bonetto (17/06): $94.936.000 — sonido e iluminación $69.736.000, LED $20.720.000, CCTV $4.480.000. Grúas y efectos aparte (la chispa fría la cobra POR MINUTO).</t>
+          <t xml:space="preserve">   · Sound-Light (16/06): el PDF no se pudo abrir, el mail pesa 33 MB. El mail del 19/06 les dice que las otras estaban "prácticamente la mitad", lo que lo ubica por encima de los $100.000.000.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Pero cotiza 40 m² de LED cuando el rider pide 65, y deja afuera grúas y energía. Vencida.</t>
+          <t xml:space="preserve">   · Bonetto (17/06): $94.936.000 — sonido e iluminación $69.736.000, LED $20.720.000, CCTV $4.480.000. Grúas y efectos aparte (la chispa fría la cobra POR MINUTO).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 2MG (24/06): $45.000.000 con descuento + IVA = $54.450.000, más $19.202.700 de adicionales. Sonido más liviano, cotizado para "2000 / 5000 pax".</t>
+          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Pero cotiza 40 m² de LED cuando el rider pide 65, y deja afuera grúas y energía. Vencida.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Dixi Group (26/06): $82.000.000 + IVA = $99.220.000 llave en mano, con rigging completo, encomiendas y 4 máquinas de chispa fría.</t>
+          <t xml:space="preserve">   · 2MG (24/06): $45.000.000 con descuento + IVA = $54.450.000, más $19.202.700 de adicionales. Sonido más liviano, cotizado para "2000 / 5000 pax".</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   · Dixi Group (26/06): $82.000.000 + IVA = $99.220.000 llave en mano, con rigging completo, encomiendas y 4 máquinas de chispa fría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">   · VMG (29/06): $15.276.250 con IVA, sólo las pantallas LED de 65 m².</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>POR QUÉ TÉCNICA NO ENTRA EN LA TABLA DE ARRIBA: Grupo MET cerró en US$60.000 ($90.600.000) y con el circuito cerrado el paquete queda cerca de $100.000.000.</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Eso es prácticamente lo mismo que Dixi llave en mano y menos que Bonetto, pero está POR ENCIMA de 2MG y de Prina. Poner esa diferencia como ahorro no se sostendría</t>
+          <t>POR QUÉ TÉCNICA NO ENTRA EN LA TABLA DE ARRIBA: Grupo MET cerró en US$60.000 ($90.600.000) y con el circuito cerrado el paquete queda cerca de $100.000.000.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>Eso es prácticamente lo mismo que Dixi llave en mano y menos que Bonetto, pero está POR ENCIMA de 2MG y de Prina. Poner esa diferencia como ahorro no se sostendría</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>delante del CEO, porque los alcances no son iguales: Prina cotizó 38% menos de LED, 2MG un sonido más chico, y Grupo MET incluye lo que se agregó tras la visita al predio.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>LO QUE SÍ SE SOSTIENE EN TÉCNICA: las 500 vallas y los efectos especiales van bonificados. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>LO QUE SÍ SE SOSTIENE EN TÉCNICA: las 500 vallas y los efectos especiales van bonificados. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Con los 6 disparos por día que pide el rider, en cualquiera de las otras propuestas eso es plata.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-    </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>FALTA UNA SOLA COSA para cerrar el ahorro de técnica con un número: el PDF de Grupo MET con el alcance final. Es el único de los siete proveedores sin presupuesto escrito en el correo.</t>
         </is>
@@ -5409,7 +5820,7 @@
       </c>
       <c r="D5" s="30" t="n"/>
       <c r="E5" s="32" t="n"/>
-      <c r="F5" s="90">
+      <c r="F5" s="97">
         <f>IF(E5="","",E5/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5452,7 +5863,7 @@
         <f>D6*1.21</f>
         <v/>
       </c>
-      <c r="F6" s="91">
+      <c r="F6" s="98">
         <f>IF(E6="","",E6/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5494,7 +5905,7 @@
       <c r="E7" s="20" t="n">
         <v>59150850</v>
       </c>
-      <c r="F7" s="91">
+      <c r="F7" s="98">
         <f>IF(E7="","",E7/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5536,7 +5947,7 @@
       <c r="E8" s="20" t="n">
         <v>54450000</v>
       </c>
-      <c r="F8" s="91">
+      <c r="F8" s="98">
         <f>IF(E8="","",E8/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5578,7 +5989,7 @@
       <c r="E9" s="20" t="n">
         <v>99220000</v>
       </c>
-      <c r="F9" s="91">
+      <c r="F9" s="98">
         <f>IF(E9="","",E9/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5620,7 +6031,7 @@
       <c r="E10" s="50" t="n">
         <v>15276250</v>
       </c>
-      <c r="F10" s="92">
+      <c r="F10" s="99">
         <f>IF(E10="","",E10/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5660,7 +6071,7 @@
       <c r="E11" s="40" t="n">
         <v>90600000</v>
       </c>
-      <c r="F11" s="93">
+      <c r="F11" s="100">
         <f>IF(E11="","",E11/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5681,7 +6092,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="87" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>CÓMO LEER ESTA TABLA — Y POR QUÉ NO SE PUEDE RESTAR SIN MÁS</t>
         </is>
@@ -5757,7 +6168,7 @@
       <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="inlineStr">
+      <c r="A25" s="101" t="inlineStr">
         <is>
           <t>PARA CERRAR EL AHORRO DE TÉCNICA FALTA UNA SOLA COSA: el PDF de Grupo MET con el alcance final. Con eso se puede comparar contra el mismo alcance en Dixi, Bonetto, 2MG y Prina, y recién ahí poner un número.</t>
         </is>
@@ -5844,1014 +6255,1014 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="95" t="inlineStr">
+      <c r="A5" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="B5" s="96" t="n"/>
-      <c r="C5" s="96" t="n"/>
-      <c r="D5" s="96" t="n"/>
-      <c r="E5" s="96" t="n"/>
-      <c r="F5" s="96" t="n"/>
-      <c r="G5" s="96" t="n"/>
-      <c r="H5" s="96" t="n"/>
+      <c r="B5" s="103" t="n"/>
+      <c r="C5" s="103" t="n"/>
+      <c r="D5" s="103" t="n"/>
+      <c r="E5" s="103" t="n"/>
+      <c r="F5" s="103" t="n"/>
+      <c r="G5" s="103" t="n"/>
+      <c r="H5" s="103" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="97" t="n">
+      <c r="A6" s="104" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="97" t="inlineStr">
+      <c r="B6" s="104" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C6" s="98" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>Oficina de producción — 25 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D6" s="99" t="n">
+      <c r="D6" s="106" t="n">
         <v>1314575</v>
       </c>
       <c r="E6" s="61">
         <f>D6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F6" s="100" t="inlineStr">
+      <c r="F6" s="107" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G6" s="101">
+      <c r="G6" s="108">
         <f>IF(F6="SÍ",D6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="97" t="inlineStr"/>
+      <c r="H6" s="104" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="97" t="n">
+      <c r="A7" s="104" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="97" t="inlineStr">
+      <c r="B7" s="104" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C7" s="98" t="inlineStr">
+      <c r="C7" s="105" t="inlineStr">
         <is>
           <t>Sala de staff — 100 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D7" s="99" t="n">
+      <c r="D7" s="106" t="n">
         <v>5258300</v>
       </c>
       <c r="E7" s="61">
         <f>D7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F7" s="100" t="inlineStr">
+      <c r="F7" s="107" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G7" s="101">
+      <c r="G7" s="108">
         <f>IF(F7="SÍ",D7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="97" t="inlineStr"/>
+      <c r="H7" s="104" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="97" t="n">
+      <c r="A8" s="104" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="97" t="inlineStr">
+      <c r="B8" s="104" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C8" s="98" t="inlineStr">
+      <c r="C8" s="105" t="inlineStr">
         <is>
           <t>Depósito 8×8 para las 2.500 barras — 64 m²</t>
         </is>
       </c>
-      <c r="D8" s="99" t="n">
+      <c r="D8" s="106" t="n">
         <v>3365312</v>
       </c>
       <c r="E8" s="61">
         <f>D8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="100" t="inlineStr">
+      <c r="F8" s="107" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G8" s="101">
+      <c r="G8" s="108">
         <f>IF(F8="SÍ",D8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="97" t="inlineStr">
+      <c r="H8" s="104" t="inlineStr">
         <is>
           <t>Depósito para las 2.500 barras de la dinámica.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="95" t="inlineStr">
+      <c r="A9" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · oficina de producción</t>
         </is>
       </c>
-      <c r="B9" s="96" t="n"/>
-      <c r="C9" s="96" t="n"/>
-      <c r="D9" s="96" t="n"/>
-      <c r="E9" s="96" t="n"/>
-      <c r="F9" s="96" t="n"/>
-      <c r="G9" s="96" t="n"/>
-      <c r="H9" s="96" t="n"/>
+      <c r="B9" s="103" t="n"/>
+      <c r="C9" s="103" t="n"/>
+      <c r="D9" s="103" t="n"/>
+      <c r="E9" s="103" t="n"/>
+      <c r="F9" s="103" t="n"/>
+      <c r="G9" s="103" t="n"/>
+      <c r="H9" s="103" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="97" t="n">
+      <c r="A10" s="104" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="97" t="inlineStr">
+      <c r="B10" s="104" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C10" s="98" t="inlineStr">
+      <c r="C10" s="105" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×2</t>
         </is>
       </c>
-      <c r="D10" s="99" t="n">
+      <c r="D10" s="106" t="n">
         <v>236000</v>
       </c>
       <c r="E10" s="61">
         <f>D10/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="100" t="inlineStr">
+      <c r="F10" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G10" s="101">
+      <c r="G10" s="108">
         <f>IF(F10="SÍ",D10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="97" t="inlineStr"/>
+      <c r="H10" s="104" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="97" t="n">
+      <c r="A11" s="104" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="97" t="inlineStr">
+      <c r="B11" s="104" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C11" s="98" t="inlineStr">
+      <c r="C11" s="105" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×10</t>
         </is>
       </c>
-      <c r="D11" s="99" t="n">
+      <c r="D11" s="106" t="n">
         <v>85000</v>
       </c>
       <c r="E11" s="61">
         <f>D11/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="100" t="inlineStr">
+      <c r="F11" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G11" s="101">
+      <c r="G11" s="108">
         <f>IF(F11="SÍ",D11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="97" t="inlineStr"/>
+      <c r="H11" s="104" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="97" t="n">
+      <c r="A12" s="104" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="97" t="inlineStr">
+      <c r="B12" s="104" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C12" s="98" t="inlineStr">
+      <c r="C12" s="105" t="inlineStr">
         <is>
           <t>Sillón Valencia 2C ×2</t>
         </is>
       </c>
-      <c r="D12" s="99" t="n">
+      <c r="D12" s="106" t="n">
         <v>254000</v>
       </c>
       <c r="E12" s="61">
         <f>D12/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="100" t="inlineStr">
+      <c r="F12" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G12" s="101">
+      <c r="G12" s="108">
         <f>IF(F12="SÍ",D12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="97" t="inlineStr"/>
+      <c r="H12" s="104" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="97" t="n">
+      <c r="A13" s="104" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="97" t="inlineStr">
+      <c r="B13" s="104" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C13" s="98" t="inlineStr">
+      <c r="C13" s="105" t="inlineStr">
         <is>
           <t>Sillón BRNO ×2</t>
         </is>
       </c>
-      <c r="D13" s="99" t="n">
+      <c r="D13" s="106" t="n">
         <v>160000</v>
       </c>
       <c r="E13" s="61">
         <f>D13/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="100" t="inlineStr">
+      <c r="F13" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="101">
+      <c r="G13" s="108">
         <f>IF(F13="SÍ",D13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="97" t="inlineStr"/>
+      <c r="H13" s="104" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="97" t="n">
+      <c r="A14" s="104" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="97" t="inlineStr">
+      <c r="B14" s="104" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C14" s="98" t="inlineStr">
+      <c r="C14" s="105" t="inlineStr">
         <is>
           <t>Mesa ratona ×1</t>
         </is>
       </c>
-      <c r="D14" s="99" t="n">
+      <c r="D14" s="106" t="n">
         <v>118000</v>
       </c>
       <c r="E14" s="61">
         <f>D14/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="100" t="inlineStr">
+      <c r="F14" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="101">
+      <c r="G14" s="108">
         <f>IF(F14="SÍ",D14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="97" t="inlineStr"/>
+      <c r="H14" s="104" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="97" t="n">
+      <c r="A15" s="104" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="97" t="inlineStr">
+      <c r="B15" s="104" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C15" s="98" t="inlineStr">
+      <c r="C15" s="105" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D15" s="99" t="n">
+      <c r="D15" s="106" t="n">
         <v>40000</v>
       </c>
       <c r="E15" s="61">
         <f>D15/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="100" t="inlineStr">
+      <c r="F15" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G15" s="101">
+      <c r="G15" s="108">
         <f>IF(F15="SÍ",D15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="97" t="inlineStr"/>
+      <c r="H15" s="104" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="97" t="n">
+      <c r="A16" s="104" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="97" t="inlineStr">
+      <c r="B16" s="104" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C16" s="98" t="inlineStr">
+      <c r="C16" s="105" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D16" s="99" t="n">
+      <c r="D16" s="106" t="n">
         <v>56300</v>
       </c>
       <c r="E16" s="61">
         <f>D16/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="100" t="inlineStr">
+      <c r="F16" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G16" s="101">
+      <c r="G16" s="108">
         <f>IF(F16="SÍ",D16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="97" t="inlineStr"/>
+      <c r="H16" s="104" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="95" t="inlineStr">
+      <c r="A17" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala de staff</t>
         </is>
       </c>
-      <c r="B17" s="96" t="n"/>
-      <c r="C17" s="96" t="n"/>
-      <c r="D17" s="96" t="n"/>
-      <c r="E17" s="96" t="n"/>
-      <c r="F17" s="96" t="n"/>
-      <c r="G17" s="96" t="n"/>
-      <c r="H17" s="96" t="n"/>
+      <c r="B17" s="103" t="n"/>
+      <c r="C17" s="103" t="n"/>
+      <c r="D17" s="103" t="n"/>
+      <c r="E17" s="103" t="n"/>
+      <c r="F17" s="103" t="n"/>
+      <c r="G17" s="103" t="n"/>
+      <c r="H17" s="103" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="97" t="n">
+      <c r="A18" s="104" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="97" t="inlineStr">
+      <c r="B18" s="104" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C18" s="98" t="inlineStr">
+      <c r="C18" s="105" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×5</t>
         </is>
       </c>
-      <c r="D18" s="99" t="n">
+      <c r="D18" s="106" t="n">
         <v>590000</v>
       </c>
       <c r="E18" s="61">
         <f>D18/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="100" t="inlineStr">
+      <c r="F18" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G18" s="101">
+      <c r="G18" s="108">
         <f>IF(F18="SÍ",D18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="97" t="inlineStr"/>
+      <c r="H18" s="104" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="97" t="n">
+      <c r="A19" s="104" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="97" t="inlineStr">
+      <c r="B19" s="104" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C19" s="98" t="inlineStr">
+      <c r="C19" s="105" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×40</t>
         </is>
       </c>
-      <c r="D19" s="99" t="n">
+      <c r="D19" s="106" t="n">
         <v>340000</v>
       </c>
       <c r="E19" s="61">
         <f>D19/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="100" t="inlineStr">
+      <c r="F19" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G19" s="101">
+      <c r="G19" s="108">
         <f>IF(F19="SÍ",D19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="97" t="inlineStr"/>
+      <c r="H19" s="104" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="97" t="n">
+      <c r="A20" s="104" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="97" t="inlineStr">
+      <c r="B20" s="104" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C20" s="98" t="inlineStr">
+      <c r="C20" s="105" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D20" s="99" t="n">
+      <c r="D20" s="106" t="n">
         <v>40000</v>
       </c>
       <c r="E20" s="61">
         <f>D20/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="100" t="inlineStr">
+      <c r="F20" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="101">
+      <c r="G20" s="108">
         <f>IF(F20="SÍ",D20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="97" t="inlineStr"/>
+      <c r="H20" s="104" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="97" t="n">
+      <c r="A21" s="104" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="97" t="inlineStr">
+      <c r="B21" s="104" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C21" s="98" t="inlineStr">
+      <c r="C21" s="105" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D21" s="99" t="n">
+      <c r="D21" s="106" t="n">
         <v>56300</v>
       </c>
       <c r="E21" s="61">
         <f>D21/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F21" s="100" t="inlineStr">
+      <c r="F21" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="101">
+      <c r="G21" s="108">
         <f>IF(F21="SÍ",D21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="97" t="inlineStr"/>
+      <c r="H21" s="104" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="95" t="inlineStr">
+      <c r="A22" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala principal</t>
         </is>
       </c>
-      <c r="B22" s="96" t="n"/>
-      <c r="C22" s="96" t="n"/>
-      <c r="D22" s="96" t="n"/>
-      <c r="E22" s="96" t="n"/>
-      <c r="F22" s="96" t="n"/>
-      <c r="G22" s="96" t="n"/>
-      <c r="H22" s="96" t="n"/>
+      <c r="B22" s="103" t="n"/>
+      <c r="C22" s="103" t="n"/>
+      <c r="D22" s="103" t="n"/>
+      <c r="E22" s="103" t="n"/>
+      <c r="F22" s="103" t="n"/>
+      <c r="G22" s="103" t="n"/>
+      <c r="H22" s="103" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="97" t="n">
+      <c r="A23" s="104" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="97" t="inlineStr">
+      <c r="B23" s="104" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C23" s="98" t="inlineStr">
+      <c r="C23" s="105" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×5.000</t>
         </is>
       </c>
-      <c r="D23" s="99" t="n">
+      <c r="D23" s="106" t="n">
         <v>42500000</v>
       </c>
       <c r="E23" s="61">
         <f>D23/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F23" s="100" t="inlineStr">
+      <c r="F23" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G23" s="101">
+      <c r="G23" s="108">
         <f>IF(F23="SÍ",D23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="97" t="inlineStr">
+      <c r="H23" s="104" t="inlineStr">
         <is>
           <t>Reemplazadas por las 5.500 sillas de FDL Eventos.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="97" t="n">
+      <c r="A24" s="104" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="97" t="inlineStr">
+      <c r="B24" s="104" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C24" s="98" t="inlineStr">
+      <c r="C24" s="105" t="inlineStr">
         <is>
           <t>Mesa 1,80 × 0,90 ×40</t>
         </is>
       </c>
-      <c r="D24" s="99" t="n">
+      <c r="D24" s="106" t="n">
         <v>2500000</v>
       </c>
       <c r="E24" s="61">
         <f>D24/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F24" s="100" t="inlineStr">
+      <c r="F24" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G24" s="101">
+      <c r="G24" s="108">
         <f>IF(F24="SÍ",D24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="97" t="inlineStr"/>
+      <c r="H24" s="104" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="97" t="n">
+      <c r="A25" s="104" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="97" t="inlineStr">
+      <c r="B25" s="104" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C25" s="98" t="inlineStr">
+      <c r="C25" s="105" t="inlineStr">
         <is>
           <t>Mantel ×40</t>
         </is>
       </c>
-      <c r="D25" s="99" t="n">
+      <c r="D25" s="106" t="n">
         <v>900000</v>
       </c>
       <c r="E25" s="61">
         <f>D25/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F25" s="100" t="inlineStr">
+      <c r="F25" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G25" s="101">
+      <c r="G25" s="108">
         <f>IF(F25="SÍ",D25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="97" t="inlineStr"/>
+      <c r="H25" s="104" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="97" t="n">
+      <c r="A26" s="104" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="97" t="inlineStr">
+      <c r="B26" s="104" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C26" s="98" t="inlineStr">
+      <c r="C26" s="105" t="inlineStr">
         <is>
           <t>Mantel redondo ×8</t>
         </is>
       </c>
-      <c r="D26" s="99" t="n">
+      <c r="D26" s="106" t="n">
         <v>256000</v>
       </c>
       <c r="E26" s="61">
         <f>D26/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F26" s="100" t="inlineStr">
+      <c r="F26" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G26" s="101">
+      <c r="G26" s="108">
         <f>IF(F26="SÍ",D26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="97" t="inlineStr"/>
+      <c r="H26" s="104" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="95" t="inlineStr">
+      <c r="A27" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · camarín de speakers</t>
         </is>
       </c>
-      <c r="B27" s="96" t="n"/>
-      <c r="C27" s="96" t="n"/>
-      <c r="D27" s="96" t="n"/>
-      <c r="E27" s="96" t="n"/>
-      <c r="F27" s="96" t="n"/>
-      <c r="G27" s="96" t="n"/>
-      <c r="H27" s="96" t="n"/>
+      <c r="B27" s="103" t="n"/>
+      <c r="C27" s="103" t="n"/>
+      <c r="D27" s="103" t="n"/>
+      <c r="E27" s="103" t="n"/>
+      <c r="F27" s="103" t="n"/>
+      <c r="G27" s="103" t="n"/>
+      <c r="H27" s="103" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="97" t="n">
+      <c r="A28" s="104" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="97" t="inlineStr">
+      <c r="B28" s="104" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C28" s="98" t="inlineStr">
+      <c r="C28" s="105" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×1</t>
         </is>
       </c>
-      <c r="D28" s="99" t="n">
+      <c r="D28" s="106" t="n">
         <v>118000</v>
       </c>
       <c r="E28" s="61">
         <f>D28/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F28" s="100" t="inlineStr">
+      <c r="F28" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G28" s="101">
+      <c r="G28" s="108">
         <f>IF(F28="SÍ",D28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="97" t="inlineStr"/>
+      <c r="H28" s="104" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="97" t="n">
+      <c r="A29" s="104" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="97" t="inlineStr">
+      <c r="B29" s="104" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C29" s="98" t="inlineStr">
+      <c r="C29" s="105" t="inlineStr">
         <is>
           <t>Espejo ×1</t>
         </is>
       </c>
-      <c r="D29" s="99" t="n">
+      <c r="D29" s="106" t="n">
         <v>79500</v>
       </c>
       <c r="E29" s="61">
         <f>D29/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F29" s="100" t="inlineStr">
+      <c r="F29" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G29" s="101">
+      <c r="G29" s="108">
         <f>IF(F29="SÍ",D29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="97" t="inlineStr"/>
+      <c r="H29" s="104" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="97" t="n">
+      <c r="A30" s="104" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="97" t="inlineStr">
+      <c r="B30" s="104" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C30" s="98" t="inlineStr">
+      <c r="C30" s="105" t="inlineStr">
         <is>
           <t>Juego de living (sillones + mesa ratona)</t>
         </is>
       </c>
-      <c r="D30" s="99" t="n">
+      <c r="D30" s="106" t="n">
         <v>1103642</v>
       </c>
       <c r="E30" s="61">
         <f>D30/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F30" s="100" t="inlineStr">
+      <c r="F30" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G30" s="101">
+      <c r="G30" s="108">
         <f>IF(F30="SÍ",D30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="97" t="inlineStr">
+      <c r="H30" s="104" t="inlineStr">
         <is>
           <t>El mobiliario "más fino" del camarín: candidato a contratárselo a La Rural.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="97" t="n">
+      <c r="A31" s="104" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="97" t="inlineStr">
+      <c r="B31" s="104" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C31" s="98" t="inlineStr">
+      <c r="C31" s="105" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D31" s="99" t="n">
+      <c r="D31" s="106" t="n">
         <v>40000</v>
       </c>
       <c r="E31" s="61">
         <f>D31/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F31" s="100" t="inlineStr">
+      <c r="F31" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G31" s="101">
+      <c r="G31" s="108">
         <f>IF(F31="SÍ",D31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="97" t="inlineStr"/>
+      <c r="H31" s="104" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="97" t="n">
+      <c r="A32" s="104" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="97" t="inlineStr">
+      <c r="B32" s="104" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C32" s="98" t="inlineStr">
+      <c r="C32" s="105" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D32" s="99" t="n">
+      <c r="D32" s="106" t="n">
         <v>56300</v>
       </c>
       <c r="E32" s="61">
         <f>D32/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F32" s="100" t="inlineStr">
+      <c r="F32" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G32" s="101">
+      <c r="G32" s="108">
         <f>IF(F32="SÍ",D32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="97" t="inlineStr"/>
+      <c r="H32" s="104" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="95" t="inlineStr">
+      <c r="A33" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · escenario y técnica</t>
         </is>
       </c>
-      <c r="B33" s="96" t="n"/>
-      <c r="C33" s="96" t="n"/>
-      <c r="D33" s="96" t="n"/>
-      <c r="E33" s="96" t="n"/>
-      <c r="F33" s="96" t="n"/>
-      <c r="G33" s="96" t="n"/>
-      <c r="H33" s="96" t="n"/>
+      <c r="B33" s="103" t="n"/>
+      <c r="C33" s="103" t="n"/>
+      <c r="D33" s="103" t="n"/>
+      <c r="E33" s="103" t="n"/>
+      <c r="F33" s="103" t="n"/>
+      <c r="G33" s="103" t="n"/>
+      <c r="H33" s="103" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="97" t="n">
+      <c r="A34" s="104" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="97" t="inlineStr">
+      <c r="B34" s="104" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C34" s="98" t="inlineStr">
+      <c r="C34" s="105" t="inlineStr">
         <is>
           <t>Mesa cocktail alta (escenario) ×1</t>
         </is>
       </c>
-      <c r="D34" s="99" t="n">
+      <c r="D34" s="106" t="n">
         <v>45000</v>
       </c>
       <c r="E34" s="61">
         <f>D34/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F34" s="100" t="inlineStr">
+      <c r="F34" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G34" s="101">
+      <c r="G34" s="108">
         <f>IF(F34="SÍ",D34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="97" t="inlineStr"/>
+      <c r="H34" s="104" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="97" t="n">
+      <c r="A35" s="104" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="97" t="inlineStr">
+      <c r="B35" s="104" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C35" s="98" t="inlineStr">
+      <c r="C35" s="105" t="inlineStr">
         <is>
           <t>Mesa alta para DJ ×1</t>
         </is>
       </c>
-      <c r="D35" s="99" t="n">
+      <c r="D35" s="106" t="n">
         <v>62300</v>
       </c>
       <c r="E35" s="61">
         <f>D35/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F35" s="100" t="inlineStr">
+      <c r="F35" s="107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G35" s="101">
+      <c r="G35" s="108">
         <f>IF(F35="SÍ",D35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="97" t="inlineStr"/>
+      <c r="H35" s="104" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="95" t="inlineStr">
+      <c r="A36" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  GENERALES</t>
         </is>
       </c>
-      <c r="B36" s="96" t="n"/>
-      <c r="C36" s="96" t="n"/>
-      <c r="D36" s="96" t="n"/>
-      <c r="E36" s="96" t="n"/>
-      <c r="F36" s="96" t="n"/>
-      <c r="G36" s="96" t="n"/>
-      <c r="H36" s="96" t="n"/>
+      <c r="B36" s="103" t="n"/>
+      <c r="C36" s="103" t="n"/>
+      <c r="D36" s="103" t="n"/>
+      <c r="E36" s="103" t="n"/>
+      <c r="F36" s="103" t="n"/>
+      <c r="G36" s="103" t="n"/>
+      <c r="H36" s="103" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="97" t="n">
+      <c r="A37" s="104" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="97" t="inlineStr">
+      <c r="B37" s="104" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C37" s="98" t="inlineStr">
+      <c r="C37" s="105" t="inlineStr">
         <is>
           <t>Dirección técnica de todo el evento + replanteo</t>
         </is>
       </c>
-      <c r="D37" s="99" t="n">
+      <c r="D37" s="106" t="n">
         <v>5149179.2</v>
       </c>
       <c r="E37" s="61">
         <f>D37/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F37" s="100" t="inlineStr">
+      <c r="F37" s="107" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G37" s="101">
+      <c r="G37" s="108">
         <f>IF(F37="SÍ",D37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="97" t="inlineStr">
+      <c r="H37" s="104" t="inlineStr">
         <is>
           <t>Ojo: el replanteo de sillas va aparte, con ingeniero propio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="97" t="n">
+      <c r="A38" s="104" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="97" t="inlineStr">
+      <c r="B38" s="104" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C38" s="98" t="inlineStr">
+      <c r="C38" s="105" t="inlineStr">
         <is>
           <t>Guardia eléctrica × 2 días</t>
         </is>
       </c>
-      <c r="D38" s="99" t="n">
+      <c r="D38" s="106" t="n">
         <v>865800</v>
       </c>
       <c r="E38" s="61">
         <f>D38/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F38" s="100" t="inlineStr">
+      <c r="F38" s="107" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G38" s="101">
+      <c r="G38" s="108">
         <f>IF(F38="SÍ",D38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="97" t="inlineStr"/>
+      <c r="H38" s="104" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="97" t="n">
+      <c r="A39" s="104" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="97" t="inlineStr">
+      <c r="B39" s="104" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C39" s="98" t="inlineStr">
+      <c r="C39" s="105" t="inlineStr">
         <is>
           <t>Guardia técnica × 2 días</t>
         </is>
       </c>
-      <c r="D39" s="99" t="n">
+      <c r="D39" s="106" t="n">
         <v>905200</v>
       </c>
       <c r="E39" s="61">
         <f>D39/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F39" s="100" t="inlineStr">
+      <c r="F39" s="107" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G39" s="101">
+      <c r="G39" s="108">
         <f>IF(F39="SÍ",D39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="97" t="inlineStr"/>
+      <c r="H39" s="104" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="3" t="inlineStr">
@@ -6859,7 +7270,7 @@
           <t>TOTAL del presupuesto de La Rural</t>
         </is>
       </c>
-      <c r="D41" s="102">
+      <c r="D41" s="109">
         <f>SUM(D6:D39)</f>
         <v/>
       </c>
@@ -6874,11 +7285,11 @@
           <t>Lo que se queda (marcado SÍ)</t>
         </is>
       </c>
-      <c r="D42" s="103">
+      <c r="D42" s="110">
         <f>SUM(G6:G39)</f>
         <v/>
       </c>
-      <c r="E42" s="104">
+      <c r="E42" s="89">
         <f>D42/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -6889,11 +7300,11 @@
           <t>Lo que se saca (marcado NO)</t>
         </is>
       </c>
-      <c r="D43" s="105">
+      <c r="D43" s="111">
         <f>D41-D42</f>
         <v/>
       </c>
-      <c r="E43" s="106">
+      <c r="E43" s="112">
         <f>D43/TABLERO!$C$4</f>
         <v/>
       </c>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -11,10 +11,11 @@
     <sheet name="COSTOS UNIFICADOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="TABLERO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="MERCH" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DECISIONES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AHORROS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="COTIZACIONES TÉCNICA" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="INFRAESTRUCTURA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PAGOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DECISIONES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AHORROS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="COTIZACIONES TÉCNICA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="INFRAESTRUCTURA" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COSTOS UNIFICADOS'!$A$4:$M$4</definedName>
@@ -237,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -445,6 +446,19 @@
     <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -464,8 +478,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5000,6 +5012,682 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cuánto se pagó, cuánto falta y cuándo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sólo lo que está documentado. Lo que no tiene fecha acordada va abajo, en el resto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Bloque</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>De dónde sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>YA PAGADO</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="95" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>La Rural — anticipo del contrato</t>
+        </is>
+      </c>
+      <c r="C6" s="96" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="89" t="n">
+        <v>43446</v>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="F6" s="95" t="inlineStr">
+        <is>
+          <t>Hoja PAGOS del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="95" t="inlineStr">
+        <is>
+          <t>Técnica</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>Grupo MET — factura INV-11</t>
+        </is>
+      </c>
+      <c r="C7" s="96" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="F7" s="95" t="inlineStr">
+        <is>
+          <t>Recibo de Mercury del 31/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="95" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>Pañuelos — 50% (parte Argentina)</t>
+        </is>
+      </c>
+      <c r="C8" s="96" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="89" t="n">
+        <v>3569.15</v>
+      </c>
+      <c r="E8" s="81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="F8" s="95" t="inlineStr">
+        <is>
+          <t>Master: 50% de US$10.982, imputado al 65%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="95" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>Gorras — 100%</t>
+        </is>
+      </c>
+      <c r="C9" s="96" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E9" s="81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="F9" s="95" t="inlineStr">
+        <is>
+          <t>Factura 2601009 de Textil Ryu</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="95" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>Lanyards — 50%</t>
+        </is>
+      </c>
+      <c r="C10" s="96" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="89" t="n">
+        <v>849</v>
+      </c>
+      <c r="E10" s="81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="F10" s="95" t="inlineStr">
+        <is>
+          <t>Hoja PAGOS del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="95" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>Gráfica Argentina — anticipo</t>
+        </is>
+      </c>
+      <c r="C11" s="96" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="n">
+        <v>642</v>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="F11" s="95" t="inlineStr">
+        <is>
+          <t>Master: total US$2.481, saldo US$1.839</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="n"/>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>Pagado a hoy</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39">
+        <f>SUM(D6:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>FALTA PAGAR · CON FECHA</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="97" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
+      <c r="B15" s="85" t="inlineStr">
+        <is>
+          <t>La Rural — saldo, cuota 1 de 2</t>
+        </is>
+      </c>
+      <c r="C15" s="98" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="99" t="n">
+        <v>15777</v>
+      </c>
+      <c r="E15" s="100" t="inlineStr">
+        <is>
+          <t>VENCIDA</t>
+        </is>
+      </c>
+      <c r="F15" s="97" t="inlineStr">
+        <is>
+          <t>Cronograma del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="97" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="B16" s="85" t="inlineStr">
+        <is>
+          <t>Intercoms — cuota 1 de 2</t>
+        </is>
+      </c>
+      <c r="C16" s="98" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="99" t="n">
+        <v>280</v>
+      </c>
+      <c r="E16" s="100" t="inlineStr">
+        <is>
+          <t>VENCIDA</t>
+        </is>
+      </c>
+      <c r="F16" s="97" t="inlineStr">
+        <is>
+          <t>Cronograma del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="97" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B17" s="85" t="inlineStr">
+        <is>
+          <t>Remeras (250)</t>
+        </is>
+      </c>
+      <c r="C17" s="98" t="inlineStr">
+        <is>
+          <t>ya facturado</t>
+        </is>
+      </c>
+      <c r="D17" s="99" t="n">
+        <v>2780.64</v>
+      </c>
+      <c r="E17" s="100" t="inlineStr">
+        <is>
+          <t>SIN PAGAR</t>
+        </is>
+      </c>
+      <c r="F17" s="97" t="inlineStr">
+        <is>
+          <t>Factura 2601017 del 16/08 · NO figura en el master</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="97" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B18" s="85" t="inlineStr">
+        <is>
+          <t>Bordado de gorras (940)</t>
+        </is>
+      </c>
+      <c r="C18" s="98" t="inlineStr">
+        <is>
+          <t>ya facturado</t>
+        </is>
+      </c>
+      <c r="D18" s="99" t="n">
+        <v>1721.95</v>
+      </c>
+      <c r="E18" s="100" t="inlineStr">
+        <is>
+          <t>SIN PAGAR</t>
+        </is>
+      </c>
+      <c r="F18" s="97" t="inlineStr">
+        <is>
+          <t>Factura 2601016 del 10/08 · NO figura en el master</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="101" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Pañuelos — saldo (parte Argentina)</t>
+        </is>
+      </c>
+      <c r="C19" s="102" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="103" t="n">
+        <v>3429.73</v>
+      </c>
+      <c r="E19" s="87" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F19" s="101" t="inlineStr">
+        <is>
+          <t>Factura 2601019 · 65% de 5.276,51 USDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="101" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B20" s="59" t="inlineStr">
+        <is>
+          <t>Gráfica Argentina — saldo</t>
+        </is>
+      </c>
+      <c r="C20" s="102" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="103" t="n">
+        <v>1192.37</v>
+      </c>
+      <c r="E20" s="87" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F20" s="101" t="inlineStr">
+        <is>
+          <t>Master. La factura 2601014 viene por el total: a confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="101" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>Lanyards — saldo</t>
+        </is>
+      </c>
+      <c r="C21" s="102" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="103" t="n">
+        <v>816.1</v>
+      </c>
+      <c r="E21" s="87" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F21" s="101" t="inlineStr">
+        <is>
+          <t>Master. La factura 2601018 viene por el total: a confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="101" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
+      <c r="B22" s="59" t="inlineStr">
+        <is>
+          <t>La Rural — saldo, cuota 2 de 2</t>
+        </is>
+      </c>
+      <c r="C22" s="102" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="103" t="n">
+        <v>15777</v>
+      </c>
+      <c r="E22" s="87" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F22" s="101" t="inlineStr">
+        <is>
+          <t>Cronograma del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="101" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>Intercoms — cuota 2 de 2</t>
+        </is>
+      </c>
+      <c r="C23" s="102" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="103" t="n">
+        <v>280</v>
+      </c>
+      <c r="E23" s="87" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F23" s="101" t="inlineStr">
+        <is>
+          <t>Cronograma del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="n"/>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>Comprometido con fecha</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39">
+        <f>SUM(D15:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="38" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>De eso, vencido o facturado sin pagar</t>
+        </is>
+      </c>
+      <c r="D25" s="99">
+        <f>SUMIF(E15:E23,"VENCIDA",D15:D23)+SUMIF(E15:E23,"SIN PAGAR",D15:D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>RESUMEN</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Costo total del evento</t>
+        </is>
+      </c>
+      <c r="D28" s="104">
+        <f>'COSTOS UNIFICADOS'!J59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Ya pagado</t>
+        </is>
+      </c>
+      <c r="D29" s="105">
+        <f>D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Falta desembolsar</t>
+        </is>
+      </c>
+      <c r="D30" s="106">
+        <f>'COSTOS UNIFICADOS'!J59-D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   de eso, con fecha acordada</t>
+        </is>
+      </c>
+      <c r="D31" s="107">
+        <f>D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   de eso, todavía sin fecha</t>
+        </is>
+      </c>
+      <c r="D32" s="107">
+        <f>'COSTOS UNIFICADOS'!J59-D12-D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Las remeras y el bordado de gorras están facturados desde agosto y no figuran en el cronograma del master: son US$4.503 que hoy no están en ningún calendario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>El resto sin fecha son los rubros cerrados y cotizados que todavía no tienen forma de pago acordada: técnica, entelado, CCTV, catering, sillas y los servicios del predio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Las facturas reemitidas de LEOTEX y Derqui vienen por el total aunque el master registra el 50% abonado. Acá se tomó la regla del 50%: si las facturas están bien, son US$2.008 más.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5252,7 +5940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5372,7 +6060,7 @@
         <f>D5-G5</f>
         <v/>
       </c>
-      <c r="I5" s="95">
+      <c r="I5" s="108">
         <f>IFERROR(H5/D5,"")</f>
         <v/>
       </c>
@@ -5416,7 +6104,7 @@
         <f>D6-G6</f>
         <v/>
       </c>
-      <c r="I6" s="95">
+      <c r="I6" s="108">
         <f>IFERROR(H6/D6,"")</f>
         <v/>
       </c>
@@ -5460,7 +6148,7 @@
         <f>D7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="95">
+      <c r="I7" s="108">
         <f>IFERROR(H7/D7,"")</f>
         <v/>
       </c>
@@ -5501,7 +6189,7 @@
         <f>D8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="95">
+      <c r="I8" s="108">
         <f>IFERROR(H8/D8,"")</f>
         <v/>
       </c>
@@ -5539,7 +6227,7 @@
         <f>D9-G9</f>
         <v/>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="108">
         <f>IFERROR(H9/D9,"")</f>
         <v/>
       </c>
@@ -5577,7 +6265,7 @@
         <f>D10-G10</f>
         <v/>
       </c>
-      <c r="I10" s="95">
+      <c r="I10" s="108">
         <f>IFERROR(H10/D10,"")</f>
         <v/>
       </c>
@@ -5593,15 +6281,15 @@
           <t>AHORRO TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="96">
+      <c r="D11" s="109">
         <f>SUM(D5:D10)</f>
         <v/>
       </c>
-      <c r="G11" s="96">
+      <c r="G11" s="109">
         <f>SUM(G5:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="96">
+      <c r="H11" s="109">
         <f>SUM(H5:H10)</f>
         <v/>
       </c>
@@ -5721,7 +6409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5820,7 +6508,7 @@
       </c>
       <c r="D5" s="30" t="n"/>
       <c r="E5" s="32" t="n"/>
-      <c r="F5" s="97">
+      <c r="F5" s="110">
         <f>IF(E5="","",E5/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5863,7 +6551,7 @@
         <f>D6*1.21</f>
         <v/>
       </c>
-      <c r="F6" s="98">
+      <c r="F6" s="111">
         <f>IF(E6="","",E6/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5905,7 +6593,7 @@
       <c r="E7" s="20" t="n">
         <v>59150850</v>
       </c>
-      <c r="F7" s="98">
+      <c r="F7" s="111">
         <f>IF(E7="","",E7/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5947,7 +6635,7 @@
       <c r="E8" s="20" t="n">
         <v>54450000</v>
       </c>
-      <c r="F8" s="98">
+      <c r="F8" s="111">
         <f>IF(E8="","",E8/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -5989,7 +6677,7 @@
       <c r="E9" s="20" t="n">
         <v>99220000</v>
       </c>
-      <c r="F9" s="98">
+      <c r="F9" s="111">
         <f>IF(E9="","",E9/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6031,7 +6719,7 @@
       <c r="E10" s="50" t="n">
         <v>15276250</v>
       </c>
-      <c r="F10" s="99">
+      <c r="F10" s="112">
         <f>IF(E10="","",E10/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6071,7 +6759,7 @@
       <c r="E11" s="40" t="n">
         <v>90600000</v>
       </c>
-      <c r="F11" s="100">
+      <c r="F11" s="113">
         <f>IF(E11="","",E11/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6168,7 +6856,7 @@
       <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="101" t="inlineStr">
+      <c r="A25" s="114" t="inlineStr">
         <is>
           <t>PARA CERRAR EL AHORRO DE TÉCNICA FALTA UNA SOLA COSA: el PDF de Grupo MET con el alcance final. Con eso se puede comparar contra el mismo alcance en Dixi, Bonetto, 2MG y Prina, y recién ahí poner un número.</t>
         </is>
@@ -6179,7 +6867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6255,1014 +6943,1014 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="102" t="inlineStr">
+      <c r="A5" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">  PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="B5" s="103" t="n"/>
-      <c r="C5" s="103" t="n"/>
-      <c r="D5" s="103" t="n"/>
-      <c r="E5" s="103" t="n"/>
-      <c r="F5" s="103" t="n"/>
-      <c r="G5" s="103" t="n"/>
-      <c r="H5" s="103" t="n"/>
+      <c r="B5" s="116" t="n"/>
+      <c r="C5" s="116" t="n"/>
+      <c r="D5" s="116" t="n"/>
+      <c r="E5" s="116" t="n"/>
+      <c r="F5" s="116" t="n"/>
+      <c r="G5" s="116" t="n"/>
+      <c r="H5" s="116" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="104" t="n">
+      <c r="A6" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="104" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C6" s="105" t="inlineStr">
+      <c r="C6" s="102" t="inlineStr">
         <is>
           <t>Oficina de producción — 25 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D6" s="106" t="n">
+      <c r="D6" s="117" t="n">
         <v>1314575</v>
       </c>
       <c r="E6" s="61">
         <f>D6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F6" s="107" t="inlineStr">
+      <c r="F6" s="118" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G6" s="108">
+      <c r="G6" s="119">
         <f>IF(F6="SÍ",D6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="104" t="inlineStr"/>
+      <c r="H6" s="101" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="104" t="n">
+      <c r="A7" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="104" t="inlineStr">
+      <c r="B7" s="101" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C7" s="105" t="inlineStr">
+      <c r="C7" s="102" t="inlineStr">
         <is>
           <t>Sala de staff — 100 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D7" s="106" t="n">
+      <c r="D7" s="117" t="n">
         <v>5258300</v>
       </c>
       <c r="E7" s="61">
         <f>D7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F7" s="107" t="inlineStr">
+      <c r="F7" s="118" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G7" s="108">
+      <c r="G7" s="119">
         <f>IF(F7="SÍ",D7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="104" t="inlineStr"/>
+      <c r="H7" s="101" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="104" t="n">
+      <c r="A8" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="104" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C8" s="105" t="inlineStr">
+      <c r="C8" s="102" t="inlineStr">
         <is>
           <t>Depósito 8×8 para las 2.500 barras — 64 m²</t>
         </is>
       </c>
-      <c r="D8" s="106" t="n">
+      <c r="D8" s="117" t="n">
         <v>3365312</v>
       </c>
       <c r="E8" s="61">
         <f>D8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="107" t="inlineStr">
+      <c r="F8" s="118" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G8" s="108">
+      <c r="G8" s="119">
         <f>IF(F8="SÍ",D8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="104" t="inlineStr">
+      <c r="H8" s="101" t="inlineStr">
         <is>
           <t>Depósito para las 2.500 barras de la dinámica.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="102" t="inlineStr">
+      <c r="A9" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · oficina de producción</t>
         </is>
       </c>
-      <c r="B9" s="103" t="n"/>
-      <c r="C9" s="103" t="n"/>
-      <c r="D9" s="103" t="n"/>
-      <c r="E9" s="103" t="n"/>
-      <c r="F9" s="103" t="n"/>
-      <c r="G9" s="103" t="n"/>
-      <c r="H9" s="103" t="n"/>
+      <c r="B9" s="116" t="n"/>
+      <c r="C9" s="116" t="n"/>
+      <c r="D9" s="116" t="n"/>
+      <c r="E9" s="116" t="n"/>
+      <c r="F9" s="116" t="n"/>
+      <c r="G9" s="116" t="n"/>
+      <c r="H9" s="116" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="104" t="n">
+      <c r="A10" s="101" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="104" t="inlineStr">
+      <c r="B10" s="101" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C10" s="105" t="inlineStr">
+      <c r="C10" s="102" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×2</t>
         </is>
       </c>
-      <c r="D10" s="106" t="n">
+      <c r="D10" s="117" t="n">
         <v>236000</v>
       </c>
       <c r="E10" s="61">
         <f>D10/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="107" t="inlineStr">
+      <c r="F10" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G10" s="108">
+      <c r="G10" s="119">
         <f>IF(F10="SÍ",D10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="104" t="inlineStr"/>
+      <c r="H10" s="101" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="104" t="n">
+      <c r="A11" s="101" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="104" t="inlineStr">
+      <c r="B11" s="101" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C11" s="105" t="inlineStr">
+      <c r="C11" s="102" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×10</t>
         </is>
       </c>
-      <c r="D11" s="106" t="n">
+      <c r="D11" s="117" t="n">
         <v>85000</v>
       </c>
       <c r="E11" s="61">
         <f>D11/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="107" t="inlineStr">
+      <c r="F11" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G11" s="108">
+      <c r="G11" s="119">
         <f>IF(F11="SÍ",D11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="104" t="inlineStr"/>
+      <c r="H11" s="101" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="104" t="n">
+      <c r="A12" s="101" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="104" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C12" s="105" t="inlineStr">
+      <c r="C12" s="102" t="inlineStr">
         <is>
           <t>Sillón Valencia 2C ×2</t>
         </is>
       </c>
-      <c r="D12" s="106" t="n">
+      <c r="D12" s="117" t="n">
         <v>254000</v>
       </c>
       <c r="E12" s="61">
         <f>D12/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="107" t="inlineStr">
+      <c r="F12" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G12" s="108">
+      <c r="G12" s="119">
         <f>IF(F12="SÍ",D12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="104" t="inlineStr"/>
+      <c r="H12" s="101" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="104" t="n">
+      <c r="A13" s="101" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="104" t="inlineStr">
+      <c r="B13" s="101" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C13" s="105" t="inlineStr">
+      <c r="C13" s="102" t="inlineStr">
         <is>
           <t>Sillón BRNO ×2</t>
         </is>
       </c>
-      <c r="D13" s="106" t="n">
+      <c r="D13" s="117" t="n">
         <v>160000</v>
       </c>
       <c r="E13" s="61">
         <f>D13/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="107" t="inlineStr">
+      <c r="F13" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="108">
+      <c r="G13" s="119">
         <f>IF(F13="SÍ",D13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="104" t="inlineStr"/>
+      <c r="H13" s="101" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="104" t="n">
+      <c r="A14" s="101" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="104" t="inlineStr">
+      <c r="B14" s="101" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C14" s="105" t="inlineStr">
+      <c r="C14" s="102" t="inlineStr">
         <is>
           <t>Mesa ratona ×1</t>
         </is>
       </c>
-      <c r="D14" s="106" t="n">
+      <c r="D14" s="117" t="n">
         <v>118000</v>
       </c>
       <c r="E14" s="61">
         <f>D14/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="107" t="inlineStr">
+      <c r="F14" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="108">
+      <c r="G14" s="119">
         <f>IF(F14="SÍ",D14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="104" t="inlineStr"/>
+      <c r="H14" s="101" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="104" t="n">
+      <c r="A15" s="101" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="104" t="inlineStr">
+      <c r="B15" s="101" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C15" s="105" t="inlineStr">
+      <c r="C15" s="102" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D15" s="106" t="n">
+      <c r="D15" s="117" t="n">
         <v>40000</v>
       </c>
       <c r="E15" s="61">
         <f>D15/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="107" t="inlineStr">
+      <c r="F15" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G15" s="108">
+      <c r="G15" s="119">
         <f>IF(F15="SÍ",D15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="104" t="inlineStr"/>
+      <c r="H15" s="101" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="104" t="n">
+      <c r="A16" s="101" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="104" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C16" s="105" t="inlineStr">
+      <c r="C16" s="102" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D16" s="106" t="n">
+      <c r="D16" s="117" t="n">
         <v>56300</v>
       </c>
       <c r="E16" s="61">
         <f>D16/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="107" t="inlineStr">
+      <c r="F16" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G16" s="108">
+      <c r="G16" s="119">
         <f>IF(F16="SÍ",D16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="104" t="inlineStr"/>
+      <c r="H16" s="101" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="102" t="inlineStr">
+      <c r="A17" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala de staff</t>
         </is>
       </c>
-      <c r="B17" s="103" t="n"/>
-      <c r="C17" s="103" t="n"/>
-      <c r="D17" s="103" t="n"/>
-      <c r="E17" s="103" t="n"/>
-      <c r="F17" s="103" t="n"/>
-      <c r="G17" s="103" t="n"/>
-      <c r="H17" s="103" t="n"/>
+      <c r="B17" s="116" t="n"/>
+      <c r="C17" s="116" t="n"/>
+      <c r="D17" s="116" t="n"/>
+      <c r="E17" s="116" t="n"/>
+      <c r="F17" s="116" t="n"/>
+      <c r="G17" s="116" t="n"/>
+      <c r="H17" s="116" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="104" t="n">
+      <c r="A18" s="101" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="104" t="inlineStr">
+      <c r="B18" s="101" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C18" s="105" t="inlineStr">
+      <c r="C18" s="102" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×5</t>
         </is>
       </c>
-      <c r="D18" s="106" t="n">
+      <c r="D18" s="117" t="n">
         <v>590000</v>
       </c>
       <c r="E18" s="61">
         <f>D18/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="107" t="inlineStr">
+      <c r="F18" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G18" s="108">
+      <c r="G18" s="119">
         <f>IF(F18="SÍ",D18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="104" t="inlineStr"/>
+      <c r="H18" s="101" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="104" t="n">
+      <c r="A19" s="101" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="104" t="inlineStr">
+      <c r="B19" s="101" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C19" s="105" t="inlineStr">
+      <c r="C19" s="102" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×40</t>
         </is>
       </c>
-      <c r="D19" s="106" t="n">
+      <c r="D19" s="117" t="n">
         <v>340000</v>
       </c>
       <c r="E19" s="61">
         <f>D19/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="107" t="inlineStr">
+      <c r="F19" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G19" s="108">
+      <c r="G19" s="119">
         <f>IF(F19="SÍ",D19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="104" t="inlineStr"/>
+      <c r="H19" s="101" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="104" t="n">
+      <c r="A20" s="101" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="104" t="inlineStr">
+      <c r="B20" s="101" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C20" s="105" t="inlineStr">
+      <c r="C20" s="102" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D20" s="106" t="n">
+      <c r="D20" s="117" t="n">
         <v>40000</v>
       </c>
       <c r="E20" s="61">
         <f>D20/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="107" t="inlineStr">
+      <c r="F20" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="108">
+      <c r="G20" s="119">
         <f>IF(F20="SÍ",D20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="104" t="inlineStr"/>
+      <c r="H20" s="101" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="104" t="n">
+      <c r="A21" s="101" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="104" t="inlineStr">
+      <c r="B21" s="101" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C21" s="105" t="inlineStr">
+      <c r="C21" s="102" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D21" s="106" t="n">
+      <c r="D21" s="117" t="n">
         <v>56300</v>
       </c>
       <c r="E21" s="61">
         <f>D21/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F21" s="107" t="inlineStr">
+      <c r="F21" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="108">
+      <c r="G21" s="119">
         <f>IF(F21="SÍ",D21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="104" t="inlineStr"/>
+      <c r="H21" s="101" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="102" t="inlineStr">
+      <c r="A22" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala principal</t>
         </is>
       </c>
-      <c r="B22" s="103" t="n"/>
-      <c r="C22" s="103" t="n"/>
-      <c r="D22" s="103" t="n"/>
-      <c r="E22" s="103" t="n"/>
-      <c r="F22" s="103" t="n"/>
-      <c r="G22" s="103" t="n"/>
-      <c r="H22" s="103" t="n"/>
+      <c r="B22" s="116" t="n"/>
+      <c r="C22" s="116" t="n"/>
+      <c r="D22" s="116" t="n"/>
+      <c r="E22" s="116" t="n"/>
+      <c r="F22" s="116" t="n"/>
+      <c r="G22" s="116" t="n"/>
+      <c r="H22" s="116" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="104" t="n">
+      <c r="A23" s="101" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="104" t="inlineStr">
+      <c r="B23" s="101" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C23" s="105" t="inlineStr">
+      <c r="C23" s="102" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×5.000</t>
         </is>
       </c>
-      <c r="D23" s="106" t="n">
+      <c r="D23" s="117" t="n">
         <v>42500000</v>
       </c>
       <c r="E23" s="61">
         <f>D23/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F23" s="107" t="inlineStr">
+      <c r="F23" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G23" s="108">
+      <c r="G23" s="119">
         <f>IF(F23="SÍ",D23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="104" t="inlineStr">
+      <c r="H23" s="101" t="inlineStr">
         <is>
           <t>Reemplazadas por las 5.500 sillas de FDL Eventos.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="104" t="n">
+      <c r="A24" s="101" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="104" t="inlineStr">
+      <c r="B24" s="101" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C24" s="105" t="inlineStr">
+      <c r="C24" s="102" t="inlineStr">
         <is>
           <t>Mesa 1,80 × 0,90 ×40</t>
         </is>
       </c>
-      <c r="D24" s="106" t="n">
+      <c r="D24" s="117" t="n">
         <v>2500000</v>
       </c>
       <c r="E24" s="61">
         <f>D24/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F24" s="107" t="inlineStr">
+      <c r="F24" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G24" s="108">
+      <c r="G24" s="119">
         <f>IF(F24="SÍ",D24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="104" t="inlineStr"/>
+      <c r="H24" s="101" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="104" t="n">
+      <c r="A25" s="101" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="104" t="inlineStr">
+      <c r="B25" s="101" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C25" s="105" t="inlineStr">
+      <c r="C25" s="102" t="inlineStr">
         <is>
           <t>Mantel ×40</t>
         </is>
       </c>
-      <c r="D25" s="106" t="n">
+      <c r="D25" s="117" t="n">
         <v>900000</v>
       </c>
       <c r="E25" s="61">
         <f>D25/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F25" s="107" t="inlineStr">
+      <c r="F25" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G25" s="108">
+      <c r="G25" s="119">
         <f>IF(F25="SÍ",D25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="104" t="inlineStr"/>
+      <c r="H25" s="101" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="104" t="n">
+      <c r="A26" s="101" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="104" t="inlineStr">
+      <c r="B26" s="101" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C26" s="105" t="inlineStr">
+      <c r="C26" s="102" t="inlineStr">
         <is>
           <t>Mantel redondo ×8</t>
         </is>
       </c>
-      <c r="D26" s="106" t="n">
+      <c r="D26" s="117" t="n">
         <v>256000</v>
       </c>
       <c r="E26" s="61">
         <f>D26/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F26" s="107" t="inlineStr">
+      <c r="F26" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G26" s="108">
+      <c r="G26" s="119">
         <f>IF(F26="SÍ",D26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="104" t="inlineStr"/>
+      <c r="H26" s="101" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="102" t="inlineStr">
+      <c r="A27" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · camarín de speakers</t>
         </is>
       </c>
-      <c r="B27" s="103" t="n"/>
-      <c r="C27" s="103" t="n"/>
-      <c r="D27" s="103" t="n"/>
-      <c r="E27" s="103" t="n"/>
-      <c r="F27" s="103" t="n"/>
-      <c r="G27" s="103" t="n"/>
-      <c r="H27" s="103" t="n"/>
+      <c r="B27" s="116" t="n"/>
+      <c r="C27" s="116" t="n"/>
+      <c r="D27" s="116" t="n"/>
+      <c r="E27" s="116" t="n"/>
+      <c r="F27" s="116" t="n"/>
+      <c r="G27" s="116" t="n"/>
+      <c r="H27" s="116" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="104" t="n">
+      <c r="A28" s="101" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="104" t="inlineStr">
+      <c r="B28" s="101" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C28" s="105" t="inlineStr">
+      <c r="C28" s="102" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×1</t>
         </is>
       </c>
-      <c r="D28" s="106" t="n">
+      <c r="D28" s="117" t="n">
         <v>118000</v>
       </c>
       <c r="E28" s="61">
         <f>D28/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F28" s="107" t="inlineStr">
+      <c r="F28" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G28" s="108">
+      <c r="G28" s="119">
         <f>IF(F28="SÍ",D28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="104" t="inlineStr"/>
+      <c r="H28" s="101" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="104" t="n">
+      <c r="A29" s="101" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="104" t="inlineStr">
+      <c r="B29" s="101" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C29" s="105" t="inlineStr">
+      <c r="C29" s="102" t="inlineStr">
         <is>
           <t>Espejo ×1</t>
         </is>
       </c>
-      <c r="D29" s="106" t="n">
+      <c r="D29" s="117" t="n">
         <v>79500</v>
       </c>
       <c r="E29" s="61">
         <f>D29/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F29" s="107" t="inlineStr">
+      <c r="F29" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G29" s="108">
+      <c r="G29" s="119">
         <f>IF(F29="SÍ",D29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="104" t="inlineStr"/>
+      <c r="H29" s="101" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="104" t="n">
+      <c r="A30" s="101" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="104" t="inlineStr">
+      <c r="B30" s="101" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C30" s="105" t="inlineStr">
+      <c r="C30" s="102" t="inlineStr">
         <is>
           <t>Juego de living (sillones + mesa ratona)</t>
         </is>
       </c>
-      <c r="D30" s="106" t="n">
+      <c r="D30" s="117" t="n">
         <v>1103642</v>
       </c>
       <c r="E30" s="61">
         <f>D30/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F30" s="107" t="inlineStr">
+      <c r="F30" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G30" s="108">
+      <c r="G30" s="119">
         <f>IF(F30="SÍ",D30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="104" t="inlineStr">
+      <c r="H30" s="101" t="inlineStr">
         <is>
           <t>El mobiliario "más fino" del camarín: candidato a contratárselo a La Rural.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="104" t="n">
+      <c r="A31" s="101" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="104" t="inlineStr">
+      <c r="B31" s="101" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C31" s="105" t="inlineStr">
+      <c r="C31" s="102" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D31" s="106" t="n">
+      <c r="D31" s="117" t="n">
         <v>40000</v>
       </c>
       <c r="E31" s="61">
         <f>D31/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F31" s="107" t="inlineStr">
+      <c r="F31" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G31" s="108">
+      <c r="G31" s="119">
         <f>IF(F31="SÍ",D31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="104" t="inlineStr"/>
+      <c r="H31" s="101" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="104" t="n">
+      <c r="A32" s="101" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="104" t="inlineStr">
+      <c r="B32" s="101" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C32" s="105" t="inlineStr">
+      <c r="C32" s="102" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D32" s="106" t="n">
+      <c r="D32" s="117" t="n">
         <v>56300</v>
       </c>
       <c r="E32" s="61">
         <f>D32/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F32" s="107" t="inlineStr">
+      <c r="F32" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G32" s="108">
+      <c r="G32" s="119">
         <f>IF(F32="SÍ",D32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="104" t="inlineStr"/>
+      <c r="H32" s="101" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="102" t="inlineStr">
+      <c r="A33" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · escenario y técnica</t>
         </is>
       </c>
-      <c r="B33" s="103" t="n"/>
-      <c r="C33" s="103" t="n"/>
-      <c r="D33" s="103" t="n"/>
-      <c r="E33" s="103" t="n"/>
-      <c r="F33" s="103" t="n"/>
-      <c r="G33" s="103" t="n"/>
-      <c r="H33" s="103" t="n"/>
+      <c r="B33" s="116" t="n"/>
+      <c r="C33" s="116" t="n"/>
+      <c r="D33" s="116" t="n"/>
+      <c r="E33" s="116" t="n"/>
+      <c r="F33" s="116" t="n"/>
+      <c r="G33" s="116" t="n"/>
+      <c r="H33" s="116" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="104" t="n">
+      <c r="A34" s="101" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="104" t="inlineStr">
+      <c r="B34" s="101" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C34" s="105" t="inlineStr">
+      <c r="C34" s="102" t="inlineStr">
         <is>
           <t>Mesa cocktail alta (escenario) ×1</t>
         </is>
       </c>
-      <c r="D34" s="106" t="n">
+      <c r="D34" s="117" t="n">
         <v>45000</v>
       </c>
       <c r="E34" s="61">
         <f>D34/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F34" s="107" t="inlineStr">
+      <c r="F34" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G34" s="108">
+      <c r="G34" s="119">
         <f>IF(F34="SÍ",D34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="104" t="inlineStr"/>
+      <c r="H34" s="101" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="104" t="n">
+      <c r="A35" s="101" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="104" t="inlineStr">
+      <c r="B35" s="101" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C35" s="105" t="inlineStr">
+      <c r="C35" s="102" t="inlineStr">
         <is>
           <t>Mesa alta para DJ ×1</t>
         </is>
       </c>
-      <c r="D35" s="106" t="n">
+      <c r="D35" s="117" t="n">
         <v>62300</v>
       </c>
       <c r="E35" s="61">
         <f>D35/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F35" s="107" t="inlineStr">
+      <c r="F35" s="118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G35" s="108">
+      <c r="G35" s="119">
         <f>IF(F35="SÍ",D35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="104" t="inlineStr"/>
+      <c r="H35" s="101" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="102" t="inlineStr">
+      <c r="A36" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">  GENERALES</t>
         </is>
       </c>
-      <c r="B36" s="103" t="n"/>
-      <c r="C36" s="103" t="n"/>
-      <c r="D36" s="103" t="n"/>
-      <c r="E36" s="103" t="n"/>
-      <c r="F36" s="103" t="n"/>
-      <c r="G36" s="103" t="n"/>
-      <c r="H36" s="103" t="n"/>
+      <c r="B36" s="116" t="n"/>
+      <c r="C36" s="116" t="n"/>
+      <c r="D36" s="116" t="n"/>
+      <c r="E36" s="116" t="n"/>
+      <c r="F36" s="116" t="n"/>
+      <c r="G36" s="116" t="n"/>
+      <c r="H36" s="116" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="104" t="n">
+      <c r="A37" s="101" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="104" t="inlineStr">
+      <c r="B37" s="101" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C37" s="105" t="inlineStr">
+      <c r="C37" s="102" t="inlineStr">
         <is>
           <t>Dirección técnica de todo el evento + replanteo</t>
         </is>
       </c>
-      <c r="D37" s="106" t="n">
+      <c r="D37" s="117" t="n">
         <v>5149179.2</v>
       </c>
       <c r="E37" s="61">
         <f>D37/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F37" s="107" t="inlineStr">
+      <c r="F37" s="118" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G37" s="108">
+      <c r="G37" s="119">
         <f>IF(F37="SÍ",D37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="104" t="inlineStr">
+      <c r="H37" s="101" t="inlineStr">
         <is>
           <t>Ojo: el replanteo de sillas va aparte, con ingeniero propio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="104" t="n">
+      <c r="A38" s="101" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="104" t="inlineStr">
+      <c r="B38" s="101" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C38" s="105" t="inlineStr">
+      <c r="C38" s="102" t="inlineStr">
         <is>
           <t>Guardia eléctrica × 2 días</t>
         </is>
       </c>
-      <c r="D38" s="106" t="n">
+      <c r="D38" s="117" t="n">
         <v>865800</v>
       </c>
       <c r="E38" s="61">
         <f>D38/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F38" s="107" t="inlineStr">
+      <c r="F38" s="118" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G38" s="108">
+      <c r="G38" s="119">
         <f>IF(F38="SÍ",D38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="104" t="inlineStr"/>
+      <c r="H38" s="101" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="104" t="n">
+      <c r="A39" s="101" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="104" t="inlineStr">
+      <c r="B39" s="101" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C39" s="105" t="inlineStr">
+      <c r="C39" s="102" t="inlineStr">
         <is>
           <t>Guardia técnica × 2 días</t>
         </is>
       </c>
-      <c r="D39" s="106" t="n">
+      <c r="D39" s="117" t="n">
         <v>905200</v>
       </c>
       <c r="E39" s="61">
         <f>D39/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F39" s="107" t="inlineStr">
+      <c r="F39" s="118" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G39" s="108">
+      <c r="G39" s="119">
         <f>IF(F39="SÍ",D39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="104" t="inlineStr"/>
+      <c r="H39" s="101" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="3" t="inlineStr">
@@ -7270,7 +7958,7 @@
           <t>TOTAL del presupuesto de La Rural</t>
         </is>
       </c>
-      <c r="D41" s="109">
+      <c r="D41" s="120">
         <f>SUM(D6:D39)</f>
         <v/>
       </c>
@@ -7285,7 +7973,7 @@
           <t>Lo que se queda (marcado SÍ)</t>
         </is>
       </c>
-      <c r="D42" s="110">
+      <c r="D42" s="121">
         <f>SUM(G6:G39)</f>
         <v/>
       </c>
@@ -7300,11 +7988,11 @@
           <t>Lo que se saca (marcado NO)</t>
         </is>
       </c>
-      <c r="D43" s="111">
+      <c r="D43" s="122">
         <f>D41-D42</f>
         <v/>
       </c>
-      <c r="E43" s="112">
+      <c r="E43" s="123">
         <f>D43/TABLERO!$C$4</f>
         <v/>
       </c>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -144,12 +144,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -278,6 +278,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -308,6 +311,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -317,64 +356,25 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -388,9 +388,9 @@
     <xf numFmtId="3" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -426,7 +426,7 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -435,15 +435,15 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -455,21 +455,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,10 +481,10 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1078,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1251,1171 +1251,1049 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Infraestructura La Rural (armado de stands)</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal Sede</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="19">
+        <f>SUMIF($D$6:$D$6,"&lt;&gt;Alternativa",$J$6:$J$6)</f>
+        <v/>
+      </c>
+      <c r="K7" s="19">
+        <f>SUM($K$6:$K$6)</f>
+        <v/>
+      </c>
+      <c r="L7" s="19">
+        <f>J7-K7</f>
+        <v/>
+      </c>
+      <c r="M7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Armado de stands</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>La Rural — Jefatura de Infraestructura</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Armado del stand de staff (100 m²), el de producción (menos de 50 m²) y el mobiliario del camarín de speakers. Falta pedirles los espejos. Las sillas del público van en su propia línea.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Cerrado</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>9270</v>
       </c>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="14">
-        <f>IF(F7="","",F7*(1+N(G7)))</f>
-        <v/>
-      </c>
-      <c r="I7" s="15" t="n">
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="14">
+        <f>IF(F9="","",F9*(1+N(G9)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="14">
-        <f>IF(OR(D7="Bonificado",D7="Reemplazado"),0,N(I7)*IF(H7="",N(K7),IF(E7="USD",H7,H7/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="14">
-        <f>IF(D7="Alternativa","",J7-N(K7))</f>
-        <v/>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="J9" s="14">
+        <f>IF(OR(D9="Bonificado",D9="Reemplazado"),0,N(I9)*IF(H9="",N(K9),IF(E9="USD",H9,H9/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="14">
+        <f>IF(D9="Alternativa","",J9-N(K9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t>Definición de Agustina sobre el presupuesto de $66.494.708 del 17/08 · ver hoja AHORROS</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal Infraestructura</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="19">
+        <f>SUMIF($D$9:$D$9,"&lt;&gt;Alternativa",$J$9:$J$9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>SUM($K$9:$K$9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f>J10-K10</f>
+        <v/>
+      </c>
+      <c r="M10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Sillas del público (5.500)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>FDL Eventos</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Presupuesto 026-2697, alquiler por 4 días: 1.000 sillas hotel caño gris tapizado negro ($7.000.000) + 4.500 sillas plásticas Munro reforzadas ($17.100.000) + flete ($1.700.000). NO incluye armado.</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F12" s="23" t="n">
         <v>25800000</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G12" s="24" t="n">
         <v>0.21</v>
       </c>
-      <c r="H8" s="22">
-        <f>IF(F8="","",F8*(1+N(G8)))</f>
-        <v/>
-      </c>
-      <c r="I8" s="23" t="n">
+      <c r="H12" s="25">
+        <f>IF(F12="","",F12*(1+N(G12)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="24">
-        <f>IF(OR(D8="Bonificado",D8="Reemplazado"),0,N(I8)*IF(H8="",N(K8),IF(E8="USD",H8,H8/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K8" s="25" t="n">
+      <c r="J12" s="27">
+        <f>IF(OR(D12="Bonificado",D12="Reemplazado"),0,N(I12)*IF(H12="",N(K12),IF(E12="USD",H12,H12/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="28" t="n">
         <v>16500</v>
       </c>
-      <c r="L8" s="24">
-        <f>IF(D8="Alternativa","",J8-N(K8))</f>
-        <v/>
-      </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="L12" s="27">
+        <f>IF(D12="Alternativa","",J12-N(K12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t>Presupuesto FDL Eventos N.º 026-2697 del 07/08/2026 · pendiente de resolver facturación al exterior</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Montaje, acomodación y desmontaje de sillas</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>En negociación</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>Montaje previo, acomodación el sábado a la noche después de la dinámica y desmontaje el domingo.</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>En negociación</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F13" s="33" t="n">
         <v>900000</v>
       </c>
-      <c r="G9" s="31" t="n"/>
-      <c r="H9" s="32">
-        <f>IF(F9="","",F9*(1+N(G9)))</f>
-        <v/>
-      </c>
-      <c r="I9" s="33" t="n">
+      <c r="G13" s="34" t="n"/>
+      <c r="H13" s="35">
+        <f>IF(F13="","",F13*(1+N(G13)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="34">
-        <f>IF(OR(D9="Bonificado",D9="Reemplazado"),0,N(I9)*IF(H9="",N(K9),IF(E9="USD",H9,H9/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K9" s="35" t="n"/>
-      <c r="L9" s="34">
-        <f>IF(D9="Alternativa","",J9-N(K9))</f>
-        <v/>
-      </c>
-      <c r="M9" s="36" t="inlineStr">
+      <c r="J13" s="37">
+        <f>IF(OR(D13="Bonificado",D13="Reemplazado"),0,N(I13)*IF(H13="",N(K13),IF(E13="USD",H13,H13/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="37">
+        <f>IF(D13="Alternativa","",J13-N(K13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="39" t="inlineStr">
         <is>
           <t>Negociación de Agustina · cerrar el número antes de firmar las sillas</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>Replanteo de sillas (ingeniero)</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>Replanteo del layout de sillas del pabellón. Confirmado que va aparte de la dirección técnica de La Rural.</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E14" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="31" t="n"/>
-      <c r="H10" s="34">
-        <f>IF(F10="","",F10*(1+N(G10)))</f>
-        <v/>
-      </c>
-      <c r="I10" s="33" t="n">
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="34" t="n"/>
+      <c r="H14" s="37">
+        <f>IF(F14="","",F14*(1+N(G14)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="34">
-        <f>IF(OR(D10="Bonificado",D10="Reemplazado"),0,N(I10)*IF(H10="",N(K10),IF(E10="USD",H10,H10/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K10" s="35" t="n"/>
-      <c r="L10" s="34">
-        <f>IF(D10="Alternativa","",J10-N(K10))</f>
-        <v/>
-      </c>
-      <c r="M10" s="36" t="inlineStr">
+      <c r="J14" s="37">
+        <f>IF(OR(D14="Bonificado",D14="Reemplazado"),0,N(I14)*IF(H14="",N(K14),IF(E14="USD",H14,H14/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="37">
+        <f>IF(D14="Alternativa","",J14-N(K14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="39" t="inlineStr">
         <is>
           <t>Pendiente de pedir presupuesto</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal Mobiliario</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="19">
+        <f>SUMIF($D$12:$D$14,"&lt;&gt;Alternativa",$J$12:$J$14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="19">
+        <f>SUM($K$12:$K$14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="19">
+        <f>J15-K15</f>
+        <v/>
+      </c>
+      <c r="M15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>TÉCNICA</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Producción técnica</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Cerrado por Agustina</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Sonido, iluminación, video y LED. Cerrado en dólares.</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="14">
+        <f>IF(F17="","",F17*(1+N(G17)))</f>
+        <v/>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="14">
+        <f>IF(OR(D17="Bonificado",D17="Reemplazado"),0,N(I17)*IF(H17="",N(K17),IF(E17="USD",H17,H17/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L17" s="14">
+        <f>IF(D17="Alternativa","",J17-N(K17))</f>
+        <v/>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina · reemplaza la cotización vencida de Prina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Entelado</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Cerrado por Agustina</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Entelado del pabellón. Negociado a la mitad de lo que estaba cotizado.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="41">
+        <f>IF(F18="","",F18*(1+N(G18)))</f>
+        <v/>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="14">
+        <f>IF(OR(D18="Bonificado",D18="Reemplazado"),0,N(I18)*IF(H18="",N(K18),IF(E18="USD",H18,H18/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="14">
+        <f>IF(D18="Alternativa","",J18-N(K18))</f>
+        <v/>
+      </c>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina · US$16.000 aprox. al dólar de referencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Circuito cerrado (CCTV)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Cerrado por Agustina</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Circuito cerrado de cámaras para el pabellón.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>6209</v>
+      </c>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="14">
+        <f>IF(F19="","",F19*(1+N(G19)))</f>
+        <v/>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="14">
+        <f>IF(OR(D19="Bonificado",D19="Reemplazado"),0,N(I19)*IF(H19="",N(K19),IF(E19="USD",H19,H19/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="14">
+        <f>IF(D19="Alternativa","",J19-N(K19))</f>
+        <v/>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>Bonificado por el proveedor de técnica</t>
+        </is>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>Sin costo</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="inlineStr">
+        <is>
+          <t>500 vallas y efectos especiales, sin cargo. Es lo que evita el gasto de vallado que estaba presupuestado.</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F20" s="45" t="n"/>
+      <c r="G20" s="46" t="n"/>
+      <c r="H20" s="47">
+        <f>IF(F20="","",F20*(1+N(G20)))</f>
+        <v/>
+      </c>
+      <c r="I20" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="47">
+        <f>IF(OR(D20="Bonificado",D20="Reemplazado"),0,N(I20)*IF(H20="",N(K20),IF(E20="USD",H20,H20/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="47">
+        <f>IF(D20="Alternativa","",J20-N(K20))</f>
+        <v/>
+      </c>
+      <c r="M20" s="49" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal Técnica</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="19">
+        <f>SUMIF($D$17:$D$20,"&lt;&gt;Alternativa",$J$17:$J$20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="19">
+        <f>SUM($K$17:$K$20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="19">
+        <f>J21-K21</f>
+        <v/>
+      </c>
+      <c r="M21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Conectividad WiFi</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>La Rural — Servicios de Conectividad</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>2 redes privadas de 30 Mbps (técnica + staff/acreditación), del 2 al 4 de octubre</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>Cotizado</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F23" s="23" t="n">
         <v>1466063.84</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G23" s="24" t="n">
         <v>0.21</v>
       </c>
-      <c r="H11" s="22">
-        <f>IF(F11="","",F11*(1+N(G11)))</f>
-        <v/>
-      </c>
-      <c r="I11" s="23" t="n">
+      <c r="H23" s="25">
+        <f>IF(F23="","",F23*(1+N(G23)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="24">
-        <f>IF(OR(D11="Bonificado",D11="Reemplazado"),0,N(I11)*IF(H11="",N(K11),IF(E11="USD",H11,H11/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K11" s="25" t="n">
+      <c r="J23" s="27">
+        <f>IF(OR(D23="Bonificado",D23="Reemplazado"),0,N(I23)*IF(H23="",N(K23),IF(E23="USD",H23,H23/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K23" s="28" t="n">
         <v>800</v>
       </c>
-      <c r="L11" s="24">
-        <f>IF(D11="Alternativa","",J11-N(K11))</f>
-        <v/>
-      </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="L23" s="27">
+        <f>IF(D23="Alternativa","",J23-N(K23))</f>
+        <v/>
+      </c>
+      <c r="M23" s="29" t="inlineStr">
         <is>
           <t>Mail conectividad@larural.com.ar 05/08/2026 · presupuesto N.º 2, base IPC junio (el del 16/06 era $1.438.728)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>Subtotal Sede</t>
-        </is>
-      </c>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n"/>
-      <c r="H12" s="38" t="n"/>
-      <c r="I12" s="38" t="n"/>
-      <c r="J12" s="39">
-        <f>SUMIF($D$6:$D$11,"&lt;&gt;Alternativa",$J$6:$J$11)</f>
-        <v/>
-      </c>
-      <c r="K12" s="39">
-        <f>SUM($K$6:$K$11)</f>
-        <v/>
-      </c>
-      <c r="L12" s="39">
-        <f>J12-K12</f>
-        <v/>
-      </c>
-      <c r="M12" s="38" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>TÉCNICA</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Producción técnica</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Cerrado por Agustina</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Sonido, iluminación, video y LED. Cerrado en dólares.</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>Seguridad y vigilancia</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Road Seguridad S.A.</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>263 horas de vigilancia (armado, evento y desarme) + planos de evacuación $715.000 + supervisión general $795.000</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>7218928.96</v>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H24" s="25">
+        <f>IF(F24="","",F24*(1+N(G24)))</f>
+        <v/>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="27">
+        <f>IF(OR(D24="Bonificado",D24="Reemplazado"),0,N(I24)*IF(H24="",N(K24),IF(E24="USD",H24,H24/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="27">
+        <f>IF(D24="Alternativa","",J24-N(K24))</f>
+        <v/>
+      </c>
+      <c r="M24" s="29" t="inlineStr">
+        <is>
+          <t>Mail presupuestos@roadseguridad.com.ar 12/08/2026 (versión V3, lista para firmar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Servicio médico</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Vittal — Socorro Médico Privado</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>1 UTIM TRI con dos médicos + enfermero/chofer, los tres días (2, 3 y 4 de octubre)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>6366521.27</v>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H25" s="25">
+        <f>IF(F25="","",F25*(1+N(G25)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="27">
+        <f>IF(OR(D25="Bonificado",D25="Reemplazado"),0,N(I25)*IF(H25="",N(K25),IF(E25="USD",H25,H25/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K25" s="28" t="n"/>
+      <c r="L25" s="27">
+        <f>IF(D25="Alternativa","",J25-N(K25))</f>
+        <v/>
+      </c>
+      <c r="M25" s="29" t="inlineStr">
+        <is>
+          <t>Mail vtomas@vittal.com.ar 28/08/2026 · tarifas actualizadas, sin consultorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Higia Eventos</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>205,5 horas de limpieza: auditorio, baños y guardarropas, del 2 al 5 de octubre</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>3367440.91</v>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H26" s="25">
+        <f>IF(F26="","",F26*(1+N(G26)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="27">
+        <f>IF(OR(D26="Bonificado",D26="Reemplazado"),0,N(I26)*IF(H26="",N(K26),IF(E26="USD",H26,H26/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="27">
+        <f>IF(D26="Alternativa","",J26-N(K26))</f>
+        <v/>
+      </c>
+      <c r="M26" s="29" t="inlineStr">
+        <is>
+          <t>Mail higiaeventos 22/06/2026 (reenviado 29/06) · 50% de anticipo antes del armado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Retiro de residuos</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Gale Servicios</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>Roll off con disposición final incluida. Cotización base abril 2026.</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>1471608.62</v>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H27" s="25">
+        <f>IF(F27="","",F27*(1+N(G27)))</f>
+        <v/>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="27">
+        <f>IF(OR(D27="Bonificado",D27="Reemplazado"),0,N(I27)*IF(H27="",N(K27),IF(E27="USD",H27,H27/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K27" s="28" t="n"/>
+      <c r="L27" s="27">
+        <f>IF(D27="Alternativa","",J27-N(K27))</f>
+        <v/>
+      </c>
+      <c r="M27" s="29" t="inlineStr">
+        <is>
+          <t>Mail higiaeventos 22/06/2026 (adjunto Gale) · se factura 100% por adelantado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Baños químicos — ecobaños</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>Decidido: ecobaños, no los químicos tradicionales. Más limpios, mejor a la vista y ecofriendly. Falta pedir presupuesto.</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="14">
-        <f>IF(F14="","",F14*(1+N(G14)))</f>
-        <v/>
-      </c>
-      <c r="I14" s="15" t="n">
+      <c r="F28" s="38" t="n"/>
+      <c r="G28" s="34" t="n"/>
+      <c r="H28" s="37">
+        <f>IF(F28="","",F28*(1+N(G28)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="14">
-        <f>IF(OR(D14="Bonificado",D14="Reemplazado"),0,N(I14)*IF(H14="",N(K14),IF(E14="USD",H14,H14/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>34000</v>
-      </c>
-      <c r="L14" s="14">
-        <f>IF(D14="Alternativa","",J14-N(K14))</f>
-        <v/>
-      </c>
-      <c r="M14" s="16" t="inlineStr">
-        <is>
-          <t>Negociación de Agustina · reemplaza la cotización vencida de Prina</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Entelado</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Cerrado por Agustina</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Entelado del pabellón. Negociado a la mitad de lo que estaba cotizado.</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="J28" s="37">
+        <f>IF(OR(D28="Bonificado",D28="Reemplazado"),0,N(I28)*IF(H28="",N(K28),IF(E28="USD",H28,H28/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K28" s="38" t="n"/>
+      <c r="L28" s="37">
+        <f>IF(D28="Alternativa","",J28-N(K28))</f>
+        <v/>
+      </c>
+      <c r="M28" s="39" t="inlineStr">
+        <is>
+          <t>Decisión de Agustina · pendiente de cotizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Seguro de accidentes personales</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>Chanes Seguros</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>Cobertura MIA (muerte, invalidez y asistencia médica) para 150 personas, exigida por La Rural</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>Cotizado</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>ARS</t>
         </is>
       </c>
-      <c r="F15" s="40" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="41">
-        <f>IF(F15="","",F15*(1+N(G15)))</f>
-        <v/>
-      </c>
-      <c r="I15" s="15" t="n">
+      <c r="F29" s="23" t="n">
+        <v>953151.9300000001</v>
+      </c>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="25">
+        <f>IF(F29="","",F29*(1+N(G29)))</f>
+        <v/>
+      </c>
+      <c r="I29" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="14">
-        <f>IF(OR(D15="Bonificado",D15="Reemplazado"),0,N(I15)*IF(H15="",N(K15),IF(E15="USD",H15,H15/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="14">
-        <f>IF(D15="Alternativa","",J15-N(K15))</f>
-        <v/>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Negociación de Agustina · US$16.000 aprox. al dólar de referencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Circuito cerrado (CCTV)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Cerrado por Agustina</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Circuito cerrado de cámaras para el pabellón.</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>6209</v>
-      </c>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14">
-        <f>IF(F16="","",F16*(1+N(G16)))</f>
-        <v/>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="14">
-        <f>IF(OR(D16="Bonificado",D16="Reemplazado"),0,N(I16)*IF(H16="",N(K16),IF(E16="USD",H16,H16/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="14">
-        <f>IF(D16="Alternativa","",J16-N(K16))</f>
-        <v/>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>Negociación de Agustina</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>Bonificado por el proveedor de técnica</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>Sin costo</t>
-        </is>
-      </c>
-      <c r="C17" s="44" t="inlineStr">
-        <is>
-          <t>500 vallas y efectos especiales, sin cargo. Es lo que evita el gasto de vallado que estaba presupuestado.</t>
-        </is>
-      </c>
-      <c r="D17" s="42" t="inlineStr">
-        <is>
-          <t>Bonificado</t>
-        </is>
-      </c>
-      <c r="E17" s="43" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F17" s="45" t="n"/>
-      <c r="G17" s="46" t="n"/>
-      <c r="H17" s="47">
-        <f>IF(F17="","",F17*(1+N(G17)))</f>
-        <v/>
-      </c>
-      <c r="I17" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="47">
-        <f>IF(OR(D17="Bonificado",D17="Reemplazado"),0,N(I17)*IF(H17="",N(K17),IF(E17="USD",H17,H17/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K17" s="45" t="n"/>
-      <c r="L17" s="47">
-        <f>IF(D17="Alternativa","",J17-N(K17))</f>
-        <v/>
-      </c>
-      <c r="M17" s="49" t="inlineStr">
-        <is>
-          <t>Negociación de Agustina</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Subtotal Técnica</t>
-        </is>
-      </c>
-      <c r="B18" s="38" t="n"/>
-      <c r="C18" s="38" t="n"/>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="38" t="n"/>
-      <c r="J18" s="39">
-        <f>SUMIF($D$14:$D$17,"&lt;&gt;Alternativa",$J$14:$J$17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="39">
-        <f>SUM($K$14:$K$17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="39">
-        <f>J18-K18</f>
-        <v/>
-      </c>
-      <c r="M18" s="38" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>SERVICIOS</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Seguridad y vigilancia</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Road Seguridad S.A.</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>263 horas de vigilancia (armado, evento y desarme) + planos de evacuación $715.000 + supervisión general $795.000</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>7218928.96</v>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H20" s="22">
-        <f>IF(F20="","",F20*(1+N(G20)))</f>
-        <v/>
-      </c>
-      <c r="I20" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="24">
-        <f>IF(OR(D20="Bonificado",D20="Reemplazado"),0,N(I20)*IF(H20="",N(K20),IF(E20="USD",H20,H20/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K20" s="25" t="n"/>
-      <c r="L20" s="24">
-        <f>IF(D20="Alternativa","",J20-N(K20))</f>
-        <v/>
-      </c>
-      <c r="M20" s="26" t="inlineStr">
-        <is>
-          <t>Mail presupuestos@roadseguridad.com.ar 12/08/2026 (versión V3, lista para firmar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Servicio médico</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>Vittal — Socorro Médico Privado</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>1 UTIM TRI con dos médicos + enfermero/chofer, los tres días (2, 3 y 4 de octubre)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>6366521.27</v>
-      </c>
-      <c r="G21" s="21" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="H21" s="22">
-        <f>IF(F21="","",F21*(1+N(G21)))</f>
-        <v/>
-      </c>
-      <c r="I21" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="24">
-        <f>IF(OR(D21="Bonificado",D21="Reemplazado"),0,N(I21)*IF(H21="",N(K21),IF(E21="USD",H21,H21/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K21" s="25" t="n"/>
-      <c r="L21" s="24">
-        <f>IF(D21="Alternativa","",J21-N(K21))</f>
-        <v/>
-      </c>
-      <c r="M21" s="26" t="inlineStr">
-        <is>
-          <t>Mail vtomas@vittal.com.ar 28/08/2026 · tarifas actualizadas, sin consultorio</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Higia Eventos</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>205,5 horas de limpieza: auditorio, baños y guardarropas, del 2 al 5 de octubre</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>3367440.91</v>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H22" s="22">
-        <f>IF(F22="","",F22*(1+N(G22)))</f>
-        <v/>
-      </c>
-      <c r="I22" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="24">
-        <f>IF(OR(D22="Bonificado",D22="Reemplazado"),0,N(I22)*IF(H22="",N(K22),IF(E22="USD",H22,H22/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="24">
-        <f>IF(D22="Alternativa","",J22-N(K22))</f>
-        <v/>
-      </c>
-      <c r="M22" s="26" t="inlineStr">
-        <is>
-          <t>Mail higiaeventos 22/06/2026 (reenviado 29/06) · 50% de anticipo antes del armado</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Retiro de residuos</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>Gale Servicios</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>Roll off con disposición final incluida. Cotización base abril 2026.</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="n">
-        <v>1471608.62</v>
-      </c>
-      <c r="G23" s="21" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H23" s="22">
-        <f>IF(F23="","",F23*(1+N(G23)))</f>
-        <v/>
-      </c>
-      <c r="I23" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="24">
-        <f>IF(OR(D23="Bonificado",D23="Reemplazado"),0,N(I23)*IF(H23="",N(K23),IF(E23="USD",H23,H23/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="24">
-        <f>IF(D23="Alternativa","",J23-N(K23))</f>
-        <v/>
-      </c>
-      <c r="M23" s="26" t="inlineStr">
-        <is>
-          <t>Mail higiaeventos 22/06/2026 (adjunto Gale) · se factura 100% por adelantado</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>Baños químicos — ecobaños</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C24" s="29" t="inlineStr">
-        <is>
-          <t>Decidido: ecobaños, no los químicos tradicionales. Más limpios, mejor a la vista y ecofriendly. Falta pedir presupuesto.</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="34">
-        <f>IF(F24="","",F24*(1+N(G24)))</f>
-        <v/>
-      </c>
-      <c r="I24" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="34">
-        <f>IF(OR(D24="Bonificado",D24="Reemplazado"),0,N(I24)*IF(H24="",N(K24),IF(E24="USD",H24,H24/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K24" s="35" t="n"/>
-      <c r="L24" s="34">
-        <f>IF(D24="Alternativa","",J24-N(K24))</f>
-        <v/>
-      </c>
-      <c r="M24" s="36" t="inlineStr">
-        <is>
-          <t>Decisión de Agustina · pendiente de cotizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>Seguro de accidentes personales</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Chanes Seguros</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>Cobertura MIA (muerte, invalidez y asistencia médica) para 150 personas, exigida por La Rural</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>Cotizado</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>953151.9300000001</v>
-      </c>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="22">
-        <f>IF(F25="","",F25*(1+N(G25)))</f>
-        <v/>
-      </c>
-      <c r="I25" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="24">
-        <f>IF(OR(D25="Bonificado",D25="Reemplazado"),0,N(I25)*IF(H25="",N(K25),IF(E25="USD",H25,H25/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K25" s="25" t="n">
+      <c r="J29" s="27">
+        <f>IF(OR(D29="Bonificado",D29="Reemplazado"),0,N(I29)*IF(H29="",N(K29),IF(E29="USD",H29,H29/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K29" s="28" t="n">
         <v>400</v>
       </c>
-      <c r="L25" s="24">
-        <f>IF(D25="Alternativa","",J25-N(K25))</f>
-        <v/>
-      </c>
-      <c r="M25" s="26" t="inlineStr">
+      <c r="L29" s="27">
+        <f>IF(D29="Alternativa","",J29-N(K29))</f>
+        <v/>
+      </c>
+      <c r="M29" s="29" t="inlineStr">
         <is>
           <t>Mail nestor@chanesseguros.com.ar 13/07/2026 · premio único, cotizado para 15-19/07</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Subtotal Servicios</t>
         </is>
       </c>
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="38" t="n"/>
-      <c r="E26" s="38" t="n"/>
-      <c r="F26" s="38" t="n"/>
-      <c r="G26" s="38" t="n"/>
-      <c r="H26" s="38" t="n"/>
-      <c r="I26" s="38" t="n"/>
-      <c r="J26" s="39">
-        <f>SUMIF($D$20:$D$25,"&lt;&gt;Alternativa",$J$20:$J$25)</f>
-        <v/>
-      </c>
-      <c r="K26" s="39">
-        <f>SUM($K$20:$K$25)</f>
-        <v/>
-      </c>
-      <c r="L26" s="39">
-        <f>J26-K26</f>
-        <v/>
-      </c>
-      <c r="M26" s="38" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="19">
+        <f>SUMIF($D$23:$D$29,"&lt;&gt;Alternativa",$J$23:$J$29)</f>
+        <v/>
+      </c>
+      <c r="K30" s="19">
+        <f>SUM($K$23:$K$29)</f>
+        <v/>
+      </c>
+      <c r="L30" s="19">
+        <f>J30-K30</f>
+        <v/>
+      </c>
+      <c r="M30" s="18" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>MERCH</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
-      <c r="L27" s="8" t="n"/>
-      <c r="M27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Pañuelos / pañoletas estampados (8.500)</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>REMERASYESTAMPADOS</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Factura 2601012 del 20/06. Compra compartida Argentina + Uruguay: se imputa a Argentina el 65% (5.500 de 8.500 unidades, la misma proporcion que la grafica). El 50% ya esta abonado; el saldo se paga con la factura 2601019 por 5.276,51 USDT, de los cuales 3.429,73 son de Argentina.</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Contratado</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="n">
-        <v>13387500</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H28" s="41">
-        <f>IF(F28="","",F28*(1+N(G28)))</f>
-        <v/>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J28" s="14">
-        <f>IF(OR(D28="Bonificado",D28="Reemplazado"),0,N(I28)*IF(H28="",N(K28),IF(E28="USD",H28,H28/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="14">
-        <f>IF(D28="Alternativa","",J28-N(K28))</f>
-        <v/>
-      </c>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>Drive · Presupuesto Pañuelos - Arg y Uru · facturas 2601012 (20/06) y 2601019 (16/08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Remeras premium estampadas (250)</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>REMERASYESTAMPADOS</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Factura 2601017 del 16/08, $14.110 por unidad. Sube de 230 a 250 unidades contra la factura original 2601011, al mismo precio unitario. SIN PAGAR: se debe el 100% (2.780,64 USDT).</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Contratado</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F29" s="40" t="n">
-        <v>3527500</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H29" s="41">
-        <f>IF(F29="","",F29*(1+N(G29)))</f>
-        <v/>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="14">
-        <f>IF(OR(D29="Bonificado",D29="Reemplazado"),0,N(I29)*IF(H29="",N(K29),IF(E29="USD",H29,H29/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="14">
-        <f>IF(D29="Alternativa","",J29-N(K29))</f>
-        <v/>
-      </c>
-      <c r="M29" s="16" t="inlineStr">
-        <is>
-          <t>Drive · Presupuestos camisetas + pañoletas · factura 2601017 (16/08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Bordado de gorras (940)</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>REMERASYESTAMPADOS</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Bordado computarizado sobre las gorras que provee el cliente. Presupuesto del 03/07 con el descuento de $411.800 ya aplicado. Precio final, no lleva IVA. SIN PAGAR: se debe el 100% (1.721,95 USDT).</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Contratado</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F30" s="40" t="n">
-        <v>2643200</v>
-      </c>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="41">
-        <f>IF(F30="","",F30*(1+N(G30)))</f>
-        <v/>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="14">
-        <f>IF(OR(D30="Bonificado",D30="Reemplazado"),0,N(I30)*IF(H30="",N(K30),IF(E30="USD",H30,H30/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="14">
-        <f>IF(D30="Alternativa","",J30-N(K30))</f>
-        <v/>
-      </c>
-      <c r="M30" s="16" t="inlineStr">
-        <is>
-          <t>Drive · Presupuesto gorras (compra y bordado) / Bordado · factura 2601016 (10/08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Gorras Flex unicolor/bicolor (940)</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>TEXTIL RYU S.R.L.</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Factura 2601009 del 20/06, pagada al 100% el 25/06. Es la compra de las gorras; el bordado va en su propia linea.</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Contratado</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F31" s="40" t="n">
-        <v>2224980</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H31" s="41">
-        <f>IF(F31="","",F31*(1+N(G31)))</f>
-        <v/>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="14">
-        <f>IF(OR(D31="Bonificado",D31="Reemplazado"),0,N(I31)*IF(H31="",N(K31),IF(E31="USD",H31,H31/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L31" s="14">
-        <f>IF(D31="Alternativa","",J31-N(K31))</f>
-        <v/>
-      </c>
-      <c r="M31" s="16" t="inlineStr">
-        <is>
-          <t>Drive · Compra de gorras · factura 2601009 · hoja PAGOS del master</t>
-        </is>
-      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Lanyards premium doble raso 25 mm (1.360)</t>
+          <t>Pañuelos / pañoletas estampados (8.500)</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>LEOTEX</t>
+          <t>REMERASYESTAMPADOS</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Sublimacion full print en ambas caras, 1.300 negros + 50 azules (la factura dice 1.360, la suma da 1.350: hay 10 de diferencia). Reemitida como 2601018 en USDT. OJO: la carpeta se llama "Nuevo pago - 50%" pero la factura viene por el total.</t>
+          <t>Factura 2601012 del 20/06. Compra compartida Argentina + Uruguay: se imputa a Argentina el 65% (5.500 de 8.500 unidades, la misma proporcion que la grafica). El 50% ya esta abonado; el saldo se paga con la factura 2601019 por 5.276,51 USDT, de los cuales 3.429,73 son de Argentina.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -2429,7 +2307,7 @@
         </is>
       </c>
       <c r="F32" s="40" t="n">
-        <v>2070600</v>
+        <v>13387500</v>
       </c>
       <c r="G32" s="13" t="n">
         <v>0.21</v>
@@ -2438,8 +2316,8 @@
         <f>IF(F32="","",F32*(1+N(G32)))</f>
         <v/>
       </c>
-      <c r="I32" s="15" t="n">
-        <v>1</v>
+      <c r="I32" s="13" t="n">
+        <v>0.65</v>
       </c>
       <c r="J32" s="14">
         <f>IF(OR(D32="Bonificado",D32="Reemplazado"),0,N(I32)*IF(H32="",N(K32),IF(E32="USD",H32,H32/TABLERO!$C$4)))</f>
@@ -2452,24 +2330,24 @@
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>Drive · Presupuesto Lanyards · facturas 2601013 (20/06) y 2601018 (16/08)</t>
+          <t>Drive · Presupuesto Pañuelos - Arg y Uru · facturas 2601012 (20/06) y 2601019 (16/08)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Grafica oficial CMC — Argentina</t>
+          <t>Remeras premium estampadas (250)</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>DERQUI IMPRESIONES</t>
+          <t>REMERASYESTAMPADOS</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>5.500 hojas A4, 5.500 tarjetas, 1.030 credenciales, 5.500 mapas y 1.000 bolsas de friselina. Reemitida el 16/08 para cambiar el medio de pago a USDT.</t>
+          <t>Factura 2601017 del 16/08, $14.110 por unidad. Sube de 230 a 250 unidades contra la factura original 2601011, al mismo precio unitario. SIN PAGAR: se debe el 100% (2.780,64 USDT).</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -2483,7 +2361,7 @@
         </is>
       </c>
       <c r="F33" s="40" t="n">
-        <v>3025260</v>
+        <v>3527500</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>0.21</v>
@@ -2506,390 +2384,453 @@
       </c>
       <c r="M33" s="16" t="inlineStr">
         <is>
+          <t>Drive · Presupuestos camisetas + pañoletas · factura 2601017 (16/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Bordado de gorras (940)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>REMERASYESTAMPADOS</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Bordado computarizado sobre las gorras que provee el cliente. Presupuesto del 03/07 con el descuento de $411.800 ya aplicado. Precio final, no lleva IVA. SIN PAGAR: se debe el 100% (1.721,95 USDT).</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Contratado</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="n">
+        <v>2643200</v>
+      </c>
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="41">
+        <f>IF(F34="","",F34*(1+N(G34)))</f>
+        <v/>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="14">
+        <f>IF(OR(D34="Bonificado",D34="Reemplazado"),0,N(I34)*IF(H34="",N(K34),IF(E34="USD",H34,H34/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="14">
+        <f>IF(D34="Alternativa","",J34-N(K34))</f>
+        <v/>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Presupuesto gorras (compra y bordado) / Bordado · factura 2601016 (10/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Gorras Flex unicolor/bicolor (940)</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>TEXTIL RYU S.R.L.</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Factura 2601009 del 20/06, pagada al 100% el 25/06. Es la compra de las gorras; el bordado va en su propia linea.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Contratado</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="n">
+        <v>2224980</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H35" s="41">
+        <f>IF(F35="","",F35*(1+N(G35)))</f>
+        <v/>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="14">
+        <f>IF(OR(D35="Bonificado",D35="Reemplazado"),0,N(I35)*IF(H35="",N(K35),IF(E35="USD",H35,H35/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L35" s="14">
+        <f>IF(D35="Alternativa","",J35-N(K35))</f>
+        <v/>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Compra de gorras · factura 2601009 · hoja PAGOS del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Lanyards premium doble raso 25 mm (1.360)</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>LEOTEX</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Sublimacion full print en ambas caras, 1.300 negros + 50 azules (la factura dice 1.360, la suma da 1.350: hay 10 de diferencia). Reemitida como 2601018 en USDT. OJO: la carpeta se llama "Nuevo pago - 50%" pero la factura viene por el total.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Contratado</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="n">
+        <v>2070600</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H36" s="41">
+        <f>IF(F36="","",F36*(1+N(G36)))</f>
+        <v/>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="14">
+        <f>IF(OR(D36="Bonificado",D36="Reemplazado"),0,N(I36)*IF(H36="",N(K36),IF(E36="USD",H36,H36/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="14">
+        <f>IF(D36="Alternativa","",J36-N(K36))</f>
+        <v/>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Drive · Presupuesto Lanyards · facturas 2601013 (20/06) y 2601018 (16/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Grafica oficial CMC — Argentina</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>DERQUI IMPRESIONES</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>5.500 hojas A4, 5.500 tarjetas, 1.030 credenciales, 5.500 mapas y 1.000 bolsas de friselina. Reemitida el 16/08 para cambiar el medio de pago a USDT.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Contratado</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="n">
+        <v>3025260</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H37" s="41">
+        <f>IF(F37="","",F37*(1+N(G37)))</f>
+        <v/>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="14">
+        <f>IF(OR(D37="Bonificado",D37="Reemplazado"),0,N(I37)*IF(H37="",N(K37),IF(E37="USD",H37,H37/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="14">
+        <f>IF(D37="Alternativa","",J37-N(K37))</f>
+        <v/>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
           <t>Drive · Factura/presu ARGENTINA · factura 2601014 (20/06, reemitida 16/08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="42" t="inlineStr">
-        <is>
-          <t>Grafica oficial CMC — Uruguay</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
-        <is>
-          <t>DERQUI IMPRESIONES</t>
-        </is>
-      </c>
-      <c r="C34" s="44" t="inlineStr">
-        <is>
-          <t>NO ES DE ARGENTINA. 2.800 hojas A4, 2.800 tarjetas, 530 credenciales, 2.800 mapas y 1.000 bolsas de friselina, para el evento de Uruguay. Se deja a la vista en cero porque en la hoja PAGOS del master estaba cargada como Argentina: es el monto que no cerraba.</t>
-        </is>
-      </c>
-      <c r="D34" s="42" t="inlineStr">
-        <is>
-          <t>Otro pais</t>
-        </is>
-      </c>
-      <c r="E34" s="43" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F34" s="50" t="n">
-        <v>1564626</v>
-      </c>
-      <c r="G34" s="46" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H34" s="51">
-        <f>IF(F34="","",F34*(1+N(G34)))</f>
-        <v/>
-      </c>
-      <c r="I34" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="47">
-        <f>IF(OR(D34="Bonificado",D34="Reemplazado"),0,N(I34)*IF(H34="",N(K34),IF(E34="USD",H34,H34/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K34" s="45" t="n"/>
-      <c r="L34" s="47">
-        <f>IF(D34="Alternativa","",J34-N(K34))</f>
-        <v/>
-      </c>
-      <c r="M34" s="49" t="inlineStr">
-        <is>
-          <t>Drive · Factura/presu URUGUAY · factura 2601015 (20/06, reemitida 16/08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="42" t="inlineStr">
-        <is>
-          <t>Cintas portacredencial (1.300) — alternativa</t>
-        </is>
-      </c>
-      <c r="B35" s="43" t="inlineStr">
-        <is>
-          <t>Blocko</t>
-        </is>
-      </c>
-      <c r="C35" s="44" t="inlineStr">
-        <is>
-          <t>Cinta raso 25 mm impresa a 4 colores dos caras + mosqueton zamak, $1.346 c/u. Es el MISMO item que los lanyards de LEOTEX, que ya esta contratado y con anticipo pagado. Estaba sumando dos veces: ahora queda como alternativa descartada.</t>
-        </is>
-      </c>
-      <c r="D35" s="42" t="inlineStr">
-        <is>
-          <t>Alternativa</t>
-        </is>
-      </c>
-      <c r="E35" s="43" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F35" s="50" t="n">
-        <v>1749800</v>
-      </c>
-      <c r="G35" s="46" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H35" s="51">
-        <f>IF(F35="","",F35*(1+N(G35)))</f>
-        <v/>
-      </c>
-      <c r="I35" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="47">
-        <f>IF(OR(D35="Bonificado",D35="Reemplazado"),0,N(I35)*IF(H35="",N(K35),IF(E35="USD",H35,H35/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K35" s="45" t="n"/>
-      <c r="L35" s="47">
-        <f>IF(D35="Alternativa","",J35-N(K35))</f>
-        <v/>
-      </c>
-      <c r="M35" s="49" t="inlineStr">
-        <is>
-          <t>Mail hola@blocko.com.ar 09/06/2026 · descartada contra la factura 2601013 de LEOTEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
-        <is>
-          <t>Marqueteria y enmarcado</t>
-        </is>
-      </c>
-      <c r="B36" s="28" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>Enmarcado de las certificaciones y los premios. Rubro nuevo, no estaba en ninguna planilla.</t>
-        </is>
-      </c>
-      <c r="D36" s="27" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F36" s="35" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="34">
-        <f>IF(F36="","",F36*(1+N(G36)))</f>
-        <v/>
-      </c>
-      <c r="I36" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="34">
-        <f>IF(OR(D36="Bonificado",D36="Reemplazado"),0,N(I36)*IF(H36="",N(K36),IF(E36="USD",H36,H36/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K36" s="35" t="n"/>
-      <c r="L36" s="34">
-        <f>IF(D36="Alternativa","",J36-N(K36))</f>
-        <v/>
-      </c>
-      <c r="M36" s="36" t="inlineStr">
-        <is>
-          <t>Agregado por Agustina · pendiente de cotizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>Cheques, escarapelas, diplomas, placas y manillas</t>
-        </is>
-      </c>
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>Lo unico del merch que las facturas de Drive NO cubren. Las camisetas, los mapas, las bolsas y las credenciales ya estan facturados arriba.</t>
-        </is>
-      </c>
-      <c r="D37" s="27" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E37" s="28" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F37" s="35" t="n"/>
-      <c r="G37" s="31" t="n"/>
-      <c r="H37" s="34">
-        <f>IF(F37="","",F37*(1+N(G37)))</f>
-        <v/>
-      </c>
-      <c r="I37" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="34">
-        <f>IF(OR(D37="Bonificado",D37="Reemplazado"),0,N(I37)*IF(H37="",N(K37),IF(E37="USD",H37,H37/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K37" s="35" t="n"/>
-      <c r="L37" s="34">
-        <f>IF(D37="Alternativa","",J37-N(K37))</f>
-        <v/>
-      </c>
-      <c r="M37" s="36" t="inlineStr">
-        <is>
-          <t>Pendiente de cotizar · antes estaba dentro del estimado global de US$8.689</t>
         </is>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="42" t="inlineStr">
         <is>
-          <t>Estimado global de merch del master (reemplazado)</t>
+          <t>Grafica oficial CMC — Uruguay</t>
         </is>
       </c>
       <c r="B38" s="43" t="inlineStr">
         <is>
-          <t>Varios</t>
+          <t>DERQUI IMPRESIONES</t>
         </is>
       </c>
       <c r="C38" s="44" t="inlineStr">
         <is>
-          <t>La hoja Argentina del master tenia US$8.689 en un solo renglon por contratos, cheques, escarapelas, bolsas, camisetas, mapas, diplomas, placas y manillas. Queda en cero como costo porque las facturas reales de arriba lo reemplazan; se conserva el estimado para poder comparar contra el presupuesto original.</t>
+          <t>NO ES DE ARGENTINA. 2.800 hojas A4, 2.800 tarjetas, 530 credenciales, 2.800 mapas y 1.000 bolsas de friselina, para el evento de Uruguay. Se deja a la vista en cero porque en la hoja PAGOS del master estaba cargada como Argentina: es el monto que no cerraba.</t>
         </is>
       </c>
       <c r="D38" s="42" t="inlineStr">
         <is>
-          <t>Reemplazado</t>
+          <t>Otro pais</t>
         </is>
       </c>
       <c r="E38" s="43" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F38" s="45" t="n"/>
-      <c r="G38" s="46" t="n"/>
-      <c r="H38" s="47">
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F38" s="50" t="n">
+        <v>1564626</v>
+      </c>
+      <c r="G38" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H38" s="51">
         <f>IF(F38="","",F38*(1+N(G38)))</f>
         <v/>
       </c>
-      <c r="I38" s="48" t="n">
-        <v>1</v>
+      <c r="I38" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="47">
         <f>IF(OR(D38="Bonificado",D38="Reemplazado"),0,N(I38)*IF(H38="",N(K38),IF(E38="USD",H38,H38/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K38" s="45" t="n">
-        <v>8689</v>
-      </c>
+      <c r="K38" s="45" t="n"/>
       <c r="L38" s="47">
         <f>IF(D38="Alternativa","",J38-N(K38))</f>
         <v/>
       </c>
       <c r="M38" s="49" t="inlineStr">
         <is>
-          <t>Hoja Argentina del master · reemplazado por las facturas 2601009 a 2601019</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="37" t="inlineStr">
-        <is>
-          <t>Subtotal Merch</t>
-        </is>
-      </c>
-      <c r="B39" s="38" t="n"/>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="38" t="n"/>
-      <c r="G39" s="38" t="n"/>
-      <c r="H39" s="38" t="n"/>
-      <c r="I39" s="38" t="n"/>
-      <c r="J39" s="39">
-        <f>SUMIF($D$28:$D$38,"&lt;&gt;Alternativa",$J$28:$J$38)</f>
-        <v/>
-      </c>
-      <c r="K39" s="39">
-        <f>SUM($K$28:$K$38)</f>
-        <v/>
-      </c>
-      <c r="L39" s="39">
-        <f>J39-K39</f>
-        <v/>
-      </c>
-      <c r="M39" s="38" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>CATERING</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-      <c r="L40" s="8" t="n"/>
-      <c r="M40" s="8" t="n"/>
+          <t>Drive · Factura/presu URUGUAY · factura 2601015 (20/06, reemitida 16/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>Cintas portacredencial (1.300) — alternativa</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Blocko</t>
+        </is>
+      </c>
+      <c r="C39" s="44" t="inlineStr">
+        <is>
+          <t>Cinta raso 25 mm impresa a 4 colores dos caras + mosqueton zamak, $1.346 c/u. Es el MISMO item que los lanyards de LEOTEX, que ya esta contratado y con anticipo pagado. Estaba sumando dos veces: ahora queda como alternativa descartada.</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Alternativa</t>
+        </is>
+      </c>
+      <c r="E39" s="43" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="F39" s="50" t="n">
+        <v>1749800</v>
+      </c>
+      <c r="G39" s="46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H39" s="51">
+        <f>IF(F39="","",F39*(1+N(G39)))</f>
+        <v/>
+      </c>
+      <c r="I39" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="47">
+        <f>IF(OR(D39="Bonificado",D39="Reemplazado"),0,N(I39)*IF(H39="",N(K39),IF(E39="USD",H39,H39/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K39" s="45" t="n"/>
+      <c r="L39" s="47">
+        <f>IF(D39="Alternativa","",J39-N(K39))</f>
+        <v/>
+      </c>
+      <c r="M39" s="49" t="inlineStr">
+        <is>
+          <t>Mail hola@blocko.com.ar 09/06/2026 · descartada contra la factura 2601013 de LEOTEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Marqueteria y enmarcado</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>Enmarcado de las certificaciones y los premios. Rubro nuevo, no estaba en ninguna planilla.</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="34" t="n"/>
+      <c r="H40" s="37">
+        <f>IF(F40="","",F40*(1+N(G40)))</f>
+        <v/>
+      </c>
+      <c r="I40" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="37">
+        <f>IF(OR(D40="Bonificado",D40="Reemplazado"),0,N(I40)*IF(H40="",N(K40),IF(E40="USD",H40,H40/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K40" s="38" t="n"/>
+      <c r="L40" s="37">
+        <f>IF(D40="Alternativa","",J40-N(K40))</f>
+        <v/>
+      </c>
+      <c r="M40" s="39" t="inlineStr">
+        <is>
+          <t>Agregado por Agustina · pendiente de cotizar</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Catering VIP, staff y equipo</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Grupo Ambient</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>Número final por las dos propuestas juntas: 600 lunchbox para los VIP + desayuno, almuerzo y cena para 150 personas.</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Cheques, escarapelas, diplomas, placas y manillas</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>Lo unico del merch que las facturas de Drive NO cubren. Las camisetas, los mapas, las bolsas y las credenciales ya estan facturados arriba.</t>
+        </is>
+      </c>
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>14569</v>
-      </c>
-      <c r="G41" s="13" t="n"/>
-      <c r="H41" s="14">
+      <c r="F41" s="38" t="n"/>
+      <c r="G41" s="34" t="n"/>
+      <c r="H41" s="37">
         <f>IF(F41="","",F41*(1+N(G41)))</f>
         <v/>
       </c>
-      <c r="I41" s="15" t="n">
+      <c r="I41" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="37">
         <f>IF(OR(D41="Bonificado",D41="Reemplazado"),0,N(I41)*IF(H41="",N(K41),IF(E41="USD",H41,H41/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K41" s="12" t="n">
-        <v>33820</v>
-      </c>
-      <c r="L41" s="14">
+      <c r="K41" s="38" t="n"/>
+      <c r="L41" s="37">
         <f>IF(D41="Alternativa","",J41-N(K41))</f>
         <v/>
       </c>
-      <c r="M41" s="16" t="inlineStr">
-        <is>
-          <t>Cierre de Agustina con Grupo Ambient · reemplaza la estimación de $25.000.000</t>
+      <c r="M41" s="39" t="inlineStr">
+        <is>
+          <t>Pendiente de cotizar · antes estaba dentro del estimado global de US$8.689</t>
         </is>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="42" t="inlineStr">
         <is>
-          <t>Food trucks</t>
+          <t>Estimado global de merch del master (reemplazado)</t>
         </is>
       </c>
       <c r="B42" s="43" t="inlineStr">
         <is>
-          <t>Sin costo</t>
+          <t>Varios</t>
         </is>
       </c>
       <c r="C42" s="44" t="inlineStr">
         <is>
-          <t>No los paga la producción.</t>
+          <t>La hoja Argentina del master tenia US$8.689 en un solo renglon por contratos, cheques, escarapelas, bolsas, camisetas, mapas, diplomas, placas y manillas. Queda en cero como costo porque las facturas reales de arriba lo reemplazan; se conserva el estimado para poder comparar contra el presupuesto original.</t>
         </is>
       </c>
       <c r="D42" s="42" t="inlineStr">
         <is>
-          <t>Bonificado</t>
+          <t>Reemplazado</t>
         </is>
       </c>
       <c r="E42" s="43" t="inlineStr">
@@ -2910,49 +2851,51 @@
         <f>IF(OR(D42="Bonificado",D42="Reemplazado"),0,N(I42)*IF(H42="",N(K42),IF(E42="USD",H42,H42/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K42" s="45" t="n"/>
+      <c r="K42" s="45" t="n">
+        <v>8689</v>
+      </c>
       <c r="L42" s="47">
         <f>IF(D42="Alternativa","",J42-N(K42))</f>
         <v/>
       </c>
       <c r="M42" s="49" t="inlineStr">
         <is>
-          <t>Confirmado por Agustina</t>
+          <t>Hoja Argentina del master · reemplazado por las facturas 2601009 a 2601019</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
-        <is>
-          <t>Subtotal Catering</t>
-        </is>
-      </c>
-      <c r="B43" s="38" t="n"/>
-      <c r="C43" s="38" t="n"/>
-      <c r="D43" s="38" t="n"/>
-      <c r="E43" s="38" t="n"/>
-      <c r="F43" s="38" t="n"/>
-      <c r="G43" s="38" t="n"/>
-      <c r="H43" s="38" t="n"/>
-      <c r="I43" s="38" t="n"/>
-      <c r="J43" s="39">
-        <f>SUMIF($D$41:$D$42,"&lt;&gt;Alternativa",$J$41:$J$42)</f>
-        <v/>
-      </c>
-      <c r="K43" s="39">
-        <f>SUM($K$41:$K$42)</f>
-        <v/>
-      </c>
-      <c r="L43" s="39">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal Merch</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="19">
+        <f>SUMIF($D$32:$D$42,"&lt;&gt;Alternativa",$J$32:$J$42)</f>
+        <v/>
+      </c>
+      <c r="K43" s="19">
+        <f>SUM($K$32:$K$42)</f>
+        <v/>
+      </c>
+      <c r="L43" s="19">
         <f>J43-K43</f>
         <v/>
       </c>
-      <c r="M43" s="38" t="n"/>
+      <c r="M43" s="18" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>PRODUCCIÓN</t>
+          <t>CATERING</t>
         </is>
       </c>
       <c r="B44" s="8" t="n"/>
@@ -2969,71 +2912,73 @@
       <c r="M44" s="8" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>Unifilas</t>
-        </is>
-      </c>
-      <c r="B45" s="28" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="inlineStr">
-        <is>
-          <t>Estimado del sheet, sin cotización</t>
-        </is>
-      </c>
-      <c r="D45" s="27" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E45" s="28" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Catering VIP, staff y equipo</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Grupo Ambient</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Número final por las dos propuestas juntas: 600 lunchbox para los VIP + desayuno, almuerzo y cena para 150 personas.</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F45" s="35" t="n"/>
-      <c r="G45" s="31" t="n"/>
-      <c r="H45" s="34">
+      <c r="F45" s="12" t="n">
+        <v>14569</v>
+      </c>
+      <c r="G45" s="13" t="n"/>
+      <c r="H45" s="14">
         <f>IF(F45="","",F45*(1+N(G45)))</f>
         <v/>
       </c>
-      <c r="I45" s="33" t="n">
+      <c r="I45" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="34">
+      <c r="J45" s="14">
         <f>IF(OR(D45="Bonificado",D45="Reemplazado"),0,N(I45)*IF(H45="",N(K45),IF(E45="USD",H45,H45/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K45" s="35" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L45" s="34">
+      <c r="K45" s="12" t="n">
+        <v>33820</v>
+      </c>
+      <c r="L45" s="14">
         <f>IF(D45="Alternativa","",J45-N(K45))</f>
         <v/>
       </c>
-      <c r="M45" s="36" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>Cierre de Agustina con Grupo Ambient · reemplaza la estimación de $25.000.000</t>
         </is>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="42" t="inlineStr">
         <is>
-          <t>Vallado (500 vallas)</t>
+          <t>Food trucks</t>
         </is>
       </c>
       <c r="B46" s="43" t="inlineStr">
         <is>
-          <t>Bonificado por técnica</t>
+          <t>Sin costo</t>
         </is>
       </c>
       <c r="C46" s="44" t="inlineStr">
         <is>
-          <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
+          <t>No los paga la producción.</t>
         </is>
       </c>
       <c r="D46" s="42" t="inlineStr">
@@ -3059,531 +3004,682 @@
         <f>IF(OR(D46="Bonificado",D46="Reemplazado"),0,N(I46)*IF(H46="",N(K46),IF(E46="USD",H46,H46/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K46" s="45" t="n">
-        <v>1250</v>
-      </c>
+      <c r="K46" s="45" t="n"/>
       <c r="L46" s="47">
         <f>IF(D46="Alternativa","",J46-N(K46))</f>
         <v/>
       </c>
       <c r="M46" s="49" t="inlineStr">
         <is>
+          <t>Confirmado por Agustina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal Catering</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="19">
+        <f>SUMIF($D$45:$D$46,"&lt;&gt;Alternativa",$J$45:$J$46)</f>
+        <v/>
+      </c>
+      <c r="K47" s="19">
+        <f>SUM($K$45:$K$46)</f>
+        <v/>
+      </c>
+      <c r="L47" s="19">
+        <f>J47-K47</f>
+        <v/>
+      </c>
+      <c r="M47" s="18" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCCIÓN</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>Unifilas</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>A definir</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>Estimado del sheet, sin cotización</t>
+        </is>
+      </c>
+      <c r="D49" s="30" t="inlineStr">
+        <is>
+          <t>Sin cotizar</t>
+        </is>
+      </c>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F49" s="38" t="n"/>
+      <c r="G49" s="34" t="n"/>
+      <c r="H49" s="37">
+        <f>IF(F49="","",F49*(1+N(G49)))</f>
+        <v/>
+      </c>
+      <c r="I49" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="37">
+        <f>IF(OR(D49="Bonificado",D49="Reemplazado"),0,N(I49)*IF(H49="",N(K49),IF(E49="USD",H49,H49/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K49" s="38" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L49" s="37">
+        <f>IF(D49="Alternativa","",J49-N(K49))</f>
+        <v/>
+      </c>
+      <c r="M49" s="39" t="inlineStr">
+        <is>
+          <t>Hoja Argentina del master</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>Vallado (500 vallas)</t>
+        </is>
+      </c>
+      <c r="B50" s="43" t="inlineStr">
+        <is>
+          <t>Bonificado por técnica</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E50" s="43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F50" s="45" t="n"/>
+      <c r="G50" s="46" t="n"/>
+      <c r="H50" s="47">
+        <f>IF(F50="","",F50*(1+N(G50)))</f>
+        <v/>
+      </c>
+      <c r="I50" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="47">
+        <f>IF(OR(D50="Bonificado",D50="Reemplazado"),0,N(I50)*IF(H50="",N(K50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K50" s="45" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L50" s="47">
+        <f>IF(D50="Alternativa","",J50-N(K50))</f>
+        <v/>
+      </c>
+      <c r="M50" s="49" t="inlineStr">
+        <is>
           <t>Negociación de Agustina</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>DJ</t>
         </is>
       </c>
-      <c r="B47" s="28" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C51" s="32" t="inlineStr">
         <is>
           <t>Estimado del sheet</t>
         </is>
       </c>
-      <c r="D47" s="27" t="inlineStr">
+      <c r="D51" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F47" s="35" t="n"/>
-      <c r="G47" s="31" t="n"/>
-      <c r="H47" s="34">
-        <f>IF(F47="","",F47*(1+N(G47)))</f>
-        <v/>
-      </c>
-      <c r="I47" s="33" t="n">
+      <c r="F51" s="38" t="n"/>
+      <c r="G51" s="34" t="n"/>
+      <c r="H51" s="37">
+        <f>IF(F51="","",F51*(1+N(G51)))</f>
+        <v/>
+      </c>
+      <c r="I51" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="34">
-        <f>IF(OR(D47="Bonificado",D47="Reemplazado"),0,N(I47)*IF(H47="",N(K47),IF(E47="USD",H47,H47/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K47" s="35" t="n">
+      <c r="J51" s="37">
+        <f>IF(OR(D51="Bonificado",D51="Reemplazado"),0,N(I51)*IF(H51="",N(K51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K51" s="38" t="n">
         <v>500</v>
       </c>
-      <c r="L47" s="34">
-        <f>IF(D47="Alternativa","",J47-N(K47))</f>
-        <v/>
-      </c>
-      <c r="M47" s="36" t="inlineStr">
+      <c r="L51" s="37">
+        <f>IF(D51="Alternativa","",J51-N(K51))</f>
+        <v/>
+      </c>
+      <c r="M51" s="39" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="27" t="inlineStr">
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>Escoltas (2)</t>
         </is>
       </c>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C48" s="29" t="inlineStr">
+      <c r="C52" s="32" t="inlineStr">
         <is>
           <t>Estimado del sheet</t>
         </is>
       </c>
-      <c r="D48" s="27" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E52" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F48" s="35" t="n"/>
-      <c r="G48" s="31" t="n"/>
-      <c r="H48" s="34">
-        <f>IF(F48="","",F48*(1+N(G48)))</f>
-        <v/>
-      </c>
-      <c r="I48" s="33" t="n">
+      <c r="F52" s="38" t="n"/>
+      <c r="G52" s="34" t="n"/>
+      <c r="H52" s="37">
+        <f>IF(F52="","",F52*(1+N(G52)))</f>
+        <v/>
+      </c>
+      <c r="I52" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="34">
-        <f>IF(OR(D48="Bonificado",D48="Reemplazado"),0,N(I48)*IF(H48="",N(K48),IF(E48="USD",H48,H48/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K48" s="35" t="n">
+      <c r="J52" s="37">
+        <f>IF(OR(D52="Bonificado",D52="Reemplazado"),0,N(I52)*IF(H52="",N(K52),IF(E52="USD",H52,H52/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K52" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="L48" s="34">
-        <f>IF(D48="Alternativa","",J48-N(K48))</f>
-        <v/>
-      </c>
-      <c r="M48" s="36" t="inlineStr">
+      <c r="L52" s="37">
+        <f>IF(D52="Alternativa","",J52-N(K52))</f>
+        <v/>
+      </c>
+      <c r="M52" s="39" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="27" t="inlineStr">
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>Master Mind Hit</t>
         </is>
       </c>
-      <c r="B49" s="28" t="inlineStr">
+      <c r="B53" s="31" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C49" s="29" t="inlineStr">
+      <c r="C53" s="32" t="inlineStr">
         <is>
           <t>Sala adicional</t>
         </is>
       </c>
-      <c r="D49" s="27" t="inlineStr">
+      <c r="D53" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E53" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F49" s="35" t="n"/>
-      <c r="G49" s="31" t="n"/>
-      <c r="H49" s="34">
-        <f>IF(F49="","",F49*(1+N(G49)))</f>
-        <v/>
-      </c>
-      <c r="I49" s="33" t="n">
+      <c r="F53" s="38" t="n"/>
+      <c r="G53" s="34" t="n"/>
+      <c r="H53" s="37">
+        <f>IF(F53="","",F53*(1+N(G53)))</f>
+        <v/>
+      </c>
+      <c r="I53" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="34">
-        <f>IF(OR(D49="Bonificado",D49="Reemplazado"),0,N(I49)*IF(H49="",N(K49),IF(E49="USD",H49,H49/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K49" s="35" t="n">
+      <c r="J53" s="37">
+        <f>IF(OR(D53="Bonificado",D53="Reemplazado"),0,N(I53)*IF(H53="",N(K53),IF(E53="USD",H53,H53/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K53" s="38" t="n">
         <v>3000</v>
       </c>
-      <c r="L49" s="34">
-        <f>IF(D49="Alternativa","",J49-N(K49))</f>
-        <v/>
-      </c>
-      <c r="M49" s="36" t="inlineStr">
+      <c r="L53" s="37">
+        <f>IF(D53="Alternativa","",J53-N(K53))</f>
+        <v/>
+      </c>
+      <c r="M53" s="39" t="inlineStr">
         <is>
           <t>Hoja Argentina del master</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="27" t="inlineStr">
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>Personal logístico</t>
         </is>
       </c>
-      <c r="B50" s="28" t="inlineStr">
+      <c r="B54" s="31" t="inlineStr">
         <is>
           <t>A definir</t>
         </is>
       </c>
-      <c r="C50" s="29" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
         <is>
           <t>La hoja del master lo tiene en US$0</t>
         </is>
       </c>
-      <c r="D50" s="27" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E54" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F50" s="35" t="n"/>
-      <c r="G50" s="31" t="n"/>
-      <c r="H50" s="34">
-        <f>IF(F50="","",F50*(1+N(G50)))</f>
-        <v/>
-      </c>
-      <c r="I50" s="33" t="n">
+      <c r="F54" s="38" t="n"/>
+      <c r="G54" s="34" t="n"/>
+      <c r="H54" s="37">
+        <f>IF(F54="","",F54*(1+N(G54)))</f>
+        <v/>
+      </c>
+      <c r="I54" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="34">
-        <f>IF(OR(D50="Bonificado",D50="Reemplazado"),0,N(I50)*IF(H50="",N(K50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K50" s="35" t="n"/>
-      <c r="L50" s="34">
-        <f>IF(D50="Alternativa","",J50-N(K50))</f>
-        <v/>
-      </c>
-      <c r="M50" s="36" t="inlineStr">
+      <c r="J54" s="37">
+        <f>IF(OR(D54="Bonificado",D54="Reemplazado"),0,N(I54)*IF(H54="",N(K54),IF(E54="USD",H54,H54/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K54" s="38" t="n"/>
+      <c r="L54" s="37">
+        <f>IF(D54="Alternativa","",J54-N(K54))</f>
+        <v/>
+      </c>
+      <c r="M54" s="39" t="inlineStr">
         <is>
           <t>Hoja Argentina del master · valor en cero</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>Intercoms</t>
         </is>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>Proveedor Colombia</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>Contrato US$560, sin abonar, 2 cuotas al 24/08 y 23/09</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Contratado</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>560</v>
       </c>
-      <c r="G51" s="13" t="n"/>
-      <c r="H51" s="14">
-        <f>IF(F51="","",F51*(1+N(G51)))</f>
-        <v/>
-      </c>
-      <c r="I51" s="15" t="n">
+      <c r="G55" s="13" t="n"/>
+      <c r="H55" s="14">
+        <f>IF(F55="","",F55*(1+N(G55)))</f>
+        <v/>
+      </c>
+      <c r="I55" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="14">
-        <f>IF(OR(D51="Bonificado",D51="Reemplazado"),0,N(I51)*IF(H51="",N(K51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="14">
-        <f>IF(D51="Alternativa","",J51-N(K51))</f>
-        <v/>
-      </c>
-      <c r="M51" s="16" t="inlineStr">
+      <c r="J55" s="14">
+        <f>IF(OR(D55="Bonificado",D55="Reemplazado"),0,N(I55)*IF(H55="",N(K55),IF(E55="USD",H55,H55/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="14">
+        <f>IF(D55="Alternativa","",J55-N(K55))</f>
+        <v/>
+      </c>
+      <c r="M55" s="16" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="37" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Subtotal Producción</t>
         </is>
       </c>
-      <c r="B52" s="38" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="38" t="n"/>
-      <c r="E52" s="38" t="n"/>
-      <c r="F52" s="38" t="n"/>
-      <c r="G52" s="38" t="n"/>
-      <c r="H52" s="38" t="n"/>
-      <c r="I52" s="38" t="n"/>
-      <c r="J52" s="39">
-        <f>SUMIF($D$45:$D$51,"&lt;&gt;Alternativa",$J$45:$J$51)</f>
-        <v/>
-      </c>
-      <c r="K52" s="39">
-        <f>SUM($K$45:$K$51)</f>
-        <v/>
-      </c>
-      <c r="L52" s="39">
-        <f>J52-K52</f>
-        <v/>
-      </c>
-      <c r="M52" s="38" t="n"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="18" t="n"/>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="19">
+        <f>SUMIF($D$49:$D$55,"&lt;&gt;Alternativa",$J$49:$J$55)</f>
+        <v/>
+      </c>
+      <c r="K56" s="19">
+        <f>SUM($K$49:$K$55)</f>
+        <v/>
+      </c>
+      <c r="L56" s="19">
+        <f>J56-K56</f>
+        <v/>
+      </c>
+      <c r="M56" s="18" t="n"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>EQUIPO</t>
         </is>
       </c>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
-      <c r="L53" s="8" t="n"/>
-      <c r="M53" s="8" t="n"/>
-    </row>
-    <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="27" t="inlineStr">
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t>Vuelos del equipo</t>
         </is>
       </c>
-      <c r="B54" s="28" t="inlineStr">
+      <c r="B58" s="31" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C54" s="29" t="inlineStr">
+      <c r="C58" s="32" t="inlineStr">
         <is>
           <t>No hay ninguna cotización de vuelos a Buenos Aires en el correo ni monto en la hoja del master</t>
         </is>
       </c>
-      <c r="D54" s="27" t="inlineStr">
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E54" s="28" t="inlineStr">
+      <c r="E58" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F54" s="35" t="n"/>
-      <c r="G54" s="31" t="n"/>
-      <c r="H54" s="34">
-        <f>IF(F54="","",F54*(1+N(G54)))</f>
-        <v/>
-      </c>
-      <c r="I54" s="33" t="n">
+      <c r="F58" s="38" t="n"/>
+      <c r="G58" s="34" t="n"/>
+      <c r="H58" s="37">
+        <f>IF(F58="","",F58*(1+N(G58)))</f>
+        <v/>
+      </c>
+      <c r="I58" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="34">
-        <f>IF(OR(D54="Bonificado",D54="Reemplazado"),0,N(I54)*IF(H54="",N(K54),IF(E54="USD",H54,H54/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K54" s="35" t="n"/>
-      <c r="L54" s="34">
-        <f>IF(D54="Alternativa","",J54-N(K54))</f>
-        <v/>
-      </c>
-      <c r="M54" s="36" t="inlineStr">
+      <c r="J58" s="37">
+        <f>IF(OR(D58="Bonificado",D58="Reemplazado"),0,N(I58)*IF(H58="",N(K58),IF(E58="USD",H58,H58/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K58" s="38" t="n"/>
+      <c r="L58" s="37">
+        <f>IF(D58="Alternativa","",J58-N(K58))</f>
+        <v/>
+      </c>
+      <c r="M58" s="39" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="27" t="inlineStr">
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
         <is>
           <t>Alojamiento del equipo</t>
         </is>
       </c>
-      <c r="B55" s="28" t="inlineStr">
+      <c r="B59" s="31" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C55" s="29" t="inlineStr">
+      <c r="C59" s="32" t="inlineStr">
         <is>
           <t>No hay cotización de hotel en Buenos Aires en el correo ni monto en la hoja del master</t>
         </is>
       </c>
-      <c r="D55" s="27" t="inlineStr">
+      <c r="D59" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E55" s="28" t="inlineStr">
+      <c r="E59" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F55" s="35" t="n"/>
-      <c r="G55" s="31" t="n"/>
-      <c r="H55" s="34">
-        <f>IF(F55="","",F55*(1+N(G55)))</f>
-        <v/>
-      </c>
-      <c r="I55" s="33" t="n">
+      <c r="F59" s="38" t="n"/>
+      <c r="G59" s="34" t="n"/>
+      <c r="H59" s="37">
+        <f>IF(F59="","",F59*(1+N(G59)))</f>
+        <v/>
+      </c>
+      <c r="I59" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="34">
-        <f>IF(OR(D55="Bonificado",D55="Reemplazado"),0,N(I55)*IF(H55="",N(K55),IF(E55="USD",H55,H55/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K55" s="35" t="n"/>
-      <c r="L55" s="34">
-        <f>IF(D55="Alternativa","",J55-N(K55))</f>
-        <v/>
-      </c>
-      <c r="M55" s="36" t="inlineStr">
+      <c r="J59" s="37">
+        <f>IF(OR(D59="Bonificado",D59="Reemplazado"),0,N(I59)*IF(H59="",N(K59),IF(E59="USD",H59,H59/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K59" s="38" t="n"/>
+      <c r="L59" s="37">
+        <f>IF(D59="Alternativa","",J59-N(K59))</f>
+        <v/>
+      </c>
+      <c r="M59" s="39" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>Traslados internos y viáticos</t>
         </is>
       </c>
-      <c r="B56" s="28" t="inlineStr">
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C56" s="29" t="inlineStr">
+      <c r="C60" s="32" t="inlineStr">
         <is>
           <t>Sin registro</t>
         </is>
       </c>
-      <c r="D56" s="27" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="E56" s="28" t="inlineStr">
+      <c r="E60" s="31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F56" s="35" t="n"/>
-      <c r="G56" s="31" t="n"/>
-      <c r="H56" s="34">
-        <f>IF(F56="","",F56*(1+N(G56)))</f>
-        <v/>
-      </c>
-      <c r="I56" s="33" t="n">
+      <c r="F60" s="38" t="n"/>
+      <c r="G60" s="34" t="n"/>
+      <c r="H60" s="37">
+        <f>IF(F60="","",F60*(1+N(G60)))</f>
+        <v/>
+      </c>
+      <c r="I60" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="34">
-        <f>IF(OR(D56="Bonificado",D56="Reemplazado"),0,N(I56)*IF(H56="",N(K56),IF(E56="USD",H56,H56/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K56" s="35" t="n"/>
-      <c r="L56" s="34">
-        <f>IF(D56="Alternativa","",J56-N(K56))</f>
-        <v/>
-      </c>
-      <c r="M56" s="36" t="inlineStr">
+      <c r="J60" s="37">
+        <f>IF(OR(D60="Bonificado",D60="Reemplazado"),0,N(I60)*IF(H60="",N(K60),IF(E60="USD",H60,H60/TABLERO!$C$4)))</f>
+        <v/>
+      </c>
+      <c r="K60" s="38" t="n"/>
+      <c r="L60" s="37">
+        <f>IF(D60="Alternativa","",J60-N(K60))</f>
+        <v/>
+      </c>
+      <c r="M60" s="39" t="inlineStr">
         <is>
           <t>No encontrado</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="37" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Subtotal Equipo</t>
         </is>
       </c>
-      <c r="B57" s="38" t="n"/>
-      <c r="C57" s="38" t="n"/>
-      <c r="D57" s="38" t="n"/>
-      <c r="E57" s="38" t="n"/>
-      <c r="F57" s="38" t="n"/>
-      <c r="G57" s="38" t="n"/>
-      <c r="H57" s="38" t="n"/>
-      <c r="I57" s="38" t="n"/>
-      <c r="J57" s="39">
-        <f>SUMIF($D$54:$D$56,"&lt;&gt;Alternativa",$J$54:$J$56)</f>
-        <v/>
-      </c>
-      <c r="K57" s="39">
-        <f>SUM($K$54:$K$56)</f>
-        <v/>
-      </c>
-      <c r="L57" s="39">
-        <f>J57-K57</f>
-        <v/>
-      </c>
-      <c r="M57" s="38" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="52" t="inlineStr">
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="19">
+        <f>SUMIF($D$58:$D$60,"&lt;&gt;Alternativa",$J$58:$J$60)</f>
+        <v/>
+      </c>
+      <c r="K61" s="19">
+        <f>SUM($K$58:$K$60)</f>
+        <v/>
+      </c>
+      <c r="L61" s="19">
+        <f>J61-K61</f>
+        <v/>
+      </c>
+      <c r="M61" s="18" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="52" t="inlineStr">
         <is>
           <t>COSTO TOTAL DEL EVENTO</t>
         </is>
       </c>
-      <c r="J59" s="53">
-        <f>J12+J18+J26+J39+J43+J52+J57</f>
-        <v/>
-      </c>
-      <c r="K59" s="53">
-        <f>K12+K18+K26+K39+K43+K52+K57</f>
-        <v/>
-      </c>
-      <c r="L59" s="53">
-        <f>L12+L18+L26+L39+L43+L52+L57</f>
+      <c r="J63" s="53">
+        <f>J7+J10+J15+J21+J30+J43+J47+J56+J61</f>
+        <v/>
+      </c>
+      <c r="K63" s="53">
+        <f>K7+K10+K15+K21+K30+K43+K47+K56+K61</f>
+        <v/>
+      </c>
+      <c r="L63" s="53">
+        <f>L7+L10+L15+L21+L30+L43+L47+L56+L61</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M4"/>
-  <mergeCells count="7">
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="A19:M19"/>
+  <mergeCells count="9">
     <mergeCell ref="A44:M44"/>
     <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="A40:M40"/>
-    <mergeCell ref="A53:M53"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A57:M57"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A11:M11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3648,7 +3744,7 @@
         </is>
       </c>
       <c r="C7" s="56">
-        <f>'COSTOS UNIFICADOS'!J59</f>
+        <f>'COSTOS UNIFICADOS'!J63</f>
         <v/>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3664,7 +3760,7 @@
         </is>
       </c>
       <c r="C8" s="56">
-        <f>'COSTOS UNIFICADOS'!K59</f>
+        <f>'COSTOS UNIFICADOS'!K63</f>
         <v/>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3680,7 +3776,7 @@
         </is>
       </c>
       <c r="C9" s="57">
-        <f>'COSTOS UNIFICADOS'!L59</f>
+        <f>'COSTOS UNIFICADOS'!L63</f>
         <v/>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4009,65 +4105,65 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>REMERASYESTAMPADOS</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Pañuelos / pañoletas estampados</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>8.500</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="31" t="inlineStr">
         <is>
           <t>2601012 → saldo 2601019</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>20/06 → 16/08</t>
         </is>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="33" t="n">
         <v>13387500</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="34" t="n">
         <v>0.21</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="35">
         <f>F5*(1+N(G5))</f>
         <v/>
       </c>
-      <c r="I5" s="35" t="n">
+      <c r="I5" s="38" t="n">
         <v>5276.51</v>
       </c>
-      <c r="J5" s="29" t="inlineStr">
+      <c r="J5" s="32" t="inlineStr">
         <is>
           <t>Argentina + Uruguay</t>
         </is>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="34" t="n">
         <v>0.65</v>
       </c>
       <c r="L5" s="65">
         <f>K5*H5/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="37">
         <f>K5*5276.51</f>
         <v/>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="37">
         <f>K5*5276.51</f>
         <v/>
       </c>
-      <c r="O5" s="36" t="inlineStr">
+      <c r="O5" s="39" t="inlineStr">
         <is>
           <t>La 2601019 ya viene emitida por el 50% restante. Falta definir con Uruguay como se reparte: aca se imputa el 65% a Argentina.</t>
         </is>
@@ -4265,130 +4361,130 @@
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>LEOTEX</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Lanyard premium doble raso 25 mm</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>1.360</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>2601013 → 2601018</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>20/06 → 16/08</t>
         </is>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="33" t="n">
         <v>2070600</v>
       </c>
-      <c r="G9" s="31" t="n">
+      <c r="G9" s="34" t="n">
         <v>0.21</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="35">
         <f>F9*(1+N(G9))</f>
         <v/>
       </c>
-      <c r="I9" s="35" t="n">
+      <c r="I9" s="38" t="n">
         <v>1632.2</v>
       </c>
-      <c r="J9" s="29" t="inlineStr">
+      <c r="J9" s="32" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="K9" s="31" t="n">
+      <c r="K9" s="34" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="65">
         <f>K9*H9/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="37">
         <f>K9*816.1</f>
         <v/>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="37">
         <f>K9*1632.2</f>
         <v/>
       </c>
-      <c r="O9" s="36" t="inlineStr">
+      <c r="O9" s="39" t="inlineStr">
         <is>
           <t>A CONFIRMAR: la carpeta se llama "Nuevo pago - 50%" pero la factura 2601018 viene por el total, igual que la original. El master registraba un saldo de US$850.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>DERQUI IMPRESIONES</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>Grafica oficial CMC — Argentina</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>2601014</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>20/06 → 16/08</t>
         </is>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="33" t="n">
         <v>3025260</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="34" t="n">
         <v>0.21</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="35">
         <f>F10*(1+N(G10))</f>
         <v/>
       </c>
-      <c r="I10" s="35" t="n">
+      <c r="I10" s="38" t="n">
         <v>2384.73</v>
       </c>
-      <c r="J10" s="29" t="inlineStr">
+      <c r="J10" s="32" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="K10" s="31" t="n">
+      <c r="K10" s="34" t="n">
         <v>1</v>
       </c>
       <c r="L10" s="65">
         <f>K10*H10/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="37">
         <f>K10*1192.37</f>
         <v/>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="37">
         <f>K10*2384.73</f>
         <v/>
       </c>
-      <c r="O10" s="36" t="inlineStr">
+      <c r="O10" s="39" t="inlineStr">
         <is>
           <t>A CONFIRMAR: la reemision del 16/08 viene por el total. El master registraba un saldo de US$1.839 al 13/09.</t>
         </is>
@@ -4895,8 +4991,8 @@
       </c>
       <c r="E31" s="92" t="n"/>
       <c r="F31" s="92" t="n"/>
-      <c r="G31" s="38" t="n"/>
-      <c r="H31" s="38" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="78" t="inlineStr">
@@ -5262,19 +5358,19 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="n"/>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Pagado a hoy</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="39">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="19">
         <f>SUM(D6:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -5559,19 +5655,19 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n"/>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Comprometido con fecha</t>
         </is>
       </c>
-      <c r="C24" s="38" t="n"/>
-      <c r="D24" s="39">
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="19">
         <f>SUM(D15:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="38" t="n"/>
-      <c r="F24" s="38" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
@@ -5603,7 +5699,7 @@
         </is>
       </c>
       <c r="D28" s="104">
-        <f>'COSTOS UNIFICADOS'!J59</f>
+        <f>'COSTOS UNIFICADOS'!J63</f>
         <v/>
       </c>
     </row>
@@ -5625,7 +5721,7 @@
         </is>
       </c>
       <c r="D30" s="106">
-        <f>'COSTOS UNIFICADOS'!J59-D12</f>
+        <f>'COSTOS UNIFICADOS'!J63-D12</f>
         <v/>
       </c>
     </row>
@@ -5647,7 +5743,7 @@
         </is>
       </c>
       <c r="D32" s="107">
-        <f>'COSTOS UNIFICADOS'!J59-D12-D24</f>
+        <f>'COSTOS UNIFICADOS'!J63-D12-D24</f>
         <v/>
       </c>
     </row>
@@ -5740,196 +5836,196 @@
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Infraestructura de La Rural</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Presupuesto completo: $66.494.708 (US$43.461), con las 5.000 sillas y todo el mobiliario</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Sólo panelería + dirección técnica + guardias: $16.858.366 (US$11.019). El mobiliario se compra aparte.</t>
         </is>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="37">
         <f>(66494708.2-16858366.2)/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Agustina marca ítem por ítem qué se queda. La hoja INFRAESTRUCTURA tiene las 28 líneas del presupuesto para filtrar.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Montaje de las sillas</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>La Rural con las sillas incluidas y armadas</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>FDL Eventos + montaje/acomodación/desmontaje negociado en $900.000</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>Con FDL a $31.218.000 más $900.000 de montaje son US$20.992 contra US$27.778 de La Rural. Cerrar el número del montaje y firmar.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Catering — cerrado</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Grupo Ambient: US$13.582 por las dos propuestas</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>La planilla tenía US$33.820 estimados</t>
         </is>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="37">
         <f>13582-33820</f>
         <v/>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>Cerrado. Es la mejor negociación del evento: US$20.238 por debajo de lo presupuestado.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Rubros nuevos sin cotizar</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Ecobaños, marquetería de certificaciones y premios, replanteo de sillas con ingeniero</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Hoy entran en US$0</t>
         </is>
       </c>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Pedir las tres cotizaciones esta semana. Son los últimos huecos que quedan además de vuelos y alojamiento.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Merch — el 50% que falta pagar</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Regla del 50%: quedan US$9.941 por transferir en USDT</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Según las facturas reemitidas en agosto: US$11.949</t>
         </is>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="37">
         <f>11949.25-9940.79</f>
         <v/>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Las facturas de LEOTEX (lanyards) y Derqui (gráfica ARG) vienen por el total aunque ya se abonó el 50%. Una consulta a cada proveedor cierra la diferencia. Lo urgente igual son las remeras (US$2.781) y el bordado de gorras (US$1.722): esos no tienen nada pagado.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Merch — cómo se reparten los pañuelos con Uruguay</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Los 8.500 pañuelos se imputan 65% a Argentina (US$6.973)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Si van todos a Argentina: US$10.728</t>
         </is>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="37">
         <f>0.35*13387500*1.21/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>La factura no separa las unidades por país. Definir el reparto con Uruguay antes de cerrar el número para el CEO.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Vuelos y alojamiento del equipo</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Sin cotizar</t>
         </is>
       </c>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>No hay ni un mail ni una línea en el sheet. Con 8 personas de equipo interno, es el hueco más grande que queda.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Facturación al exterior</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>FDL Eventos y Vittal no confirmaron si pueden facturar a la empresa de EE.UU.</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Buscar proveedores que sí facturen, o resolver un circuito de pago local</t>
         </is>
       </c>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Resolverlo antes de firmar: puede trabar los dos contratos.</t>
         </is>
@@ -5946,7 +6042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6028,32 +6124,30 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Infraestructura y mobiliario</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Grupo MET, cotización de mobiliario</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="D5" s="24">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Infraestructura — armado de stands</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>La Rural: panelería + dirección técnica + guardias</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>16858366.2</v>
+      </c>
+      <c r="D5" s="27">
         <f>C5/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>Armado de stands + mobiliario, definido por Agustina</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="n">
-        <v>14183100</v>
-      </c>
-      <c r="G5" s="25" t="n">
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>Armado del stand de staff, el de producción y el camarín</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="28" t="n">
         <v>9270</v>
       </c>
       <c r="H5" s="76">
@@ -6064,39 +6158,39 @@
         <f>IFERROR(H5/D5,"")</f>
         <v/>
       </c>
-      <c r="J5" s="26" t="inlineStr">
-        <is>
-          <t>La cotización de Grupo MET no está en el correo: dato aportado por Agustina. En el correo sí está el presupuesto de La Rural del 17/08 por $66.494.708 (con las 5.000 sillas adentro).</t>
+      <c r="J5" s="29" t="inlineStr">
+        <is>
+          <t>Presupuesto de La Rural del 17/08 (mail criccio@larural.com.ar): panelería $9.938.187 más generales $6.920.179. Cerrado por Agustina en US$9.270.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Sillas del público</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>La Rural: 5.000 sillas imperio bordó, armado incluido</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>42500000</v>
-      </c>
-      <c r="D6" s="24">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Mobiliario</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Grupo MET y La Rural, ambos alrededor de $40.000.000</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="D6" s="27">
         <f>C6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>FDL Eventos 5.500 sillas + montaje, acomodación y desmontaje</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>32118000</v>
-      </c>
-      <c r="G6" s="24">
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Conseguido aparte por Agustina</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="G6" s="27">
         <f>F6/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -6108,39 +6202,39 @@
         <f>IFERROR(H6/D6,"")</f>
         <v/>
       </c>
-      <c r="J6" s="26" t="inlineStr">
-        <is>
-          <t>Mail criccio@larural.com.ar 17/08 y mail fdleventos@gmail.com 07/08. El montaje ($900.000) está en negociación.</t>
+      <c r="J6" s="29" t="inlineStr">
+        <is>
+          <t>A CONFIRMAR: dato aportado por Agustina, no está en el correo. Usa los mismos dos números que la fila del entelado ($40.000.000 y $24.500.000) y además ese costo no aparece como línea en COSTOS UNIFICADOS. Antes de firmar el informe hay que confirmar que son dos negociaciones distintas y no una contada dos veces.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Entelado</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Primer presupuesto de Grupo MET</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="D7" s="24">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Sillas del público — aparte</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>La Rural: 5.000 sillas imperio bordó, armado incluido</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="D7" s="27">
         <f>C7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>Negociado a poco más de la mitad</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="G7" s="24">
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>FDL Eventos 5.500 sillas + montaje, acomodación y desmontaje</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>32118000</v>
+      </c>
+      <c r="G7" s="27">
         <f>F7/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -6152,38 +6246,41 @@
         <f>IFERROR(H7/D7,"")</f>
         <v/>
       </c>
-      <c r="J7" s="26" t="inlineStr">
-        <is>
-          <t>Dato aportado por Agustina: ni el presupuesto inicial ni el cierre están en el correo. OJO: primero dijo $24.500.000 (que es el número cargado, y el que da los US$16.225 que ella misma usa) y después $25.500.000. Confirmar cuál es antes de firmar el informe.</t>
+      <c r="J7" s="29" t="inlineStr">
+        <is>
+          <t>Mail criccio@larural.com.ar 17/08 y mail fdleventos@gmail.com 07/08. El montaje ($900.000) está en negociación.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Catering</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>Primera propuesta de Grupo Ambient</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D8" s="24">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>Entelado</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Primer presupuesto de Grupo MET</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="D8" s="27">
         <f>C8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>600 lunchbox VIP + desayuno, almuerzo y cena para 150 personas</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="25" t="n">
-        <v>14569</v>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Negociado a poco más de la mitad</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="G8" s="27">
+        <f>F8/TABLERO!$C$4</f>
+        <v/>
       </c>
       <c r="H8" s="76">
         <f>D8-G8</f>
@@ -6193,35 +6290,38 @@
         <f>IFERROR(H8/D8,"")</f>
         <v/>
       </c>
-      <c r="J8" s="26" t="inlineStr">
-        <is>
-          <t>Cierre informado por Agustina. En el correo está la propuesta de AmbientHouse del 16/06 a $28.500 + IVA por persona por día con base mínima de 480.</t>
+      <c r="J8" s="29" t="inlineStr">
+        <is>
+          <t>Dato aportado por Agustina: ni el presupuesto inicial ni el cierre están en el correo. OJO: primero dijo $24.500.000 (que es el número cargado, y el que da los US$16.225 que ella misma usa) y después $25.500.000. Confirmar cuál es antes de firmar el informe.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Merch e impresos</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>Proveedor de Cumbre, precios unitarios al 06/07</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="25" t="n">
-        <v>16261.12</v>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>Proveedores argentinos conseguidos por Agustina</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="25" t="n">
-        <v>5067.97</v>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Primera propuesta de Grupo Ambient</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="D9" s="27">
+        <f>C9/TABLERO!$C$4</f>
+        <v/>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>600 lunchbox VIP + desayuno, almuerzo y cena para 150 personas</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="28" t="n">
+        <v>14569</v>
       </c>
       <c r="H9" s="76">
         <f>D9-G9</f>
@@ -6231,35 +6331,35 @@
         <f>IFERROR(H9/D9,"")</f>
         <v/>
       </c>
-      <c r="J9" s="26" t="inlineStr">
-        <is>
-          <t>Comparativa de merch.cmc2026.com al 06/07/2026 (dólar $1.515). Es una canasta cerrada de siete ítems: remeras, gorras, lanyards, credenciales, hojas A4, tarjetas y bolsas de friselina. Las pulseras tyvek quedan fuera de los dos lados porque no hay precio comparable. NO es el total del rubro merch: los pañuelos y el bordado de gorras no entran en esta comparación.</t>
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>Cierre informado por Agustina. En el correo está la propuesta de AmbientHouse del 16/06 a $28.500 + IVA por persona por día con base mínima de 480.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>Vallado del público</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Presupuestado en la hoja de Argentina</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="25" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>500 vallas bonificadas por el proveedor de técnica</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="25" t="n">
-        <v>0</v>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Merch e impresos</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Proveedor de Cumbre, precios unitarios al 06/07</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="28" t="n">
+        <v>16261.12</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Proveedores argentinos conseguidos por Agustina</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="28" t="n">
+        <v>5067.97</v>
       </c>
       <c r="H10" s="76">
         <f>D10-G10</f>
@@ -6269,136 +6369,174 @@
         <f>IFERROR(H10/D10,"")</f>
         <v/>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="29" t="inlineStr">
+        <is>
+          <t>Comparativa de merch.cmc2026.com al 06/07/2026 (dólar $1.515). Es una canasta cerrada de siete ítems: remeras, gorras, lanyards, credenciales, hojas A4, tarjetas y bolsas de friselina. Las pulseras tyvek quedan fuera de los dos lados porque no hay precio comparable. NO es el total del rubro merch: los pañuelos y el bordado de gorras no entran en esta comparación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Vallado del público</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Presupuestado en la hoja de Argentina</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="28" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>500 vallas bonificadas por el proveedor de técnica</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="76">
+        <f>D11-G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="108">
+        <f>IFERROR(H11/D11,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="29" t="inlineStr">
         <is>
           <t>Negociación de Agustina. Además bonifican los efectos especiales, que no estaban valorizados.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="52" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>AHORRO TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="109">
-        <f>SUM(D5:D10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="109">
-        <f>SUM(G5:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="109">
-        <f>SUM(H5:H10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="94" t="inlineStr">
+      <c r="D12" s="109">
+        <f>SUM(D5:D11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="109">
+        <f>SUM(G5:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="109">
+        <f>SUM(H5:H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>TÉCNICA — la comparación no es directa</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Se pidió cotización de técnica a NUEVE empresas el 13 y 14 de junio. Respondieron seis con número. El detalle completo está en la hoja COTIZACIONES TÉCNICA.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · Sound-Light (16/06): el PDF no se pudo abrir, el mail pesa 33 MB. El mail del 19/06 les dice que las otras estaban "prácticamente la mitad", lo que lo ubica por encima de los $100.000.000.</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Bonetto (17/06): $94.936.000 — sonido e iluminación $69.736.000, LED $20.720.000, CCTV $4.480.000. Grúas y efectos aparte (la chispa fría la cobra POR MINUTO).</t>
+          <t xml:space="preserve">   · Sound-Light (16/06): el PDF no se pudo abrir, el mail pesa 33 MB. El mail del 19/06 les dice que las otras estaban "prácticamente la mitad", lo que lo ubica por encima de los $100.000.000.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Pero cotiza 40 m² de LED cuando el rider pide 65, y deja afuera grúas y energía. Vencida.</t>
+          <t xml:space="preserve">   · Bonetto (17/06): $94.936.000 — sonido e iluminación $69.736.000, LED $20.720.000, CCTV $4.480.000. Grúas y efectos aparte (la chispa fría la cobra POR MINUTO).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 2MG (24/06): $45.000.000 con descuento + IVA = $54.450.000, más $19.202.700 de adicionales. Sonido más liviano, cotizado para "2000 / 5000 pax".</t>
+          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Pero cotiza 40 m² de LED cuando el rider pide 65, y deja afuera grúas y energía. Vencida.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Dixi Group (26/06): $82.000.000 + IVA = $99.220.000 llave en mano, con rigging completo, encomiendas y 4 máquinas de chispa fría.</t>
+          <t xml:space="preserve">   · 2MG (24/06): $45.000.000 con descuento + IVA = $54.450.000, más $19.202.700 de adicionales. Sonido más liviano, cotizado para "2000 / 5000 pax".</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">   · Dixi Group (26/06): $82.000.000 + IVA = $99.220.000 llave en mano, con rigging completo, encomiendas y 4 máquinas de chispa fría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">   · VMG (29/06): $15.276.250 con IVA, sólo las pantallas LED de 65 m².</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>POR QUÉ TÉCNICA NO ENTRA EN LA TABLA DE ARRIBA: Grupo MET cerró en US$60.000 ($90.600.000) y con el circuito cerrado el paquete queda cerca de $100.000.000.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Eso es prácticamente lo mismo que Dixi llave en mano y menos que Bonetto, pero está POR ENCIMA de 2MG y de Prina. Poner esa diferencia como ahorro no se sostendría</t>
+          <t>POR QUÉ TÉCNICA NO ENTRA EN LA TABLA DE ARRIBA: Grupo MET cerró en US$60.000 ($90.600.000) y con el circuito cerrado el paquete queda cerca de $100.000.000.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>Eso es prácticamente lo mismo que Dixi llave en mano y menos que Bonetto, pero está POR ENCIMA de 2MG y de Prina. Poner esa diferencia como ahorro no se sostendría</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>delante del CEO, porque los alcances no son iguales: Prina cotizó 38% menos de LED, 2MG un sonido más chico, y Grupo MET incluye lo que se agregó tras la visita al predio.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>LO QUE SÍ SE SOSTIENE EN TÉCNICA: las 500 vallas y los efectos especiales van bonificados. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>LO QUE SÍ SE SOSTIENE EN TÉCNICA: las 500 vallas y los efectos especiales van bonificados. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>Con los 6 disparos por día que pide el rider, en cualquiera de las otras propuestas eso es plata.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>FALTA UNA SOLA COSA para cerrar el ahorro de técnica con un número: el PDF de Grupo MET con el alcance final. Es el único de los siete proveedores sin presupuesto escrito en el correo.</t>
         </is>
@@ -6491,63 +6629,63 @@
       </c>
     </row>
     <row r="5" ht="86" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Sound-Light</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>ventas@sound-light.com.ar (Noelia Escudero)</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="32" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="35" t="n"/>
       <c r="F5" s="110">
         <f>IF(E5="","",E5/TABLERO!$C$4)</f>
         <v/>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t>Técnica integral sobre el pliego base.</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>Sin detalle: no se pudo abrir el adjunto.</t>
         </is>
       </c>
-      <c r="I5" s="36" t="inlineStr">
+      <c r="I5" s="39" t="inlineStr">
         <is>
           <t>El mail pesa 33 MB y el PDF no se puede extraer desde acá. Lo que sí está documentado es el mail del 19/06 en el que Agustina les dice que las otras cotizaciones estaban "prácticamente la mitad de lo cotizado por ustedes". Sobre las de esa fecha (Bonetto y Prina) eso lo ubica por encima de los $100.000.000.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="86" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Bonetto Sonido e Iluminación</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>cristian@bonetto.net</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="23" t="n">
         <v>94936000</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <f>D6*1.21</f>
         <v/>
       </c>
@@ -6555,143 +6693,143 @@
         <f>IF(E6="","",E6/TABLERO!$C$4)</f>
         <v/>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>Sonido e iluminación $69.736.000 · pantallas LED $20.720.000 · CCTV $4.480.000. 16 L-Acoustics Kiva II, 240 LED ST18-15, 322 truss box, consola Yamaha QL5.</t>
         </is>
       </c>
-      <c r="H6" s="19" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>Grúas (2 autoelevadores tijera x 3 días) $4.480.000 · máquina de humo $300.000 · 2 máquinas de chispa fría $600.000 POR MINUTO · minuto adicional $150.000.</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>Presupuesto PR26-287 V.1. El PDF viene con el texto vectorizado: hubo que renderizarlo a imagen para leerlo. No aclara si los valores llevan IVA. Dice expresamente "NO CONTEMPLA RIDER DE BANDA".</t>
         </is>
       </c>
     </row>
     <row r="7" ht="86" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Prina</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>valentin.andina@prina.net</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="23" t="n">
         <v>48885000</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="23" t="n">
         <v>59150850</v>
       </c>
       <c r="F7" s="111">
         <f>IF(E7="","",E7/TABLERO!$C$4)</f>
         <v/>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>LED 40 m² $6.700.000 · CCTV 2 cámaras $4.510.000 · sonido (16 Adamson Y10) $10.465.000 · iluminación $12.490.000 · RRHH y logística $14.720.000.</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>Incluye 2 máquinas Sparkular y máquina de humo.</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>OJO CON EL ALCANCE: cotiza 40 m² de LED (6×4 + 2 de 2×4) cuando el rider pide 65 m² (7×5 + 2 de 3×5). No incluye grúas, brazos articulados ni tijeras, ni la generación de energía. Validez de 10 días: vencida desde el 28/06.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="86" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2MG</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>rocio.g@2mg.net</t>
         </is>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="23" t="n">
         <v>45000000</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="23" t="n">
         <v>54450000</v>
       </c>
       <c r="F8" s="111">
         <f>IF(E8="","",E8/TABLERO!$C$4)</f>
         <v/>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>Sonido, video (LED 65 m², medida correcta), iluminación, CCTV, efectos especiales, RRHH y logística. Total de lista $53.655.470, con descuento especial $45.000.000.</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>Extras de iluminación $10.177.500 · escenario 13×3 m con pasarela $5.692.500. Los dos juntos suman $15.870.000 sin IVA.</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>Incluye certificación de planos por escribano, eléctrico matriculado y autoelevadora, hasta 8 puntos de colgado. El sonido es más liviano que el de los otros (12 gabinetes DVA T8) y el presupuesto dice "2000 / 5000 pax". Validez 15 días.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="86" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Dixi Group</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>26/06/2026</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>g.judcovski@dixieventos.com.ar</t>
         </is>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="23" t="n">
         <v>82000000</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="23" t="n">
         <v>99220000</v>
       </c>
       <c r="F9" s="111">
         <f>IF(E9="","",E9/TABLERO!$C$4)</f>
         <v/>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>Llave en mano: sonido, iluminación (90 par LED, 6 beam, 8 wash), video (LED 65 m²), CCTV y rigging completo (6 puentes de 12 m, 14 aparejos de 1 T, motores).</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>Nada: es llave en mano.</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>Es el alcance más completo de todos. Incluye 4 máquinas de chispa fría con 8 disparos por día, plano general con puntos de colgado firmado por arquitecto, encomienda eléctrica de profesional matriculado y productores generales de técnica.</t>
         </is>
@@ -7962,7 +8100,7 @@
         <f>SUM(D6:D39)</f>
         <v/>
       </c>
-      <c r="E41" s="39">
+      <c r="E41" s="19">
         <f>D41/TABLERO!$C$4</f>
         <v/>
       </c>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -6042,7 +6042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6167,32 +6167,26 @@
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>Mobiliario</t>
+          <t>Mobiliario — sillas y montaje</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>Grupo MET y La Rural, ambos alrededor de $40.000.000</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="D6" s="27">
-        <f>C6/TABLERO!$C$4</f>
-        <v/>
+          <t>La Rural: 5.000 sillas imperio bordó, armado incluido</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="28" t="n">
+        <v>28431</v>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>Conseguido aparte por Agustina</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="G6" s="27">
-        <f>F6/TABLERO!$C$4</f>
-        <v/>
+          <t>FDL Eventos: 5.500 sillas + flete, más el montaje, la acomodación y el desmontaje</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="28" t="n">
+        <v>17450</v>
       </c>
       <c r="H6" s="76">
         <f>D6-G6</f>
@@ -6204,39 +6198,33 @@
       </c>
       <c r="J6" s="29" t="inlineStr">
         <is>
-          <t>A CONFIRMAR: dato aportado por Agustina, no está en el correo. Usa los mismos dos números que la fila del entelado ($40.000.000 y $24.500.000) y además ese costo no aparece como línea en COSTOS UNIFICADOS. Antes de firmar el informe hay que confirmar que son dos negociaciones distintas y no una contada dos veces.</t>
+          <t>Cifras de Agustina, sin IVA. Reemplaza la fila que estaba aparte como "sillas": es la misma negociación, estaba contada dos veces. Verificado: 17.450 al dólar de referencia son $26.698.500, que es el presupuesto FDL 026-2697 ($25.800.000) más los $900.000 del montaje. Agustina tiene los presupuestos anteriores para adjuntar.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Sillas del público — aparte</t>
+          <t>Entelado</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>La Rural: 5.000 sillas imperio bordó, armado incluido</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="n">
-        <v>42500000</v>
-      </c>
-      <c r="D7" s="27">
-        <f>C7/TABLERO!$C$4</f>
-        <v/>
+          <t>Primer presupuesto recibido</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="28" t="n">
+        <v>25490</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>FDL Eventos 5.500 sillas + montaje, acomodación y desmontaje</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>32118000</v>
-      </c>
-      <c r="G7" s="27">
-        <f>F7/TABLERO!$C$4</f>
-        <v/>
+          <t>Negociado por Agustina</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="28" t="n">
+        <v>16500</v>
       </c>
       <c r="H7" s="76">
         <f>D7-G7</f>
@@ -6248,23 +6236,23 @@
       </c>
       <c r="J7" s="29" t="inlineStr">
         <is>
-          <t>Mail criccio@larural.com.ar 17/08 y mail fdleventos@gmail.com 07/08. El montaje ($900.000) está en negociación.</t>
+          <t>Cifras de Agustina, sin IVA. Verificado: 25.490 al dólar de referencia son $39.000.000 exactos, que es la primera cotización. Agustina tiene el presupuesto anterior para adjuntar.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Entelado</t>
+          <t>Catering</t>
         </is>
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Primer presupuesto de Grupo MET</t>
+          <t>Primera propuesta de Grupo Ambient</t>
         </is>
       </c>
       <c r="C8" s="23" t="n">
-        <v>40000000</v>
+        <v>30000000</v>
       </c>
       <c r="D8" s="27">
         <f>C8/TABLERO!$C$4</f>
@@ -6272,15 +6260,12 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>Negociado a poco más de la mitad</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="G8" s="27">
-        <f>F8/TABLERO!$C$4</f>
-        <v/>
+          <t>600 lunchbox VIP + desayuno, almuerzo y cena para 150 personas</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="28" t="n">
+        <v>14569</v>
       </c>
       <c r="H8" s="76">
         <f>D8-G8</f>
@@ -6292,36 +6277,33 @@
       </c>
       <c r="J8" s="29" t="inlineStr">
         <is>
-          <t>Dato aportado por Agustina: ni el presupuesto inicial ni el cierre están en el correo. OJO: primero dijo $24.500.000 (que es el número cargado, y el que da los US$16.225 que ella misma usa) y después $25.500.000. Confirmar cuál es antes de firmar el informe.</t>
+          <t>Cierre informado por Agustina. En el correo está la propuesta de AmbientHouse del 16/06 a $28.500 + IVA por persona por día con base mínima de 480.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Catering</t>
+          <t>Merch e impresos</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Primera propuesta de Grupo Ambient</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="D9" s="27">
-        <f>C9/TABLERO!$C$4</f>
-        <v/>
+          <t>Proveedor de Cumbre, precios unitarios al 06/07</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="28" t="n">
+        <v>16261.12</v>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>600 lunchbox VIP + desayuno, almuerzo y cena para 150 personas</t>
+          <t>Proveedores argentinos conseguidos por Agustina</t>
         </is>
       </c>
       <c r="F9" s="23" t="n"/>
       <c r="G9" s="28" t="n">
-        <v>14569</v>
+        <v>5067.97</v>
       </c>
       <c r="H9" s="76">
         <f>D9-G9</f>
@@ -6333,33 +6315,33 @@
       </c>
       <c r="J9" s="29" t="inlineStr">
         <is>
-          <t>Cierre informado por Agustina. En el correo está la propuesta de AmbientHouse del 16/06 a $28.500 + IVA por persona por día con base mínima de 480.</t>
+          <t>Comparativa de merch.cmc2026.com al 06/07/2026 (dólar $1.515). Es una canasta cerrada de siete ítems: remeras, gorras, lanyards, credenciales, hojas A4, tarjetas y bolsas de friselina. Las pulseras tyvek quedan fuera de los dos lados porque no hay precio comparable. NO es el total del rubro merch: los pañuelos y el bordado de gorras no entran en esta comparación.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Merch e impresos</t>
+          <t>Vallado del público</t>
         </is>
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Proveedor de Cumbre, precios unitarios al 06/07</t>
+          <t>Presupuestado en la hoja de Argentina</t>
         </is>
       </c>
       <c r="C10" s="23" t="n"/>
       <c r="D10" s="28" t="n">
-        <v>16261.12</v>
+        <v>1250</v>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Proveedores argentinos conseguidos por Agustina</t>
+          <t>500 vallas bonificadas por el proveedor de técnica</t>
         </is>
       </c>
       <c r="F10" s="23" t="n"/>
       <c r="G10" s="28" t="n">
-        <v>5067.97</v>
+        <v>0</v>
       </c>
       <c r="H10" s="76">
         <f>D10-G10</f>
@@ -6371,172 +6353,134 @@
       </c>
       <c r="J10" s="29" t="inlineStr">
         <is>
-          <t>Comparativa de merch.cmc2026.com al 06/07/2026 (dólar $1.515). Es una canasta cerrada de siete ítems: remeras, gorras, lanyards, credenciales, hojas A4, tarjetas y bolsas de friselina. Las pulseras tyvek quedan fuera de los dos lados porque no hay precio comparable. NO es el total del rubro merch: los pañuelos y el bordado de gorras no entran en esta comparación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Vallado del público</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>Presupuestado en la hoja de Argentina</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="28" t="n">
-        <v>1250</v>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>500 vallas bonificadas por el proveedor de técnica</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="76">
-        <f>D11-G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="108">
-        <f>IFERROR(H11/D11,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="29" t="inlineStr">
-        <is>
           <t>Negociación de Agustina. Además bonifican los efectos especiales, que no estaban valorizados.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="52" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>AHORRO TOTAL</t>
         </is>
       </c>
-      <c r="D12" s="109">
-        <f>SUM(D5:D11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="109">
-        <f>SUM(G5:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="109">
-        <f>SUM(H5:H11)</f>
-        <v/>
+      <c r="D11" s="109">
+        <f>SUM(D5:D10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="109">
+        <f>SUM(G5:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="109">
+        <f>SUM(H5:H10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>TÉCNICA — la comparación no es directa</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="inlineStr">
-        <is>
-          <t>TÉCNICA — la comparación no es directa</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Se pidió cotización de técnica a NUEVE empresas el 13 y 14 de junio. Respondieron seis con número. El detalle completo está en la hoja COTIZACIONES TÉCNICA.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Se pidió cotización de técnica a NUEVE empresas el 13 y 14 de junio. Respondieron seis con número. El detalle completo está en la hoja COTIZACIONES TÉCNICA.</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · Sound-Light (16/06): el PDF no se pudo abrir, el mail pesa 33 MB. El mail del 19/06 les dice que las otras estaban "prácticamente la mitad", lo que lo ubica por encima de los $100.000.000.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Sound-Light (16/06): el PDF no se pudo abrir, el mail pesa 33 MB. El mail del 19/06 les dice que las otras estaban "prácticamente la mitad", lo que lo ubica por encima de los $100.000.000.</t>
+          <t xml:space="preserve">   · Bonetto (17/06): $94.936.000 — sonido e iluminación $69.736.000, LED $20.720.000, CCTV $4.480.000. Grúas y efectos aparte (la chispa fría la cobra POR MINUTO).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Bonetto (17/06): $94.936.000 — sonido e iluminación $69.736.000, LED $20.720.000, CCTV $4.480.000. Grúas y efectos aparte (la chispa fría la cobra POR MINUTO).</t>
+          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Pero cotiza 40 m² de LED cuando el rider pide 65, y deja afuera grúas y energía. Vencida.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Prina (18/06): $48.885.000 + IVA = $59.150.850. Pero cotiza 40 m² de LED cuando el rider pide 65, y deja afuera grúas y energía. Vencida.</t>
+          <t xml:space="preserve">   · 2MG (24/06): $45.000.000 con descuento + IVA = $54.450.000, más $19.202.700 de adicionales. Sonido más liviano, cotizado para "2000 / 5000 pax".</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 2MG (24/06): $45.000.000 con descuento + IVA = $54.450.000, más $19.202.700 de adicionales. Sonido más liviano, cotizado para "2000 / 5000 pax".</t>
+          <t xml:space="preserve">   · Dixi Group (26/06): $82.000.000 + IVA = $99.220.000 llave en mano, con rigging completo, encomiendas y 4 máquinas de chispa fría.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · Dixi Group (26/06): $82.000.000 + IVA = $99.220.000 llave en mano, con rigging completo, encomiendas y 4 máquinas de chispa fría.</t>
+          <t xml:space="preserve">   · VMG (29/06): $15.276.250 con IVA, sólo las pantallas LED de 65 m².</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · VMG (29/06): $15.276.250 con IVA, sólo las pantallas LED de 65 m².</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>POR QUÉ TÉCNICA NO ENTRA EN LA TABLA DE ARRIBA: Grupo MET cerró en US$60.000 ($90.600.000) y con el circuito cerrado el paquete queda cerca de $100.000.000.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>POR QUÉ TÉCNICA NO ENTRA EN LA TABLA DE ARRIBA: Grupo MET cerró en US$60.000 ($90.600.000) y con el circuito cerrado el paquete queda cerca de $100.000.000.</t>
+          <t>Eso es prácticamente lo mismo que Dixi llave en mano y menos que Bonetto, pero está POR ENCIMA de 2MG y de Prina. Poner esa diferencia como ahorro no se sostendría</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Eso es prácticamente lo mismo que Dixi llave en mano y menos que Bonetto, pero está POR ENCIMA de 2MG y de Prina. Poner esa diferencia como ahorro no se sostendría</t>
+          <t>delante del CEO, porque los alcances no son iguales: Prina cotizó 38% menos de LED, 2MG un sonido más chico, y Grupo MET incluye lo que se agregó tras la visita al predio.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>delante del CEO, porque los alcances no son iguales: Prina cotizó 38% menos de LED, 2MG un sonido más chico, y Grupo MET incluye lo que se agregó tras la visita al predio.</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LO QUE SÍ SE SOSTIENE EN TÉCNICA: las 500 vallas y los efectos especiales van bonificados. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LO QUE SÍ SE SOSTIENE EN TÉCNICA: las 500 vallas y los efectos especiales van bonificados. Bonetto los cobra: $300.000 la máquina de humo y $600.000 POR MINUTO las dos de chispa fría.</t>
+          <t>Con los 6 disparos por día que pide el rider, en cualquiera de las otras propuestas eso es plata.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Con los 6 disparos por día que pide el rider, en cualquiera de las otras propuestas eso es plata.</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>FALTA UNA SOLA COSA para cerrar el ahorro de técnica con un número: el PDF de Grupo MET con el alcance final. Es el único de los siete proveedores sin presupuesto escrito en el correo.</t>
         </is>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -109,6 +109,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
@@ -117,12 +123,6 @@
       <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="9">
@@ -238,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -438,14 +438,18 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -475,9 +479,7 @@
     <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3380,17 +3382,17 @@
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>Proveedor Colombia</t>
+          <t>Proveedor a confirmar</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Contrato US$560, sin abonar, 2 cuotas al 24/08 y 23/09</t>
+          <t>Ya comprados y pagados al 100%. El master los tenía en 2 cuotas al 24/08 y 23/09, sin abonar.</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Contratado</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -3420,7 +3422,7 @@
       </c>
       <c r="M55" s="16" t="inlineStr">
         <is>
-          <t>Hoja PAGOS del master</t>
+          <t>Confirmado por Agustina el 03/09</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4751,337 +4753,579 @@
     <row r="24">
       <c r="A24" s="87" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ARGENTINA</t>
+        </is>
+      </c>
+      <c r="B24" s="88" t="n"/>
+      <c r="C24" s="88" t="n"/>
+      <c r="D24" s="88" t="n"/>
+      <c r="E24" s="88" t="n"/>
+      <c r="F24" s="88" t="n"/>
+      <c r="G24" s="88" t="n"/>
+      <c r="H24" s="88" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="89" t="inlineStr">
+        <is>
           <t>Remeras estampadas</t>
         </is>
       </c>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="C24" s="88" t="n">
+      <c r="C25" s="90" t="n">
         <v>16.17</v>
       </c>
-      <c r="D24" s="88" t="n">
+      <c r="D25" s="90" t="n">
         <v>1617.16</v>
       </c>
-      <c r="E24" s="88" t="n">
+      <c r="E25" s="90" t="n">
         <v>9.31</v>
       </c>
-      <c r="F24" s="88" t="n">
+      <c r="F25" s="90" t="n">
         <v>931.35</v>
       </c>
-      <c r="G24" s="89">
-        <f>D24-F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="90">
-        <f>G24/D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="87" t="inlineStr">
+      <c r="G25" s="91">
+        <f>D25-F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="92">
+        <f>G25/D25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="89" t="inlineStr">
         <is>
           <t>Gorras negras</t>
         </is>
       </c>
-      <c r="B25" s="59" t="inlineStr">
+      <c r="B26" s="59" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="C25" s="88" t="n">
+      <c r="C26" s="90" t="n">
         <v>9.9</v>
       </c>
-      <c r="D25" s="88" t="n">
+      <c r="D26" s="90" t="n">
         <v>9900.99</v>
       </c>
-      <c r="E25" s="88" t="n">
+      <c r="E26" s="90" t="n">
         <v>1.64</v>
       </c>
-      <c r="F25" s="88" t="n">
+      <c r="F26" s="90" t="n">
         <v>1636.96</v>
       </c>
-      <c r="G25" s="89">
-        <f>D25-F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="90">
-        <f>G25/D25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="87" t="inlineStr">
+      <c r="G26" s="91">
+        <f>D26-F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="92">
+        <f>G26/D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="89" t="inlineStr">
         <is>
           <t>Cinta colgante / lanyard</t>
         </is>
       </c>
-      <c r="B26" s="59" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="C26" s="88" t="n">
+      <c r="C27" s="90" t="n">
         <v>1.25</v>
       </c>
-      <c r="D26" s="88" t="n">
+      <c r="D27" s="90" t="n">
         <v>1247.52</v>
       </c>
-      <c r="E26" s="88" t="n">
+      <c r="E27" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="88" t="n">
+      <c r="F27" s="90" t="n">
         <v>1004.95</v>
       </c>
-      <c r="G26" s="89">
-        <f>D26-F26</f>
-        <v/>
-      </c>
-      <c r="H26" s="90">
-        <f>G26/D26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="87" t="inlineStr">
+      <c r="G27" s="91">
+        <f>D27-F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="92">
+        <f>G27/D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="89" t="inlineStr">
         <is>
           <t>Credenciales 10 × 13 cm</t>
         </is>
       </c>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B28" s="59" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="C27" s="88" t="n">
+      <c r="C28" s="90" t="n">
         <v>0.57</v>
       </c>
-      <c r="D27" s="88" t="n">
+      <c r="D28" s="90" t="n">
         <v>574.65</v>
       </c>
-      <c r="E27" s="88" t="n">
+      <c r="E28" s="90" t="n">
         <v>0.48</v>
       </c>
-      <c r="F27" s="88" t="n">
+      <c r="F28" s="90" t="n">
         <v>475.06</v>
       </c>
-      <c r="G27" s="89">
-        <f>D27-F27</f>
-        <v/>
-      </c>
-      <c r="H27" s="90">
-        <f>G27/D27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="87" t="inlineStr">
+      <c r="G28" s="91">
+        <f>D28-F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="92">
+        <f>G28/D28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="89" t="inlineStr">
         <is>
           <t>Hojas A4 (contrato)</t>
         </is>
       </c>
-      <c r="B28" s="59" t="inlineStr">
+      <c r="B29" s="59" t="inlineStr">
         <is>
           <t>5.500</t>
         </is>
       </c>
-      <c r="C28" s="88" t="n">
+      <c r="C29" s="90" t="n">
         <v>0.2</v>
       </c>
-      <c r="D28" s="88" t="n">
+      <c r="D29" s="90" t="n">
         <v>1107.26</v>
       </c>
-      <c r="E28" s="88" t="n">
+      <c r="E29" s="90" t="n">
         <v>0.05</v>
       </c>
-      <c r="F28" s="88" t="n">
+      <c r="F29" s="90" t="n">
         <v>265.31</v>
       </c>
-      <c r="G28" s="89">
-        <f>D28-F28</f>
-        <v/>
-      </c>
-      <c r="H28" s="90">
-        <f>G28/D28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="87" t="inlineStr">
+      <c r="G29" s="91">
+        <f>D29-F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="92">
+        <f>G29/D29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="89" t="inlineStr">
         <is>
           <t>Tarjetas 21,5 × 10 cm (cheque)</t>
         </is>
       </c>
-      <c r="B29" s="59" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>5.500</t>
         </is>
       </c>
-      <c r="C29" s="88" t="n">
+      <c r="C30" s="90" t="n">
         <v>0.12</v>
       </c>
-      <c r="D29" s="88" t="n">
+      <c r="D30" s="90" t="n">
         <v>671.62</v>
       </c>
-      <c r="E29" s="88" t="n">
+      <c r="E30" s="90" t="n">
         <v>0.02</v>
       </c>
-      <c r="F29" s="88" t="n">
+      <c r="F30" s="90" t="n">
         <v>109.78</v>
       </c>
-      <c r="G29" s="89">
-        <f>D29-F29</f>
-        <v/>
-      </c>
-      <c r="H29" s="90">
-        <f>G29/D29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="87" t="inlineStr">
+      <c r="G30" s="91">
+        <f>D30-F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="92">
+        <f>G30/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="89" t="inlineStr">
         <is>
           <t>Bolsas de friselina, 2 colores</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="C30" s="88" t="n">
+      <c r="C31" s="90" t="n">
         <v>1.14</v>
       </c>
-      <c r="D30" s="88" t="n">
+      <c r="D31" s="90" t="n">
         <v>1141.91</v>
       </c>
-      <c r="E30" s="88" t="n">
+      <c r="E31" s="90" t="n">
         <v>0.64</v>
       </c>
-      <c r="F30" s="88" t="n">
+      <c r="F31" s="90" t="n">
         <v>644.55</v>
       </c>
-      <c r="G30" s="89">
-        <f>D30-F30</f>
-        <v/>
-      </c>
-      <c r="H30" s="90">
-        <f>G30/D30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="91" t="inlineStr">
+      <c r="G31" s="91">
+        <f>D31-F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="92">
+        <f>G31/D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="93" t="inlineStr">
         <is>
           <t>Pulseras tyvek — fuera de la comparación</t>
         </is>
       </c>
-      <c r="B31" s="86" t="inlineStr">
+      <c r="B32" s="86" t="inlineStr">
         <is>
           <t>5.500</t>
         </is>
       </c>
-      <c r="C31" s="92" t="n">
+      <c r="C32" s="94" t="n">
         <v>0.1</v>
       </c>
-      <c r="D31" s="92" t="n">
+      <c r="D32" s="94" t="n">
         <v>544.55</v>
       </c>
-      <c r="E31" s="92" t="n"/>
-      <c r="F31" s="92" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="78" t="inlineStr">
-        <is>
-          <t>TOTAL DE LA CANASTA COMPARADA</t>
-        </is>
-      </c>
-      <c r="D32" s="79">
-        <f>SUM(D24:D30)</f>
-        <v/>
-      </c>
-      <c r="F32" s="79">
-        <f>SUM(F24:F30)</f>
-        <v/>
-      </c>
-      <c r="G32" s="79">
-        <f>SUM(G24:G30)</f>
-        <v/>
-      </c>
-      <c r="H32" s="93">
-        <f>G32/D32</f>
+      <c r="E32" s="94" t="n"/>
+      <c r="F32" s="94" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="89" t="inlineStr">
+        <is>
+          <t>Subtotal Argentina</t>
+        </is>
+      </c>
+      <c r="B33" s="95" t="n"/>
+      <c r="C33" s="95" t="n"/>
+      <c r="D33" s="19">
+        <f>SUMIF($F$25:$F$32,"&lt;&gt;",D25:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="95" t="n"/>
+      <c r="F33" s="19">
+        <f>SUMIF($F$25:$F$32,"&lt;&gt;",F25:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="19">
+        <f>SUMIF($F$25:$F$32,"&lt;&gt;",G25:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="96">
+        <f>IFERROR(G33/D33,"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  URUGUAY</t>
+        </is>
+      </c>
+      <c r="B34" s="88" t="n"/>
+      <c r="C34" s="88" t="n"/>
+      <c r="D34" s="88" t="n"/>
+      <c r="E34" s="88" t="n"/>
+      <c r="F34" s="88" t="n"/>
+      <c r="G34" s="88" t="n"/>
+      <c r="H34" s="88" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="89" t="inlineStr">
+        <is>
+          <t>Mapas de niveles de consciencia</t>
+        </is>
+      </c>
+      <c r="B35" s="59" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="C35" s="90" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="D35" s="90" t="n">
+        <v>763</v>
+      </c>
+      <c r="E35" s="90" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="F35" s="90" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="G35" s="91">
+        <f>D35-F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="92">
+        <f>G35/D35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="89" t="inlineStr">
+        <is>
+          <t>Escarapelas / credenciales</t>
+        </is>
+      </c>
+      <c r="B36" s="59" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C36" s="90" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="D36" s="90" t="n">
+        <v>793</v>
+      </c>
+      <c r="E36" s="90" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="F36" s="90" t="n">
+        <v>285.03</v>
+      </c>
+      <c r="G36" s="91">
+        <f>D36-F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="92">
+        <f>G36/D36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="89" t="inlineStr">
+        <is>
+          <t>Contratos (hojas A4)</t>
+        </is>
+      </c>
+      <c r="B37" s="59" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="C37" s="90" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="D37" s="90" t="n">
+        <v>458</v>
+      </c>
+      <c r="E37" s="90" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F37" s="90" t="n">
+        <v>144.71</v>
+      </c>
+      <c r="G37" s="91">
+        <f>D37-F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="92">
+        <f>G37/D37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="89" t="inlineStr">
+        <is>
+          <t>Cheques (tarjetas)</t>
+        </is>
+      </c>
+      <c r="B38" s="59" t="inlineStr">
+        <is>
+          <t>3.000</t>
+        </is>
+      </c>
+      <c r="C38" s="90" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="D38" s="90" t="n">
+        <v>382</v>
+      </c>
+      <c r="E38" s="90" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F38" s="90" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="G38" s="91">
+        <f>D38-F38</f>
+        <v/>
+      </c>
+      <c r="H38" s="92">
+        <f>G38/D38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="93" t="inlineStr">
+        <is>
+          <t>Cordones con mosquetón — fuera de la comparación</t>
+        </is>
+      </c>
+      <c r="B39" s="86" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C39" s="94" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D39" s="94" t="n"/>
+      <c r="E39" s="94" t="n"/>
+      <c r="F39" s="94" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="89" t="inlineStr">
+        <is>
+          <t>Subtotal Uruguay</t>
+        </is>
+      </c>
+      <c r="B40" s="95" t="n"/>
+      <c r="C40" s="95" t="n"/>
+      <c r="D40" s="19">
+        <f>SUMIF($F$35:$F$39,"&lt;&gt;",D35:D39)</f>
+        <v/>
+      </c>
+      <c r="E40" s="95" t="n"/>
+      <c r="F40" s="19">
+        <f>SUMIF($F$35:$F$39,"&lt;&gt;",F35:F39)</f>
+        <v/>
+      </c>
+      <c r="G40" s="19">
+        <f>SUMIF($F$35:$F$39,"&lt;&gt;",G35:G39)</f>
+        <v/>
+      </c>
+      <c r="H40" s="96">
+        <f>IFERROR(G40/D40,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="78" t="inlineStr">
+        <is>
+          <t>TOTAL DE LA CANASTA — ARGENTINA + URUGUAY</t>
+        </is>
+      </c>
+      <c r="D41" s="79">
+        <f>D33+D40</f>
+        <v/>
+      </c>
+      <c r="F41" s="79">
+        <f>F33+F40</f>
+        <v/>
+      </c>
+      <c r="G41" s="79">
+        <f>G33+G40</f>
+        <v/>
+      </c>
+      <c r="H41" s="97">
+        <f>G41/D41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>La gorra sola explica la mitad del ahorro: el proveedor de Cumbre la cobraba US$9,90 y Agustina la consiguió a US$1,64. Sobre 1.000 unidades son US$8.264.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Las pulseras tyvek quedan fuera de los dos lados de la cuenta porque no hay precio comparable del lado argentino.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>OJO: esta canasta NO es el total del rubro merch. Los pañuelos (US$6.973) y el bordado de gorras (US$1.750) no entran en la comparación, y las cantidades</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>del sitio no son exactamente las de las facturas finales (remeras 100 contra 250, gorras 1.000 contra 940). Sirve para medir el ahorro por precio unitario,</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>no para reemplazar el costo del rubro, que sale de las nueve facturas de arriba.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Uruguay tiene su propia comparativa en el mismo sitio: US$2.396,00 contra US$755,77, con un ahorro de US$1.640,23. No entra en el costo de Argentina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="94" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Uruguay va con su propio subtotal: US$2.396,00 contra US$755,77, US$1.640,23 de ahorro. Es la misma negociación con los mismos proveedores, pero NO entra en el costo del evento de Argentina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Los cordones con mosquetón de Uruguay quedan fuera de la cuenta por la misma razón que las pulseras tyvek: no hay precio comparable del lado argentino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Sumando los dos países, la canasta pasa de US$18.657,12 a US$5.823,74: US$12.833,38 de ahorro, un 68,8%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="98" t="inlineStr">
         <is>
           <t>TRES COSAS QUE HAY QUE CONFIRMAR</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>1) Lanyards y gráfica de Argentina: las facturas reemitidas en agosto vienen por el TOTAL, pero la carpeta y el master dicen que ya se abonó el 50%. Si las facturas están bien, hay que pagar US$2.008 más de lo que sale por la regla del 50%. Una sola consulta a LEOTEX y a Derqui lo resuelve.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>2) Pañuelos: son 8.500 unidades compartidas entre Argentina y Uruguay y la factura no las separa. Acá se imputó el 65% a Argentina (5.500 de 8.500, la misma proporción que la gráfica). Si van todos a Argentina, el costo sube US$3.755.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>3) La gráfica de Uruguay (US$1.233) estaba cargada en el master como Argentina. Ya quedó fuera del costo argentino, pero conviene corregirla también en el master para que no se arrastre.</t>
         </is>
@@ -5089,14 +5333,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:O4"/>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A55:O55"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="A54:O54"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A42:O42"/>
-    <mergeCell ref="A44:O44"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A53:O53"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5108,7 +5354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5178,7 +5424,7 @@
       <c r="F5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="95" t="inlineStr">
+      <c r="A6" s="99" t="inlineStr">
         <is>
           <t>Sede</t>
         </is>
@@ -5188,12 +5434,12 @@
           <t>La Rural — anticipo del contrato</t>
         </is>
       </c>
-      <c r="C6" s="96" t="inlineStr">
+      <c r="C6" s="100" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="D6" s="89" t="n">
+      <c r="D6" s="91" t="n">
         <v>43446</v>
       </c>
       <c r="E6" s="81" t="inlineStr">
@@ -5201,578 +5447,548 @@
           <t>Pagado</t>
         </is>
       </c>
-      <c r="F6" s="95" t="inlineStr">
+      <c r="F6" s="99" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="95" t="inlineStr">
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>Intercoms — 100%</t>
+        </is>
+      </c>
+      <c r="C7" s="100" t="inlineStr">
+        <is>
+          <t>ya comprados</t>
+        </is>
+      </c>
+      <c r="D7" s="91" t="n">
+        <v>560</v>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
+          <t>Pagado</t>
+        </is>
+      </c>
+      <c r="F7" s="99" t="inlineStr">
+        <is>
+          <t>Confirmado por Agustina el 03/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="99" t="inlineStr">
         <is>
           <t>Técnica</t>
         </is>
       </c>
-      <c r="B7" s="81" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>Grupo MET — factura INV-11</t>
         </is>
       </c>
-      <c r="C7" s="96" t="inlineStr">
+      <c r="C8" s="100" t="inlineStr">
         <is>
           <t>31/07/2026</t>
         </is>
       </c>
-      <c r="D7" s="89" t="n">
+      <c r="D8" s="91" t="n">
         <v>5000</v>
       </c>
-      <c r="E7" s="81" t="inlineStr">
+      <c r="E8" s="81" t="inlineStr">
         <is>
           <t>Pagado</t>
         </is>
       </c>
-      <c r="F7" s="95" t="inlineStr">
+      <c r="F8" s="99" t="inlineStr">
         <is>
           <t>Recibo de Mercury del 31/07</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="95" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
         <is>
           <t>Merch</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B9" s="81" t="inlineStr">
         <is>
           <t>Pañuelos — 50% (parte Argentina)</t>
         </is>
       </c>
-      <c r="C8" s="96" t="inlineStr">
+      <c r="C9" s="100" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="D8" s="89" t="n">
+      <c r="D9" s="91" t="n">
         <v>3569.15</v>
       </c>
-      <c r="E8" s="81" t="inlineStr">
+      <c r="E9" s="81" t="inlineStr">
         <is>
           <t>Pagado</t>
         </is>
       </c>
-      <c r="F8" s="95" t="inlineStr">
+      <c r="F9" s="99" t="inlineStr">
         <is>
           <t>Master: 50% de US$10.982, imputado al 65%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="95" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>Merch</t>
         </is>
       </c>
-      <c r="B9" s="81" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>Gorras — 100%</t>
         </is>
       </c>
-      <c r="C9" s="96" t="inlineStr">
+      <c r="C10" s="100" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="D9" s="89" t="n">
+      <c r="D10" s="91" t="n">
         <v>1825</v>
       </c>
-      <c r="E9" s="81" t="inlineStr">
+      <c r="E10" s="81" t="inlineStr">
         <is>
           <t>Pagado</t>
         </is>
       </c>
-      <c r="F9" s="95" t="inlineStr">
+      <c r="F10" s="99" t="inlineStr">
         <is>
           <t>Factura 2601009 de Textil Ryu</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="95" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
         <is>
           <t>Merch</t>
         </is>
       </c>
-      <c r="B10" s="81" t="inlineStr">
+      <c r="B11" s="81" t="inlineStr">
         <is>
           <t>Lanyards — 50%</t>
         </is>
       </c>
-      <c r="C10" s="96" t="inlineStr">
+      <c r="C11" s="100" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="D10" s="89" t="n">
+      <c r="D11" s="91" t="n">
         <v>849</v>
       </c>
-      <c r="E10" s="81" t="inlineStr">
+      <c r="E11" s="81" t="inlineStr">
         <is>
           <t>Pagado</t>
         </is>
       </c>
-      <c r="F10" s="95" t="inlineStr">
+      <c r="F11" s="99" t="inlineStr">
         <is>
           <t>Hoja PAGOS del master</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="95" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
         <is>
           <t>Merch</t>
         </is>
       </c>
-      <c r="B11" s="81" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Gráfica Argentina — anticipo</t>
         </is>
       </c>
-      <c r="C11" s="96" t="inlineStr">
+      <c r="C12" s="100" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="D11" s="89" t="n">
+      <c r="D12" s="91" t="n">
         <v>642</v>
       </c>
-      <c r="E11" s="81" t="inlineStr">
+      <c r="E12" s="81" t="inlineStr">
         <is>
           <t>Pagado</t>
         </is>
       </c>
-      <c r="F11" s="95" t="inlineStr">
+      <c r="F12" s="99" t="inlineStr">
         <is>
           <t>Master: total US$2.481, saldo US$1.839</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="18" t="n"/>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Pagado a hoy</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="19">
-        <f>SUM(D6:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="19">
+        <f>SUM(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FALTA PAGAR · CON FECHA</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="97" t="inlineStr">
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="101" t="inlineStr">
         <is>
           <t>Sede</t>
         </is>
       </c>
-      <c r="B15" s="85" t="inlineStr">
+      <c r="B16" s="85" t="inlineStr">
         <is>
           <t>La Rural — saldo, cuota 1 de 2</t>
         </is>
       </c>
-      <c r="C15" s="98" t="inlineStr">
+      <c r="C16" s="102" t="inlineStr">
         <is>
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="D15" s="99" t="n">
+      <c r="D16" s="103" t="n">
         <v>15777</v>
       </c>
-      <c r="E15" s="100" t="inlineStr">
+      <c r="E16" s="104" t="inlineStr">
         <is>
           <t>VENCIDA</t>
         </is>
       </c>
-      <c r="F15" s="97" t="inlineStr">
+      <c r="F16" s="101" t="inlineStr">
         <is>
           <t>Cronograma del master</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="97" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="B16" s="85" t="inlineStr">
-        <is>
-          <t>Intercoms — cuota 1 de 2</t>
-        </is>
-      </c>
-      <c r="C16" s="98" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="99" t="n">
-        <v>280</v>
-      </c>
-      <c r="E16" s="100" t="inlineStr">
-        <is>
-          <t>VENCIDA</t>
-        </is>
-      </c>
-      <c r="F16" s="97" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="101" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B17" s="85" t="inlineStr">
+        <is>
+          <t>Remeras (250)</t>
+        </is>
+      </c>
+      <c r="C17" s="102" t="inlineStr">
+        <is>
+          <t>ya facturado</t>
+        </is>
+      </c>
+      <c r="D17" s="103" t="n">
+        <v>2780.64</v>
+      </c>
+      <c r="E17" s="104" t="inlineStr">
+        <is>
+          <t>SIN PAGAR</t>
+        </is>
+      </c>
+      <c r="F17" s="101" t="inlineStr">
+        <is>
+          <t>Factura 2601017 del 16/08 · NO figura en el master</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="101" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B18" s="85" t="inlineStr">
+        <is>
+          <t>Bordado de gorras (940)</t>
+        </is>
+      </c>
+      <c r="C18" s="102" t="inlineStr">
+        <is>
+          <t>ya facturado</t>
+        </is>
+      </c>
+      <c r="D18" s="103" t="n">
+        <v>1721.95</v>
+      </c>
+      <c r="E18" s="104" t="inlineStr">
+        <is>
+          <t>SIN PAGAR</t>
+        </is>
+      </c>
+      <c r="F18" s="101" t="inlineStr">
+        <is>
+          <t>Factura 2601016 del 10/08 · NO figura en el master</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="105" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Pañuelos — saldo (parte Argentina)</t>
+        </is>
+      </c>
+      <c r="C19" s="106" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="107" t="n">
+        <v>3429.73</v>
+      </c>
+      <c r="E19" s="89" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F19" s="105" t="inlineStr">
+        <is>
+          <t>Factura 2601019 · 65% de 5.276,51 USDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="105" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B20" s="59" t="inlineStr">
+        <is>
+          <t>Gráfica Argentina — saldo</t>
+        </is>
+      </c>
+      <c r="C20" s="106" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="107" t="n">
+        <v>1192.37</v>
+      </c>
+      <c r="E20" s="89" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F20" s="105" t="inlineStr">
+        <is>
+          <t>Master. La factura 2601014 viene por el total: a confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="105" t="inlineStr">
+        <is>
+          <t>Merch</t>
+        </is>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>Lanyards — saldo</t>
+        </is>
+      </c>
+      <c r="C21" s="106" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="107" t="n">
+        <v>816.1</v>
+      </c>
+      <c r="E21" s="89" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F21" s="105" t="inlineStr">
+        <is>
+          <t>Master. La factura 2601018 viene por el total: a confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="105" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
+      <c r="B22" s="59" t="inlineStr">
+        <is>
+          <t>La Rural — saldo, cuota 2 de 2</t>
+        </is>
+      </c>
+      <c r="C22" s="106" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="107" t="n">
+        <v>15777</v>
+      </c>
+      <c r="E22" s="89" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+      <c r="F22" s="105" t="inlineStr">
         <is>
           <t>Cronograma del master</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="97" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="B17" s="85" t="inlineStr">
-        <is>
-          <t>Remeras (250)</t>
-        </is>
-      </c>
-      <c r="C17" s="98" t="inlineStr">
-        <is>
-          <t>ya facturado</t>
-        </is>
-      </c>
-      <c r="D17" s="99" t="n">
-        <v>2780.64</v>
-      </c>
-      <c r="E17" s="100" t="inlineStr">
-        <is>
-          <t>SIN PAGAR</t>
-        </is>
-      </c>
-      <c r="F17" s="97" t="inlineStr">
-        <is>
-          <t>Factura 2601017 del 16/08 · NO figura en el master</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="97" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="B18" s="85" t="inlineStr">
-        <is>
-          <t>Bordado de gorras (940)</t>
-        </is>
-      </c>
-      <c r="C18" s="98" t="inlineStr">
-        <is>
-          <t>ya facturado</t>
-        </is>
-      </c>
-      <c r="D18" s="99" t="n">
-        <v>1721.95</v>
-      </c>
-      <c r="E18" s="100" t="inlineStr">
-        <is>
-          <t>SIN PAGAR</t>
-        </is>
-      </c>
-      <c r="F18" s="97" t="inlineStr">
-        <is>
-          <t>Factura 2601016 del 10/08 · NO figura en el master</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="101" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="B19" s="59" t="inlineStr">
-        <is>
-          <t>Pañuelos — saldo (parte Argentina)</t>
-        </is>
-      </c>
-      <c r="C19" s="102" t="inlineStr">
-        <is>
-          <t>13/09/2026</t>
-        </is>
-      </c>
-      <c r="D19" s="103" t="n">
-        <v>3429.73</v>
-      </c>
-      <c r="E19" s="87" t="inlineStr">
-        <is>
-          <t>Programado</t>
-        </is>
-      </c>
-      <c r="F19" s="101" t="inlineStr">
-        <is>
-          <t>Factura 2601019 · 65% de 5.276,51 USDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="101" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="B20" s="59" t="inlineStr">
-        <is>
-          <t>Gráfica Argentina — saldo</t>
-        </is>
-      </c>
-      <c r="C20" s="102" t="inlineStr">
-        <is>
-          <t>13/09/2026</t>
-        </is>
-      </c>
-      <c r="D20" s="103" t="n">
-        <v>1192.37</v>
-      </c>
-      <c r="E20" s="87" t="inlineStr">
-        <is>
-          <t>Programado</t>
-        </is>
-      </c>
-      <c r="F20" s="101" t="inlineStr">
-        <is>
-          <t>Master. La factura 2601014 viene por el total: a confirmar</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="101" t="inlineStr">
-        <is>
-          <t>Merch</t>
-        </is>
-      </c>
-      <c r="B21" s="59" t="inlineStr">
-        <is>
-          <t>Lanyards — saldo</t>
-        </is>
-      </c>
-      <c r="C21" s="102" t="inlineStr">
-        <is>
-          <t>13/09/2026</t>
-        </is>
-      </c>
-      <c r="D21" s="103" t="n">
-        <v>816.1</v>
-      </c>
-      <c r="E21" s="87" t="inlineStr">
-        <is>
-          <t>Programado</t>
-        </is>
-      </c>
-      <c r="F21" s="101" t="inlineStr">
-        <is>
-          <t>Master. La factura 2601018 viene por el total: a confirmar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="101" t="inlineStr">
-        <is>
-          <t>Sede</t>
-        </is>
-      </c>
-      <c r="B22" s="59" t="inlineStr">
-        <is>
-          <t>La Rural — saldo, cuota 2 de 2</t>
-        </is>
-      </c>
-      <c r="C22" s="102" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="D22" s="103" t="n">
-        <v>15777</v>
-      </c>
-      <c r="E22" s="87" t="inlineStr">
-        <is>
-          <t>Programado</t>
-        </is>
-      </c>
-      <c r="F22" s="101" t="inlineStr">
-        <is>
-          <t>Cronograma del master</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="101" t="inlineStr">
-        <is>
-          <t>Producción</t>
-        </is>
-      </c>
-      <c r="B23" s="59" t="inlineStr">
-        <is>
-          <t>Intercoms — cuota 2 de 2</t>
-        </is>
-      </c>
-      <c r="C23" s="102" t="inlineStr">
-        <is>
-          <t>23/09/2026</t>
-        </is>
-      </c>
-      <c r="D23" s="103" t="n">
-        <v>280</v>
-      </c>
-      <c r="E23" s="87" t="inlineStr">
-        <is>
-          <t>Programado</t>
-        </is>
-      </c>
-      <c r="F23" s="101" t="inlineStr">
-        <is>
-          <t>Cronograma del master</t>
-        </is>
-      </c>
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Comprometido con fecha</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="19">
+        <f>SUM(D16:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n"/>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>Comprometido con fecha</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="19">
-        <f>SUM(D15:D23)</f>
-        <v/>
-      </c>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>De eso, vencido o facturado sin pagar</t>
         </is>
       </c>
-      <c r="D25" s="99">
-        <f>SUMIF(E15:E23,"VENCIDA",D15:D23)+SUMIF(E15:E23,"SIN PAGAR",D15:D23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="D24" s="103">
+        <f>SUMIF(E16:E22,"VENCIDA",D16:D22)+SUMIF(E16:E22,"SIN PAGAR",D16:D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Costo total del evento</t>
+        </is>
+      </c>
+      <c r="D27" s="108">
+        <f>'COSTOS UNIFICADOS'!J63</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Costo total del evento</t>
-        </is>
-      </c>
-      <c r="D28" s="104">
-        <f>'COSTOS UNIFICADOS'!J63</f>
+          <t>Ya pagado</t>
+        </is>
+      </c>
+      <c r="D28" s="109">
+        <f>D13</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Ya pagado</t>
-        </is>
-      </c>
-      <c r="D29" s="105">
-        <f>D12</f>
+          <t>Falta desembolsar</t>
+        </is>
+      </c>
+      <c r="D29" s="110">
+        <f>'COSTOS UNIFICADOS'!J63-D13</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Falta desembolsar</t>
-        </is>
-      </c>
-      <c r="D30" s="106">
-        <f>'COSTOS UNIFICADOS'!J63-D12</f>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   de eso, con fecha acordada</t>
+        </is>
+      </c>
+      <c r="D30" s="111">
+        <f>D23</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   de eso, con fecha acordada</t>
-        </is>
-      </c>
-      <c r="D31" s="107">
-        <f>D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
           <t xml:space="preserve">   de eso, todavía sin fecha</t>
         </is>
       </c>
-      <c r="D32" s="107">
-        <f>'COSTOS UNIFICADOS'!J63-D12-D24</f>
-        <v/>
+      <c r="D31" s="111">
+        <f>'COSTOS UNIFICADOS'!J63-D13-D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Las remeras y el bordado de gorras están facturados desde agosto y no figuran en el cronograma del master: son US$4.503 que hoy no están en ningún calendario.</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Las remeras y el bordado de gorras están facturados desde agosto y no figuran en el cronograma del master: son US$4.503 que hoy no están en ningún calendario.</t>
+          <t>El resto sin fecha son los rubros cerrados y cotizados que todavía no tienen forma de pago acordada: técnica, entelado, CCTV, catering, sillas y los servicios del predio.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>El resto sin fecha son los rubros cerrados y cotizados que todavía no tienen forma de pago acordada: técnica, entelado, CCTV, catering, sillas y los servicios del predio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
           <t>Las facturas reemitidas de LEOTEX y Derqui vienen por el total aunque el master registra el 50% abonado. Acá se tomó la regla del 50%: si las facturas están bien, son US$2.008 más.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6154,7 +6370,7 @@
         <f>D5-G5</f>
         <v/>
       </c>
-      <c r="I5" s="108">
+      <c r="I5" s="112">
         <f>IFERROR(H5/D5,"")</f>
         <v/>
       </c>
@@ -6192,7 +6408,7 @@
         <f>D6-G6</f>
         <v/>
       </c>
-      <c r="I6" s="108">
+      <c r="I6" s="112">
         <f>IFERROR(H6/D6,"")</f>
         <v/>
       </c>
@@ -6230,7 +6446,7 @@
         <f>D7-G7</f>
         <v/>
       </c>
-      <c r="I7" s="108">
+      <c r="I7" s="112">
         <f>IFERROR(H7/D7,"")</f>
         <v/>
       </c>
@@ -6271,7 +6487,7 @@
         <f>D8-G8</f>
         <v/>
       </c>
-      <c r="I8" s="108">
+      <c r="I8" s="112">
         <f>IFERROR(H8/D8,"")</f>
         <v/>
       </c>
@@ -6309,7 +6525,7 @@
         <f>D9-G9</f>
         <v/>
       </c>
-      <c r="I9" s="108">
+      <c r="I9" s="112">
         <f>IFERROR(H9/D9,"")</f>
         <v/>
       </c>
@@ -6347,7 +6563,7 @@
         <f>D10-G10</f>
         <v/>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="112">
         <f>IFERROR(H10/D10,"")</f>
         <v/>
       </c>
@@ -6363,21 +6579,21 @@
           <t>AHORRO TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="109">
+      <c r="D11" s="113">
         <f>SUM(D5:D10)</f>
         <v/>
       </c>
-      <c r="G11" s="109">
+      <c r="G11" s="113">
         <f>SUM(G5:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="109">
+      <c r="H11" s="113">
         <f>SUM(H5:H10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="inlineStr">
+      <c r="A13" s="98" t="inlineStr">
         <is>
           <t>TÉCNICA — la comparación no es directa</t>
         </is>
@@ -6590,7 +6806,7 @@
       </c>
       <c r="D5" s="33" t="n"/>
       <c r="E5" s="35" t="n"/>
-      <c r="F5" s="110">
+      <c r="F5" s="114">
         <f>IF(E5="","",E5/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6633,7 +6849,7 @@
         <f>D6*1.21</f>
         <v/>
       </c>
-      <c r="F6" s="111">
+      <c r="F6" s="115">
         <f>IF(E6="","",E6/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6675,7 +6891,7 @@
       <c r="E7" s="23" t="n">
         <v>59150850</v>
       </c>
-      <c r="F7" s="111">
+      <c r="F7" s="115">
         <f>IF(E7="","",E7/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6717,7 +6933,7 @@
       <c r="E8" s="23" t="n">
         <v>54450000</v>
       </c>
-      <c r="F8" s="111">
+      <c r="F8" s="115">
         <f>IF(E8="","",E8/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6759,7 +6975,7 @@
       <c r="E9" s="23" t="n">
         <v>99220000</v>
       </c>
-      <c r="F9" s="111">
+      <c r="F9" s="115">
         <f>IF(E9="","",E9/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6801,7 +7017,7 @@
       <c r="E10" s="50" t="n">
         <v>15276250</v>
       </c>
-      <c r="F10" s="112">
+      <c r="F10" s="116">
         <f>IF(E10="","",E10/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6841,7 +7057,7 @@
       <c r="E11" s="40" t="n">
         <v>90600000</v>
       </c>
-      <c r="F11" s="113">
+      <c r="F11" s="117">
         <f>IF(E11="","",E11/TABLERO!$C$4)</f>
         <v/>
       </c>
@@ -6862,7 +7078,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="inlineStr">
+      <c r="A13" s="98" t="inlineStr">
         <is>
           <t>CÓMO LEER ESTA TABLA — Y POR QUÉ NO SE PUEDE RESTAR SIN MÁS</t>
         </is>
@@ -6938,7 +7154,7 @@
       <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="114" t="inlineStr">
+      <c r="A25" s="118" t="inlineStr">
         <is>
           <t>PARA CERRAR EL AHORRO DE TÉCNICA FALTA UNA SOLA COSA: el PDF de Grupo MET con el alcance final. Con eso se puede comparar contra el mismo alcance en Dixi, Bonetto, 2MG y Prina, y recién ahí poner un número.</t>
         </is>
@@ -7025,1014 +7241,1014 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="115" t="inlineStr">
+      <c r="A5" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">  PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="B5" s="116" t="n"/>
-      <c r="C5" s="116" t="n"/>
-      <c r="D5" s="116" t="n"/>
-      <c r="E5" s="116" t="n"/>
-      <c r="F5" s="116" t="n"/>
-      <c r="G5" s="116" t="n"/>
-      <c r="H5" s="116" t="n"/>
+      <c r="B5" s="88" t="n"/>
+      <c r="C5" s="88" t="n"/>
+      <c r="D5" s="88" t="n"/>
+      <c r="E5" s="88" t="n"/>
+      <c r="F5" s="88" t="n"/>
+      <c r="G5" s="88" t="n"/>
+      <c r="H5" s="88" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="101" t="n">
+      <c r="A6" s="105" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="101" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C6" s="102" t="inlineStr">
+      <c r="C6" s="106" t="inlineStr">
         <is>
           <t>Oficina de producción — 25 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D6" s="117" t="n">
+      <c r="D6" s="119" t="n">
         <v>1314575</v>
       </c>
       <c r="E6" s="61">
         <f>D6/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F6" s="118" t="inlineStr">
+      <c r="F6" s="120" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G6" s="119">
+      <c r="G6" s="121">
         <f>IF(F6="SÍ",D6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="101" t="inlineStr"/>
+      <c r="H6" s="105" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="101" t="n">
+      <c r="A7" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="101" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C7" s="102" t="inlineStr">
+      <c r="C7" s="106" t="inlineStr">
         <is>
           <t>Sala de staff — 100 m² (panelería + puerta + iluminación)</t>
         </is>
       </c>
-      <c r="D7" s="117" t="n">
+      <c r="D7" s="119" t="n">
         <v>5258300</v>
       </c>
       <c r="E7" s="61">
         <f>D7/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F7" s="118" t="inlineStr">
+      <c r="F7" s="120" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G7" s="119">
+      <c r="G7" s="121">
         <f>IF(F7="SÍ",D7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="101" t="inlineStr"/>
+      <c r="H7" s="105" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="101" t="n">
+      <c r="A8" s="105" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="101" t="inlineStr">
+      <c r="B8" s="105" t="inlineStr">
         <is>
           <t>PANELERÍA (montaje de estructuras)</t>
         </is>
       </c>
-      <c r="C8" s="102" t="inlineStr">
+      <c r="C8" s="106" t="inlineStr">
         <is>
           <t>Depósito 8×8 para las 2.500 barras — 64 m²</t>
         </is>
       </c>
-      <c r="D8" s="117" t="n">
+      <c r="D8" s="119" t="n">
         <v>3365312</v>
       </c>
       <c r="E8" s="61">
         <f>D8/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F8" s="118" t="inlineStr">
+      <c r="F8" s="120" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G8" s="119">
+      <c r="G8" s="121">
         <f>IF(F8="SÍ",D8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="101" t="inlineStr">
+      <c r="H8" s="105" t="inlineStr">
         <is>
           <t>Depósito para las 2.500 barras de la dinámica.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="115" t="inlineStr">
+      <c r="A9" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · oficina de producción</t>
         </is>
       </c>
-      <c r="B9" s="116" t="n"/>
-      <c r="C9" s="116" t="n"/>
-      <c r="D9" s="116" t="n"/>
-      <c r="E9" s="116" t="n"/>
-      <c r="F9" s="116" t="n"/>
-      <c r="G9" s="116" t="n"/>
-      <c r="H9" s="116" t="n"/>
+      <c r="B9" s="88" t="n"/>
+      <c r="C9" s="88" t="n"/>
+      <c r="D9" s="88" t="n"/>
+      <c r="E9" s="88" t="n"/>
+      <c r="F9" s="88" t="n"/>
+      <c r="G9" s="88" t="n"/>
+      <c r="H9" s="88" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="101" t="n">
+      <c r="A10" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="101" t="inlineStr">
+      <c r="B10" s="105" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C10" s="102" t="inlineStr">
+      <c r="C10" s="106" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×2</t>
         </is>
       </c>
-      <c r="D10" s="117" t="n">
+      <c r="D10" s="119" t="n">
         <v>236000</v>
       </c>
       <c r="E10" s="61">
         <f>D10/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F10" s="118" t="inlineStr">
+      <c r="F10" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G10" s="119">
+      <c r="G10" s="121">
         <f>IF(F10="SÍ",D10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="101" t="inlineStr"/>
+      <c r="H10" s="105" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="101" t="n">
+      <c r="A11" s="105" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="101" t="inlineStr">
+      <c r="B11" s="105" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C11" s="102" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×10</t>
         </is>
       </c>
-      <c r="D11" s="117" t="n">
+      <c r="D11" s="119" t="n">
         <v>85000</v>
       </c>
       <c r="E11" s="61">
         <f>D11/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F11" s="118" t="inlineStr">
+      <c r="F11" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G11" s="119">
+      <c r="G11" s="121">
         <f>IF(F11="SÍ",D11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="101" t="inlineStr"/>
+      <c r="H11" s="105" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="101" t="n">
+      <c r="A12" s="105" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="101" t="inlineStr">
+      <c r="B12" s="105" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C12" s="102" t="inlineStr">
+      <c r="C12" s="106" t="inlineStr">
         <is>
           <t>Sillón Valencia 2C ×2</t>
         </is>
       </c>
-      <c r="D12" s="117" t="n">
+      <c r="D12" s="119" t="n">
         <v>254000</v>
       </c>
       <c r="E12" s="61">
         <f>D12/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F12" s="118" t="inlineStr">
+      <c r="F12" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G12" s="119">
+      <c r="G12" s="121">
         <f>IF(F12="SÍ",D12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="101" t="inlineStr"/>
+      <c r="H12" s="105" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="101" t="n">
+      <c r="A13" s="105" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="101" t="inlineStr">
+      <c r="B13" s="105" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C13" s="102" t="inlineStr">
+      <c r="C13" s="106" t="inlineStr">
         <is>
           <t>Sillón BRNO ×2</t>
         </is>
       </c>
-      <c r="D13" s="117" t="n">
+      <c r="D13" s="119" t="n">
         <v>160000</v>
       </c>
       <c r="E13" s="61">
         <f>D13/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F13" s="118" t="inlineStr">
+      <c r="F13" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="119">
+      <c r="G13" s="121">
         <f>IF(F13="SÍ",D13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="101" t="inlineStr"/>
+      <c r="H13" s="105" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="101" t="n">
+      <c r="A14" s="105" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="101" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C14" s="102" t="inlineStr">
+      <c r="C14" s="106" t="inlineStr">
         <is>
           <t>Mesa ratona ×1</t>
         </is>
       </c>
-      <c r="D14" s="117" t="n">
+      <c r="D14" s="119" t="n">
         <v>118000</v>
       </c>
       <c r="E14" s="61">
         <f>D14/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F14" s="118" t="inlineStr">
+      <c r="F14" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="119">
+      <c r="G14" s="121">
         <f>IF(F14="SÍ",D14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="101" t="inlineStr"/>
+      <c r="H14" s="105" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="101" t="n">
+      <c r="A15" s="105" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="101" t="inlineStr">
+      <c r="B15" s="105" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C15" s="102" t="inlineStr">
+      <c r="C15" s="106" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D15" s="117" t="n">
+      <c r="D15" s="119" t="n">
         <v>40000</v>
       </c>
       <c r="E15" s="61">
         <f>D15/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F15" s="118" t="inlineStr">
+      <c r="F15" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G15" s="119">
+      <c r="G15" s="121">
         <f>IF(F15="SÍ",D15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="101" t="inlineStr"/>
+      <c r="H15" s="105" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="101" t="n">
+      <c r="A16" s="105" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="101" t="inlineStr">
+      <c r="B16" s="105" t="inlineStr">
         <is>
           <t>oficina de producción</t>
         </is>
       </c>
-      <c r="C16" s="102" t="inlineStr">
+      <c r="C16" s="106" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D16" s="117" t="n">
+      <c r="D16" s="119" t="n">
         <v>56300</v>
       </c>
       <c r="E16" s="61">
         <f>D16/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F16" s="118" t="inlineStr">
+      <c r="F16" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G16" s="119">
+      <c r="G16" s="121">
         <f>IF(F16="SÍ",D16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="101" t="inlineStr"/>
+      <c r="H16" s="105" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="115" t="inlineStr">
+      <c r="A17" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala de staff</t>
         </is>
       </c>
-      <c r="B17" s="116" t="n"/>
-      <c r="C17" s="116" t="n"/>
-      <c r="D17" s="116" t="n"/>
-      <c r="E17" s="116" t="n"/>
-      <c r="F17" s="116" t="n"/>
-      <c r="G17" s="116" t="n"/>
-      <c r="H17" s="116" t="n"/>
+      <c r="B17" s="88" t="n"/>
+      <c r="C17" s="88" t="n"/>
+      <c r="D17" s="88" t="n"/>
+      <c r="E17" s="88" t="n"/>
+      <c r="F17" s="88" t="n"/>
+      <c r="G17" s="88" t="n"/>
+      <c r="H17" s="88" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="101" t="n">
+      <c r="A18" s="105" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="101" t="inlineStr">
+      <c r="B18" s="105" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C18" s="102" t="inlineStr">
+      <c r="C18" s="106" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×5</t>
         </is>
       </c>
-      <c r="D18" s="117" t="n">
+      <c r="D18" s="119" t="n">
         <v>590000</v>
       </c>
       <c r="E18" s="61">
         <f>D18/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F18" s="118" t="inlineStr">
+      <c r="F18" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G18" s="119">
+      <c r="G18" s="121">
         <f>IF(F18="SÍ",D18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="101" t="inlineStr"/>
+      <c r="H18" s="105" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="101" t="n">
+      <c r="A19" s="105" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="101" t="inlineStr">
+      <c r="B19" s="105" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C19" s="102" t="inlineStr">
+      <c r="C19" s="106" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×40</t>
         </is>
       </c>
-      <c r="D19" s="117" t="n">
+      <c r="D19" s="119" t="n">
         <v>340000</v>
       </c>
       <c r="E19" s="61">
         <f>D19/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="118" t="inlineStr">
+      <c r="F19" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G19" s="119">
+      <c r="G19" s="121">
         <f>IF(F19="SÍ",D19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="101" t="inlineStr"/>
+      <c r="H19" s="105" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="101" t="n">
+      <c r="A20" s="105" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="101" t="inlineStr">
+      <c r="B20" s="105" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C20" s="102" t="inlineStr">
+      <c r="C20" s="106" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D20" s="117" t="n">
+      <c r="D20" s="119" t="n">
         <v>40000</v>
       </c>
       <c r="E20" s="61">
         <f>D20/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F20" s="118" t="inlineStr">
+      <c r="F20" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="119">
+      <c r="G20" s="121">
         <f>IF(F20="SÍ",D20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="101" t="inlineStr"/>
+      <c r="H20" s="105" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="101" t="n">
+      <c r="A21" s="105" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="101" t="inlineStr">
+      <c r="B21" s="105" t="inlineStr">
         <is>
           <t>sala de staff</t>
         </is>
       </c>
-      <c r="C21" s="102" t="inlineStr">
+      <c r="C21" s="106" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D21" s="117" t="n">
+      <c r="D21" s="119" t="n">
         <v>56300</v>
       </c>
       <c r="E21" s="61">
         <f>D21/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F21" s="118" t="inlineStr">
+      <c r="F21" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="119">
+      <c r="G21" s="121">
         <f>IF(F21="SÍ",D21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="101" t="inlineStr"/>
+      <c r="H21" s="105" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="115" t="inlineStr">
+      <c r="A22" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · sala principal</t>
         </is>
       </c>
-      <c r="B22" s="116" t="n"/>
-      <c r="C22" s="116" t="n"/>
-      <c r="D22" s="116" t="n"/>
-      <c r="E22" s="116" t="n"/>
-      <c r="F22" s="116" t="n"/>
-      <c r="G22" s="116" t="n"/>
-      <c r="H22" s="116" t="n"/>
+      <c r="B22" s="88" t="n"/>
+      <c r="C22" s="88" t="n"/>
+      <c r="D22" s="88" t="n"/>
+      <c r="E22" s="88" t="n"/>
+      <c r="F22" s="88" t="n"/>
+      <c r="G22" s="88" t="n"/>
+      <c r="H22" s="88" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="101" t="n">
+      <c r="A23" s="105" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="101" t="inlineStr">
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C23" s="102" t="inlineStr">
+      <c r="C23" s="106" t="inlineStr">
         <is>
           <t>Silla imperio bordó ×5.000</t>
         </is>
       </c>
-      <c r="D23" s="117" t="n">
+      <c r="D23" s="119" t="n">
         <v>42500000</v>
       </c>
       <c r="E23" s="61">
         <f>D23/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F23" s="118" t="inlineStr">
+      <c r="F23" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G23" s="119">
+      <c r="G23" s="121">
         <f>IF(F23="SÍ",D23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="101" t="inlineStr">
+      <c r="H23" s="105" t="inlineStr">
         <is>
           <t>Reemplazadas por las 5.500 sillas de FDL Eventos.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="101" t="n">
+      <c r="A24" s="105" t="n">
         <v>16</v>
       </c>
-      <c r="B24" s="101" t="inlineStr">
+      <c r="B24" s="105" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C24" s="102" t="inlineStr">
+      <c r="C24" s="106" t="inlineStr">
         <is>
           <t>Mesa 1,80 × 0,90 ×40</t>
         </is>
       </c>
-      <c r="D24" s="117" t="n">
+      <c r="D24" s="119" t="n">
         <v>2500000</v>
       </c>
       <c r="E24" s="61">
         <f>D24/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F24" s="118" t="inlineStr">
+      <c r="F24" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G24" s="119">
+      <c r="G24" s="121">
         <f>IF(F24="SÍ",D24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="101" t="inlineStr"/>
+      <c r="H24" s="105" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="101" t="n">
+      <c r="A25" s="105" t="n">
         <v>17</v>
       </c>
-      <c r="B25" s="101" t="inlineStr">
+      <c r="B25" s="105" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C25" s="102" t="inlineStr">
+      <c r="C25" s="106" t="inlineStr">
         <is>
           <t>Mantel ×40</t>
         </is>
       </c>
-      <c r="D25" s="117" t="n">
+      <c r="D25" s="119" t="n">
         <v>900000</v>
       </c>
       <c r="E25" s="61">
         <f>D25/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F25" s="118" t="inlineStr">
+      <c r="F25" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G25" s="119">
+      <c r="G25" s="121">
         <f>IF(F25="SÍ",D25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="101" t="inlineStr"/>
+      <c r="H25" s="105" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="101" t="n">
+      <c r="A26" s="105" t="n">
         <v>18</v>
       </c>
-      <c r="B26" s="101" t="inlineStr">
+      <c r="B26" s="105" t="inlineStr">
         <is>
           <t>sala principal</t>
         </is>
       </c>
-      <c r="C26" s="102" t="inlineStr">
+      <c r="C26" s="106" t="inlineStr">
         <is>
           <t>Mantel redondo ×8</t>
         </is>
       </c>
-      <c r="D26" s="117" t="n">
+      <c r="D26" s="119" t="n">
         <v>256000</v>
       </c>
       <c r="E26" s="61">
         <f>D26/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F26" s="118" t="inlineStr">
+      <c r="F26" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G26" s="119">
+      <c r="G26" s="121">
         <f>IF(F26="SÍ",D26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="101" t="inlineStr"/>
+      <c r="H26" s="105" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="115" t="inlineStr">
+      <c r="A27" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · camarín de speakers</t>
         </is>
       </c>
-      <c r="B27" s="116" t="n"/>
-      <c r="C27" s="116" t="n"/>
-      <c r="D27" s="116" t="n"/>
-      <c r="E27" s="116" t="n"/>
-      <c r="F27" s="116" t="n"/>
-      <c r="G27" s="116" t="n"/>
-      <c r="H27" s="116" t="n"/>
+      <c r="B27" s="88" t="n"/>
+      <c r="C27" s="88" t="n"/>
+      <c r="D27" s="88" t="n"/>
+      <c r="E27" s="88" t="n"/>
+      <c r="F27" s="88" t="n"/>
+      <c r="G27" s="88" t="n"/>
+      <c r="H27" s="88" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="101" t="n">
+      <c r="A28" s="105" t="n">
         <v>19</v>
       </c>
-      <c r="B28" s="101" t="inlineStr">
+      <c r="B28" s="105" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C28" s="102" t="inlineStr">
+      <c r="C28" s="106" t="inlineStr">
         <is>
           <t>Mesa redonda 1,60 ×1</t>
         </is>
       </c>
-      <c r="D28" s="117" t="n">
+      <c r="D28" s="119" t="n">
         <v>118000</v>
       </c>
       <c r="E28" s="61">
         <f>D28/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F28" s="118" t="inlineStr">
+      <c r="F28" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G28" s="119">
+      <c r="G28" s="121">
         <f>IF(F28="SÍ",D28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="101" t="inlineStr"/>
+      <c r="H28" s="105" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="101" t="n">
+      <c r="A29" s="105" t="n">
         <v>20</v>
       </c>
-      <c r="B29" s="101" t="inlineStr">
+      <c r="B29" s="105" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C29" s="102" t="inlineStr">
+      <c r="C29" s="106" t="inlineStr">
         <is>
           <t>Espejo ×1</t>
         </is>
       </c>
-      <c r="D29" s="117" t="n">
+      <c r="D29" s="119" t="n">
         <v>79500</v>
       </c>
       <c r="E29" s="61">
         <f>D29/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F29" s="118" t="inlineStr">
+      <c r="F29" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G29" s="119">
+      <c r="G29" s="121">
         <f>IF(F29="SÍ",D29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="101" t="inlineStr"/>
+      <c r="H29" s="105" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="101" t="n">
+      <c r="A30" s="105" t="n">
         <v>21</v>
       </c>
-      <c r="B30" s="101" t="inlineStr">
+      <c r="B30" s="105" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C30" s="102" t="inlineStr">
+      <c r="C30" s="106" t="inlineStr">
         <is>
           <t>Juego de living (sillones + mesa ratona)</t>
         </is>
       </c>
-      <c r="D30" s="117" t="n">
+      <c r="D30" s="119" t="n">
         <v>1103642</v>
       </c>
       <c r="E30" s="61">
         <f>D30/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F30" s="118" t="inlineStr">
+      <c r="F30" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G30" s="119">
+      <c r="G30" s="121">
         <f>IF(F30="SÍ",D30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="101" t="inlineStr">
+      <c r="H30" s="105" t="inlineStr">
         <is>
           <t>El mobiliario "más fino" del camarín: candidato a contratárselo a La Rural.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="101" t="n">
+      <c r="A31" s="105" t="n">
         <v>22</v>
       </c>
-      <c r="B31" s="101" t="inlineStr">
+      <c r="B31" s="105" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C31" s="102" t="inlineStr">
+      <c r="C31" s="106" t="inlineStr">
         <is>
           <t>Perchero de pie ×1</t>
         </is>
       </c>
-      <c r="D31" s="117" t="n">
+      <c r="D31" s="119" t="n">
         <v>40000</v>
       </c>
       <c r="E31" s="61">
         <f>D31/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F31" s="118" t="inlineStr">
+      <c r="F31" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G31" s="119">
+      <c r="G31" s="121">
         <f>IF(F31="SÍ",D31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="101" t="inlineStr"/>
+      <c r="H31" s="105" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="101" t="n">
+      <c r="A32" s="105" t="n">
         <v>23</v>
       </c>
-      <c r="B32" s="101" t="inlineStr">
+      <c r="B32" s="105" t="inlineStr">
         <is>
           <t>camarín de speakers</t>
         </is>
       </c>
-      <c r="C32" s="102" t="inlineStr">
+      <c r="C32" s="106" t="inlineStr">
         <is>
           <t>Tacho de basura grande ×1</t>
         </is>
       </c>
-      <c r="D32" s="117" t="n">
+      <c r="D32" s="119" t="n">
         <v>56300</v>
       </c>
       <c r="E32" s="61">
         <f>D32/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F32" s="118" t="inlineStr">
+      <c r="F32" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G32" s="119">
+      <c r="G32" s="121">
         <f>IF(F32="SÍ",D32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="101" t="inlineStr"/>
+      <c r="H32" s="105" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="115" t="inlineStr">
+      <c r="A33" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">  MOBILIARIO · escenario y técnica</t>
         </is>
       </c>
-      <c r="B33" s="116" t="n"/>
-      <c r="C33" s="116" t="n"/>
-      <c r="D33" s="116" t="n"/>
-      <c r="E33" s="116" t="n"/>
-      <c r="F33" s="116" t="n"/>
-      <c r="G33" s="116" t="n"/>
-      <c r="H33" s="116" t="n"/>
+      <c r="B33" s="88" t="n"/>
+      <c r="C33" s="88" t="n"/>
+      <c r="D33" s="88" t="n"/>
+      <c r="E33" s="88" t="n"/>
+      <c r="F33" s="88" t="n"/>
+      <c r="G33" s="88" t="n"/>
+      <c r="H33" s="88" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="101" t="n">
+      <c r="A34" s="105" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="101" t="inlineStr">
+      <c r="B34" s="105" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C34" s="102" t="inlineStr">
+      <c r="C34" s="106" t="inlineStr">
         <is>
           <t>Mesa cocktail alta (escenario) ×1</t>
         </is>
       </c>
-      <c r="D34" s="117" t="n">
+      <c r="D34" s="119" t="n">
         <v>45000</v>
       </c>
       <c r="E34" s="61">
         <f>D34/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F34" s="118" t="inlineStr">
+      <c r="F34" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G34" s="119">
+      <c r="G34" s="121">
         <f>IF(F34="SÍ",D34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="101" t="inlineStr"/>
+      <c r="H34" s="105" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="101" t="n">
+      <c r="A35" s="105" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="101" t="inlineStr">
+      <c r="B35" s="105" t="inlineStr">
         <is>
           <t>escenario y técnica</t>
         </is>
       </c>
-      <c r="C35" s="102" t="inlineStr">
+      <c r="C35" s="106" t="inlineStr">
         <is>
           <t>Mesa alta para DJ ×1</t>
         </is>
       </c>
-      <c r="D35" s="117" t="n">
+      <c r="D35" s="119" t="n">
         <v>62300</v>
       </c>
       <c r="E35" s="61">
         <f>D35/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F35" s="118" t="inlineStr">
+      <c r="F35" s="120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G35" s="119">
+      <c r="G35" s="121">
         <f>IF(F35="SÍ",D35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="101" t="inlineStr"/>
+      <c r="H35" s="105" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="115" t="inlineStr">
+      <c r="A36" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">  GENERALES</t>
         </is>
       </c>
-      <c r="B36" s="116" t="n"/>
-      <c r="C36" s="116" t="n"/>
-      <c r="D36" s="116" t="n"/>
-      <c r="E36" s="116" t="n"/>
-      <c r="F36" s="116" t="n"/>
-      <c r="G36" s="116" t="n"/>
-      <c r="H36" s="116" t="n"/>
+      <c r="B36" s="88" t="n"/>
+      <c r="C36" s="88" t="n"/>
+      <c r="D36" s="88" t="n"/>
+      <c r="E36" s="88" t="n"/>
+      <c r="F36" s="88" t="n"/>
+      <c r="G36" s="88" t="n"/>
+      <c r="H36" s="88" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="101" t="n">
+      <c r="A37" s="105" t="n">
         <v>26</v>
       </c>
-      <c r="B37" s="101" t="inlineStr">
+      <c r="B37" s="105" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C37" s="102" t="inlineStr">
+      <c r="C37" s="106" t="inlineStr">
         <is>
           <t>Dirección técnica de todo el evento + replanteo</t>
         </is>
       </c>
-      <c r="D37" s="117" t="n">
+      <c r="D37" s="119" t="n">
         <v>5149179.2</v>
       </c>
       <c r="E37" s="61">
         <f>D37/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F37" s="118" t="inlineStr">
+      <c r="F37" s="120" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G37" s="119">
+      <c r="G37" s="121">
         <f>IF(F37="SÍ",D37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="101" t="inlineStr">
+      <c r="H37" s="105" t="inlineStr">
         <is>
           <t>Ojo: el replanteo de sillas va aparte, con ingeniero propio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="101" t="n">
+      <c r="A38" s="105" t="n">
         <v>27</v>
       </c>
-      <c r="B38" s="101" t="inlineStr">
+      <c r="B38" s="105" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C38" s="102" t="inlineStr">
+      <c r="C38" s="106" t="inlineStr">
         <is>
           <t>Guardia eléctrica × 2 días</t>
         </is>
       </c>
-      <c r="D38" s="117" t="n">
+      <c r="D38" s="119" t="n">
         <v>865800</v>
       </c>
       <c r="E38" s="61">
         <f>D38/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F38" s="118" t="inlineStr">
+      <c r="F38" s="120" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G38" s="119">
+      <c r="G38" s="121">
         <f>IF(F38="SÍ",D38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="101" t="inlineStr"/>
+      <c r="H38" s="105" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="101" t="n">
+      <c r="A39" s="105" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="101" t="inlineStr">
+      <c r="B39" s="105" t="inlineStr">
         <is>
           <t>GENERALES</t>
         </is>
       </c>
-      <c r="C39" s="102" t="inlineStr">
+      <c r="C39" s="106" t="inlineStr">
         <is>
           <t>Guardia técnica × 2 días</t>
         </is>
       </c>
-      <c r="D39" s="117" t="n">
+      <c r="D39" s="119" t="n">
         <v>905200</v>
       </c>
       <c r="E39" s="61">
         <f>D39/TABLERO!$C$4</f>
         <v/>
       </c>
-      <c r="F39" s="118" t="inlineStr">
+      <c r="F39" s="120" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="G39" s="119">
+      <c r="G39" s="121">
         <f>IF(F39="SÍ",D39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="101" t="inlineStr"/>
+      <c r="H39" s="105" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="3" t="inlineStr">
@@ -8040,7 +8256,7 @@
           <t>TOTAL del presupuesto de La Rural</t>
         </is>
       </c>
-      <c r="D41" s="120">
+      <c r="D41" s="122">
         <f>SUM(D6:D39)</f>
         <v/>
       </c>
@@ -8055,11 +8271,11 @@
           <t>Lo que se queda (marcado SÍ)</t>
         </is>
       </c>
-      <c r="D42" s="121">
+      <c r="D42" s="123">
         <f>SUM(G6:G39)</f>
         <v/>
       </c>
-      <c r="E42" s="89">
+      <c r="E42" s="91">
         <f>D42/TABLERO!$C$4</f>
         <v/>
       </c>
@@ -8070,11 +8286,11 @@
           <t>Lo que se saca (marcado NO)</t>
         </is>
       </c>
-      <c r="D43" s="122">
+      <c r="D43" s="124">
         <f>D41-D42</f>
         <v/>
       </c>
-      <c r="E43" s="123">
+      <c r="E43" s="125">
         <f>D43/TABLERO!$C$4</f>
         <v/>
       </c>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>Grupo Ambient: US$13.582 por las dos propuestas</t>
+          <t>Grupo Ambient: US$14.569 por las dos propuestas</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6117,12 +6117,12 @@
         </is>
       </c>
       <c r="D7" s="37">
-        <f>13582-33820</f>
+        <f>14569-33820</f>
         <v/>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>Cerrado. Es la mejor negociación del evento: US$20.238 por debajo de lo presupuestado.</t>
+          <t>Cerrado: 600 desayunos VIP (no 800) + comidas para 150 personas. US$19.251 por debajo de lo presupuestado. OJO: la factura 2601021 está calculada sobre 800 desayunos; pedirle a Ángeles que la reemita por 600 antes de pagar el anticipo.</t>
         </is>
       </c>
     </row>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -1080,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3065,621 +3065,165 @@
       <c r="M48" s="8" t="n"/>
     </row>
     <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>Unifilas</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>Estimado del sheet, sin cotización</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="inlineStr">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>Vallado (500 vallas)</t>
+        </is>
+      </c>
+      <c r="B49" s="43" t="inlineStr">
+        <is>
+          <t>Bonificado por técnica</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>Bonificado</t>
+        </is>
+      </c>
+      <c r="E49" s="43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F49" s="38" t="n"/>
-      <c r="G49" s="34" t="n"/>
-      <c r="H49" s="37">
+      <c r="F49" s="45" t="n"/>
+      <c r="G49" s="46" t="n"/>
+      <c r="H49" s="47">
         <f>IF(F49="","",F49*(1+N(G49)))</f>
         <v/>
       </c>
-      <c r="I49" s="36" t="n">
+      <c r="I49" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="37">
+      <c r="J49" s="47">
         <f>IF(OR(D49="Bonificado",D49="Reemplazado"),0,N(I49)*IF(H49="",N(K49),IF(E49="USD",H49,H49/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K49" s="38" t="n">
-        <v>1200</v>
-      </c>
-      <c r="L49" s="37">
+      <c r="K49" s="45" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L49" s="47">
         <f>IF(D49="Alternativa","",J49-N(K49))</f>
         <v/>
       </c>
-      <c r="M49" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
+      <c r="M49" s="49" t="inlineStr">
+        <is>
+          <t>Negociación de Agustina</t>
         </is>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="42" t="inlineStr">
-        <is>
-          <t>Vallado (500 vallas)</t>
-        </is>
-      </c>
-      <c r="B50" s="43" t="inlineStr">
-        <is>
-          <t>Bonificado por técnica</t>
-        </is>
-      </c>
-      <c r="C50" s="44" t="inlineStr">
-        <is>
-          <t>Las 500 vallas las regala el proveedor de técnica. Estaban presupuestadas en US$1.250.</t>
-        </is>
-      </c>
-      <c r="D50" s="42" t="inlineStr">
-        <is>
-          <t>Bonificado</t>
-        </is>
-      </c>
-      <c r="E50" s="43" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Intercoms</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Proveedor a confirmar</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Ya comprados y pagados al 100%. El master los tenía en 2 cuotas al 24/08 y 23/09, sin abonar.</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F50" s="45" t="n"/>
-      <c r="G50" s="46" t="n"/>
-      <c r="H50" s="47">
+      <c r="F50" s="12" t="n">
+        <v>560</v>
+      </c>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="14">
         <f>IF(F50="","",F50*(1+N(G50)))</f>
         <v/>
       </c>
-      <c r="I50" s="48" t="n">
+      <c r="I50" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="47">
+      <c r="J50" s="14">
         <f>IF(OR(D50="Bonificado",D50="Reemplazado"),0,N(I50)*IF(H50="",N(K50),IF(E50="USD",H50,H50/TABLERO!$C$4)))</f>
         <v/>
       </c>
-      <c r="K50" s="45" t="n">
-        <v>1250</v>
-      </c>
-      <c r="L50" s="47">
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="14">
         <f>IF(D50="Alternativa","",J50-N(K50))</f>
         <v/>
       </c>
-      <c r="M50" s="49" t="inlineStr">
-        <is>
-          <t>Negociación de Agustina</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>Estimado del sheet</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F51" s="38" t="n"/>
-      <c r="G51" s="34" t="n"/>
-      <c r="H51" s="37">
-        <f>IF(F51="","",F51*(1+N(G51)))</f>
-        <v/>
-      </c>
-      <c r="I51" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="37">
-        <f>IF(OR(D51="Bonificado",D51="Reemplazado"),0,N(I51)*IF(H51="",N(K51),IF(E51="USD",H51,H51/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K51" s="38" t="n">
-        <v>500</v>
-      </c>
-      <c r="L51" s="37">
-        <f>IF(D51="Alternativa","",J51-N(K51))</f>
-        <v/>
-      </c>
-      <c r="M51" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
-        <is>
-          <t>Escoltas (2)</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>Estimado del sheet</t>
-        </is>
-      </c>
-      <c r="D52" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F52" s="38" t="n"/>
-      <c r="G52" s="34" t="n"/>
-      <c r="H52" s="37">
-        <f>IF(F52="","",F52*(1+N(G52)))</f>
-        <v/>
-      </c>
-      <c r="I52" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="37">
-        <f>IF(OR(D52="Bonificado",D52="Reemplazado"),0,N(I52)*IF(H52="",N(K52),IF(E52="USD",H52,H52/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K52" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L52" s="37">
-        <f>IF(D52="Alternativa","",J52-N(K52))</f>
-        <v/>
-      </c>
-      <c r="M52" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
-        <is>
-          <t>Master Mind Hit</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>Sala adicional</t>
-        </is>
-      </c>
-      <c r="D53" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F53" s="38" t="n"/>
-      <c r="G53" s="34" t="n"/>
-      <c r="H53" s="37">
-        <f>IF(F53="","",F53*(1+N(G53)))</f>
-        <v/>
-      </c>
-      <c r="I53" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="37">
-        <f>IF(OR(D53="Bonificado",D53="Reemplazado"),0,N(I53)*IF(H53="",N(K53),IF(E53="USD",H53,H53/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K53" s="38" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L53" s="37">
-        <f>IF(D53="Alternativa","",J53-N(K53))</f>
-        <v/>
-      </c>
-      <c r="M53" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
-        <is>
-          <t>Personal logístico</t>
-        </is>
-      </c>
-      <c r="B54" s="31" t="inlineStr">
-        <is>
-          <t>A definir</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr">
-        <is>
-          <t>La hoja del master lo tiene en US$0</t>
-        </is>
-      </c>
-      <c r="D54" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E54" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F54" s="38" t="n"/>
-      <c r="G54" s="34" t="n"/>
-      <c r="H54" s="37">
-        <f>IF(F54="","",F54*(1+N(G54)))</f>
-        <v/>
-      </c>
-      <c r="I54" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="37">
-        <f>IF(OR(D54="Bonificado",D54="Reemplazado"),0,N(I54)*IF(H54="",N(K54),IF(E54="USD",H54,H54/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K54" s="38" t="n"/>
-      <c r="L54" s="37">
-        <f>IF(D54="Alternativa","",J54-N(K54))</f>
-        <v/>
-      </c>
-      <c r="M54" s="39" t="inlineStr">
-        <is>
-          <t>Hoja Argentina del master · valor en cero</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Intercoms</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Proveedor a confirmar</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>Ya comprados y pagados al 100%. El master los tenía en 2 cuotas al 24/08 y 23/09, sin abonar.</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>560</v>
-      </c>
-      <c r="G55" s="13" t="n"/>
-      <c r="H55" s="14">
-        <f>IF(F55="","",F55*(1+N(G55)))</f>
-        <v/>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="14">
-        <f>IF(OR(D55="Bonificado",D55="Reemplazado"),0,N(I55)*IF(H55="",N(K55),IF(E55="USD",H55,H55/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="14">
-        <f>IF(D55="Alternativa","",J55-N(K55))</f>
-        <v/>
-      </c>
-      <c r="M55" s="16" t="inlineStr">
+      <c r="M50" s="16" t="inlineStr">
         <is>
           <t>Confirmado por Agustina el 03/09</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Subtotal Producción</t>
         </is>
       </c>
-      <c r="B56" s="18" t="n"/>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="18" t="n"/>
-      <c r="F56" s="18" t="n"/>
-      <c r="G56" s="18" t="n"/>
-      <c r="H56" s="18" t="n"/>
-      <c r="I56" s="18" t="n"/>
-      <c r="J56" s="19">
-        <f>SUMIF($D$49:$D$55,"&lt;&gt;Alternativa",$J$49:$J$55)</f>
-        <v/>
-      </c>
-      <c r="K56" s="19">
-        <f>SUM($K$49:$K$55)</f>
-        <v/>
-      </c>
-      <c r="L56" s="19">
-        <f>J56-K56</f>
-        <v/>
-      </c>
-      <c r="M56" s="18" t="n"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>EQUIPO</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
-      <c r="L57" s="8" t="n"/>
-      <c r="M57" s="8" t="n"/>
-    </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="30" t="inlineStr">
-        <is>
-          <t>Vuelos del equipo</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C58" s="32" t="inlineStr">
-        <is>
-          <t>No hay ninguna cotización de vuelos a Buenos Aires en el correo ni monto en la hoja del master</t>
-        </is>
-      </c>
-      <c r="D58" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E58" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="34" t="n"/>
-      <c r="H58" s="37">
-        <f>IF(F58="","",F58*(1+N(G58)))</f>
-        <v/>
-      </c>
-      <c r="I58" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="37">
-        <f>IF(OR(D58="Bonificado",D58="Reemplazado"),0,N(I58)*IF(H58="",N(K58),IF(E58="USD",H58,H58/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K58" s="38" t="n"/>
-      <c r="L58" s="37">
-        <f>IF(D58="Alternativa","",J58-N(K58))</f>
-        <v/>
-      </c>
-      <c r="M58" s="39" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
-        <is>
-          <t>Alojamiento del equipo</t>
-        </is>
-      </c>
-      <c r="B59" s="31" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t>No hay cotización de hotel en Buenos Aires en el correo ni monto en la hoja del master</t>
-        </is>
-      </c>
-      <c r="D59" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F59" s="38" t="n"/>
-      <c r="G59" s="34" t="n"/>
-      <c r="H59" s="37">
-        <f>IF(F59="","",F59*(1+N(G59)))</f>
-        <v/>
-      </c>
-      <c r="I59" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="37">
-        <f>IF(OR(D59="Bonificado",D59="Reemplazado"),0,N(I59)*IF(H59="",N(K59),IF(E59="USD",H59,H59/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K59" s="38" t="n"/>
-      <c r="L59" s="37">
-        <f>IF(D59="Alternativa","",J59-N(K59))</f>
-        <v/>
-      </c>
-      <c r="M59" s="39" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
-        <is>
-          <t>Traslados internos y viáticos</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>Sin registro</t>
-        </is>
-      </c>
-      <c r="D60" s="30" t="inlineStr">
-        <is>
-          <t>Sin cotizar</t>
-        </is>
-      </c>
-      <c r="E60" s="31" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F60" s="38" t="n"/>
-      <c r="G60" s="34" t="n"/>
-      <c r="H60" s="37">
-        <f>IF(F60="","",F60*(1+N(G60)))</f>
-        <v/>
-      </c>
-      <c r="I60" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="37">
-        <f>IF(OR(D60="Bonificado",D60="Reemplazado"),0,N(I60)*IF(H60="",N(K60),IF(E60="USD",H60,H60/TABLERO!$C$4)))</f>
-        <v/>
-      </c>
-      <c r="K60" s="38" t="n"/>
-      <c r="L60" s="37">
-        <f>IF(D60="Alternativa","",J60-N(K60))</f>
-        <v/>
-      </c>
-      <c r="M60" s="39" t="inlineStr">
-        <is>
-          <t>No encontrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal Equipo</t>
-        </is>
-      </c>
-      <c r="B61" s="18" t="n"/>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="18" t="n"/>
-      <c r="I61" s="18" t="n"/>
-      <c r="J61" s="19">
-        <f>SUMIF($D$58:$D$60,"&lt;&gt;Alternativa",$J$58:$J$60)</f>
-        <v/>
-      </c>
-      <c r="K61" s="19">
-        <f>SUM($K$58:$K$60)</f>
-        <v/>
-      </c>
-      <c r="L61" s="19">
-        <f>J61-K61</f>
-        <v/>
-      </c>
-      <c r="M61" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="52" t="inlineStr">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="19">
+        <f>SUMIF($D$49:$D$50,"&lt;&gt;Alternativa",$J$49:$J$50)</f>
+        <v/>
+      </c>
+      <c r="K51" s="19">
+        <f>SUM($K$49:$K$50)</f>
+        <v/>
+      </c>
+      <c r="L51" s="19">
+        <f>J51-K51</f>
+        <v/>
+      </c>
+      <c r="M51" s="18" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="52" t="inlineStr">
         <is>
           <t>COSTO TOTAL DEL EVENTO</t>
         </is>
       </c>
-      <c r="J63" s="53">
-        <f>J7+J10+J15+J21+J30+J43+J47+J56+J61</f>
-        <v/>
-      </c>
-      <c r="K63" s="53">
-        <f>K7+K10+K15+K21+K30+K43+K47+K56+K61</f>
-        <v/>
-      </c>
-      <c r="L63" s="53">
-        <f>L7+L10+L15+L21+L30+L43+L47+L56+L61</f>
+      <c r="J53" s="53">
+        <f>J7+J10+J15+J21+J30+J43+J47+J51</f>
+        <v/>
+      </c>
+      <c r="K53" s="53">
+        <f>K7+K10+K15+K21+K30+K43+K47+K51</f>
+        <v/>
+      </c>
+      <c r="L53" s="53">
+        <f>L7+L10+L15+L21+L30+L43+L47+L51</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M4"/>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A44:M44"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A31:M31"/>
     <mergeCell ref="A22:M22"/>
     <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A57:M57"/>
     <mergeCell ref="A16:M16"/>
     <mergeCell ref="A11:M11"/>
   </mergeCells>
@@ -3746,7 +3290,7 @@
         </is>
       </c>
       <c r="C7" s="56">
-        <f>'COSTOS UNIFICADOS'!J63</f>
+        <f>'COSTOS UNIFICADOS'!J53</f>
         <v/>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3762,7 +3306,7 @@
         </is>
       </c>
       <c r="C8" s="56">
-        <f>'COSTOS UNIFICADOS'!K63</f>
+        <f>'COSTOS UNIFICADOS'!K53</f>
         <v/>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3778,7 +3322,7 @@
         </is>
       </c>
       <c r="C9" s="57">
-        <f>'COSTOS UNIFICADOS'!L63</f>
+        <f>'COSTOS UNIFICADOS'!L53</f>
         <v/>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5915,7 +5459,7 @@
         </is>
       </c>
       <c r="D27" s="108">
-        <f>'COSTOS UNIFICADOS'!J63</f>
+        <f>'COSTOS UNIFICADOS'!J53</f>
         <v/>
       </c>
     </row>
@@ -5937,7 +5481,7 @@
         </is>
       </c>
       <c r="D29" s="110">
-        <f>'COSTOS UNIFICADOS'!J63-D13</f>
+        <f>'COSTOS UNIFICADOS'!J53-D13</f>
         <v/>
       </c>
     </row>
@@ -5959,7 +5503,7 @@
         </is>
       </c>
       <c r="D31" s="111">
-        <f>'COSTOS UNIFICADOS'!J63-D13-D23</f>
+        <f>'COSTOS UNIFICADOS'!J53-D13-D23</f>
         <v/>
       </c>
     </row>

--- a/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
+++ b/ops/finanzas/ARGENTINA_CMC2026_Costo_Total.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Vuelos y alojamiento del equipo entran en cero: no hay cotización ni estimado. Tampoco están cotizados los ecobaños, la marquetería, el replanteo de sillas ni los cheques, escarapelas, diplomas, placas y manillas. El costo por persona es, por lo tanto, un piso.</t>
+          <t>Esta hoja tiene sólo lo que cargó Agustina. Los ecobaños, la marquetería, el replanteo de sillas y los cheques/escarapelas/diplomas/placas/manillas están definidos pero todavía sin precio, así que entran en cero. El costo por persona es, por lo tanto, un piso.</t>
         </is>
       </c>
     </row>
